--- a/plan_phase/majid/tp_miim_tx.xlsx
+++ b/plan_phase/majid/tp_miim_tx.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="398">
   <si>
     <t xml:space="preserve">Section no.</t>
   </si>
@@ -437,54 +437,6 @@
     <t xml:space="preserve">Medium deferral check.</t>
   </si>
   <si>
-    <t xml:space="preserve">ERROR HANDLING &amp; INTERRUPTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc_tx_underrun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starve the TX FIFO mid-frame. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core forces a clean frame abort, deasserts MTxEn, and sets the Underrun (UR) status indicator inside the active TX BD. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error Injection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_error_cg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interconnect bottleneck resilience.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc_tx_done_interrupt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activate the Interrupt Request bit (IRQ = 1) inside a standard TX BD. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immediately following frame transmission completion, the TXB bit in INT_SOURCE fires and the hardware line INTA_O goes high. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_int_cg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interrupt subsystem handshake test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tc_tx_error_interrupt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Induce an underrun condition on a TX BD that has IRQ = 1 enabled. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TXE (Transmit Error) interrupt flag triggers inside the INT_SOURCE register concurrently with the transmission failure. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception signaling accuracy.</t>
-  </si>
-  <si>
     <t xml:space="preserve">HALF-DUPLEX &amp; COLLISION SCENARIOS</t>
   </si>
   <si>
@@ -495,6 +447,9 @@
   </si>
   <si>
     <t xml:space="preserve">Core stops active data transmission, drives a 4-byte jam pattern (0x99999999), carries out binary backoff, and increments RTRY.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error Injection</t>
   </si>
   <si>
     <t xml:space="preserve">tx_collision_cg</t>
@@ -558,6 +513,9 @@
   </si>
   <si>
     <t xml:space="preserve">Packet completes transmission, but the Carrier Sense Lost (CS) status flag is logged inside the respective Buffer Descriptor. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_error_cg</t>
   </si>
   <si>
     <t xml:space="preserve">Wire-fault diagnosis check.</t>
@@ -953,10 +911,22 @@
     <t xml:space="preserve">Edge-case error rejection test.</t>
   </si>
   <si>
+    <t xml:space="preserve">ERROR HANDLING &amp; INTERRUPTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tc_tx_underrun</t>
+  </si>
+  <si>
     <t xml:space="preserve">Artificially throttle the system WISHBONE master bus to starve the TX FIFO mid-frame. PDF</t>
   </si>
   <si>
     <t xml:space="preserve">Core forces a clean frame abort, deasserts MTxEn, and sets the Underrun (UR) status indicator inside the active TX BD. PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interconnect bottleneck resilience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tc_tx_done_interrupt</t>
   </si>
   <si>
     <t xml:space="preserve">Activate the Interrupt Request bit (IRQ = 1) inside a standard TX BD. PDF</t>
@@ -965,10 +935,22 @@
     <t xml:space="preserve">Immediately following frame transmission completion, the TXB bit in INT_SOURCE fires and the hardware line INTA_O goes high. PDF</t>
   </si>
   <si>
+    <t xml:space="preserve">tx_int_cg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interrupt subsystem handshake test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tc_tx_error_interrupt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Induce an underrun condition on a TX BD that has IRQ = 1 enabled. PDF</t>
   </si>
   <si>
     <t xml:space="preserve">The TXE (Transmit Error) interrupt flag triggers inside the INT_SOURCE register concurrently with the transmission failure. PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception signaling accuracy.</t>
   </si>
   <si>
     <t xml:space="preserve">Force continuous collisions that exceed the maximum limit (COLLCONF.MAXRET + 1). PDF</t>
@@ -1596,7 +1578,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1735,10 +1717,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -44205,7 +44183,7 @@
       <c r="C39" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="35" t="s">
         <v>125</v>
       </c>
       <c r="E39" s="4" t="n">
@@ -44237,6 +44215,7 @@
       <c r="A40" s="12"/>
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>14</v>
@@ -44251,44 +44230,45 @@
         <v>134</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="J40" s="23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K40" s="34"/>
       <c r="L40" s="34"/>
       <c r="M40" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
-      <c r="C41" s="35"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>15</v>
       </c>
       <c r="F41" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="H41" s="23" t="s">
         <v>138</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>139</v>
       </c>
       <c r="I41" s="23" t="s">
         <v>129</v>
       </c>
       <c r="J41" s="23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K41" s="34"/>
       <c r="L41" s="34"/>
       <c r="M41" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -44297,117 +44277,119 @@
       <c r="C42" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="36" t="s">
-        <v>141</v>
-      </c>
+      <c r="D42" s="35"/>
       <c r="E42" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>16</v>
       </c>
       <c r="F42" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" s="23" t="s">
         <v>142</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>144</v>
       </c>
       <c r="I42" s="23" t="s">
         <v>129</v>
       </c>
       <c r="J42" s="23" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="K42" s="34"/>
       <c r="L42" s="34"/>
       <c r="M42" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="36"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>17</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="J43" s="23" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="K43" s="34"/>
       <c r="L43" s="34"/>
       <c r="M43" s="23" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
-      <c r="D44" s="36"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>18</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I44" s="23" t="s">
         <v>129</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K44" s="34"/>
       <c r="L44" s="34"/>
       <c r="M44" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
       <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="36"/>
+      <c r="C45" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>153</v>
+      </c>
       <c r="E45" s="4" t="n">
         <f aca="false">ROW()-26</f>
         <v>19</v>
       </c>
       <c r="F45" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="H45" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="H45" s="23" t="s">
+      <c r="I45" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="23" t="s">
         <v>157</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="J45" s="23" t="s">
-        <v>145</v>
       </c>
       <c r="K45" s="34"/>
       <c r="L45" s="34"/>
@@ -44419,170 +44401,92 @@
       <c r="A46" s="12"/>
       <c r="B46" s="13"/>
       <c r="C46" s="14"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="4" t="n">
-        <f aca="false">ROW()-26</f>
-        <v>20</v>
+      <c r="D46" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>28</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="J46" s="23" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="K46" s="34"/>
       <c r="L46" s="34"/>
       <c r="M46" s="23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12"/>
       <c r="B47" s="13"/>
       <c r="C47" s="14"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="4" t="n">
-        <f aca="false">ROW()-26</f>
-        <v>21</v>
+      <c r="D47" s="37"/>
+      <c r="E47" s="23" t="n">
+        <v>29</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="K47" s="34"/>
       <c r="L47" s="34"/>
       <c r="M47" s="23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12"/>
       <c r="B48" s="13"/>
-      <c r="C48" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <f aca="false">ROW()-26</f>
-        <v>22</v>
-      </c>
-      <c r="F48" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G48" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H48" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="I48" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="23" t="s">
-        <v>172</v>
-      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="38"/>
+      <c r="H48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12"/>
       <c r="B49" s="13"/>
-      <c r="C49" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="J49" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="23" t="s">
-        <v>178</v>
-      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="4"/>
+      <c r="H49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12"/>
       <c r="B50" s="13"/>
       <c r="C50" s="14"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="23" t="s">
-        <v>183</v>
-      </c>
+      <c r="H50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12"/>
       <c r="B51" s="13"/>
       <c r="C51" s="14"/>
-      <c r="D51" s="39"/>
       <c r="H51" s="15"/>
     </row>
     <row r="52" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12"/>
       <c r="B52" s="13"/>
       <c r="C52" s="14"/>
-      <c r="D52" s="4"/>
       <c r="H52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -44804,26 +44708,38 @@
     <row r="89" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="12"/>
       <c r="B89" s="13"/>
-      <c r="C89" s="14"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="40"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
       <c r="H89" s="15"/>
     </row>
     <row r="90" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="12"/>
       <c r="B90" s="13"/>
-      <c r="C90" s="14"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
       <c r="H90" s="15"/>
     </row>
     <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="12"/>
       <c r="B91" s="13"/>
-      <c r="C91" s="14"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="40"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
       <c r="H91" s="15"/>
     </row>
     <row r="92" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="12"/>
       <c r="B92" s="13"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="41"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="40"/>
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="22"/>
@@ -44832,8 +44748,8 @@
     <row r="93" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="12"/>
       <c r="B93" s="13"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="41"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="40"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22"/>
       <c r="G93" s="22"/>
@@ -44842,18 +44758,18 @@
     <row r="94" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="12"/>
       <c r="B94" s="13"/>
-      <c r="C94" s="40"/>
-      <c r="D94" s="41"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="40"/>
       <c r="E94" s="22"/>
       <c r="F94" s="22"/>
       <c r="G94" s="22"/>
       <c r="H94" s="15"/>
     </row>
-    <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="12"/>
       <c r="B95" s="13"/>
-      <c r="C95" s="40"/>
-      <c r="D95" s="41"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="40"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
       <c r="G95" s="22"/>
@@ -44862,8 +44778,8 @@
     <row r="96" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="12"/>
       <c r="B96" s="13"/>
-      <c r="C96" s="40"/>
-      <c r="D96" s="41"/>
+      <c r="C96" s="39"/>
+      <c r="D96" s="40"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22"/>
       <c r="G96" s="22"/>
@@ -44872,18 +44788,18 @@
     <row r="97" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="12"/>
       <c r="B97" s="13"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="41"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="40"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
       <c r="G97" s="22"/>
       <c r="H97" s="15"/>
     </row>
-    <row r="98" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="12"/>
       <c r="B98" s="13"/>
-      <c r="C98" s="40"/>
-      <c r="D98" s="41"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="40"/>
       <c r="E98" s="22"/>
       <c r="F98" s="22"/>
       <c r="G98" s="22"/>
@@ -44892,8 +44808,8 @@
     <row r="99" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="12"/>
       <c r="B99" s="13"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="41"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="40"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
       <c r="G99" s="22"/>
@@ -44902,8 +44818,8 @@
     <row r="100" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="12"/>
       <c r="B100" s="13"/>
-      <c r="C100" s="40"/>
-      <c r="D100" s="41"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="40"/>
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="22"/>
@@ -44912,8 +44828,8 @@
     <row r="101" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="12"/>
       <c r="B101" s="13"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="41"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="40"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
       <c r="G101" s="22"/>
@@ -44922,8 +44838,8 @@
     <row r="102" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="12"/>
       <c r="B102" s="13"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="41"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="40"/>
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="22"/>
@@ -44932,189 +44848,183 @@
     <row r="103" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="12"/>
       <c r="B103" s="13"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="41"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="40"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
       <c r="G103" s="22"/>
       <c r="H103" s="15"/>
     </row>
     <row r="104" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12"/>
+      <c r="A104" s="41"/>
       <c r="B104" s="13"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="41"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="40"/>
       <c r="E104" s="22"/>
       <c r="F104" s="22"/>
       <c r="G104" s="22"/>
-      <c r="H104" s="15"/>
     </row>
     <row r="105" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12"/>
+      <c r="A105" s="41"/>
       <c r="B105" s="13"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="41"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="40"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
       <c r="G105" s="22"/>
-      <c r="H105" s="15"/>
     </row>
     <row r="106" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12"/>
+      <c r="A106" s="41"/>
       <c r="B106" s="13"/>
-      <c r="C106" s="40"/>
-      <c r="D106" s="41"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="40"/>
       <c r="E106" s="22"/>
       <c r="F106" s="22"/>
       <c r="G106" s="22"/>
-      <c r="H106" s="15"/>
     </row>
     <row r="107" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="42"/>
+      <c r="A107" s="41"/>
       <c r="B107" s="13"/>
       <c r="C107" s="4"/>
-      <c r="D107" s="41"/>
+      <c r="D107" s="40"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
       <c r="G107" s="22"/>
     </row>
     <row r="108" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="42"/>
+      <c r="A108" s="41"/>
       <c r="B108" s="13"/>
       <c r="C108" s="4"/>
-      <c r="D108" s="41"/>
+      <c r="D108" s="40"/>
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="22"/>
     </row>
     <row r="109" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="42"/>
+      <c r="A109" s="41"/>
       <c r="B109" s="13"/>
       <c r="C109" s="4"/>
-      <c r="D109" s="41"/>
+      <c r="D109" s="40"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
       <c r="G109" s="22"/>
     </row>
     <row r="110" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="42"/>
+      <c r="A110" s="41"/>
       <c r="B110" s="13"/>
       <c r="C110" s="4"/>
-      <c r="D110" s="41"/>
+      <c r="D110" s="40"/>
       <c r="E110" s="22"/>
       <c r="F110" s="22"/>
       <c r="G110" s="22"/>
     </row>
     <row r="111" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="42"/>
+      <c r="A111" s="41"/>
       <c r="B111" s="13"/>
       <c r="C111" s="4"/>
-      <c r="D111" s="41"/>
+      <c r="D111" s="40"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
       <c r="G111" s="22"/>
     </row>
     <row r="112" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="42"/>
+      <c r="A112" s="41"/>
       <c r="B112" s="13"/>
       <c r="C112" s="4"/>
-      <c r="D112" s="41"/>
+      <c r="D112" s="40"/>
       <c r="E112" s="22"/>
       <c r="F112" s="22"/>
       <c r="G112" s="22"/>
     </row>
     <row r="113" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="42"/>
+      <c r="A113" s="41"/>
       <c r="B113" s="13"/>
       <c r="C113" s="4"/>
-      <c r="D113" s="41"/>
+      <c r="D113" s="40"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
       <c r="G113" s="22"/>
     </row>
     <row r="114" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="42"/>
+      <c r="A114" s="41"/>
       <c r="B114" s="13"/>
       <c r="C114" s="4"/>
-      <c r="D114" s="41"/>
+      <c r="D114" s="40"/>
       <c r="E114" s="22"/>
       <c r="F114" s="22"/>
       <c r="G114" s="22"/>
     </row>
     <row r="115" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="42"/>
+      <c r="A115" s="41"/>
       <c r="B115" s="13"/>
       <c r="C115" s="4"/>
-      <c r="D115" s="41"/>
+      <c r="D115" s="40"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
       <c r="G115" s="22"/>
     </row>
     <row r="116" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="42"/>
+      <c r="A116" s="41"/>
       <c r="B116" s="13"/>
       <c r="C116" s="4"/>
-      <c r="D116" s="41"/>
+      <c r="D116" s="40"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="22"/>
     </row>
     <row r="117" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="42"/>
+      <c r="A117" s="41"/>
       <c r="B117" s="13"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="41"/>
+      <c r="D117" s="40"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
       <c r="G117" s="22"/>
     </row>
     <row r="118" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="42"/>
+      <c r="A118" s="41"/>
       <c r="B118" s="13"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="41"/>
+      <c r="D118" s="40"/>
       <c r="E118" s="22"/>
       <c r="F118" s="22"/>
       <c r="G118" s="22"/>
     </row>
     <row r="119" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="42"/>
+      <c r="A119" s="41"/>
       <c r="B119" s="13"/>
       <c r="C119" s="4"/>
-      <c r="D119" s="41"/>
+      <c r="D119" s="40"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
       <c r="G119" s="22"/>
     </row>
     <row r="120" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="42"/>
+      <c r="A120" s="41"/>
       <c r="B120" s="13"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="41"/>
       <c r="E120" s="22"/>
       <c r="F120" s="22"/>
       <c r="G120" s="22"/>
     </row>
     <row r="121" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="42"/>
+      <c r="A121" s="41"/>
       <c r="B121" s="13"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="41"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
       <c r="G121" s="22"/>
     </row>
     <row r="122" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="42"/>
+      <c r="A122" s="41"/>
       <c r="B122" s="13"/>
       <c r="C122" s="4"/>
-      <c r="D122" s="41"/>
       <c r="E122" s="22"/>
       <c r="F122" s="22"/>
       <c r="G122" s="22"/>
     </row>
     <row r="123" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="42"/>
+      <c r="A123" s="41"/>
       <c r="B123" s="13"/>
       <c r="C123" s="4"/>
       <c r="E123" s="22"/>
@@ -45122,7 +45032,7 @@
       <c r="G123" s="22"/>
     </row>
     <row r="124" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="42"/>
+      <c r="A124" s="41"/>
       <c r="B124" s="13"/>
       <c r="C124" s="4"/>
       <c r="E124" s="22"/>
@@ -45130,7 +45040,7 @@
       <c r="G124" s="22"/>
     </row>
     <row r="125" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="42"/>
+      <c r="A125" s="41"/>
       <c r="B125" s="13"/>
       <c r="C125" s="4"/>
       <c r="E125" s="22"/>
@@ -45138,7 +45048,7 @@
       <c r="G125" s="22"/>
     </row>
     <row r="126" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="42"/>
+      <c r="A126" s="41"/>
       <c r="B126" s="13"/>
       <c r="C126" s="4"/>
       <c r="E126" s="22"/>
@@ -45146,7 +45056,7 @@
       <c r="G126" s="22"/>
     </row>
     <row r="127" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="42"/>
+      <c r="A127" s="41"/>
       <c r="B127" s="13"/>
       <c r="C127" s="4"/>
       <c r="E127" s="22"/>
@@ -45154,7 +45064,7 @@
       <c r="G127" s="22"/>
     </row>
     <row r="128" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="42"/>
+      <c r="A128" s="41"/>
       <c r="B128" s="13"/>
       <c r="C128" s="4"/>
       <c r="E128" s="22"/>
@@ -45162,7 +45072,7 @@
       <c r="G128" s="22"/>
     </row>
     <row r="129" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="42"/>
+      <c r="A129" s="41"/>
       <c r="B129" s="13"/>
       <c r="C129" s="4"/>
       <c r="E129" s="22"/>
@@ -45170,7 +45080,7 @@
       <c r="G129" s="22"/>
     </row>
     <row r="130" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="42"/>
+      <c r="A130" s="41"/>
       <c r="B130" s="13"/>
       <c r="C130" s="4"/>
       <c r="E130" s="22"/>
@@ -45178,7 +45088,7 @@
       <c r="G130" s="22"/>
     </row>
     <row r="131" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="42"/>
+      <c r="A131" s="41"/>
       <c r="B131" s="13"/>
       <c r="C131" s="4"/>
       <c r="E131" s="22"/>
@@ -45186,7 +45096,7 @@
       <c r="G131" s="22"/>
     </row>
     <row r="132" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="42"/>
+      <c r="A132" s="41"/>
       <c r="B132" s="13"/>
       <c r="C132" s="4"/>
       <c r="E132" s="22"/>
@@ -45194,7 +45104,7 @@
       <c r="G132" s="22"/>
     </row>
     <row r="133" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="42"/>
+      <c r="A133" s="41"/>
       <c r="B133" s="13"/>
       <c r="C133" s="4"/>
       <c r="E133" s="22"/>
@@ -45202,7 +45112,7 @@
       <c r="G133" s="22"/>
     </row>
     <row r="134" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="42"/>
+      <c r="A134" s="41"/>
       <c r="B134" s="13"/>
       <c r="C134" s="4"/>
       <c r="E134" s="22"/>
@@ -45210,7 +45120,7 @@
       <c r="G134" s="22"/>
     </row>
     <row r="135" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="42"/>
+      <c r="A135" s="41"/>
       <c r="B135" s="13"/>
       <c r="C135" s="4"/>
       <c r="E135" s="22"/>
@@ -45218,7 +45128,7 @@
       <c r="G135" s="22"/>
     </row>
     <row r="136" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="42"/>
+      <c r="A136" s="41"/>
       <c r="B136" s="13"/>
       <c r="C136" s="4"/>
       <c r="E136" s="22"/>
@@ -45226,7 +45136,7 @@
       <c r="G136" s="22"/>
     </row>
     <row r="137" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="42"/>
+      <c r="A137" s="41"/>
       <c r="B137" s="13"/>
       <c r="C137" s="4"/>
       <c r="E137" s="22"/>
@@ -45234,7 +45144,7 @@
       <c r="G137" s="22"/>
     </row>
     <row r="138" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="42"/>
+      <c r="A138" s="41"/>
       <c r="B138" s="13"/>
       <c r="C138" s="4"/>
       <c r="E138" s="22"/>
@@ -45242,7 +45152,7 @@
       <c r="G138" s="22"/>
     </row>
     <row r="139" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="42"/>
+      <c r="A139" s="41"/>
       <c r="B139" s="13"/>
       <c r="C139" s="4"/>
       <c r="E139" s="22"/>
@@ -45250,7 +45160,7 @@
       <c r="G139" s="22"/>
     </row>
     <row r="140" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="42"/>
+      <c r="A140" s="41"/>
       <c r="B140" s="13"/>
       <c r="C140" s="4"/>
       <c r="E140" s="22"/>
@@ -45258,7 +45168,7 @@
       <c r="G140" s="22"/>
     </row>
     <row r="141" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="42"/>
+      <c r="A141" s="41"/>
       <c r="B141" s="13"/>
       <c r="C141" s="4"/>
       <c r="E141" s="22"/>
@@ -45266,7 +45176,7 @@
       <c r="G141" s="22"/>
     </row>
     <row r="142" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="42"/>
+      <c r="A142" s="41"/>
       <c r="B142" s="13"/>
       <c r="C142" s="4"/>
       <c r="E142" s="22"/>
@@ -45274,7 +45184,7 @@
       <c r="G142" s="22"/>
     </row>
     <row r="143" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="42"/>
+      <c r="A143" s="41"/>
       <c r="B143" s="13"/>
       <c r="C143" s="4"/>
       <c r="E143" s="22"/>
@@ -45282,7 +45192,7 @@
       <c r="G143" s="22"/>
     </row>
     <row r="144" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="42"/>
+      <c r="A144" s="41"/>
       <c r="B144" s="13"/>
       <c r="C144" s="4"/>
       <c r="E144" s="22"/>
@@ -45290,7 +45200,7 @@
       <c r="G144" s="22"/>
     </row>
     <row r="145" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="42"/>
+      <c r="A145" s="41"/>
       <c r="B145" s="13"/>
       <c r="C145" s="4"/>
       <c r="E145" s="22"/>
@@ -45298,7 +45208,7 @@
       <c r="G145" s="22"/>
     </row>
     <row r="146" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="42"/>
+      <c r="A146" s="41"/>
       <c r="B146" s="13"/>
       <c r="C146" s="4"/>
       <c r="E146" s="22"/>
@@ -45306,7 +45216,7 @@
       <c r="G146" s="22"/>
     </row>
     <row r="147" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="42"/>
+      <c r="A147" s="41"/>
       <c r="B147" s="13"/>
       <c r="C147" s="4"/>
       <c r="E147" s="22"/>
@@ -45314,7 +45224,7 @@
       <c r="G147" s="22"/>
     </row>
     <row r="148" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="42"/>
+      <c r="A148" s="41"/>
       <c r="B148" s="13"/>
       <c r="C148" s="4"/>
       <c r="E148" s="22"/>
@@ -45322,7 +45232,7 @@
       <c r="G148" s="22"/>
     </row>
     <row r="149" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="42"/>
+      <c r="A149" s="41"/>
       <c r="B149" s="13"/>
       <c r="C149" s="4"/>
       <c r="E149" s="22"/>
@@ -45330,7 +45240,7 @@
       <c r="G149" s="22"/>
     </row>
     <row r="150" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="42"/>
+      <c r="A150" s="41"/>
       <c r="B150" s="13"/>
       <c r="C150" s="4"/>
       <c r="E150" s="22"/>
@@ -45338,7 +45248,7 @@
       <c r="G150" s="22"/>
     </row>
     <row r="151" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="42"/>
+      <c r="A151" s="41"/>
       <c r="B151" s="13"/>
       <c r="C151" s="4"/>
       <c r="E151" s="22"/>
@@ -45346,7 +45256,7 @@
       <c r="G151" s="22"/>
     </row>
     <row r="152" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="42"/>
+      <c r="A152" s="41"/>
       <c r="B152" s="13"/>
       <c r="C152" s="4"/>
       <c r="E152" s="22"/>
@@ -45354,7 +45264,7 @@
       <c r="G152" s="22"/>
     </row>
     <row r="153" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="42"/>
+      <c r="A153" s="41"/>
       <c r="B153" s="13"/>
       <c r="C153" s="4"/>
       <c r="E153" s="22"/>
@@ -45362,7 +45272,7 @@
       <c r="G153" s="22"/>
     </row>
     <row r="154" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="42"/>
+      <c r="A154" s="41"/>
       <c r="B154" s="13"/>
       <c r="C154" s="4"/>
       <c r="E154" s="22"/>
@@ -45370,7 +45280,7 @@
       <c r="G154" s="22"/>
     </row>
     <row r="155" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="42"/>
+      <c r="A155" s="41"/>
       <c r="B155" s="13"/>
       <c r="C155" s="4"/>
       <c r="E155" s="22"/>
@@ -45378,7 +45288,7 @@
       <c r="G155" s="22"/>
     </row>
     <row r="156" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="42"/>
+      <c r="A156" s="41"/>
       <c r="B156" s="13"/>
       <c r="C156" s="4"/>
       <c r="E156" s="22"/>
@@ -45386,7 +45296,7 @@
       <c r="G156" s="22"/>
     </row>
     <row r="157" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="42"/>
+      <c r="A157" s="41"/>
       <c r="B157" s="13"/>
       <c r="C157" s="4"/>
       <c r="E157" s="22"/>
@@ -45394,7 +45304,7 @@
       <c r="G157" s="22"/>
     </row>
     <row r="158" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="42"/>
+      <c r="A158" s="41"/>
       <c r="B158" s="13"/>
       <c r="C158" s="4"/>
       <c r="E158" s="22"/>
@@ -45402,7 +45312,7 @@
       <c r="G158" s="22"/>
     </row>
     <row r="159" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="42"/>
+      <c r="A159" s="41"/>
       <c r="B159" s="13"/>
       <c r="C159" s="4"/>
       <c r="E159" s="22"/>
@@ -45410,7 +45320,7 @@
       <c r="G159" s="22"/>
     </row>
     <row r="160" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="42"/>
+      <c r="A160" s="41"/>
       <c r="B160" s="13"/>
       <c r="C160" s="4"/>
       <c r="E160" s="22"/>
@@ -45418,7 +45328,7 @@
       <c r="G160" s="22"/>
     </row>
     <row r="161" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="42"/>
+      <c r="A161" s="41"/>
       <c r="B161" s="13"/>
       <c r="C161" s="4"/>
       <c r="E161" s="22"/>
@@ -45426,7 +45336,7 @@
       <c r="G161" s="22"/>
     </row>
     <row r="162" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="42"/>
+      <c r="A162" s="41"/>
       <c r="B162" s="13"/>
       <c r="C162" s="4"/>
       <c r="E162" s="22"/>
@@ -45434,7 +45344,7 @@
       <c r="G162" s="22"/>
     </row>
     <row r="163" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="42"/>
+      <c r="A163" s="41"/>
       <c r="B163" s="13"/>
       <c r="C163" s="4"/>
       <c r="E163" s="22"/>
@@ -45442,7 +45352,7 @@
       <c r="G163" s="22"/>
     </row>
     <row r="164" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="42"/>
+      <c r="A164" s="41"/>
       <c r="B164" s="13"/>
       <c r="C164" s="4"/>
       <c r="E164" s="22"/>
@@ -45450,7 +45360,7 @@
       <c r="G164" s="22"/>
     </row>
     <row r="165" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="42"/>
+      <c r="A165" s="41"/>
       <c r="B165" s="13"/>
       <c r="C165" s="4"/>
       <c r="E165" s="22"/>
@@ -45458,7 +45368,7 @@
       <c r="G165" s="22"/>
     </row>
     <row r="166" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="42"/>
+      <c r="A166" s="41"/>
       <c r="B166" s="13"/>
       <c r="C166" s="4"/>
       <c r="E166" s="22"/>
@@ -45466,7 +45376,7 @@
       <c r="G166" s="22"/>
     </row>
     <row r="167" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="42"/>
+      <c r="A167" s="41"/>
       <c r="B167" s="13"/>
       <c r="C167" s="4"/>
       <c r="E167" s="22"/>
@@ -45474,7 +45384,7 @@
       <c r="G167" s="22"/>
     </row>
     <row r="168" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="42"/>
+      <c r="A168" s="41"/>
       <c r="B168" s="13"/>
       <c r="C168" s="4"/>
       <c r="E168" s="22"/>
@@ -45482,7 +45392,7 @@
       <c r="G168" s="22"/>
     </row>
     <row r="169" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="42"/>
+      <c r="A169" s="41"/>
       <c r="B169" s="13"/>
       <c r="C169" s="4"/>
       <c r="E169" s="22"/>
@@ -45490,7 +45400,7 @@
       <c r="G169" s="22"/>
     </row>
     <row r="170" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="42"/>
+      <c r="A170" s="41"/>
       <c r="B170" s="13"/>
       <c r="C170" s="4"/>
       <c r="E170" s="22"/>
@@ -45498,7 +45408,7 @@
       <c r="G170" s="22"/>
     </row>
     <row r="171" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="42"/>
+      <c r="A171" s="41"/>
       <c r="B171" s="13"/>
       <c r="C171" s="4"/>
       <c r="E171" s="22"/>
@@ -45506,7 +45416,7 @@
       <c r="G171" s="22"/>
     </row>
     <row r="172" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="42"/>
+      <c r="A172" s="41"/>
       <c r="B172" s="13"/>
       <c r="C172" s="4"/>
       <c r="E172" s="22"/>
@@ -45514,7 +45424,7 @@
       <c r="G172" s="22"/>
     </row>
     <row r="173" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="42"/>
+      <c r="A173" s="41"/>
       <c r="B173" s="13"/>
       <c r="C173" s="4"/>
       <c r="E173" s="22"/>
@@ -45522,7 +45432,7 @@
       <c r="G173" s="22"/>
     </row>
     <row r="174" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="42"/>
+      <c r="A174" s="41"/>
       <c r="B174" s="13"/>
       <c r="C174" s="4"/>
       <c r="E174" s="22"/>
@@ -45530,7 +45440,7 @@
       <c r="G174" s="22"/>
     </row>
     <row r="175" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="42"/>
+      <c r="A175" s="41"/>
       <c r="B175" s="13"/>
       <c r="C175" s="4"/>
       <c r="E175" s="22"/>
@@ -45538,7 +45448,7 @@
       <c r="G175" s="22"/>
     </row>
     <row r="176" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="42"/>
+      <c r="A176" s="41"/>
       <c r="B176" s="13"/>
       <c r="C176" s="4"/>
       <c r="E176" s="22"/>
@@ -45546,7 +45456,7 @@
       <c r="G176" s="22"/>
     </row>
     <row r="177" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="42"/>
+      <c r="A177" s="41"/>
       <c r="B177" s="13"/>
       <c r="C177" s="4"/>
       <c r="E177" s="22"/>
@@ -45554,7 +45464,7 @@
       <c r="G177" s="22"/>
     </row>
     <row r="178" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="42"/>
+      <c r="A178" s="41"/>
       <c r="B178" s="13"/>
       <c r="C178" s="4"/>
       <c r="E178" s="22"/>
@@ -45562,7 +45472,7 @@
       <c r="G178" s="22"/>
     </row>
     <row r="179" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="42"/>
+      <c r="A179" s="41"/>
       <c r="B179" s="13"/>
       <c r="C179" s="4"/>
       <c r="E179" s="22"/>
@@ -45570,7 +45480,7 @@
       <c r="G179" s="22"/>
     </row>
     <row r="180" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="42"/>
+      <c r="A180" s="41"/>
       <c r="B180" s="13"/>
       <c r="C180" s="4"/>
       <c r="E180" s="22"/>
@@ -45578,7 +45488,7 @@
       <c r="G180" s="22"/>
     </row>
     <row r="181" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="42"/>
+      <c r="A181" s="41"/>
       <c r="B181" s="13"/>
       <c r="C181" s="4"/>
       <c r="E181" s="22"/>
@@ -45586,7 +45496,7 @@
       <c r="G181" s="22"/>
     </row>
     <row r="182" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="42"/>
+      <c r="A182" s="41"/>
       <c r="B182" s="13"/>
       <c r="C182" s="4"/>
       <c r="E182" s="22"/>
@@ -45594,7 +45504,7 @@
       <c r="G182" s="22"/>
     </row>
     <row r="183" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="42"/>
+      <c r="A183" s="41"/>
       <c r="B183" s="13"/>
       <c r="C183" s="4"/>
       <c r="E183" s="22"/>
@@ -45602,7 +45512,7 @@
       <c r="G183" s="22"/>
     </row>
     <row r="184" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="42"/>
+      <c r="A184" s="41"/>
       <c r="B184" s="13"/>
       <c r="C184" s="4"/>
       <c r="E184" s="22"/>
@@ -45610,7 +45520,7 @@
       <c r="G184" s="22"/>
     </row>
     <row r="185" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="42"/>
+      <c r="A185" s="41"/>
       <c r="B185" s="13"/>
       <c r="C185" s="4"/>
       <c r="E185" s="22"/>
@@ -45618,7 +45528,7 @@
       <c r="G185" s="22"/>
     </row>
     <row r="186" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="42"/>
+      <c r="A186" s="41"/>
       <c r="B186" s="13"/>
       <c r="C186" s="4"/>
       <c r="E186" s="22"/>
@@ -45626,7 +45536,7 @@
       <c r="G186" s="22"/>
     </row>
     <row r="187" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="42"/>
+      <c r="A187" s="41"/>
       <c r="B187" s="13"/>
       <c r="C187" s="4"/>
       <c r="E187" s="22"/>
@@ -45634,7 +45544,7 @@
       <c r="G187" s="22"/>
     </row>
     <row r="188" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="42"/>
+      <c r="A188" s="41"/>
       <c r="B188" s="13"/>
       <c r="C188" s="4"/>
       <c r="E188" s="22"/>
@@ -45642,7 +45552,7 @@
       <c r="G188" s="22"/>
     </row>
     <row r="189" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="42"/>
+      <c r="A189" s="41"/>
       <c r="B189" s="13"/>
       <c r="C189" s="4"/>
       <c r="E189" s="22"/>
@@ -45650,7 +45560,7 @@
       <c r="G189" s="22"/>
     </row>
     <row r="190" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="42"/>
+      <c r="A190" s="41"/>
       <c r="B190" s="13"/>
       <c r="C190" s="4"/>
       <c r="E190" s="22"/>
@@ -45658,7 +45568,7 @@
       <c r="G190" s="22"/>
     </row>
     <row r="191" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="42"/>
+      <c r="A191" s="41"/>
       <c r="B191" s="13"/>
       <c r="C191" s="4"/>
       <c r="E191" s="22"/>
@@ -45666,7 +45576,7 @@
       <c r="G191" s="22"/>
     </row>
     <row r="192" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="42"/>
+      <c r="A192" s="41"/>
       <c r="B192" s="13"/>
       <c r="C192" s="4"/>
       <c r="E192" s="22"/>
@@ -45674,7 +45584,7 @@
       <c r="G192" s="22"/>
     </row>
     <row r="193" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="42"/>
+      <c r="A193" s="41"/>
       <c r="B193" s="13"/>
       <c r="C193" s="4"/>
       <c r="E193" s="22"/>
@@ -45682,7 +45592,7 @@
       <c r="G193" s="22"/>
     </row>
     <row r="194" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="42"/>
+      <c r="A194" s="41"/>
       <c r="B194" s="13"/>
       <c r="C194" s="4"/>
       <c r="E194" s="22"/>
@@ -45690,7 +45600,7 @@
       <c r="G194" s="22"/>
     </row>
     <row r="195" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="42"/>
+      <c r="A195" s="41"/>
       <c r="B195" s="13"/>
       <c r="C195" s="4"/>
       <c r="E195" s="22"/>
@@ -45698,7 +45608,7 @@
       <c r="G195" s="22"/>
     </row>
     <row r="196" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="42"/>
+      <c r="A196" s="41"/>
       <c r="B196" s="13"/>
       <c r="C196" s="4"/>
       <c r="E196" s="22"/>
@@ -45706,7 +45616,7 @@
       <c r="G196" s="22"/>
     </row>
     <row r="197" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="42"/>
+      <c r="A197" s="41"/>
       <c r="B197" s="13"/>
       <c r="C197" s="4"/>
       <c r="E197" s="22"/>
@@ -45714,7 +45624,7 @@
       <c r="G197" s="22"/>
     </row>
     <row r="198" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="42"/>
+      <c r="A198" s="41"/>
       <c r="B198" s="13"/>
       <c r="C198" s="4"/>
       <c r="E198" s="22"/>
@@ -45722,7 +45632,7 @@
       <c r="G198" s="22"/>
     </row>
     <row r="199" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="42"/>
+      <c r="A199" s="41"/>
       <c r="B199" s="13"/>
       <c r="C199" s="4"/>
       <c r="E199" s="22"/>
@@ -45730,7 +45640,7 @@
       <c r="G199" s="22"/>
     </row>
     <row r="200" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="42"/>
+      <c r="A200" s="41"/>
       <c r="B200" s="13"/>
       <c r="C200" s="4"/>
       <c r="E200" s="22"/>
@@ -45738,7 +45648,7 @@
       <c r="G200" s="22"/>
     </row>
     <row r="201" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="42"/>
+      <c r="A201" s="41"/>
       <c r="B201" s="13"/>
       <c r="C201" s="4"/>
       <c r="E201" s="22"/>
@@ -45746,7 +45656,7 @@
       <c r="G201" s="22"/>
     </row>
     <row r="202" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="42"/>
+      <c r="A202" s="41"/>
       <c r="B202" s="13"/>
       <c r="C202" s="4"/>
       <c r="E202" s="22"/>
@@ -45754,7 +45664,7 @@
       <c r="G202" s="22"/>
     </row>
     <row r="203" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="42"/>
+      <c r="A203" s="41"/>
       <c r="B203" s="13"/>
       <c r="C203" s="4"/>
       <c r="E203" s="22"/>
@@ -45762,7 +45672,7 @@
       <c r="G203" s="22"/>
     </row>
     <row r="204" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="42"/>
+      <c r="A204" s="41"/>
       <c r="B204" s="13"/>
       <c r="C204" s="4"/>
       <c r="E204" s="22"/>
@@ -45770,7 +45680,7 @@
       <c r="G204" s="22"/>
     </row>
     <row r="205" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="42"/>
+      <c r="A205" s="41"/>
       <c r="B205" s="13"/>
       <c r="C205" s="4"/>
       <c r="E205" s="22"/>
@@ -45778,7 +45688,7 @@
       <c r="G205" s="22"/>
     </row>
     <row r="206" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="42"/>
+      <c r="A206" s="41"/>
       <c r="B206" s="13"/>
       <c r="C206" s="4"/>
       <c r="E206" s="22"/>
@@ -45786,7 +45696,7 @@
       <c r="G206" s="22"/>
     </row>
     <row r="207" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="42"/>
+      <c r="A207" s="41"/>
       <c r="B207" s="13"/>
       <c r="C207" s="4"/>
       <c r="E207" s="22"/>
@@ -45794,7 +45704,7 @@
       <c r="G207" s="22"/>
     </row>
     <row r="208" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="42"/>
+      <c r="A208" s="41"/>
       <c r="B208" s="13"/>
       <c r="C208" s="4"/>
       <c r="E208" s="22"/>
@@ -45802,7 +45712,7 @@
       <c r="G208" s="22"/>
     </row>
     <row r="209" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="42"/>
+      <c r="A209" s="41"/>
       <c r="B209" s="13"/>
       <c r="C209" s="4"/>
       <c r="E209" s="22"/>
@@ -45810,7 +45720,7 @@
       <c r="G209" s="22"/>
     </row>
     <row r="210" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="42"/>
+      <c r="A210" s="41"/>
       <c r="B210" s="13"/>
       <c r="C210" s="4"/>
       <c r="E210" s="22"/>
@@ -45818,7 +45728,7 @@
       <c r="G210" s="22"/>
     </row>
     <row r="211" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="42"/>
+      <c r="A211" s="41"/>
       <c r="B211" s="13"/>
       <c r="C211" s="4"/>
       <c r="E211" s="22"/>
@@ -45826,7 +45736,7 @@
       <c r="G211" s="22"/>
     </row>
     <row r="212" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="42"/>
+      <c r="A212" s="41"/>
       <c r="B212" s="13"/>
       <c r="C212" s="4"/>
       <c r="E212" s="22"/>
@@ -45834,7 +45744,7 @@
       <c r="G212" s="22"/>
     </row>
     <row r="213" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="42"/>
+      <c r="A213" s="41"/>
       <c r="B213" s="13"/>
       <c r="C213" s="4"/>
       <c r="E213" s="22"/>
@@ -45842,7 +45752,7 @@
       <c r="G213" s="22"/>
     </row>
     <row r="214" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="42"/>
+      <c r="A214" s="41"/>
       <c r="B214" s="13"/>
       <c r="C214" s="4"/>
       <c r="E214" s="22"/>
@@ -45850,7 +45760,7 @@
       <c r="G214" s="22"/>
     </row>
     <row r="215" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="42"/>
+      <c r="A215" s="41"/>
       <c r="B215" s="13"/>
       <c r="C215" s="4"/>
       <c r="E215" s="22"/>
@@ -45858,7 +45768,7 @@
       <c r="G215" s="22"/>
     </row>
     <row r="216" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="42"/>
+      <c r="A216" s="41"/>
       <c r="B216" s="13"/>
       <c r="C216" s="4"/>
       <c r="E216" s="22"/>
@@ -45866,7 +45776,7 @@
       <c r="G216" s="22"/>
     </row>
     <row r="217" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="42"/>
+      <c r="A217" s="41"/>
       <c r="B217" s="13"/>
       <c r="C217" s="4"/>
       <c r="E217" s="22"/>
@@ -45874,7 +45784,7 @@
       <c r="G217" s="22"/>
     </row>
     <row r="218" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="42"/>
+      <c r="A218" s="41"/>
       <c r="B218" s="13"/>
       <c r="C218" s="4"/>
       <c r="E218" s="22"/>
@@ -45882,7 +45792,7 @@
       <c r="G218" s="22"/>
     </row>
     <row r="219" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="42"/>
+      <c r="A219" s="41"/>
       <c r="B219" s="13"/>
       <c r="C219" s="4"/>
       <c r="E219" s="22"/>
@@ -45890,7 +45800,7 @@
       <c r="G219" s="22"/>
     </row>
     <row r="220" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="42"/>
+      <c r="A220" s="41"/>
       <c r="B220" s="13"/>
       <c r="C220" s="4"/>
       <c r="E220" s="22"/>
@@ -45898,7 +45808,7 @@
       <c r="G220" s="22"/>
     </row>
     <row r="221" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="42"/>
+      <c r="A221" s="41"/>
       <c r="B221" s="13"/>
       <c r="C221" s="4"/>
       <c r="E221" s="22"/>
@@ -45906,7 +45816,7 @@
       <c r="G221" s="22"/>
     </row>
     <row r="222" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="42"/>
+      <c r="A222" s="41"/>
       <c r="B222" s="13"/>
       <c r="C222" s="4"/>
       <c r="E222" s="22"/>
@@ -45914,7 +45824,7 @@
       <c r="G222" s="22"/>
     </row>
     <row r="223" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="42"/>
+      <c r="A223" s="41"/>
       <c r="B223" s="13"/>
       <c r="C223" s="4"/>
       <c r="E223" s="22"/>
@@ -45922,7 +45832,7 @@
       <c r="G223" s="22"/>
     </row>
     <row r="224" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="42"/>
+      <c r="A224" s="41"/>
       <c r="B224" s="13"/>
       <c r="C224" s="4"/>
       <c r="E224" s="22"/>
@@ -45930,7 +45840,7 @@
       <c r="G224" s="22"/>
     </row>
     <row r="225" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="42"/>
+      <c r="A225" s="41"/>
       <c r="B225" s="13"/>
       <c r="C225" s="4"/>
       <c r="E225" s="22"/>
@@ -45938,7 +45848,7 @@
       <c r="G225" s="22"/>
     </row>
     <row r="226" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="42"/>
+      <c r="A226" s="41"/>
       <c r="B226" s="13"/>
       <c r="C226" s="4"/>
       <c r="E226" s="22"/>
@@ -45946,7 +45856,7 @@
       <c r="G226" s="22"/>
     </row>
     <row r="227" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="42"/>
+      <c r="A227" s="41"/>
       <c r="B227" s="13"/>
       <c r="C227" s="4"/>
       <c r="E227" s="22"/>
@@ -45954,7 +45864,7 @@
       <c r="G227" s="22"/>
     </row>
     <row r="228" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="42"/>
+      <c r="A228" s="41"/>
       <c r="B228" s="13"/>
       <c r="C228" s="4"/>
       <c r="E228" s="22"/>
@@ -45962,7 +45872,7 @@
       <c r="G228" s="22"/>
     </row>
     <row r="229" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="42"/>
+      <c r="A229" s="41"/>
       <c r="B229" s="13"/>
       <c r="C229" s="4"/>
       <c r="E229" s="22"/>
@@ -45970,7 +45880,7 @@
       <c r="G229" s="22"/>
     </row>
     <row r="230" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="42"/>
+      <c r="A230" s="41"/>
       <c r="B230" s="13"/>
       <c r="C230" s="4"/>
       <c r="E230" s="22"/>
@@ -45978,7 +45888,7 @@
       <c r="G230" s="22"/>
     </row>
     <row r="231" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="42"/>
+      <c r="A231" s="41"/>
       <c r="B231" s="13"/>
       <c r="C231" s="4"/>
       <c r="E231" s="22"/>
@@ -45986,7 +45896,7 @@
       <c r="G231" s="22"/>
     </row>
     <row r="232" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="42"/>
+      <c r="A232" s="41"/>
       <c r="B232" s="13"/>
       <c r="C232" s="4"/>
       <c r="E232" s="22"/>
@@ -45994,7 +45904,7 @@
       <c r="G232" s="22"/>
     </row>
     <row r="233" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="42"/>
+      <c r="A233" s="41"/>
       <c r="B233" s="13"/>
       <c r="C233" s="4"/>
       <c r="E233" s="22"/>
@@ -46002,7 +45912,7 @@
       <c r="G233" s="22"/>
     </row>
     <row r="234" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="42"/>
+      <c r="A234" s="41"/>
       <c r="B234" s="13"/>
       <c r="C234" s="4"/>
       <c r="E234" s="22"/>
@@ -46010,7 +45920,7 @@
       <c r="G234" s="22"/>
     </row>
     <row r="235" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="42"/>
+      <c r="A235" s="41"/>
       <c r="B235" s="13"/>
       <c r="C235" s="4"/>
       <c r="E235" s="22"/>
@@ -46018,7 +45928,7 @@
       <c r="G235" s="22"/>
     </row>
     <row r="236" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="42"/>
+      <c r="A236" s="41"/>
       <c r="B236" s="13"/>
       <c r="C236" s="4"/>
       <c r="E236" s="22"/>
@@ -46026,7 +45936,7 @@
       <c r="G236" s="22"/>
     </row>
     <row r="237" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="42"/>
+      <c r="A237" s="41"/>
       <c r="B237" s="13"/>
       <c r="C237" s="4"/>
       <c r="E237" s="22"/>
@@ -46034,7 +45944,7 @@
       <c r="G237" s="22"/>
     </row>
     <row r="238" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="42"/>
+      <c r="A238" s="41"/>
       <c r="B238" s="13"/>
       <c r="C238" s="4"/>
       <c r="E238" s="22"/>
@@ -46042,7 +45952,7 @@
       <c r="G238" s="22"/>
     </row>
     <row r="239" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="42"/>
+      <c r="A239" s="41"/>
       <c r="B239" s="13"/>
       <c r="C239" s="4"/>
       <c r="E239" s="22"/>
@@ -46050,7 +45960,7 @@
       <c r="G239" s="22"/>
     </row>
     <row r="240" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="42"/>
+      <c r="A240" s="41"/>
       <c r="B240" s="13"/>
       <c r="C240" s="4"/>
       <c r="E240" s="22"/>
@@ -46058,7 +45968,7 @@
       <c r="G240" s="22"/>
     </row>
     <row r="241" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="42"/>
+      <c r="A241" s="41"/>
       <c r="B241" s="13"/>
       <c r="C241" s="4"/>
       <c r="E241" s="22"/>
@@ -46066,7 +45976,7 @@
       <c r="G241" s="22"/>
     </row>
     <row r="242" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="42"/>
+      <c r="A242" s="41"/>
       <c r="B242" s="13"/>
       <c r="C242" s="4"/>
       <c r="E242" s="22"/>
@@ -46074,7 +45984,7 @@
       <c r="G242" s="22"/>
     </row>
     <row r="243" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="42"/>
+      <c r="A243" s="41"/>
       <c r="B243" s="13"/>
       <c r="C243" s="4"/>
       <c r="E243" s="22"/>
@@ -46082,7 +45992,7 @@
       <c r="G243" s="22"/>
     </row>
     <row r="244" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="42"/>
+      <c r="A244" s="41"/>
       <c r="B244" s="13"/>
       <c r="C244" s="4"/>
       <c r="E244" s="22"/>
@@ -46090,7 +46000,7 @@
       <c r="G244" s="22"/>
     </row>
     <row r="245" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="42"/>
+      <c r="A245" s="41"/>
       <c r="B245" s="13"/>
       <c r="C245" s="4"/>
       <c r="E245" s="22"/>
@@ -46098,7 +46008,7 @@
       <c r="G245" s="22"/>
     </row>
     <row r="246" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="42"/>
+      <c r="A246" s="41"/>
       <c r="B246" s="13"/>
       <c r="C246" s="4"/>
       <c r="E246" s="22"/>
@@ -46106,7 +46016,7 @@
       <c r="G246" s="22"/>
     </row>
     <row r="247" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="42"/>
+      <c r="A247" s="41"/>
       <c r="B247" s="13"/>
       <c r="C247" s="4"/>
       <c r="E247" s="22"/>
@@ -46115,2267 +46025,2246 @@
     </row>
     <row r="248" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="42"/>
-      <c r="B248" s="13"/>
-      <c r="C248" s="4"/>
-      <c r="E248" s="22"/>
-      <c r="F248" s="22"/>
-      <c r="G248" s="22"/>
-    </row>
-    <row r="249" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="42"/>
+      <c r="B248" s="43"/>
+      <c r="C248" s="44"/>
+      <c r="D248" s="45"/>
+      <c r="E248" s="46"/>
+      <c r="F248" s="46"/>
+      <c r="G248" s="46"/>
+      <c r="H248" s="44"/>
+      <c r="I248" s="44"/>
+      <c r="J248" s="44"/>
+      <c r="K248" s="47"/>
+      <c r="L248" s="47"/>
+    </row>
+    <row r="249" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="48"/>
       <c r="B249" s="13"/>
-      <c r="C249" s="4"/>
-      <c r="E249" s="22"/>
-      <c r="F249" s="22"/>
-      <c r="G249" s="22"/>
-    </row>
-    <row r="250" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="42"/>
+    </row>
+    <row r="250" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="48"/>
       <c r="B250" s="13"/>
-      <c r="C250" s="4"/>
-      <c r="E250" s="22"/>
-      <c r="F250" s="22"/>
-      <c r="G250" s="22"/>
-    </row>
-    <row r="251" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="43"/>
-      <c r="B251" s="44"/>
-      <c r="C251" s="45"/>
-      <c r="D251" s="46"/>
-      <c r="E251" s="47"/>
-      <c r="F251" s="47"/>
-      <c r="G251" s="47"/>
-      <c r="H251" s="45"/>
-      <c r="I251" s="45"/>
-      <c r="J251" s="45"/>
-      <c r="K251" s="48"/>
-      <c r="L251" s="48"/>
-    </row>
-    <row r="252" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="49"/>
+    </row>
+    <row r="251" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="48"/>
+      <c r="B251" s="13"/>
+    </row>
+    <row r="252" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="48"/>
       <c r="B252" s="13"/>
     </row>
     <row r="253" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="49"/>
+      <c r="A253" s="48"/>
       <c r="B253" s="13"/>
     </row>
     <row r="254" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="49"/>
+      <c r="A254" s="48"/>
       <c r="B254" s="13"/>
     </row>
     <row r="255" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="49"/>
+      <c r="A255" s="48"/>
       <c r="B255" s="13"/>
     </row>
     <row r="256" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="49"/>
+      <c r="A256" s="48"/>
       <c r="B256" s="13"/>
     </row>
-    <row r="257" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A257" s="49"/>
+    <row r="257" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A257" s="48"/>
       <c r="B257" s="13"/>
     </row>
-    <row r="258" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="49"/>
+    <row r="258" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A258" s="48"/>
       <c r="B258" s="13"/>
     </row>
-    <row r="259" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="49"/>
+    <row r="259" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="48"/>
       <c r="B259" s="13"/>
     </row>
     <row r="260" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="49"/>
+      <c r="A260" s="48"/>
       <c r="B260" s="13"/>
     </row>
     <row r="261" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="49"/>
+      <c r="A261" s="48"/>
       <c r="B261" s="13"/>
     </row>
     <row r="262" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="49"/>
+      <c r="A262" s="48"/>
       <c r="B262" s="13"/>
     </row>
     <row r="263" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="49"/>
+      <c r="A263" s="48"/>
       <c r="B263" s="13"/>
     </row>
     <row r="264" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A264" s="49"/>
+      <c r="A264" s="48"/>
       <c r="B264" s="13"/>
     </row>
     <row r="265" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="49"/>
+      <c r="A265" s="48"/>
       <c r="B265" s="13"/>
     </row>
     <row r="266" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="49"/>
+      <c r="A266" s="48"/>
       <c r="B266" s="13"/>
     </row>
     <row r="267" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="49"/>
+      <c r="A267" s="48"/>
       <c r="B267" s="13"/>
     </row>
     <row r="268" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="49"/>
+      <c r="A268" s="48"/>
       <c r="B268" s="13"/>
     </row>
     <row r="269" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="49"/>
+      <c r="A269" s="48"/>
       <c r="B269" s="13"/>
     </row>
     <row r="270" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="49"/>
+      <c r="A270" s="48"/>
       <c r="B270" s="13"/>
     </row>
     <row r="271" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="49"/>
+      <c r="A271" s="48"/>
       <c r="B271" s="13"/>
     </row>
     <row r="272" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A272" s="49"/>
+      <c r="A272" s="48"/>
       <c r="B272" s="13"/>
     </row>
     <row r="273" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="49"/>
+      <c r="A273" s="48"/>
       <c r="B273" s="13"/>
     </row>
     <row r="274" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="49"/>
+      <c r="A274" s="48"/>
       <c r="B274" s="13"/>
     </row>
     <row r="275" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="49"/>
+      <c r="A275" s="48"/>
       <c r="B275" s="13"/>
     </row>
     <row r="276" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="49"/>
+      <c r="A276" s="48"/>
       <c r="B276" s="13"/>
     </row>
     <row r="277" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="49"/>
+      <c r="A277" s="48"/>
       <c r="B277" s="13"/>
     </row>
     <row r="278" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="49"/>
+      <c r="A278" s="48"/>
       <c r="B278" s="13"/>
     </row>
     <row r="279" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="49"/>
+      <c r="A279" s="48"/>
       <c r="B279" s="13"/>
     </row>
     <row r="280" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="49"/>
+      <c r="A280" s="48"/>
       <c r="B280" s="13"/>
     </row>
     <row r="281" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="49"/>
+      <c r="A281" s="48"/>
       <c r="B281" s="13"/>
     </row>
     <row r="282" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="49"/>
+      <c r="A282" s="48"/>
       <c r="B282" s="13"/>
     </row>
     <row r="283" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="49"/>
+      <c r="A283" s="48"/>
       <c r="B283" s="13"/>
     </row>
     <row r="284" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="49"/>
+      <c r="A284" s="48"/>
       <c r="B284" s="13"/>
     </row>
     <row r="285" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="49"/>
+      <c r="A285" s="48"/>
       <c r="B285" s="13"/>
     </row>
     <row r="286" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A286" s="49"/>
+      <c r="A286" s="48"/>
       <c r="B286" s="13"/>
     </row>
     <row r="287" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="49"/>
+      <c r="A287" s="48"/>
       <c r="B287" s="13"/>
     </row>
     <row r="288" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="49"/>
+      <c r="A288" s="48"/>
       <c r="B288" s="13"/>
     </row>
     <row r="289" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="49"/>
+      <c r="A289" s="48"/>
       <c r="B289" s="13"/>
     </row>
     <row r="290" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="49"/>
+      <c r="A290" s="48"/>
       <c r="B290" s="13"/>
     </row>
     <row r="291" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="49"/>
+      <c r="A291" s="48"/>
       <c r="B291" s="13"/>
     </row>
     <row r="292" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="49"/>
+      <c r="A292" s="48"/>
       <c r="B292" s="13"/>
     </row>
     <row r="293" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A293" s="49"/>
+      <c r="A293" s="48"/>
       <c r="B293" s="13"/>
     </row>
     <row r="294" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A294" s="49"/>
+      <c r="A294" s="48"/>
       <c r="B294" s="13"/>
     </row>
     <row r="295" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="49"/>
+      <c r="A295" s="48"/>
       <c r="B295" s="13"/>
     </row>
     <row r="296" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="49"/>
+      <c r="A296" s="48"/>
       <c r="B296" s="13"/>
     </row>
     <row r="297" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="49"/>
+      <c r="A297" s="48"/>
       <c r="B297" s="13"/>
     </row>
     <row r="298" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="49"/>
+      <c r="A298" s="48"/>
       <c r="B298" s="13"/>
     </row>
     <row r="299" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A299" s="49"/>
+      <c r="A299" s="48"/>
       <c r="B299" s="13"/>
     </row>
     <row r="300" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="49"/>
+      <c r="A300" s="48"/>
       <c r="B300" s="13"/>
     </row>
     <row r="301" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="49"/>
+      <c r="A301" s="48"/>
       <c r="B301" s="13"/>
     </row>
     <row r="302" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A302" s="49"/>
+      <c r="A302" s="48"/>
       <c r="B302" s="13"/>
     </row>
     <row r="303" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A303" s="49"/>
+      <c r="A303" s="48"/>
       <c r="B303" s="13"/>
     </row>
     <row r="304" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A304" s="49"/>
+      <c r="A304" s="48"/>
       <c r="B304" s="13"/>
     </row>
     <row r="305" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A305" s="49"/>
+      <c r="A305" s="48"/>
       <c r="B305" s="13"/>
     </row>
     <row r="306" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A306" s="49"/>
+      <c r="A306" s="48"/>
       <c r="B306" s="13"/>
     </row>
     <row r="307" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A307" s="49"/>
+      <c r="A307" s="48"/>
       <c r="B307" s="13"/>
     </row>
     <row r="308" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="49"/>
+      <c r="A308" s="48"/>
       <c r="B308" s="13"/>
     </row>
-    <row r="309" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="49"/>
-      <c r="B309" s="13"/>
-    </row>
-    <row r="310" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A310" s="49"/>
+      <c r="B309" s="43"/>
+      <c r="C309" s="50"/>
+      <c r="D309" s="45"/>
+      <c r="E309" s="51"/>
+      <c r="F309" s="51"/>
+      <c r="G309" s="52"/>
+      <c r="H309" s="44"/>
+      <c r="I309" s="44"/>
+      <c r="J309" s="44"/>
+      <c r="K309" s="47"/>
+      <c r="L309" s="47"/>
+    </row>
+    <row r="310" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A310" s="48"/>
       <c r="B310" s="13"/>
     </row>
-    <row r="311" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A311" s="49"/>
+    <row r="311" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A311" s="48"/>
       <c r="B311" s="13"/>
     </row>
-    <row r="312" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="50"/>
-      <c r="B312" s="44"/>
-      <c r="C312" s="51"/>
-      <c r="D312" s="46"/>
-      <c r="E312" s="52"/>
-      <c r="F312" s="52"/>
-      <c r="G312" s="53"/>
-      <c r="H312" s="45"/>
-      <c r="I312" s="45"/>
-      <c r="J312" s="45"/>
-      <c r="K312" s="48"/>
-      <c r="L312" s="48"/>
+    <row r="312" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A312" s="48"/>
+      <c r="B312" s="13"/>
     </row>
     <row r="313" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="49"/>
+      <c r="A313" s="48"/>
       <c r="B313" s="13"/>
     </row>
     <row r="314" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A314" s="49"/>
+      <c r="A314" s="48"/>
       <c r="B314" s="13"/>
     </row>
     <row r="315" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A315" s="49"/>
+      <c r="A315" s="48"/>
       <c r="B315" s="13"/>
     </row>
     <row r="316" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A316" s="49"/>
+      <c r="A316" s="48"/>
       <c r="B316" s="13"/>
     </row>
     <row r="317" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A317" s="49"/>
+      <c r="A317" s="48"/>
       <c r="B317" s="13"/>
     </row>
     <row r="318" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="49"/>
+      <c r="A318" s="48"/>
       <c r="B318" s="13"/>
     </row>
     <row r="319" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A319" s="49"/>
+      <c r="A319" s="48"/>
       <c r="B319" s="13"/>
     </row>
     <row r="320" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A320" s="49"/>
+      <c r="A320" s="48"/>
       <c r="B320" s="13"/>
     </row>
     <row r="321" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A321" s="49"/>
+      <c r="A321" s="48"/>
       <c r="B321" s="13"/>
     </row>
     <row r="322" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A322" s="49"/>
+      <c r="A322" s="48"/>
       <c r="B322" s="13"/>
     </row>
     <row r="323" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A323" s="49"/>
+      <c r="A323" s="48"/>
       <c r="B323" s="13"/>
     </row>
     <row r="324" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A324" s="49"/>
+      <c r="A324" s="48"/>
       <c r="B324" s="13"/>
     </row>
     <row r="325" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="49"/>
+      <c r="A325" s="48"/>
       <c r="B325" s="13"/>
     </row>
     <row r="326" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="49"/>
+      <c r="A326" s="48"/>
       <c r="B326" s="13"/>
     </row>
     <row r="327" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A327" s="49"/>
+      <c r="A327" s="48"/>
       <c r="B327" s="13"/>
     </row>
     <row r="328" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A328" s="49"/>
+      <c r="A328" s="48"/>
       <c r="B328" s="13"/>
     </row>
     <row r="329" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A329" s="49"/>
+      <c r="A329" s="48"/>
       <c r="B329" s="13"/>
     </row>
     <row r="330" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A330" s="49"/>
+      <c r="A330" s="48"/>
       <c r="B330" s="13"/>
     </row>
     <row r="331" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A331" s="49"/>
+      <c r="A331" s="48"/>
       <c r="B331" s="13"/>
     </row>
     <row r="332" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A332" s="49"/>
+      <c r="A332" s="48"/>
       <c r="B332" s="13"/>
     </row>
     <row r="333" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A333" s="49"/>
+      <c r="A333" s="48"/>
       <c r="B333" s="13"/>
     </row>
     <row r="334" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A334" s="49"/>
+      <c r="A334" s="48"/>
       <c r="B334" s="13"/>
     </row>
     <row r="335" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A335" s="49"/>
+      <c r="A335" s="48"/>
       <c r="B335" s="13"/>
     </row>
     <row r="336" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A336" s="49"/>
+      <c r="A336" s="48"/>
       <c r="B336" s="13"/>
     </row>
     <row r="337" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A337" s="49"/>
+      <c r="A337" s="48"/>
       <c r="B337" s="13"/>
     </row>
     <row r="338" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A338" s="49"/>
+      <c r="A338" s="48"/>
       <c r="B338" s="13"/>
     </row>
     <row r="339" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A339" s="49"/>
+      <c r="A339" s="48"/>
       <c r="B339" s="13"/>
     </row>
-    <row r="340" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A340" s="49"/>
-      <c r="B340" s="13"/>
-    </row>
-    <row r="341" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A341" s="49"/>
-      <c r="B341" s="13"/>
-    </row>
-    <row r="342" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A342" s="49"/>
-      <c r="B342" s="13"/>
+    <row r="340" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="53"/>
+      <c r="B340" s="53"/>
+      <c r="C340" s="53"/>
+      <c r="D340" s="53"/>
+      <c r="E340" s="53"/>
+      <c r="F340" s="53"/>
+      <c r="G340" s="53"/>
+      <c r="H340" s="53"/>
+      <c r="I340" s="53"/>
+      <c r="J340" s="53"/>
+      <c r="K340" s="53"/>
+      <c r="L340" s="53"/>
+    </row>
+    <row r="341" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="53"/>
+      <c r="B341" s="53"/>
+      <c r="C341" s="53"/>
+      <c r="D341" s="53"/>
+      <c r="E341" s="53"/>
+      <c r="F341" s="53"/>
+      <c r="G341" s="53"/>
+      <c r="H341" s="53"/>
+      <c r="I341" s="53"/>
+      <c r="J341" s="53"/>
+      <c r="K341" s="53"/>
+      <c r="L341" s="53"/>
+    </row>
+    <row r="342" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="53"/>
+      <c r="B342" s="53"/>
+      <c r="C342" s="53"/>
+      <c r="D342" s="53"/>
+      <c r="E342" s="53"/>
+      <c r="F342" s="53"/>
+      <c r="G342" s="53"/>
+      <c r="H342" s="53"/>
+      <c r="I342" s="53"/>
+      <c r="J342" s="53"/>
+      <c r="K342" s="53"/>
+      <c r="L342" s="53"/>
     </row>
     <row r="343" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="54"/>
-      <c r="B343" s="54"/>
-      <c r="C343" s="54"/>
-      <c r="D343" s="54"/>
-      <c r="E343" s="54"/>
-      <c r="F343" s="54"/>
-      <c r="G343" s="54"/>
-      <c r="H343" s="54"/>
-      <c r="I343" s="54"/>
-      <c r="J343" s="54"/>
-      <c r="K343" s="54"/>
-      <c r="L343" s="54"/>
+      <c r="A343" s="53"/>
+      <c r="B343" s="53"/>
+      <c r="C343" s="53"/>
+      <c r="D343" s="53"/>
+      <c r="E343" s="53"/>
+      <c r="F343" s="53"/>
+      <c r="G343" s="53"/>
+      <c r="H343" s="53"/>
+      <c r="I343" s="53"/>
+      <c r="J343" s="53"/>
+      <c r="K343" s="53"/>
+      <c r="L343" s="53"/>
     </row>
     <row r="344" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="54"/>
-      <c r="B344" s="54"/>
-      <c r="C344" s="54"/>
-      <c r="D344" s="54"/>
-      <c r="E344" s="54"/>
-      <c r="F344" s="54"/>
-      <c r="G344" s="54"/>
-      <c r="H344" s="54"/>
-      <c r="I344" s="54"/>
-      <c r="J344" s="54"/>
-      <c r="K344" s="54"/>
-      <c r="L344" s="54"/>
-    </row>
-    <row r="345" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="53"/>
+      <c r="B344" s="53"/>
+      <c r="C344" s="53"/>
+      <c r="D344" s="53"/>
+      <c r="E344" s="53"/>
+      <c r="F344" s="53"/>
+      <c r="G344" s="53"/>
+      <c r="H344" s="53"/>
+      <c r="I344" s="53"/>
+      <c r="J344" s="53"/>
+      <c r="K344" s="53"/>
+      <c r="L344" s="53"/>
+    </row>
+    <row r="345" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="54"/>
-      <c r="B345" s="54"/>
-      <c r="C345" s="54"/>
-      <c r="D345" s="54"/>
-      <c r="E345" s="54"/>
-      <c r="F345" s="54"/>
-      <c r="G345" s="54"/>
-      <c r="H345" s="54"/>
-      <c r="I345" s="54"/>
-      <c r="J345" s="54"/>
-      <c r="K345" s="54"/>
-      <c r="L345" s="54"/>
+      <c r="B345" s="55"/>
+      <c r="C345" s="56"/>
+      <c r="D345" s="57"/>
+      <c r="E345" s="58"/>
+      <c r="F345" s="58"/>
+      <c r="G345" s="59"/>
+      <c r="M345" s="60"/>
+      <c r="N345" s="61"/>
+      <c r="O345" s="61"/>
     </row>
     <row r="346" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="54"/>
-      <c r="B346" s="54"/>
-      <c r="C346" s="54"/>
-      <c r="D346" s="54"/>
-      <c r="E346" s="54"/>
-      <c r="F346" s="54"/>
-      <c r="G346" s="54"/>
-      <c r="H346" s="54"/>
-      <c r="I346" s="54"/>
-      <c r="J346" s="54"/>
-      <c r="K346" s="54"/>
-      <c r="L346" s="54"/>
+      <c r="B346" s="55"/>
+      <c r="C346" s="56"/>
+      <c r="D346" s="57"/>
+      <c r="E346" s="58"/>
+      <c r="F346" s="58"/>
+      <c r="G346" s="59"/>
+      <c r="M346" s="62"/>
+      <c r="N346" s="61"/>
+      <c r="O346" s="61"/>
     </row>
     <row r="347" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="54"/>
-      <c r="B347" s="54"/>
-      <c r="C347" s="54"/>
-      <c r="D347" s="54"/>
-      <c r="E347" s="54"/>
-      <c r="F347" s="54"/>
-      <c r="G347" s="54"/>
-      <c r="H347" s="54"/>
-      <c r="I347" s="54"/>
-      <c r="J347" s="54"/>
-      <c r="K347" s="54"/>
-      <c r="L347" s="54"/>
-    </row>
-    <row r="348" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A348" s="55"/>
-      <c r="B348" s="56"/>
-      <c r="C348" s="57"/>
-      <c r="D348" s="58"/>
-      <c r="E348" s="59"/>
-      <c r="F348" s="59"/>
-      <c r="G348" s="60"/>
-      <c r="M348" s="61"/>
-      <c r="N348" s="62"/>
-      <c r="O348" s="62"/>
+      <c r="B347" s="55"/>
+      <c r="C347" s="56"/>
+      <c r="D347" s="57"/>
+      <c r="E347" s="58"/>
+      <c r="F347" s="58"/>
+      <c r="G347" s="59"/>
+    </row>
+    <row r="348" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="54"/>
+      <c r="B348" s="55"/>
+      <c r="C348" s="56"/>
+      <c r="D348" s="57"/>
+      <c r="E348" s="58"/>
+      <c r="F348" s="58"/>
+      <c r="G348" s="59"/>
     </row>
     <row r="349" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="55"/>
-      <c r="B349" s="56"/>
-      <c r="C349" s="57"/>
-      <c r="D349" s="58"/>
-      <c r="E349" s="59"/>
-      <c r="F349" s="59"/>
-      <c r="G349" s="60"/>
-      <c r="M349" s="63"/>
-      <c r="N349" s="62"/>
-      <c r="O349" s="62"/>
+      <c r="A349" s="54"/>
+      <c r="B349" s="55"/>
+      <c r="C349" s="56"/>
+      <c r="D349" s="57"/>
+      <c r="E349" s="58"/>
+      <c r="F349" s="58"/>
+      <c r="G349" s="59"/>
     </row>
     <row r="350" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="55"/>
-      <c r="B350" s="56"/>
-      <c r="C350" s="57"/>
-      <c r="D350" s="58"/>
-      <c r="E350" s="59"/>
-      <c r="F350" s="59"/>
-      <c r="G350" s="60"/>
+      <c r="A350" s="54"/>
+      <c r="B350" s="55"/>
+      <c r="C350" s="56"/>
+      <c r="D350" s="57"/>
+      <c r="E350" s="58"/>
+      <c r="F350" s="58"/>
+      <c r="G350" s="59"/>
     </row>
     <row r="351" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="55"/>
-      <c r="B351" s="56"/>
-      <c r="C351" s="57"/>
-      <c r="D351" s="58"/>
-      <c r="E351" s="59"/>
-      <c r="F351" s="59"/>
-      <c r="G351" s="60"/>
+      <c r="A351" s="54"/>
+      <c r="B351" s="55"/>
+      <c r="C351" s="56"/>
+      <c r="D351" s="57"/>
+      <c r="E351" s="58"/>
+      <c r="F351" s="58"/>
+      <c r="G351" s="59"/>
     </row>
     <row r="352" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="55"/>
-      <c r="B352" s="56"/>
-      <c r="C352" s="57"/>
-      <c r="D352" s="58"/>
-      <c r="E352" s="59"/>
-      <c r="F352" s="59"/>
-      <c r="G352" s="60"/>
+      <c r="A352" s="54"/>
+      <c r="B352" s="55"/>
+      <c r="C352" s="56"/>
+      <c r="D352" s="57"/>
+      <c r="E352" s="58"/>
+      <c r="F352" s="58"/>
+      <c r="G352" s="59"/>
     </row>
     <row r="353" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="55"/>
-      <c r="B353" s="56"/>
-      <c r="C353" s="57"/>
-      <c r="D353" s="58"/>
-      <c r="E353" s="59"/>
-      <c r="F353" s="59"/>
-      <c r="G353" s="60"/>
+      <c r="A353" s="54"/>
+      <c r="B353" s="55"/>
+      <c r="C353" s="56"/>
+      <c r="D353" s="57"/>
+      <c r="E353" s="58"/>
+      <c r="F353" s="58"/>
+      <c r="G353" s="59"/>
     </row>
     <row r="354" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="55"/>
-      <c r="B354" s="56"/>
-      <c r="C354" s="57"/>
-      <c r="D354" s="58"/>
-      <c r="E354" s="59"/>
-      <c r="F354" s="59"/>
-      <c r="G354" s="60"/>
+      <c r="A354" s="54"/>
+      <c r="B354" s="55"/>
+      <c r="C354" s="56"/>
+      <c r="D354" s="57"/>
+      <c r="E354" s="58"/>
+      <c r="F354" s="58"/>
+      <c r="G354" s="59"/>
     </row>
     <row r="355" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="55"/>
-      <c r="B355" s="56"/>
-      <c r="C355" s="57"/>
-      <c r="D355" s="58"/>
-      <c r="E355" s="59"/>
-      <c r="F355" s="59"/>
-      <c r="G355" s="60"/>
+      <c r="A355" s="54"/>
+      <c r="B355" s="55"/>
+      <c r="C355" s="56"/>
+      <c r="D355" s="57"/>
+      <c r="E355" s="58"/>
+      <c r="F355" s="58"/>
+      <c r="G355" s="59"/>
     </row>
     <row r="356" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="55"/>
-      <c r="B356" s="56"/>
-      <c r="C356" s="57"/>
-      <c r="D356" s="58"/>
-      <c r="E356" s="59"/>
-      <c r="F356" s="59"/>
-      <c r="G356" s="60"/>
+      <c r="A356" s="54"/>
+      <c r="B356" s="55"/>
+      <c r="C356" s="56"/>
+      <c r="D356" s="57"/>
+      <c r="E356" s="58"/>
+      <c r="F356" s="58"/>
+      <c r="G356" s="59"/>
     </row>
     <row r="357" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="55"/>
-      <c r="B357" s="56"/>
-      <c r="C357" s="57"/>
-      <c r="D357" s="58"/>
-      <c r="E357" s="59"/>
-      <c r="F357" s="59"/>
-      <c r="G357" s="60"/>
+      <c r="A357" s="54"/>
+      <c r="B357" s="55"/>
+      <c r="C357" s="56"/>
+      <c r="D357" s="57"/>
+      <c r="E357" s="58"/>
+      <c r="F357" s="58"/>
+      <c r="G357" s="59"/>
     </row>
     <row r="358" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="55"/>
-      <c r="B358" s="56"/>
-      <c r="C358" s="57"/>
-      <c r="D358" s="58"/>
-      <c r="E358" s="59"/>
-      <c r="F358" s="59"/>
-      <c r="G358" s="60"/>
+      <c r="A358" s="54"/>
+      <c r="B358" s="55"/>
+      <c r="C358" s="56"/>
+      <c r="D358" s="57"/>
+      <c r="E358" s="58"/>
+      <c r="F358" s="58"/>
+      <c r="G358" s="59"/>
     </row>
     <row r="359" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="55"/>
-      <c r="B359" s="56"/>
-      <c r="C359" s="57"/>
-      <c r="D359" s="58"/>
-      <c r="E359" s="59"/>
-      <c r="F359" s="59"/>
-      <c r="G359" s="60"/>
+      <c r="A359" s="54"/>
+      <c r="B359" s="55"/>
+      <c r="C359" s="56"/>
+      <c r="D359" s="57"/>
+      <c r="E359" s="58"/>
+      <c r="F359" s="58"/>
+      <c r="G359" s="59"/>
     </row>
     <row r="360" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="55"/>
-      <c r="B360" s="56"/>
-      <c r="C360" s="57"/>
-      <c r="D360" s="58"/>
-      <c r="E360" s="59"/>
-      <c r="F360" s="59"/>
-      <c r="G360" s="60"/>
+      <c r="A360" s="54"/>
+      <c r="B360" s="55"/>
+      <c r="C360" s="56"/>
+      <c r="D360" s="57"/>
+      <c r="E360" s="58"/>
+      <c r="F360" s="58"/>
+      <c r="G360" s="59"/>
     </row>
     <row r="361" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="55"/>
-      <c r="B361" s="56"/>
-      <c r="C361" s="57"/>
-      <c r="D361" s="58"/>
-      <c r="E361" s="59"/>
-      <c r="F361" s="59"/>
-      <c r="G361" s="60"/>
+      <c r="A361" s="54"/>
+      <c r="B361" s="55"/>
+      <c r="C361" s="56"/>
+      <c r="D361" s="57"/>
+      <c r="E361" s="58"/>
+      <c r="F361" s="58"/>
+      <c r="G361" s="59"/>
     </row>
     <row r="362" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="55"/>
-      <c r="B362" s="56"/>
-      <c r="C362" s="57"/>
-      <c r="D362" s="58"/>
-      <c r="E362" s="59"/>
-      <c r="F362" s="59"/>
-      <c r="G362" s="60"/>
+      <c r="A362" s="54"/>
+      <c r="B362" s="55"/>
+      <c r="C362" s="56"/>
+      <c r="D362" s="57"/>
+      <c r="E362" s="58"/>
+      <c r="F362" s="58"/>
+      <c r="G362" s="59"/>
     </row>
     <row r="363" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="55"/>
-      <c r="B363" s="56"/>
-      <c r="C363" s="57"/>
-      <c r="D363" s="58"/>
-      <c r="E363" s="59"/>
-      <c r="F363" s="59"/>
-      <c r="G363" s="60"/>
+      <c r="A363" s="54"/>
+      <c r="B363" s="55"/>
+      <c r="C363" s="56"/>
+      <c r="D363" s="57"/>
+      <c r="E363" s="58"/>
+      <c r="F363" s="58"/>
+      <c r="G363" s="59"/>
     </row>
     <row r="364" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="55"/>
-      <c r="B364" s="56"/>
-      <c r="C364" s="57"/>
-      <c r="D364" s="58"/>
-      <c r="E364" s="59"/>
-      <c r="F364" s="59"/>
-      <c r="G364" s="60"/>
+      <c r="A364" s="54"/>
+      <c r="B364" s="55"/>
+      <c r="C364" s="56"/>
+      <c r="D364" s="57"/>
+      <c r="E364" s="58"/>
+      <c r="F364" s="58"/>
+      <c r="G364" s="59"/>
     </row>
     <row r="365" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="55"/>
-      <c r="B365" s="56"/>
-      <c r="C365" s="57"/>
-      <c r="D365" s="58"/>
-      <c r="E365" s="59"/>
-      <c r="F365" s="59"/>
-      <c r="G365" s="60"/>
+      <c r="A365" s="54"/>
+      <c r="B365" s="55"/>
+      <c r="C365" s="56"/>
+      <c r="D365" s="57"/>
+      <c r="E365" s="58"/>
+      <c r="F365" s="58"/>
+      <c r="G365" s="59"/>
     </row>
     <row r="366" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="55"/>
-      <c r="B366" s="56"/>
-      <c r="C366" s="57"/>
-      <c r="D366" s="58"/>
-      <c r="E366" s="59"/>
-      <c r="F366" s="59"/>
-      <c r="G366" s="60"/>
+      <c r="A366" s="54"/>
+      <c r="B366" s="55"/>
+      <c r="C366" s="56"/>
+      <c r="D366" s="57"/>
+      <c r="E366" s="58"/>
+      <c r="F366" s="58"/>
+      <c r="G366" s="59"/>
     </row>
     <row r="367" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="55"/>
-      <c r="B367" s="56"/>
-      <c r="C367" s="57"/>
-      <c r="D367" s="58"/>
-      <c r="E367" s="59"/>
-      <c r="F367" s="59"/>
-      <c r="G367" s="60"/>
+      <c r="A367" s="54"/>
+      <c r="B367" s="55"/>
+      <c r="C367" s="56"/>
+      <c r="D367" s="57"/>
+      <c r="E367" s="58"/>
+      <c r="F367" s="58"/>
+      <c r="G367" s="59"/>
     </row>
     <row r="368" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="55"/>
-      <c r="B368" s="56"/>
-      <c r="C368" s="57"/>
-      <c r="D368" s="58"/>
-      <c r="E368" s="59"/>
-      <c r="F368" s="59"/>
-      <c r="G368" s="60"/>
+      <c r="A368" s="54"/>
+      <c r="B368" s="55"/>
+      <c r="C368" s="56"/>
+      <c r="D368" s="57"/>
+      <c r="E368" s="58"/>
+      <c r="F368" s="58"/>
+      <c r="G368" s="59"/>
     </row>
     <row r="369" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="55"/>
-      <c r="B369" s="56"/>
-      <c r="C369" s="57"/>
-      <c r="D369" s="58"/>
-      <c r="E369" s="59"/>
-      <c r="F369" s="59"/>
-      <c r="G369" s="60"/>
+      <c r="A369" s="54"/>
+      <c r="B369" s="55"/>
+      <c r="C369" s="56"/>
+      <c r="D369" s="57"/>
+      <c r="E369" s="58"/>
+      <c r="F369" s="58"/>
+      <c r="G369" s="59"/>
     </row>
     <row r="370" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="55"/>
-      <c r="B370" s="56"/>
-      <c r="C370" s="57"/>
-      <c r="D370" s="58"/>
-      <c r="E370" s="59"/>
-      <c r="F370" s="59"/>
-      <c r="G370" s="60"/>
+      <c r="A370" s="54"/>
+      <c r="B370" s="55"/>
+      <c r="C370" s="56"/>
+      <c r="D370" s="57"/>
+      <c r="E370" s="58"/>
+      <c r="F370" s="58"/>
+      <c r="G370" s="59"/>
     </row>
     <row r="371" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="55"/>
-      <c r="B371" s="56"/>
-      <c r="C371" s="57"/>
-      <c r="D371" s="58"/>
-      <c r="E371" s="59"/>
-      <c r="F371" s="59"/>
-      <c r="G371" s="60"/>
+      <c r="A371" s="54"/>
+      <c r="B371" s="55"/>
+      <c r="C371" s="56"/>
+      <c r="D371" s="57"/>
+      <c r="E371" s="58"/>
+      <c r="F371" s="58"/>
+      <c r="G371" s="59"/>
     </row>
     <row r="372" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="55"/>
-      <c r="B372" s="56"/>
-      <c r="C372" s="57"/>
-      <c r="D372" s="58"/>
-      <c r="E372" s="59"/>
-      <c r="F372" s="59"/>
-      <c r="G372" s="60"/>
+      <c r="A372" s="54"/>
+      <c r="B372" s="55"/>
+      <c r="C372" s="56"/>
+      <c r="D372" s="57"/>
+      <c r="E372" s="58"/>
+      <c r="F372" s="58"/>
+      <c r="G372" s="59"/>
     </row>
     <row r="373" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="55"/>
-      <c r="B373" s="56"/>
-      <c r="C373" s="57"/>
-      <c r="D373" s="58"/>
-      <c r="E373" s="59"/>
-      <c r="F373" s="59"/>
-      <c r="G373" s="60"/>
+      <c r="A373" s="54"/>
+      <c r="B373" s="55"/>
+      <c r="C373" s="56"/>
+      <c r="D373" s="57"/>
+      <c r="E373" s="58"/>
+      <c r="F373" s="58"/>
+      <c r="G373" s="59"/>
     </row>
     <row r="374" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="55"/>
-      <c r="B374" s="56"/>
-      <c r="C374" s="57"/>
-      <c r="D374" s="58"/>
-      <c r="E374" s="59"/>
-      <c r="F374" s="59"/>
-      <c r="G374" s="60"/>
+      <c r="A374" s="54"/>
+      <c r="B374" s="55"/>
+      <c r="C374" s="56"/>
+      <c r="D374" s="57"/>
+      <c r="E374" s="58"/>
+      <c r="F374" s="58"/>
+      <c r="G374" s="59"/>
     </row>
     <row r="375" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="55"/>
-      <c r="B375" s="56"/>
-      <c r="C375" s="57"/>
-      <c r="D375" s="58"/>
-      <c r="E375" s="59"/>
-      <c r="F375" s="59"/>
-      <c r="G375" s="60"/>
+      <c r="A375" s="54"/>
+      <c r="B375" s="55"/>
+      <c r="C375" s="56"/>
+      <c r="D375" s="57"/>
+      <c r="E375" s="58"/>
+      <c r="F375" s="58"/>
+      <c r="G375" s="59"/>
     </row>
     <row r="376" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="55"/>
-      <c r="B376" s="56"/>
-      <c r="C376" s="57"/>
-      <c r="D376" s="58"/>
-      <c r="E376" s="59"/>
-      <c r="F376" s="59"/>
-      <c r="G376" s="60"/>
+      <c r="A376" s="54"/>
+      <c r="B376" s="55"/>
+      <c r="C376" s="56"/>
+      <c r="D376" s="57"/>
+      <c r="E376" s="58"/>
+      <c r="F376" s="58"/>
+      <c r="G376" s="59"/>
     </row>
     <row r="377" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="55"/>
-      <c r="B377" s="56"/>
-      <c r="C377" s="57"/>
-      <c r="D377" s="58"/>
-      <c r="E377" s="59"/>
-      <c r="F377" s="59"/>
-      <c r="G377" s="60"/>
+      <c r="A377" s="54"/>
+      <c r="B377" s="55"/>
+      <c r="C377" s="56"/>
+      <c r="D377" s="57"/>
+      <c r="E377" s="58"/>
+      <c r="F377" s="58"/>
+      <c r="G377" s="59"/>
     </row>
     <row r="378" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="55"/>
-      <c r="B378" s="56"/>
-      <c r="C378" s="57"/>
-      <c r="D378" s="58"/>
-      <c r="E378" s="59"/>
-      <c r="F378" s="59"/>
-      <c r="G378" s="60"/>
+      <c r="A378" s="54"/>
+      <c r="B378" s="55"/>
+      <c r="C378" s="56"/>
+      <c r="D378" s="57"/>
+      <c r="E378" s="58"/>
+      <c r="F378" s="58"/>
+      <c r="G378" s="59"/>
     </row>
     <row r="379" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="55"/>
-      <c r="B379" s="56"/>
-      <c r="C379" s="57"/>
-      <c r="D379" s="58"/>
-      <c r="E379" s="59"/>
-      <c r="F379" s="59"/>
-      <c r="G379" s="60"/>
+      <c r="A379" s="54"/>
+      <c r="B379" s="55"/>
+      <c r="C379" s="56"/>
+      <c r="D379" s="57"/>
+      <c r="E379" s="58"/>
+      <c r="F379" s="58"/>
+      <c r="G379" s="59"/>
     </row>
     <row r="380" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="55"/>
-      <c r="B380" s="56"/>
-      <c r="C380" s="57"/>
-      <c r="D380" s="58"/>
-      <c r="E380" s="59"/>
-      <c r="F380" s="59"/>
-      <c r="G380" s="60"/>
+      <c r="A380" s="54"/>
+      <c r="B380" s="55"/>
+      <c r="C380" s="56"/>
+      <c r="D380" s="57"/>
+      <c r="E380" s="58"/>
+      <c r="F380" s="58"/>
+      <c r="G380" s="59"/>
     </row>
     <row r="381" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="55"/>
-      <c r="B381" s="56"/>
-      <c r="C381" s="57"/>
-      <c r="D381" s="58"/>
-      <c r="E381" s="59"/>
-      <c r="F381" s="59"/>
-      <c r="G381" s="60"/>
+      <c r="A381" s="54"/>
+      <c r="B381" s="55"/>
+      <c r="C381" s="56"/>
+      <c r="D381" s="57"/>
+      <c r="E381" s="58"/>
+      <c r="F381" s="58"/>
+      <c r="G381" s="59"/>
     </row>
     <row r="382" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="55"/>
-      <c r="B382" s="56"/>
-      <c r="C382" s="57"/>
-      <c r="D382" s="58"/>
-      <c r="E382" s="59"/>
-      <c r="F382" s="59"/>
-      <c r="G382" s="60"/>
+      <c r="A382" s="54"/>
+      <c r="B382" s="55"/>
+      <c r="C382" s="56"/>
+      <c r="D382" s="57"/>
+      <c r="E382" s="58"/>
+      <c r="F382" s="58"/>
+      <c r="G382" s="59"/>
     </row>
     <row r="383" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="55"/>
-      <c r="B383" s="56"/>
-      <c r="C383" s="57"/>
-      <c r="D383" s="58"/>
-      <c r="E383" s="59"/>
-      <c r="F383" s="59"/>
-      <c r="G383" s="60"/>
+      <c r="A383" s="54"/>
+      <c r="B383" s="55"/>
+      <c r="C383" s="56"/>
+      <c r="D383" s="57"/>
+      <c r="E383" s="58"/>
+      <c r="F383" s="58"/>
+      <c r="G383" s="59"/>
     </row>
     <row r="384" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="55"/>
-      <c r="B384" s="56"/>
-      <c r="C384" s="57"/>
-      <c r="D384" s="58"/>
-      <c r="E384" s="59"/>
-      <c r="F384" s="59"/>
-      <c r="G384" s="60"/>
+      <c r="A384" s="54"/>
+      <c r="B384" s="55"/>
+      <c r="C384" s="56"/>
+      <c r="D384" s="57"/>
+      <c r="E384" s="58"/>
+      <c r="F384" s="58"/>
+      <c r="G384" s="59"/>
     </row>
     <row r="385" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="55"/>
-      <c r="B385" s="56"/>
-      <c r="C385" s="57"/>
-      <c r="D385" s="58"/>
-      <c r="E385" s="59"/>
-      <c r="F385" s="59"/>
-      <c r="G385" s="60"/>
-    </row>
-    <row r="386" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="55"/>
-      <c r="B386" s="56"/>
-      <c r="C386" s="57"/>
-      <c r="D386" s="58"/>
-      <c r="E386" s="59"/>
-      <c r="F386" s="59"/>
-      <c r="G386" s="60"/>
-    </row>
-    <row r="387" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="55"/>
-      <c r="B387" s="56"/>
-      <c r="C387" s="57"/>
-      <c r="D387" s="58"/>
-      <c r="E387" s="59"/>
-      <c r="F387" s="59"/>
-      <c r="G387" s="60"/>
-    </row>
-    <row r="388" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="55"/>
-      <c r="B388" s="56"/>
-      <c r="C388" s="57"/>
-      <c r="D388" s="58"/>
-      <c r="E388" s="59"/>
-      <c r="F388" s="59"/>
-      <c r="G388" s="60"/>
+      <c r="A385" s="54"/>
+      <c r="B385" s="55"/>
+      <c r="C385" s="56"/>
+      <c r="D385" s="57"/>
+      <c r="E385" s="58"/>
+      <c r="F385" s="58"/>
+      <c r="G385" s="59"/>
+    </row>
+    <row r="386" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A386" s="53"/>
+      <c r="B386" s="53"/>
+      <c r="C386" s="53"/>
+      <c r="D386" s="53"/>
+      <c r="E386" s="53"/>
+      <c r="F386" s="53"/>
+      <c r="G386" s="53"/>
+      <c r="H386" s="53"/>
+      <c r="I386" s="53"/>
+      <c r="J386" s="53"/>
+      <c r="K386" s="53"/>
+      <c r="L386" s="53"/>
+    </row>
+    <row r="387" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A387" s="53"/>
+      <c r="B387" s="53"/>
+      <c r="C387" s="53"/>
+      <c r="D387" s="53"/>
+      <c r="E387" s="53"/>
+      <c r="F387" s="53"/>
+      <c r="G387" s="53"/>
+      <c r="H387" s="53"/>
+      <c r="I387" s="53"/>
+      <c r="J387" s="53"/>
+      <c r="K387" s="53"/>
+      <c r="L387" s="53"/>
+    </row>
+    <row r="388" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A388" s="53"/>
+      <c r="B388" s="53"/>
+      <c r="C388" s="53"/>
+      <c r="D388" s="53"/>
+      <c r="E388" s="53"/>
+      <c r="F388" s="53"/>
+      <c r="G388" s="53"/>
+      <c r="H388" s="53"/>
+      <c r="I388" s="53"/>
+      <c r="J388" s="53"/>
+      <c r="K388" s="53"/>
+      <c r="L388" s="53"/>
     </row>
     <row r="389" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A389" s="54"/>
-      <c r="B389" s="54"/>
-      <c r="C389" s="54"/>
-      <c r="D389" s="54"/>
-      <c r="E389" s="54"/>
-      <c r="F389" s="54"/>
-      <c r="G389" s="54"/>
-      <c r="H389" s="54"/>
-      <c r="I389" s="54"/>
-      <c r="J389" s="54"/>
-      <c r="K389" s="54"/>
-      <c r="L389" s="54"/>
+      <c r="A389" s="53"/>
+      <c r="B389" s="53"/>
+      <c r="C389" s="53"/>
+      <c r="D389" s="53"/>
+      <c r="E389" s="53"/>
+      <c r="F389" s="53"/>
+      <c r="G389" s="53"/>
+      <c r="H389" s="53"/>
+      <c r="I389" s="53"/>
+      <c r="J389" s="53"/>
+      <c r="K389" s="53"/>
+      <c r="L389" s="53"/>
     </row>
     <row r="390" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A390" s="54"/>
-      <c r="B390" s="54"/>
-      <c r="C390" s="54"/>
-      <c r="D390" s="54"/>
-      <c r="E390" s="54"/>
-      <c r="F390" s="54"/>
-      <c r="G390" s="54"/>
-      <c r="H390" s="54"/>
-      <c r="I390" s="54"/>
-      <c r="J390" s="54"/>
-      <c r="K390" s="54"/>
-      <c r="L390" s="54"/>
-    </row>
-    <row r="391" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A391" s="54"/>
-      <c r="B391" s="54"/>
-      <c r="C391" s="54"/>
-      <c r="D391" s="54"/>
-      <c r="E391" s="54"/>
-      <c r="F391" s="54"/>
-      <c r="G391" s="54"/>
-      <c r="H391" s="54"/>
-      <c r="I391" s="54"/>
-      <c r="J391" s="54"/>
-      <c r="K391" s="54"/>
-      <c r="L391" s="54"/>
-    </row>
-    <row r="392" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A392" s="54"/>
-      <c r="B392" s="54"/>
-      <c r="C392" s="54"/>
-      <c r="D392" s="54"/>
-      <c r="E392" s="54"/>
-      <c r="F392" s="54"/>
-      <c r="G392" s="54"/>
-      <c r="H392" s="54"/>
-      <c r="I392" s="54"/>
-      <c r="J392" s="54"/>
-      <c r="K392" s="54"/>
-      <c r="L392" s="54"/>
-    </row>
-    <row r="393" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="54"/>
-      <c r="B393" s="54"/>
-      <c r="C393" s="54"/>
-      <c r="D393" s="54"/>
-      <c r="E393" s="54"/>
-      <c r="F393" s="54"/>
-      <c r="G393" s="54"/>
-      <c r="H393" s="54"/>
-      <c r="I393" s="54"/>
-      <c r="J393" s="54"/>
-      <c r="K393" s="54"/>
-      <c r="L393" s="54"/>
+      <c r="A390" s="53"/>
+      <c r="B390" s="53"/>
+      <c r="C390" s="53"/>
+      <c r="D390" s="53"/>
+      <c r="E390" s="53"/>
+      <c r="F390" s="53"/>
+      <c r="G390" s="53"/>
+      <c r="H390" s="53"/>
+      <c r="I390" s="53"/>
+      <c r="J390" s="53"/>
+      <c r="K390" s="53"/>
+      <c r="L390" s="53"/>
+    </row>
+    <row r="391" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A391" s="41"/>
+      <c r="B391" s="13"/>
+      <c r="C391" s="15"/>
+      <c r="D391" s="63"/>
+      <c r="E391" s="15"/>
+      <c r="F391" s="15"/>
+      <c r="G391" s="15"/>
+    </row>
+    <row r="392" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A392" s="41"/>
+      <c r="B392" s="13"/>
+      <c r="C392" s="15"/>
+      <c r="D392" s="63"/>
+      <c r="E392" s="15"/>
+      <c r="F392" s="15"/>
+      <c r="G392" s="15"/>
+    </row>
+    <row r="393" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A393" s="41"/>
+      <c r="B393" s="13"/>
+      <c r="C393" s="15"/>
+      <c r="D393" s="63"/>
+      <c r="E393" s="15"/>
+      <c r="F393" s="15"/>
+      <c r="G393" s="15"/>
     </row>
     <row r="394" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="42"/>
+      <c r="A394" s="41"/>
       <c r="B394" s="13"/>
       <c r="C394" s="15"/>
-      <c r="D394" s="64"/>
+      <c r="D394" s="63"/>
       <c r="E394" s="15"/>
       <c r="F394" s="15"/>
       <c r="G394" s="15"/>
     </row>
     <row r="395" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A395" s="42"/>
+      <c r="A395" s="41"/>
       <c r="B395" s="13"/>
       <c r="C395" s="15"/>
-      <c r="D395" s="64"/>
+      <c r="D395" s="63"/>
       <c r="E395" s="15"/>
       <c r="F395" s="15"/>
       <c r="G395" s="15"/>
     </row>
     <row r="396" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A396" s="42"/>
+      <c r="A396" s="41"/>
       <c r="B396" s="13"/>
       <c r="C396" s="15"/>
-      <c r="D396" s="64"/>
+      <c r="D396" s="63"/>
       <c r="E396" s="15"/>
       <c r="F396" s="15"/>
       <c r="G396" s="15"/>
     </row>
     <row r="397" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A397" s="42"/>
+      <c r="A397" s="41"/>
       <c r="B397" s="13"/>
       <c r="C397" s="15"/>
-      <c r="D397" s="64"/>
+      <c r="D397" s="63"/>
       <c r="E397" s="15"/>
       <c r="F397" s="15"/>
       <c r="G397" s="15"/>
     </row>
     <row r="398" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A398" s="42"/>
+      <c r="A398" s="41"/>
       <c r="B398" s="13"/>
       <c r="C398" s="15"/>
-      <c r="D398" s="64"/>
+      <c r="D398" s="63"/>
       <c r="E398" s="15"/>
       <c r="F398" s="15"/>
       <c r="G398" s="15"/>
     </row>
     <row r="399" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A399" s="42"/>
+      <c r="A399" s="41"/>
       <c r="B399" s="13"/>
       <c r="C399" s="15"/>
-      <c r="D399" s="64"/>
+      <c r="D399" s="63"/>
       <c r="E399" s="15"/>
       <c r="F399" s="15"/>
       <c r="G399" s="15"/>
     </row>
     <row r="400" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A400" s="42"/>
+      <c r="A400" s="41"/>
       <c r="B400" s="13"/>
       <c r="C400" s="15"/>
-      <c r="D400" s="64"/>
+      <c r="D400" s="63"/>
       <c r="E400" s="15"/>
       <c r="F400" s="15"/>
       <c r="G400" s="15"/>
     </row>
     <row r="401" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A401" s="42"/>
+      <c r="A401" s="41"/>
       <c r="B401" s="13"/>
       <c r="C401" s="15"/>
-      <c r="D401" s="64"/>
+      <c r="D401" s="63"/>
       <c r="E401" s="15"/>
       <c r="F401" s="15"/>
       <c r="G401" s="15"/>
     </row>
     <row r="402" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A402" s="42"/>
+      <c r="A402" s="41"/>
       <c r="B402" s="13"/>
       <c r="C402" s="15"/>
-      <c r="D402" s="64"/>
+      <c r="D402" s="63"/>
       <c r="E402" s="15"/>
       <c r="F402" s="15"/>
       <c r="G402" s="15"/>
     </row>
     <row r="403" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A403" s="42"/>
+      <c r="A403" s="41"/>
       <c r="B403" s="13"/>
       <c r="C403" s="15"/>
-      <c r="D403" s="64"/>
+      <c r="D403" s="63"/>
       <c r="E403" s="15"/>
       <c r="F403" s="15"/>
       <c r="G403" s="15"/>
     </row>
     <row r="404" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A404" s="42"/>
+      <c r="A404" s="41"/>
       <c r="B404" s="13"/>
       <c r="C404" s="15"/>
-      <c r="D404" s="64"/>
+      <c r="D404" s="63"/>
       <c r="E404" s="15"/>
       <c r="F404" s="15"/>
       <c r="G404" s="15"/>
     </row>
     <row r="405" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A405" s="42"/>
+      <c r="A405" s="41"/>
       <c r="B405" s="13"/>
       <c r="C405" s="15"/>
-      <c r="D405" s="64"/>
+      <c r="D405" s="63"/>
       <c r="E405" s="15"/>
       <c r="F405" s="15"/>
       <c r="G405" s="15"/>
     </row>
     <row r="406" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A406" s="42"/>
+      <c r="A406" s="41"/>
       <c r="B406" s="13"/>
       <c r="C406" s="15"/>
-      <c r="D406" s="64"/>
+      <c r="D406" s="63"/>
       <c r="E406" s="15"/>
       <c r="F406" s="15"/>
       <c r="G406" s="15"/>
     </row>
     <row r="407" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A407" s="42"/>
+      <c r="A407" s="41"/>
       <c r="B407" s="13"/>
       <c r="C407" s="15"/>
-      <c r="D407" s="64"/>
+      <c r="D407" s="63"/>
       <c r="E407" s="15"/>
       <c r="F407" s="15"/>
       <c r="G407" s="15"/>
     </row>
     <row r="408" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A408" s="42"/>
+      <c r="A408" s="41"/>
       <c r="B408" s="13"/>
       <c r="C408" s="15"/>
-      <c r="D408" s="64"/>
+      <c r="D408" s="63"/>
       <c r="E408" s="15"/>
       <c r="F408" s="15"/>
       <c r="G408" s="15"/>
     </row>
     <row r="409" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A409" s="42"/>
+      <c r="A409" s="41"/>
       <c r="B409" s="13"/>
       <c r="C409" s="15"/>
-      <c r="D409" s="64"/>
+      <c r="D409" s="63"/>
       <c r="E409" s="15"/>
       <c r="F409" s="15"/>
       <c r="G409" s="15"/>
     </row>
     <row r="410" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A410" s="42"/>
+      <c r="A410" s="41"/>
       <c r="B410" s="13"/>
       <c r="C410" s="15"/>
-      <c r="D410" s="64"/>
+      <c r="D410" s="63"/>
       <c r="E410" s="15"/>
       <c r="F410" s="15"/>
       <c r="G410" s="15"/>
     </row>
     <row r="411" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A411" s="42"/>
+      <c r="A411" s="41"/>
       <c r="B411" s="13"/>
       <c r="C411" s="15"/>
-      <c r="D411" s="64"/>
+      <c r="D411" s="63"/>
       <c r="E411" s="15"/>
       <c r="F411" s="15"/>
       <c r="G411" s="15"/>
     </row>
     <row r="412" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A412" s="42"/>
+      <c r="A412" s="41"/>
       <c r="B412" s="13"/>
       <c r="C412" s="15"/>
-      <c r="D412" s="64"/>
+      <c r="D412" s="63"/>
       <c r="E412" s="15"/>
       <c r="F412" s="15"/>
       <c r="G412" s="15"/>
     </row>
     <row r="413" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A413" s="42"/>
+      <c r="A413" s="41"/>
       <c r="B413" s="13"/>
       <c r="C413" s="15"/>
-      <c r="D413" s="64"/>
+      <c r="D413" s="63"/>
       <c r="E413" s="15"/>
       <c r="F413" s="15"/>
       <c r="G413" s="15"/>
     </row>
     <row r="414" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A414" s="42"/>
+      <c r="A414" s="41"/>
       <c r="B414" s="13"/>
       <c r="C414" s="15"/>
-      <c r="D414" s="64"/>
+      <c r="D414" s="63"/>
       <c r="E414" s="15"/>
       <c r="F414" s="15"/>
       <c r="G414" s="15"/>
     </row>
     <row r="415" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A415" s="42"/>
+      <c r="A415" s="41"/>
       <c r="B415" s="13"/>
       <c r="C415" s="15"/>
-      <c r="D415" s="64"/>
+      <c r="D415" s="63"/>
       <c r="E415" s="15"/>
       <c r="F415" s="15"/>
       <c r="G415" s="15"/>
     </row>
     <row r="416" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A416" s="42"/>
+      <c r="A416" s="41"/>
       <c r="B416" s="13"/>
       <c r="C416" s="15"/>
-      <c r="D416" s="64"/>
+      <c r="D416" s="63"/>
       <c r="E416" s="15"/>
       <c r="F416" s="15"/>
       <c r="G416" s="15"/>
     </row>
     <row r="417" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A417" s="42"/>
+      <c r="A417" s="41"/>
       <c r="B417" s="13"/>
       <c r="C417" s="15"/>
-      <c r="D417" s="64"/>
+      <c r="D417" s="63"/>
       <c r="E417" s="15"/>
       <c r="F417" s="15"/>
       <c r="G417" s="15"/>
     </row>
     <row r="418" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A418" s="42"/>
+      <c r="A418" s="41"/>
       <c r="B418" s="13"/>
       <c r="C418" s="15"/>
-      <c r="D418" s="64"/>
+      <c r="D418" s="63"/>
       <c r="E418" s="15"/>
       <c r="F418" s="15"/>
       <c r="G418" s="15"/>
     </row>
     <row r="419" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A419" s="42"/>
+      <c r="A419" s="41"/>
       <c r="B419" s="13"/>
       <c r="C419" s="15"/>
-      <c r="D419" s="64"/>
+      <c r="D419" s="63"/>
       <c r="E419" s="15"/>
       <c r="F419" s="15"/>
       <c r="G419" s="15"/>
     </row>
     <row r="420" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A420" s="42"/>
+      <c r="A420" s="41"/>
       <c r="B420" s="13"/>
       <c r="C420" s="15"/>
-      <c r="D420" s="64"/>
+      <c r="D420" s="63"/>
       <c r="E420" s="15"/>
       <c r="F420" s="15"/>
       <c r="G420" s="15"/>
     </row>
     <row r="421" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A421" s="42"/>
+      <c r="A421" s="41"/>
       <c r="B421" s="13"/>
       <c r="C421" s="15"/>
-      <c r="D421" s="64"/>
+      <c r="D421" s="63"/>
       <c r="E421" s="15"/>
       <c r="F421" s="15"/>
       <c r="G421" s="15"/>
     </row>
     <row r="422" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A422" s="42"/>
+      <c r="A422" s="41"/>
       <c r="B422" s="13"/>
       <c r="C422" s="15"/>
-      <c r="D422" s="64"/>
+      <c r="D422" s="63"/>
       <c r="E422" s="15"/>
       <c r="F422" s="15"/>
       <c r="G422" s="15"/>
     </row>
     <row r="423" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A423" s="42"/>
+      <c r="A423" s="41"/>
       <c r="B423" s="13"/>
       <c r="C423" s="15"/>
-      <c r="D423" s="64"/>
+      <c r="D423" s="63"/>
       <c r="E423" s="15"/>
       <c r="F423" s="15"/>
       <c r="G423" s="15"/>
     </row>
     <row r="424" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A424" s="42"/>
+      <c r="A424" s="41"/>
       <c r="B424" s="13"/>
       <c r="C424" s="15"/>
-      <c r="D424" s="64"/>
+      <c r="D424" s="63"/>
       <c r="E424" s="15"/>
       <c r="F424" s="15"/>
       <c r="G424" s="15"/>
     </row>
     <row r="425" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A425" s="42"/>
+      <c r="A425" s="41"/>
       <c r="B425" s="13"/>
       <c r="C425" s="15"/>
-      <c r="D425" s="64"/>
+      <c r="D425" s="63"/>
       <c r="E425" s="15"/>
       <c r="F425" s="15"/>
       <c r="G425" s="15"/>
     </row>
     <row r="426" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A426" s="42"/>
+      <c r="A426" s="41"/>
       <c r="B426" s="13"/>
       <c r="C426" s="15"/>
-      <c r="D426" s="64"/>
+      <c r="D426" s="63"/>
       <c r="E426" s="15"/>
       <c r="F426" s="15"/>
       <c r="G426" s="15"/>
     </row>
     <row r="427" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A427" s="42"/>
+      <c r="A427" s="41"/>
       <c r="B427" s="13"/>
       <c r="C427" s="15"/>
-      <c r="D427" s="64"/>
+      <c r="D427" s="63"/>
       <c r="E427" s="15"/>
       <c r="F427" s="15"/>
       <c r="G427" s="15"/>
     </row>
     <row r="428" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A428" s="42"/>
+      <c r="A428" s="41"/>
       <c r="B428" s="13"/>
       <c r="C428" s="15"/>
-      <c r="D428" s="64"/>
+      <c r="D428" s="63"/>
       <c r="E428" s="15"/>
       <c r="F428" s="15"/>
       <c r="G428" s="15"/>
     </row>
     <row r="429" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A429" s="42"/>
+      <c r="A429" s="41"/>
       <c r="B429" s="13"/>
       <c r="C429" s="15"/>
-      <c r="D429" s="64"/>
+      <c r="D429" s="63"/>
       <c r="E429" s="15"/>
       <c r="F429" s="15"/>
       <c r="G429" s="15"/>
     </row>
     <row r="430" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A430" s="42"/>
+      <c r="A430" s="41"/>
       <c r="B430" s="13"/>
       <c r="C430" s="15"/>
-      <c r="D430" s="64"/>
+      <c r="D430" s="63"/>
       <c r="E430" s="15"/>
       <c r="F430" s="15"/>
       <c r="G430" s="15"/>
     </row>
     <row r="431" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A431" s="42"/>
+      <c r="A431" s="41"/>
       <c r="B431" s="13"/>
       <c r="C431" s="15"/>
-      <c r="D431" s="64"/>
+      <c r="D431" s="63"/>
       <c r="E431" s="15"/>
       <c r="F431" s="15"/>
       <c r="G431" s="15"/>
     </row>
     <row r="432" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A432" s="42"/>
+      <c r="A432" s="41"/>
       <c r="B432" s="13"/>
       <c r="C432" s="15"/>
-      <c r="D432" s="64"/>
+      <c r="D432" s="63"/>
       <c r="E432" s="15"/>
       <c r="F432" s="15"/>
       <c r="G432" s="15"/>
     </row>
     <row r="433" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A433" s="42"/>
+      <c r="A433" s="41"/>
       <c r="B433" s="13"/>
       <c r="C433" s="15"/>
-      <c r="D433" s="64"/>
+      <c r="D433" s="63"/>
       <c r="E433" s="15"/>
       <c r="F433" s="15"/>
       <c r="G433" s="15"/>
     </row>
     <row r="434" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A434" s="42"/>
+      <c r="A434" s="41"/>
       <c r="B434" s="13"/>
       <c r="C434" s="15"/>
-      <c r="D434" s="64"/>
+      <c r="D434" s="63"/>
       <c r="E434" s="15"/>
       <c r="F434" s="15"/>
       <c r="G434" s="15"/>
     </row>
     <row r="435" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A435" s="42"/>
+      <c r="A435" s="41"/>
       <c r="B435" s="13"/>
       <c r="C435" s="15"/>
-      <c r="D435" s="64"/>
+      <c r="D435" s="63"/>
       <c r="E435" s="15"/>
       <c r="F435" s="15"/>
       <c r="G435" s="15"/>
     </row>
     <row r="436" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A436" s="42"/>
+      <c r="A436" s="41"/>
       <c r="B436" s="13"/>
       <c r="C436" s="15"/>
-      <c r="D436" s="64"/>
+      <c r="D436" s="63"/>
       <c r="E436" s="15"/>
       <c r="F436" s="15"/>
       <c r="G436" s="15"/>
     </row>
     <row r="437" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A437" s="42"/>
+      <c r="A437" s="41"/>
       <c r="B437" s="13"/>
       <c r="C437" s="15"/>
-      <c r="D437" s="64"/>
+      <c r="D437" s="63"/>
       <c r="E437" s="15"/>
       <c r="F437" s="15"/>
       <c r="G437" s="15"/>
     </row>
     <row r="438" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A438" s="42"/>
+      <c r="A438" s="41"/>
       <c r="B438" s="13"/>
       <c r="C438" s="15"/>
-      <c r="D438" s="64"/>
+      <c r="D438" s="63"/>
       <c r="E438" s="15"/>
       <c r="F438" s="15"/>
       <c r="G438" s="15"/>
     </row>
     <row r="439" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A439" s="42"/>
+      <c r="A439" s="41"/>
       <c r="B439" s="13"/>
       <c r="C439" s="15"/>
-      <c r="D439" s="64"/>
+      <c r="D439" s="63"/>
       <c r="E439" s="15"/>
       <c r="F439" s="15"/>
       <c r="G439" s="15"/>
     </row>
-    <row r="440" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A440" s="42"/>
-      <c r="B440" s="13"/>
-      <c r="C440" s="15"/>
-      <c r="D440" s="64"/>
-      <c r="E440" s="15"/>
-      <c r="F440" s="15"/>
-      <c r="G440" s="15"/>
-    </row>
-    <row r="441" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A441" s="42"/>
-      <c r="B441" s="13"/>
-      <c r="C441" s="15"/>
-      <c r="D441" s="64"/>
-      <c r="E441" s="15"/>
-      <c r="F441" s="15"/>
-      <c r="G441" s="15"/>
-    </row>
-    <row r="442" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A442" s="42"/>
-      <c r="B442" s="13"/>
-      <c r="C442" s="15"/>
-      <c r="D442" s="64"/>
-      <c r="E442" s="15"/>
-      <c r="F442" s="15"/>
-      <c r="G442" s="15"/>
+    <row r="440" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A440" s="53"/>
+      <c r="B440" s="53"/>
+      <c r="C440" s="53"/>
+      <c r="D440" s="53"/>
+      <c r="E440" s="53"/>
+      <c r="F440" s="53"/>
+      <c r="G440" s="53"/>
+      <c r="H440" s="53"/>
+      <c r="I440" s="53"/>
+      <c r="J440" s="53"/>
+      <c r="K440" s="53"/>
+      <c r="L440" s="53"/>
+    </row>
+    <row r="441" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A441" s="53"/>
+      <c r="B441" s="53"/>
+      <c r="C441" s="53"/>
+      <c r="D441" s="53"/>
+      <c r="E441" s="53"/>
+      <c r="F441" s="53"/>
+      <c r="G441" s="53"/>
+      <c r="H441" s="53"/>
+      <c r="I441" s="53"/>
+      <c r="J441" s="53"/>
+      <c r="K441" s="53"/>
+      <c r="L441" s="53"/>
+    </row>
+    <row r="442" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="53"/>
+      <c r="B442" s="53"/>
+      <c r="C442" s="53"/>
+      <c r="D442" s="53"/>
+      <c r="E442" s="53"/>
+      <c r="F442" s="53"/>
+      <c r="G442" s="53"/>
+      <c r="H442" s="53"/>
+      <c r="I442" s="53"/>
+      <c r="J442" s="53"/>
+      <c r="K442" s="53"/>
+      <c r="L442" s="53"/>
     </row>
     <row r="443" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="54"/>
-      <c r="B443" s="54"/>
-      <c r="C443" s="54"/>
-      <c r="D443" s="54"/>
-      <c r="E443" s="54"/>
-      <c r="F443" s="54"/>
-      <c r="G443" s="54"/>
-      <c r="H443" s="54"/>
-      <c r="I443" s="54"/>
-      <c r="J443" s="54"/>
-      <c r="K443" s="54"/>
-      <c r="L443" s="54"/>
+      <c r="A443" s="53"/>
+      <c r="B443" s="53"/>
+      <c r="C443" s="53"/>
+      <c r="D443" s="53"/>
+      <c r="E443" s="53"/>
+      <c r="F443" s="53"/>
+      <c r="G443" s="53"/>
+      <c r="H443" s="53"/>
+      <c r="I443" s="53"/>
+      <c r="J443" s="53"/>
+      <c r="K443" s="53"/>
+      <c r="L443" s="53"/>
     </row>
     <row r="444" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="54"/>
-      <c r="B444" s="54"/>
-      <c r="C444" s="54"/>
-      <c r="D444" s="54"/>
-      <c r="E444" s="54"/>
-      <c r="F444" s="54"/>
-      <c r="G444" s="54"/>
-      <c r="H444" s="54"/>
-      <c r="I444" s="54"/>
-      <c r="J444" s="54"/>
-      <c r="K444" s="54"/>
-      <c r="L444" s="54"/>
-    </row>
-    <row r="445" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="54"/>
-      <c r="B445" s="54"/>
-      <c r="C445" s="54"/>
-      <c r="D445" s="54"/>
-      <c r="E445" s="54"/>
-      <c r="F445" s="54"/>
-      <c r="G445" s="54"/>
-      <c r="H445" s="54"/>
-      <c r="I445" s="54"/>
-      <c r="J445" s="54"/>
-      <c r="K445" s="54"/>
-      <c r="L445" s="54"/>
-    </row>
-    <row r="446" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="54"/>
-      <c r="B446" s="54"/>
-      <c r="C446" s="54"/>
-      <c r="D446" s="54"/>
-      <c r="E446" s="54"/>
-      <c r="F446" s="54"/>
-      <c r="G446" s="54"/>
-      <c r="H446" s="54"/>
-      <c r="I446" s="54"/>
-      <c r="J446" s="54"/>
-      <c r="K446" s="54"/>
-      <c r="L446" s="54"/>
-    </row>
-    <row r="447" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="54"/>
-      <c r="B447" s="54"/>
-      <c r="C447" s="54"/>
-      <c r="D447" s="54"/>
-      <c r="E447" s="54"/>
-      <c r="F447" s="54"/>
-      <c r="G447" s="54"/>
-      <c r="H447" s="54"/>
-      <c r="I447" s="54"/>
-      <c r="J447" s="54"/>
-      <c r="K447" s="54"/>
-      <c r="L447" s="54"/>
+      <c r="A444" s="53"/>
+      <c r="B444" s="53"/>
+      <c r="C444" s="53"/>
+      <c r="D444" s="53"/>
+      <c r="E444" s="53"/>
+      <c r="F444" s="53"/>
+      <c r="G444" s="53"/>
+      <c r="H444" s="53"/>
+      <c r="I444" s="53"/>
+      <c r="J444" s="53"/>
+      <c r="K444" s="53"/>
+      <c r="L444" s="53"/>
+    </row>
+    <row r="445" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A445" s="64"/>
+      <c r="B445" s="65"/>
+      <c r="C445" s="66"/>
+      <c r="D445" s="67"/>
+      <c r="E445" s="17"/>
+      <c r="F445" s="17"/>
+      <c r="G445" s="17"/>
+    </row>
+    <row r="446" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A446" s="64"/>
+      <c r="B446" s="65"/>
+      <c r="C446" s="66"/>
+      <c r="D446" s="67"/>
+      <c r="E446" s="17"/>
+      <c r="F446" s="17"/>
+      <c r="G446" s="17"/>
+    </row>
+    <row r="447" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A447" s="64"/>
+      <c r="B447" s="65"/>
+      <c r="C447" s="66"/>
+      <c r="D447" s="67"/>
+      <c r="E447" s="17"/>
+      <c r="F447" s="17"/>
+      <c r="G447" s="17"/>
     </row>
     <row r="448" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A448" s="65"/>
-      <c r="B448" s="66"/>
-      <c r="C448" s="67"/>
-      <c r="D448" s="68"/>
+      <c r="A448" s="64"/>
+      <c r="B448" s="65"/>
+      <c r="C448" s="66"/>
+      <c r="D448" s="67"/>
       <c r="E448" s="17"/>
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
     </row>
     <row r="449" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A449" s="65"/>
-      <c r="B449" s="66"/>
-      <c r="C449" s="67"/>
-      <c r="D449" s="68"/>
+      <c r="A449" s="64"/>
+      <c r="B449" s="65"/>
+      <c r="C449" s="66"/>
+      <c r="D449" s="67"/>
       <c r="E449" s="17"/>
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
     </row>
     <row r="450" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A450" s="65"/>
-      <c r="B450" s="66"/>
-      <c r="C450" s="67"/>
-      <c r="D450" s="68"/>
+      <c r="A450" s="64"/>
+      <c r="B450" s="65"/>
+      <c r="C450" s="66"/>
+      <c r="D450" s="67"/>
       <c r="E450" s="17"/>
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
     </row>
     <row r="451" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A451" s="65"/>
-      <c r="B451" s="66"/>
-      <c r="C451" s="67"/>
-      <c r="D451" s="68"/>
+      <c r="A451" s="64"/>
+      <c r="B451" s="65"/>
+      <c r="C451" s="66"/>
+      <c r="D451" s="67"/>
       <c r="E451" s="17"/>
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
     </row>
     <row r="452" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A452" s="65"/>
-      <c r="B452" s="66"/>
-      <c r="C452" s="67"/>
-      <c r="D452" s="68"/>
+      <c r="A452" s="64"/>
+      <c r="B452" s="65"/>
+      <c r="C452" s="66"/>
+      <c r="D452" s="67"/>
       <c r="E452" s="17"/>
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
     </row>
     <row r="453" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A453" s="65"/>
-      <c r="B453" s="66"/>
-      <c r="C453" s="67"/>
-      <c r="D453" s="68"/>
+      <c r="A453" s="64"/>
+      <c r="B453" s="65"/>
+      <c r="C453" s="66"/>
+      <c r="D453" s="67"/>
       <c r="E453" s="17"/>
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
     </row>
     <row r="454" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A454" s="65"/>
-      <c r="B454" s="66"/>
-      <c r="C454" s="67"/>
-      <c r="D454" s="68"/>
+      <c r="A454" s="64"/>
+      <c r="B454" s="65"/>
+      <c r="C454" s="66"/>
+      <c r="D454" s="67"/>
       <c r="E454" s="17"/>
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
     </row>
     <row r="455" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A455" s="65"/>
-      <c r="B455" s="66"/>
-      <c r="C455" s="67"/>
-      <c r="D455" s="68"/>
+      <c r="A455" s="64"/>
+      <c r="B455" s="65"/>
+      <c r="C455" s="66"/>
+      <c r="D455" s="67"/>
       <c r="E455" s="17"/>
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
     </row>
     <row r="456" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A456" s="65"/>
-      <c r="B456" s="66"/>
-      <c r="C456" s="67"/>
-      <c r="D456" s="68"/>
+      <c r="A456" s="64"/>
+      <c r="B456" s="65"/>
+      <c r="C456" s="66"/>
+      <c r="D456" s="67"/>
       <c r="E456" s="17"/>
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
     </row>
     <row r="457" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A457" s="65"/>
-      <c r="B457" s="66"/>
-      <c r="C457" s="67"/>
-      <c r="D457" s="68"/>
+      <c r="A457" s="64"/>
+      <c r="B457" s="65"/>
+      <c r="C457" s="66"/>
+      <c r="D457" s="67"/>
       <c r="E457" s="17"/>
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
     </row>
     <row r="458" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A458" s="65"/>
-      <c r="B458" s="66"/>
-      <c r="C458" s="67"/>
-      <c r="D458" s="68"/>
+      <c r="A458" s="64"/>
+      <c r="B458" s="65"/>
+      <c r="C458" s="66"/>
+      <c r="D458" s="67"/>
       <c r="E458" s="17"/>
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
     </row>
     <row r="459" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A459" s="65"/>
-      <c r="B459" s="66"/>
-      <c r="C459" s="67"/>
-      <c r="D459" s="68"/>
+      <c r="A459" s="64"/>
+      <c r="B459" s="65"/>
+      <c r="C459" s="66"/>
+      <c r="D459" s="67"/>
       <c r="E459" s="17"/>
       <c r="F459" s="17"/>
       <c r="G459" s="17"/>
     </row>
     <row r="460" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A460" s="65"/>
-      <c r="B460" s="66"/>
-      <c r="C460" s="67"/>
-      <c r="D460" s="68"/>
+      <c r="A460" s="64"/>
+      <c r="B460" s="65"/>
+      <c r="C460" s="66"/>
+      <c r="D460" s="67"/>
       <c r="E460" s="17"/>
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
     </row>
     <row r="461" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A461" s="65"/>
-      <c r="B461" s="66"/>
-      <c r="C461" s="67"/>
-      <c r="D461" s="68"/>
+      <c r="A461" s="64"/>
+      <c r="B461" s="65"/>
+      <c r="C461" s="66"/>
+      <c r="D461" s="67"/>
       <c r="E461" s="17"/>
       <c r="F461" s="17"/>
       <c r="G461" s="17"/>
     </row>
     <row r="462" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A462" s="65"/>
-      <c r="B462" s="66"/>
-      <c r="C462" s="67"/>
-      <c r="D462" s="68"/>
+      <c r="A462" s="64"/>
+      <c r="B462" s="65"/>
+      <c r="C462" s="66"/>
+      <c r="D462" s="67"/>
       <c r="E462" s="17"/>
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
     </row>
     <row r="463" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A463" s="65"/>
-      <c r="B463" s="66"/>
-      <c r="C463" s="67"/>
-      <c r="D463" s="68"/>
+      <c r="A463" s="64"/>
+      <c r="B463" s="65"/>
+      <c r="C463" s="66"/>
+      <c r="D463" s="67"/>
       <c r="E463" s="17"/>
       <c r="F463" s="17"/>
       <c r="G463" s="17"/>
     </row>
     <row r="464" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A464" s="65"/>
-      <c r="B464" s="66"/>
-      <c r="C464" s="67"/>
-      <c r="D464" s="68"/>
+      <c r="A464" s="64"/>
+      <c r="B464" s="65"/>
+      <c r="C464" s="66"/>
+      <c r="D464" s="67"/>
       <c r="E464" s="17"/>
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
     </row>
     <row r="465" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A465" s="65"/>
-      <c r="B465" s="66"/>
-      <c r="C465" s="67"/>
-      <c r="D465" s="68"/>
+      <c r="A465" s="64"/>
+      <c r="B465" s="65"/>
+      <c r="C465" s="66"/>
+      <c r="D465" s="67"/>
       <c r="E465" s="17"/>
       <c r="F465" s="17"/>
       <c r="G465" s="17"/>
     </row>
     <row r="466" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A466" s="65"/>
-      <c r="B466" s="66"/>
-      <c r="C466" s="67"/>
-      <c r="D466" s="68"/>
+      <c r="A466" s="64"/>
+      <c r="B466" s="65"/>
+      <c r="C466" s="66"/>
+      <c r="D466" s="67"/>
       <c r="E466" s="17"/>
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
     </row>
     <row r="467" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A467" s="65"/>
-      <c r="B467" s="66"/>
-      <c r="C467" s="67"/>
-      <c r="D467" s="68"/>
+      <c r="A467" s="64"/>
+      <c r="B467" s="65"/>
+      <c r="C467" s="66"/>
+      <c r="D467" s="67"/>
       <c r="E467" s="17"/>
       <c r="F467" s="17"/>
       <c r="G467" s="17"/>
     </row>
     <row r="468" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A468" s="65"/>
-      <c r="B468" s="66"/>
-      <c r="C468" s="67"/>
-      <c r="D468" s="68"/>
+      <c r="A468" s="64"/>
+      <c r="B468" s="65"/>
+      <c r="C468" s="66"/>
+      <c r="D468" s="67"/>
       <c r="E468" s="17"/>
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
     </row>
     <row r="469" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A469" s="65"/>
-      <c r="B469" s="66"/>
-      <c r="C469" s="67"/>
-      <c r="D469" s="68"/>
+      <c r="A469" s="64"/>
+      <c r="B469" s="65"/>
+      <c r="C469" s="66"/>
+      <c r="D469" s="67"/>
       <c r="E469" s="17"/>
       <c r="F469" s="17"/>
       <c r="G469" s="17"/>
     </row>
     <row r="470" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A470" s="65"/>
-      <c r="B470" s="66"/>
-      <c r="C470" s="67"/>
-      <c r="D470" s="68"/>
+      <c r="A470" s="64"/>
+      <c r="B470" s="65"/>
+      <c r="C470" s="66"/>
+      <c r="D470" s="67"/>
       <c r="E470" s="17"/>
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
     </row>
     <row r="471" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A471" s="65"/>
-      <c r="B471" s="66"/>
-      <c r="C471" s="67"/>
-      <c r="D471" s="68"/>
+      <c r="A471" s="64"/>
+      <c r="B471" s="65"/>
+      <c r="C471" s="66"/>
+      <c r="D471" s="67"/>
       <c r="E471" s="17"/>
       <c r="F471" s="17"/>
       <c r="G471" s="17"/>
     </row>
     <row r="472" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A472" s="65"/>
-      <c r="B472" s="66"/>
-      <c r="C472" s="67"/>
-      <c r="D472" s="68"/>
+      <c r="A472" s="64"/>
+      <c r="B472" s="65"/>
+      <c r="C472" s="66"/>
+      <c r="D472" s="67"/>
       <c r="E472" s="17"/>
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
     </row>
     <row r="473" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A473" s="65"/>
-      <c r="B473" s="66"/>
-      <c r="C473" s="67"/>
-      <c r="D473" s="68"/>
+      <c r="A473" s="64"/>
+      <c r="B473" s="65"/>
+      <c r="C473" s="66"/>
+      <c r="D473" s="67"/>
       <c r="E473" s="17"/>
       <c r="F473" s="17"/>
       <c r="G473" s="17"/>
     </row>
     <row r="474" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A474" s="65"/>
-      <c r="B474" s="66"/>
-      <c r="C474" s="67"/>
-      <c r="D474" s="68"/>
+      <c r="A474" s="64"/>
+      <c r="B474" s="65"/>
+      <c r="C474" s="66"/>
+      <c r="D474" s="67"/>
       <c r="E474" s="17"/>
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
     </row>
     <row r="475" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A475" s="65"/>
-      <c r="B475" s="66"/>
-      <c r="C475" s="67"/>
-      <c r="D475" s="68"/>
+      <c r="A475" s="64"/>
+      <c r="B475" s="65"/>
+      <c r="C475" s="66"/>
+      <c r="D475" s="67"/>
       <c r="E475" s="17"/>
       <c r="F475" s="17"/>
       <c r="G475" s="17"/>
     </row>
     <row r="476" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A476" s="65"/>
-      <c r="B476" s="66"/>
-      <c r="C476" s="67"/>
-      <c r="D476" s="68"/>
+      <c r="A476" s="64"/>
+      <c r="B476" s="65"/>
+      <c r="C476" s="66"/>
+      <c r="D476" s="67"/>
       <c r="E476" s="17"/>
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
     </row>
     <row r="477" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A477" s="65"/>
-      <c r="B477" s="66"/>
-      <c r="C477" s="67"/>
-      <c r="D477" s="68"/>
+      <c r="A477" s="64"/>
+      <c r="B477" s="65"/>
+      <c r="C477" s="66"/>
+      <c r="D477" s="67"/>
       <c r="E477" s="17"/>
       <c r="F477" s="17"/>
       <c r="G477" s="17"/>
     </row>
     <row r="478" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A478" s="65"/>
-      <c r="B478" s="66"/>
-      <c r="C478" s="67"/>
-      <c r="D478" s="68"/>
+      <c r="A478" s="64"/>
+      <c r="B478" s="65"/>
+      <c r="C478" s="66"/>
+      <c r="D478" s="67"/>
       <c r="E478" s="17"/>
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
     </row>
     <row r="479" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A479" s="65"/>
-      <c r="B479" s="66"/>
-      <c r="C479" s="67"/>
-      <c r="D479" s="68"/>
+      <c r="A479" s="64"/>
+      <c r="B479" s="65"/>
+      <c r="C479" s="66"/>
+      <c r="D479" s="67"/>
       <c r="E479" s="17"/>
       <c r="F479" s="17"/>
       <c r="G479" s="17"/>
     </row>
     <row r="480" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A480" s="65"/>
-      <c r="B480" s="66"/>
-      <c r="C480" s="67"/>
-      <c r="D480" s="68"/>
+      <c r="A480" s="64"/>
+      <c r="B480" s="65"/>
+      <c r="C480" s="66"/>
+      <c r="D480" s="67"/>
       <c r="E480" s="17"/>
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
     </row>
     <row r="481" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A481" s="65"/>
-      <c r="B481" s="66"/>
-      <c r="C481" s="67"/>
-      <c r="D481" s="68"/>
+      <c r="A481" s="64"/>
+      <c r="B481" s="65"/>
+      <c r="C481" s="66"/>
+      <c r="D481" s="67"/>
       <c r="E481" s="17"/>
       <c r="F481" s="17"/>
       <c r="G481" s="17"/>
     </row>
     <row r="482" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A482" s="65"/>
-      <c r="B482" s="66"/>
-      <c r="C482" s="67"/>
-      <c r="D482" s="68"/>
+      <c r="A482" s="64"/>
+      <c r="B482" s="65"/>
+      <c r="C482" s="66"/>
+      <c r="D482" s="67"/>
       <c r="E482" s="17"/>
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
     </row>
     <row r="483" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A483" s="65"/>
-      <c r="B483" s="66"/>
-      <c r="C483" s="67"/>
-      <c r="D483" s="68"/>
+      <c r="A483" s="64"/>
+      <c r="B483" s="65"/>
+      <c r="C483" s="66"/>
+      <c r="D483" s="67"/>
       <c r="E483" s="17"/>
       <c r="F483" s="17"/>
       <c r="G483" s="17"/>
     </row>
     <row r="484" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A484" s="65"/>
-      <c r="B484" s="66"/>
-      <c r="C484" s="67"/>
-      <c r="D484" s="68"/>
+      <c r="A484" s="64"/>
+      <c r="B484" s="65"/>
+      <c r="C484" s="66"/>
+      <c r="D484" s="67"/>
       <c r="E484" s="17"/>
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
     </row>
     <row r="485" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A485" s="65"/>
-      <c r="B485" s="66"/>
-      <c r="C485" s="67"/>
-      <c r="D485" s="68"/>
+      <c r="A485" s="64"/>
+      <c r="B485" s="65"/>
+      <c r="C485" s="66"/>
+      <c r="D485" s="67"/>
       <c r="E485" s="17"/>
       <c r="F485" s="17"/>
       <c r="G485" s="17"/>
     </row>
     <row r="486" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A486" s="65"/>
-      <c r="B486" s="66"/>
-      <c r="C486" s="67"/>
-      <c r="D486" s="68"/>
+      <c r="A486" s="64"/>
+      <c r="B486" s="65"/>
+      <c r="C486" s="66"/>
+      <c r="D486" s="67"/>
       <c r="E486" s="17"/>
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
     </row>
     <row r="487" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A487" s="65"/>
-      <c r="B487" s="66"/>
-      <c r="C487" s="67"/>
-      <c r="D487" s="68"/>
+      <c r="A487" s="64"/>
+      <c r="B487" s="65"/>
+      <c r="C487" s="66"/>
+      <c r="D487" s="67"/>
       <c r="E487" s="17"/>
       <c r="F487" s="17"/>
       <c r="G487" s="17"/>
     </row>
     <row r="488" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A488" s="65"/>
-      <c r="B488" s="66"/>
-      <c r="C488" s="67"/>
-      <c r="D488" s="68"/>
+      <c r="A488" s="64"/>
+      <c r="B488" s="65"/>
+      <c r="C488" s="66"/>
+      <c r="D488" s="67"/>
       <c r="E488" s="17"/>
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
     </row>
     <row r="489" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A489" s="65"/>
-      <c r="B489" s="66"/>
-      <c r="C489" s="67"/>
-      <c r="D489" s="68"/>
+      <c r="A489" s="64"/>
+      <c r="B489" s="65"/>
+      <c r="C489" s="66"/>
+      <c r="D489" s="67"/>
       <c r="E489" s="17"/>
       <c r="F489" s="17"/>
       <c r="G489" s="17"/>
     </row>
     <row r="490" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A490" s="65"/>
-      <c r="B490" s="66"/>
-      <c r="C490" s="67"/>
-      <c r="D490" s="68"/>
+      <c r="A490" s="64"/>
+      <c r="B490" s="65"/>
+      <c r="C490" s="66"/>
+      <c r="D490" s="67"/>
       <c r="E490" s="17"/>
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
     </row>
     <row r="491" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A491" s="65"/>
-      <c r="B491" s="66"/>
-      <c r="C491" s="67"/>
-      <c r="D491" s="68"/>
+      <c r="A491" s="64"/>
+      <c r="B491" s="65"/>
+      <c r="C491" s="66"/>
+      <c r="D491" s="67"/>
       <c r="E491" s="17"/>
       <c r="F491" s="17"/>
       <c r="G491" s="17"/>
     </row>
     <row r="492" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A492" s="65"/>
-      <c r="B492" s="66"/>
-      <c r="C492" s="67"/>
-      <c r="D492" s="68"/>
+      <c r="A492" s="64"/>
+      <c r="B492" s="65"/>
+      <c r="C492" s="66"/>
+      <c r="D492" s="67"/>
       <c r="E492" s="17"/>
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
     </row>
     <row r="493" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A493" s="65"/>
-      <c r="B493" s="66"/>
-      <c r="C493" s="67"/>
-      <c r="D493" s="68"/>
+      <c r="A493" s="64"/>
+      <c r="B493" s="65"/>
+      <c r="C493" s="66"/>
+      <c r="D493" s="67"/>
       <c r="E493" s="17"/>
       <c r="F493" s="17"/>
       <c r="G493" s="17"/>
     </row>
     <row r="494" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A494" s="65"/>
-      <c r="B494" s="66"/>
-      <c r="C494" s="67"/>
-      <c r="D494" s="68"/>
+      <c r="A494" s="64"/>
+      <c r="B494" s="65"/>
+      <c r="C494" s="66"/>
+      <c r="D494" s="67"/>
       <c r="E494" s="17"/>
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
     </row>
     <row r="495" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A495" s="65"/>
-      <c r="B495" s="66"/>
-      <c r="C495" s="67"/>
-      <c r="D495" s="68"/>
+      <c r="A495" s="64"/>
+      <c r="B495" s="65"/>
+      <c r="C495" s="66"/>
+      <c r="D495" s="67"/>
       <c r="E495" s="17"/>
       <c r="F495" s="17"/>
       <c r="G495" s="17"/>
     </row>
     <row r="496" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A496" s="65"/>
-      <c r="B496" s="66"/>
-      <c r="C496" s="67"/>
-      <c r="D496" s="68"/>
+      <c r="A496" s="64"/>
+      <c r="B496" s="65"/>
+      <c r="C496" s="66"/>
+      <c r="D496" s="67"/>
       <c r="E496" s="17"/>
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
     </row>
     <row r="497" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A497" s="65"/>
-      <c r="B497" s="66"/>
-      <c r="C497" s="67"/>
-      <c r="D497" s="68"/>
+      <c r="A497" s="64"/>
+      <c r="B497" s="65"/>
+      <c r="C497" s="66"/>
+      <c r="D497" s="67"/>
       <c r="E497" s="17"/>
       <c r="F497" s="17"/>
       <c r="G497" s="17"/>
     </row>
     <row r="498" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A498" s="65"/>
-      <c r="B498" s="66"/>
-      <c r="C498" s="67"/>
-      <c r="D498" s="68"/>
+      <c r="A498" s="64"/>
+      <c r="B498" s="65"/>
+      <c r="C498" s="66"/>
+      <c r="D498" s="67"/>
       <c r="E498" s="17"/>
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
     </row>
     <row r="499" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A499" s="65"/>
-      <c r="B499" s="66"/>
-      <c r="C499" s="67"/>
-      <c r="D499" s="68"/>
+      <c r="A499" s="64"/>
+      <c r="B499" s="65"/>
+      <c r="C499" s="66"/>
+      <c r="D499" s="67"/>
       <c r="E499" s="17"/>
       <c r="F499" s="17"/>
       <c r="G499" s="17"/>
     </row>
     <row r="500" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A500" s="65"/>
-      <c r="B500" s="66"/>
-      <c r="C500" s="67"/>
-      <c r="D500" s="68"/>
+      <c r="A500" s="64"/>
+      <c r="B500" s="65"/>
+      <c r="C500" s="66"/>
+      <c r="D500" s="67"/>
       <c r="E500" s="17"/>
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
     </row>
     <row r="501" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A501" s="65"/>
-      <c r="B501" s="66"/>
-      <c r="C501" s="67"/>
-      <c r="D501" s="68"/>
+      <c r="A501" s="64"/>
+      <c r="B501" s="65"/>
+      <c r="C501" s="66"/>
+      <c r="D501" s="67"/>
       <c r="E501" s="17"/>
       <c r="F501" s="17"/>
       <c r="G501" s="17"/>
     </row>
     <row r="502" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A502" s="65"/>
-      <c r="B502" s="66"/>
-      <c r="C502" s="67"/>
-      <c r="D502" s="68"/>
+      <c r="A502" s="64"/>
+      <c r="B502" s="65"/>
+      <c r="C502" s="66"/>
+      <c r="D502" s="67"/>
       <c r="E502" s="17"/>
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
     </row>
     <row r="503" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A503" s="65"/>
-      <c r="B503" s="66"/>
-      <c r="C503" s="67"/>
-      <c r="D503" s="68"/>
+      <c r="A503" s="64"/>
+      <c r="B503" s="65"/>
+      <c r="C503" s="66"/>
+      <c r="D503" s="67"/>
       <c r="E503" s="17"/>
       <c r="F503" s="17"/>
       <c r="G503" s="17"/>
     </row>
     <row r="504" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A504" s="65"/>
-      <c r="B504" s="66"/>
-      <c r="C504" s="67"/>
-      <c r="D504" s="68"/>
+      <c r="A504" s="64"/>
+      <c r="B504" s="65"/>
+      <c r="C504" s="66"/>
+      <c r="D504" s="67"/>
       <c r="E504" s="17"/>
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
     </row>
     <row r="505" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A505" s="65"/>
-      <c r="B505" s="66"/>
-      <c r="C505" s="67"/>
-      <c r="D505" s="68"/>
+      <c r="A505" s="64"/>
+      <c r="B505" s="65"/>
+      <c r="C505" s="66"/>
+      <c r="D505" s="67"/>
       <c r="E505" s="17"/>
       <c r="F505" s="17"/>
       <c r="G505" s="17"/>
     </row>
     <row r="506" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A506" s="65"/>
-      <c r="B506" s="66"/>
-      <c r="C506" s="67"/>
-      <c r="D506" s="68"/>
+      <c r="A506" s="64"/>
+      <c r="B506" s="65"/>
+      <c r="C506" s="66"/>
+      <c r="D506" s="67"/>
       <c r="E506" s="17"/>
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
     </row>
     <row r="507" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A507" s="65"/>
-      <c r="B507" s="66"/>
-      <c r="C507" s="67"/>
-      <c r="D507" s="68"/>
+      <c r="A507" s="64"/>
+      <c r="B507" s="65"/>
+      <c r="C507" s="66"/>
+      <c r="D507" s="67"/>
       <c r="E507" s="17"/>
       <c r="F507" s="17"/>
       <c r="G507" s="17"/>
     </row>
     <row r="508" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A508" s="65"/>
-      <c r="B508" s="66"/>
-      <c r="C508" s="67"/>
-      <c r="D508" s="68"/>
+      <c r="A508" s="64"/>
+      <c r="B508" s="65"/>
+      <c r="C508" s="66"/>
+      <c r="D508" s="67"/>
       <c r="E508" s="17"/>
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
     </row>
     <row r="509" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A509" s="65"/>
-      <c r="B509" s="66"/>
-      <c r="C509" s="67"/>
-      <c r="D509" s="68"/>
+      <c r="A509" s="64"/>
+      <c r="B509" s="65"/>
+      <c r="C509" s="66"/>
+      <c r="D509" s="67"/>
       <c r="E509" s="17"/>
       <c r="F509" s="17"/>
       <c r="G509" s="17"/>
     </row>
     <row r="510" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A510" s="65"/>
-      <c r="B510" s="66"/>
-      <c r="C510" s="67"/>
-      <c r="D510" s="68"/>
+      <c r="A510" s="64"/>
+      <c r="B510" s="65"/>
+      <c r="C510" s="66"/>
+      <c r="D510" s="67"/>
       <c r="E510" s="17"/>
       <c r="F510" s="17"/>
       <c r="G510" s="17"/>
     </row>
     <row r="511" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A511" s="65"/>
-      <c r="B511" s="66"/>
-      <c r="C511" s="67"/>
-      <c r="D511" s="68"/>
+      <c r="A511" s="64"/>
+      <c r="B511" s="65"/>
+      <c r="C511" s="66"/>
+      <c r="D511" s="67"/>
       <c r="E511" s="17"/>
       <c r="F511" s="17"/>
       <c r="G511" s="17"/>
     </row>
     <row r="512" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A512" s="65"/>
-      <c r="B512" s="66"/>
-      <c r="C512" s="67"/>
-      <c r="D512" s="68"/>
+      <c r="A512" s="64"/>
+      <c r="B512" s="65"/>
+      <c r="C512" s="66"/>
+      <c r="D512" s="67"/>
       <c r="E512" s="17"/>
       <c r="F512" s="17"/>
       <c r="G512" s="17"/>
     </row>
     <row r="513" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A513" s="65"/>
-      <c r="B513" s="66"/>
-      <c r="C513" s="67"/>
-      <c r="D513" s="68"/>
+      <c r="A513" s="64"/>
+      <c r="B513" s="65"/>
+      <c r="C513" s="66"/>
+      <c r="D513" s="67"/>
       <c r="E513" s="17"/>
       <c r="F513" s="17"/>
       <c r="G513" s="17"/>
     </row>
     <row r="514" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A514" s="65"/>
-      <c r="B514" s="66"/>
-      <c r="C514" s="67"/>
-      <c r="D514" s="68"/>
+      <c r="A514" s="64"/>
+      <c r="B514" s="65"/>
+      <c r="C514" s="66"/>
+      <c r="D514" s="67"/>
       <c r="E514" s="17"/>
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
     </row>
     <row r="515" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A515" s="65"/>
-      <c r="B515" s="66"/>
-      <c r="C515" s="67"/>
-      <c r="D515" s="68"/>
+      <c r="A515" s="64"/>
+      <c r="B515" s="65"/>
+      <c r="C515" s="66"/>
+      <c r="D515" s="67"/>
       <c r="E515" s="17"/>
       <c r="F515" s="17"/>
       <c r="G515" s="17"/>
     </row>
     <row r="516" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A516" s="65"/>
-      <c r="B516" s="66"/>
-      <c r="C516" s="67"/>
-      <c r="D516" s="68"/>
+      <c r="A516" s="64"/>
+      <c r="B516" s="65"/>
+      <c r="C516" s="66"/>
+      <c r="D516" s="67"/>
       <c r="E516" s="17"/>
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
     </row>
     <row r="517" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A517" s="65"/>
-      <c r="B517" s="66"/>
-      <c r="C517" s="67"/>
-      <c r="D517" s="68"/>
+      <c r="A517" s="64"/>
+      <c r="B517" s="65"/>
+      <c r="C517" s="66"/>
+      <c r="D517" s="67"/>
       <c r="E517" s="17"/>
       <c r="F517" s="17"/>
       <c r="G517" s="17"/>
     </row>
     <row r="518" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A518" s="65"/>
-      <c r="B518" s="66"/>
-      <c r="C518" s="67"/>
-      <c r="D518" s="68"/>
+      <c r="A518" s="64"/>
+      <c r="B518" s="65"/>
+      <c r="C518" s="66"/>
+      <c r="D518" s="67"/>
       <c r="E518" s="17"/>
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
     </row>
     <row r="519" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A519" s="65"/>
-      <c r="B519" s="66"/>
-      <c r="C519" s="67"/>
-      <c r="D519" s="68"/>
+      <c r="A519" s="64"/>
+      <c r="B519" s="65"/>
+      <c r="C519" s="66"/>
+      <c r="D519" s="67"/>
       <c r="E519" s="17"/>
       <c r="F519" s="17"/>
       <c r="G519" s="17"/>
     </row>
     <row r="520" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A520" s="65"/>
-      <c r="B520" s="66"/>
-      <c r="C520" s="67"/>
-      <c r="D520" s="68"/>
+      <c r="A520" s="64"/>
+      <c r="B520" s="65"/>
+      <c r="C520" s="66"/>
+      <c r="D520" s="67"/>
       <c r="E520" s="17"/>
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
     </row>
     <row r="521" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A521" s="65"/>
-      <c r="B521" s="66"/>
-      <c r="C521" s="67"/>
-      <c r="D521" s="68"/>
+      <c r="A521" s="64"/>
+      <c r="B521" s="65"/>
+      <c r="C521" s="66"/>
+      <c r="D521" s="67"/>
       <c r="E521" s="17"/>
       <c r="F521" s="17"/>
       <c r="G521" s="17"/>
     </row>
     <row r="522" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A522" s="65"/>
-      <c r="B522" s="66"/>
-      <c r="C522" s="67"/>
-      <c r="D522" s="68"/>
+      <c r="A522" s="64"/>
+      <c r="B522" s="65"/>
+      <c r="C522" s="66"/>
+      <c r="D522" s="67"/>
       <c r="E522" s="17"/>
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
     </row>
     <row r="523" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A523" s="65"/>
-      <c r="B523" s="66"/>
-      <c r="C523" s="67"/>
-      <c r="D523" s="68"/>
+      <c r="A523" s="64"/>
+      <c r="B523" s="65"/>
+      <c r="C523" s="66"/>
+      <c r="D523" s="67"/>
       <c r="E523" s="17"/>
       <c r="F523" s="17"/>
       <c r="G523" s="17"/>
     </row>
     <row r="524" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A524" s="65"/>
-      <c r="B524" s="66"/>
-      <c r="C524" s="67"/>
-      <c r="D524" s="68"/>
+      <c r="A524" s="64"/>
+      <c r="B524" s="65"/>
+      <c r="C524" s="66"/>
+      <c r="D524" s="67"/>
       <c r="E524" s="17"/>
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
     </row>
     <row r="525" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A525" s="65"/>
-      <c r="B525" s="66"/>
-      <c r="C525" s="67"/>
-      <c r="D525" s="68"/>
+      <c r="A525" s="64"/>
+      <c r="B525" s="65"/>
+      <c r="C525" s="66"/>
+      <c r="D525" s="67"/>
       <c r="E525" s="17"/>
       <c r="F525" s="17"/>
       <c r="G525" s="17"/>
     </row>
     <row r="526" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A526" s="65"/>
-      <c r="B526" s="66"/>
-      <c r="C526" s="67"/>
-      <c r="D526" s="68"/>
+      <c r="A526" s="64"/>
+      <c r="B526" s="65"/>
+      <c r="C526" s="66"/>
+      <c r="D526" s="67"/>
       <c r="E526" s="17"/>
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
     </row>
     <row r="527" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A527" s="65"/>
-      <c r="B527" s="66"/>
-      <c r="C527" s="67"/>
-      <c r="D527" s="68"/>
+      <c r="A527" s="64"/>
+      <c r="B527" s="65"/>
+      <c r="C527" s="17"/>
+      <c r="D527" s="67"/>
       <c r="E527" s="17"/>
       <c r="F527" s="17"/>
       <c r="G527" s="17"/>
     </row>
     <row r="528" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A528" s="65"/>
-      <c r="B528" s="66"/>
-      <c r="C528" s="67"/>
-      <c r="D528" s="68"/>
+      <c r="A528" s="64"/>
+      <c r="B528" s="65"/>
+      <c r="C528" s="17"/>
+      <c r="D528" s="67"/>
       <c r="E528" s="17"/>
       <c r="F528" s="17"/>
       <c r="G528" s="17"/>
     </row>
     <row r="529" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A529" s="65"/>
-      <c r="B529" s="66"/>
-      <c r="C529" s="67"/>
-      <c r="D529" s="68"/>
+      <c r="A529" s="64"/>
+      <c r="B529" s="65"/>
+      <c r="C529" s="17"/>
+      <c r="D529" s="67"/>
       <c r="E529" s="17"/>
       <c r="F529" s="17"/>
       <c r="G529" s="17"/>
     </row>
     <row r="530" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A530" s="65"/>
-      <c r="B530" s="66"/>
+      <c r="A530" s="64"/>
+      <c r="B530" s="65"/>
       <c r="C530" s="17"/>
-      <c r="D530" s="68"/>
+      <c r="D530" s="67"/>
       <c r="E530" s="17"/>
       <c r="F530" s="17"/>
       <c r="G530" s="17"/>
     </row>
     <row r="531" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A531" s="65"/>
-      <c r="B531" s="66"/>
+      <c r="A531" s="64"/>
+      <c r="B531" s="65"/>
       <c r="C531" s="17"/>
-      <c r="D531" s="68"/>
+      <c r="D531" s="67"/>
       <c r="E531" s="17"/>
       <c r="F531" s="17"/>
       <c r="G531" s="17"/>
     </row>
     <row r="532" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A532" s="65"/>
-      <c r="B532" s="66"/>
+      <c r="A532" s="64"/>
+      <c r="B532" s="65"/>
       <c r="C532" s="17"/>
-      <c r="D532" s="68"/>
+      <c r="D532" s="67"/>
       <c r="E532" s="17"/>
       <c r="F532" s="17"/>
       <c r="G532" s="17"/>
     </row>
     <row r="533" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A533" s="65"/>
-      <c r="B533" s="66"/>
+      <c r="A533" s="64"/>
+      <c r="B533" s="65"/>
       <c r="C533" s="17"/>
-      <c r="D533" s="68"/>
+      <c r="D533" s="67"/>
       <c r="E533" s="17"/>
       <c r="F533" s="17"/>
       <c r="G533" s="17"/>
     </row>
     <row r="534" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A534" s="65"/>
-      <c r="B534" s="66"/>
+      <c r="A534" s="64"/>
+      <c r="B534" s="65"/>
       <c r="C534" s="17"/>
-      <c r="D534" s="68"/>
+      <c r="D534" s="67"/>
       <c r="E534" s="17"/>
       <c r="F534" s="17"/>
       <c r="G534" s="17"/>
     </row>
     <row r="535" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A535" s="65"/>
-      <c r="B535" s="66"/>
+      <c r="A535" s="64"/>
+      <c r="B535" s="65"/>
       <c r="C535" s="17"/>
-      <c r="D535" s="68"/>
+      <c r="D535" s="67"/>
       <c r="E535" s="17"/>
       <c r="F535" s="17"/>
       <c r="G535" s="17"/>
     </row>
-    <row r="536" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A536" s="65"/>
-      <c r="B536" s="66"/>
-      <c r="C536" s="17"/>
-      <c r="D536" s="68"/>
-      <c r="E536" s="17"/>
-      <c r="F536" s="17"/>
-      <c r="G536" s="17"/>
-    </row>
-    <row r="537" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A537" s="65"/>
-      <c r="B537" s="66"/>
-      <c r="C537" s="17"/>
-      <c r="D537" s="68"/>
-      <c r="E537" s="17"/>
-      <c r="F537" s="17"/>
-      <c r="G537" s="17"/>
-    </row>
-    <row r="538" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A538" s="65"/>
-      <c r="B538" s="66"/>
-      <c r="C538" s="17"/>
-      <c r="D538" s="68"/>
-      <c r="E538" s="17"/>
-      <c r="F538" s="17"/>
-      <c r="G538" s="17"/>
-    </row>
-    <row r="1048565" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1048565" s="4" t="n">
+    <row r="1048562" customFormat="false" ht="44.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E1048562" s="4" t="n">
         <f aca="false">COUNT(E1:E9)</f>
         <v>8</v>
       </c>
     </row>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -48384,7 +48273,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="171">
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="B2:B13"/>
     <mergeCell ref="C3:C5"/>
@@ -48396,168 +48285,173 @@
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A27:A48"/>
-    <mergeCell ref="B27:B48"/>
+    <mergeCell ref="A27:A47"/>
+    <mergeCell ref="B27:B47"/>
+    <mergeCell ref="C27:C32"/>
     <mergeCell ref="D27:D32"/>
+    <mergeCell ref="C33:C35"/>
     <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C36:C38"/>
     <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D47"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A107:A250"/>
-    <mergeCell ref="B107:B250"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="D127:D129"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="C134:C139"/>
-    <mergeCell ref="D134:D139"/>
-    <mergeCell ref="C140:C146"/>
-    <mergeCell ref="D140:D146"/>
-    <mergeCell ref="C147:C154"/>
-    <mergeCell ref="D147:D154"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="C157:C160"/>
-    <mergeCell ref="D157:D160"/>
-    <mergeCell ref="C161:C166"/>
-    <mergeCell ref="D161:D166"/>
-    <mergeCell ref="C167:C173"/>
-    <mergeCell ref="D167:D173"/>
-    <mergeCell ref="C174:C179"/>
-    <mergeCell ref="D174:D179"/>
-    <mergeCell ref="C180:C185"/>
-    <mergeCell ref="D180:D185"/>
-    <mergeCell ref="C186:C191"/>
-    <mergeCell ref="D186:D191"/>
-    <mergeCell ref="C192:C198"/>
-    <mergeCell ref="D192:D198"/>
-    <mergeCell ref="C199:C210"/>
-    <mergeCell ref="D199:D210"/>
-    <mergeCell ref="C211:C222"/>
-    <mergeCell ref="D211:D222"/>
-    <mergeCell ref="C223:C229"/>
-    <mergeCell ref="D223:D229"/>
-    <mergeCell ref="C230:C237"/>
-    <mergeCell ref="D230:D237"/>
-    <mergeCell ref="C238:C242"/>
-    <mergeCell ref="D238:D242"/>
-    <mergeCell ref="C243:C246"/>
-    <mergeCell ref="D243:D246"/>
-    <mergeCell ref="C247:C250"/>
-    <mergeCell ref="D247:D250"/>
-    <mergeCell ref="A252:A311"/>
-    <mergeCell ref="B252:B311"/>
-    <mergeCell ref="C252:C259"/>
-    <mergeCell ref="D252:D259"/>
-    <mergeCell ref="C260:C266"/>
-    <mergeCell ref="D260:D266"/>
-    <mergeCell ref="C267:C271"/>
-    <mergeCell ref="D267:D271"/>
-    <mergeCell ref="C272:C277"/>
-    <mergeCell ref="D272:D277"/>
-    <mergeCell ref="C278:C286"/>
-    <mergeCell ref="D278:D286"/>
-    <mergeCell ref="C287:C292"/>
-    <mergeCell ref="D287:D292"/>
-    <mergeCell ref="C293:C299"/>
-    <mergeCell ref="D293:D299"/>
-    <mergeCell ref="C300:C306"/>
-    <mergeCell ref="D300:D306"/>
-    <mergeCell ref="C307:C311"/>
-    <mergeCell ref="D307:D311"/>
-    <mergeCell ref="A313:A342"/>
-    <mergeCell ref="B313:B342"/>
-    <mergeCell ref="C313:C318"/>
-    <mergeCell ref="D313:D318"/>
-    <mergeCell ref="C319:C326"/>
-    <mergeCell ref="D319:D326"/>
-    <mergeCell ref="C327:C330"/>
-    <mergeCell ref="D327:D330"/>
-    <mergeCell ref="C331:C338"/>
-    <mergeCell ref="D331:D338"/>
-    <mergeCell ref="C339:C342"/>
-    <mergeCell ref="D339:D342"/>
-    <mergeCell ref="A343:L347"/>
-    <mergeCell ref="A348:A388"/>
-    <mergeCell ref="B348:B388"/>
-    <mergeCell ref="C348:C352"/>
-    <mergeCell ref="D348:D352"/>
-    <mergeCell ref="C353:C354"/>
-    <mergeCell ref="D353:D354"/>
-    <mergeCell ref="C355:C356"/>
-    <mergeCell ref="D355:D356"/>
-    <mergeCell ref="C357:C359"/>
-    <mergeCell ref="D357:D359"/>
-    <mergeCell ref="C360:C364"/>
-    <mergeCell ref="D360:D364"/>
-    <mergeCell ref="C365:C369"/>
-    <mergeCell ref="D365:D369"/>
-    <mergeCell ref="C370:C371"/>
-    <mergeCell ref="D370:D371"/>
-    <mergeCell ref="C372:C373"/>
-    <mergeCell ref="D372:D373"/>
-    <mergeCell ref="C374:C375"/>
-    <mergeCell ref="D374:D375"/>
-    <mergeCell ref="C378:C379"/>
-    <mergeCell ref="D378:D379"/>
-    <mergeCell ref="C380:C383"/>
-    <mergeCell ref="D380:D383"/>
-    <mergeCell ref="C384:C386"/>
-    <mergeCell ref="D384:D386"/>
-    <mergeCell ref="C387:C388"/>
-    <mergeCell ref="D387:D388"/>
-    <mergeCell ref="A389:L393"/>
-    <mergeCell ref="A394:A442"/>
-    <mergeCell ref="B394:B442"/>
-    <mergeCell ref="C394:C403"/>
-    <mergeCell ref="D394:D403"/>
-    <mergeCell ref="C404:C410"/>
-    <mergeCell ref="D404:D410"/>
-    <mergeCell ref="C411:C421"/>
-    <mergeCell ref="D411:D421"/>
-    <mergeCell ref="C422:C426"/>
-    <mergeCell ref="D422:D426"/>
-    <mergeCell ref="C427:C436"/>
-    <mergeCell ref="D427:D436"/>
-    <mergeCell ref="C437:C442"/>
-    <mergeCell ref="D437:D442"/>
-    <mergeCell ref="A443:L447"/>
-    <mergeCell ref="A448:A538"/>
-    <mergeCell ref="B448:B538"/>
-    <mergeCell ref="C448:C468"/>
-    <mergeCell ref="D448:D468"/>
-    <mergeCell ref="C469:C475"/>
-    <mergeCell ref="D469:D475"/>
-    <mergeCell ref="C476:C481"/>
-    <mergeCell ref="D476:D481"/>
-    <mergeCell ref="C482:C490"/>
-    <mergeCell ref="D482:D490"/>
-    <mergeCell ref="C491:C493"/>
-    <mergeCell ref="D491:D493"/>
-    <mergeCell ref="C494:C499"/>
-    <mergeCell ref="D494:D499"/>
-    <mergeCell ref="C500:C507"/>
-    <mergeCell ref="D500:D507"/>
-    <mergeCell ref="C508:C512"/>
-    <mergeCell ref="D508:D512"/>
-    <mergeCell ref="C513:C517"/>
-    <mergeCell ref="D513:D517"/>
-    <mergeCell ref="C518:C520"/>
-    <mergeCell ref="D518:D520"/>
-    <mergeCell ref="C522:C529"/>
-    <mergeCell ref="D522:D529"/>
-    <mergeCell ref="C530:C538"/>
-    <mergeCell ref="D530:D538"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="A104:A247"/>
+    <mergeCell ref="B104:B247"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="C124:C126"/>
+    <mergeCell ref="D124:D126"/>
+    <mergeCell ref="C127:C130"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="C131:C136"/>
+    <mergeCell ref="D131:D136"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="C144:C151"/>
+    <mergeCell ref="D144:D151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="C158:C163"/>
+    <mergeCell ref="D158:D163"/>
+    <mergeCell ref="C164:C170"/>
+    <mergeCell ref="D164:D170"/>
+    <mergeCell ref="C171:C176"/>
+    <mergeCell ref="D171:D176"/>
+    <mergeCell ref="C177:C182"/>
+    <mergeCell ref="D177:D182"/>
+    <mergeCell ref="C183:C188"/>
+    <mergeCell ref="D183:D188"/>
+    <mergeCell ref="C189:C195"/>
+    <mergeCell ref="D189:D195"/>
+    <mergeCell ref="C196:C207"/>
+    <mergeCell ref="D196:D207"/>
+    <mergeCell ref="C208:C219"/>
+    <mergeCell ref="D208:D219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="D220:D226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="D227:D234"/>
+    <mergeCell ref="C235:C239"/>
+    <mergeCell ref="D235:D239"/>
+    <mergeCell ref="C240:C243"/>
+    <mergeCell ref="D240:D243"/>
+    <mergeCell ref="C244:C247"/>
+    <mergeCell ref="D244:D247"/>
+    <mergeCell ref="A249:A308"/>
+    <mergeCell ref="B249:B308"/>
+    <mergeCell ref="C249:C256"/>
+    <mergeCell ref="D249:D256"/>
+    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="D257:D263"/>
+    <mergeCell ref="C264:C268"/>
+    <mergeCell ref="D264:D268"/>
+    <mergeCell ref="C269:C274"/>
+    <mergeCell ref="D269:D274"/>
+    <mergeCell ref="C275:C283"/>
+    <mergeCell ref="D275:D283"/>
+    <mergeCell ref="C284:C289"/>
+    <mergeCell ref="D284:D289"/>
+    <mergeCell ref="C290:C296"/>
+    <mergeCell ref="D290:D296"/>
+    <mergeCell ref="C297:C303"/>
+    <mergeCell ref="D297:D303"/>
+    <mergeCell ref="C304:C308"/>
+    <mergeCell ref="D304:D308"/>
+    <mergeCell ref="A310:A339"/>
+    <mergeCell ref="B310:B339"/>
+    <mergeCell ref="C310:C315"/>
+    <mergeCell ref="D310:D315"/>
+    <mergeCell ref="C316:C323"/>
+    <mergeCell ref="D316:D323"/>
+    <mergeCell ref="C324:C327"/>
+    <mergeCell ref="D324:D327"/>
+    <mergeCell ref="C328:C335"/>
+    <mergeCell ref="D328:D335"/>
+    <mergeCell ref="C336:C339"/>
+    <mergeCell ref="D336:D339"/>
+    <mergeCell ref="A340:L344"/>
+    <mergeCell ref="A345:A385"/>
+    <mergeCell ref="B345:B385"/>
+    <mergeCell ref="C345:C349"/>
+    <mergeCell ref="D345:D349"/>
+    <mergeCell ref="C350:C351"/>
+    <mergeCell ref="D350:D351"/>
+    <mergeCell ref="C352:C353"/>
+    <mergeCell ref="D352:D353"/>
+    <mergeCell ref="C354:C356"/>
+    <mergeCell ref="D354:D356"/>
+    <mergeCell ref="C357:C361"/>
+    <mergeCell ref="D357:D361"/>
+    <mergeCell ref="C362:C366"/>
+    <mergeCell ref="D362:D366"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="D367:D368"/>
+    <mergeCell ref="C369:C370"/>
+    <mergeCell ref="D369:D370"/>
+    <mergeCell ref="C371:C372"/>
+    <mergeCell ref="D371:D372"/>
+    <mergeCell ref="C375:C376"/>
+    <mergeCell ref="D375:D376"/>
+    <mergeCell ref="C377:C380"/>
+    <mergeCell ref="D377:D380"/>
+    <mergeCell ref="C381:C383"/>
+    <mergeCell ref="D381:D383"/>
+    <mergeCell ref="C384:C385"/>
+    <mergeCell ref="D384:D385"/>
+    <mergeCell ref="A386:L390"/>
+    <mergeCell ref="A391:A439"/>
+    <mergeCell ref="B391:B439"/>
+    <mergeCell ref="C391:C400"/>
+    <mergeCell ref="D391:D400"/>
+    <mergeCell ref="C401:C407"/>
+    <mergeCell ref="D401:D407"/>
+    <mergeCell ref="C408:C418"/>
+    <mergeCell ref="D408:D418"/>
+    <mergeCell ref="C419:C423"/>
+    <mergeCell ref="D419:D423"/>
+    <mergeCell ref="C424:C433"/>
+    <mergeCell ref="D424:D433"/>
+    <mergeCell ref="C434:C439"/>
+    <mergeCell ref="D434:D439"/>
+    <mergeCell ref="A440:L444"/>
+    <mergeCell ref="A445:A535"/>
+    <mergeCell ref="B445:B535"/>
+    <mergeCell ref="C445:C465"/>
+    <mergeCell ref="D445:D465"/>
+    <mergeCell ref="C466:C472"/>
+    <mergeCell ref="D466:D472"/>
+    <mergeCell ref="C473:C478"/>
+    <mergeCell ref="D473:D478"/>
+    <mergeCell ref="C479:C487"/>
+    <mergeCell ref="D479:D487"/>
+    <mergeCell ref="C488:C490"/>
+    <mergeCell ref="D488:D490"/>
+    <mergeCell ref="C491:C496"/>
+    <mergeCell ref="D491:D496"/>
+    <mergeCell ref="C497:C504"/>
+    <mergeCell ref="D497:D504"/>
+    <mergeCell ref="C505:C509"/>
+    <mergeCell ref="D505:D509"/>
+    <mergeCell ref="C510:C514"/>
+    <mergeCell ref="D510:D514"/>
+    <mergeCell ref="C515:C517"/>
+    <mergeCell ref="D515:D517"/>
+    <mergeCell ref="C519:C526"/>
+    <mergeCell ref="D519:D526"/>
+    <mergeCell ref="C527:C535"/>
+    <mergeCell ref="D527:D535"/>
   </mergeCells>
-  <conditionalFormatting sqref="L348:L388 L394:L442 L448:L1048576 L3 L6:L8 L51:L342 L17:L25 L10:L13 L28:L48">
+  <conditionalFormatting sqref="L345:L385 L391:L439 L445:L1048576 L3 L6:L8 L48:L339 L17:L25 L10:L13 L28:L45">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="None" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("None",L3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K348:K388 K394:K442 K448:K1048576 K3 K6:K8 K51:K342 K17:K25 K10:K13 K28:K48">
+  <conditionalFormatting sqref="K345:K385 K391:K439 K445:K1048576 K3 K6:K8 K48:K339 K17:K25 K10:K13 K28:K45">
     <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Completed" dxfId="1">
       <formula>NOT(ISERROR(SEARCH("Completed",K3)))</formula>
     </cfRule>
@@ -48568,7 +48462,7 @@
       <formula>NOT(ISERROR(SEARCH("Not started",K3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L348:L388 L394:L442 L448:L1048576 L3 L6:L8 L51:L342 L17:L25 L10:L13 L28:L48">
+  <conditionalFormatting sqref="L345:L385 L391:L439 L445:L1048576 L3 L6:L8 L48:L339 L17:L25 L10:L13 L28:L45">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="fail" dxfId="4">
       <formula>NOT(ISERROR(SEARCH("fail",L3)))</formula>
     </cfRule>
@@ -48985,19 +48879,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K18:K25 K51:K342 K348:K388 K394:K442 K448:K1048576" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K18:K25 K48:K339 K345:K385 K391:K439 K445:K1048576" type="list">
       <formula1>"Not started,ongoing,Completed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I17:I25 I51:I250 I252:I311 I313:I342" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I17:I25 I48:I247 I249:I308 I310:I339" type="list">
       <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H107:H250 H252:H306" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H104:H247 H249:H303" type="list">
       <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L17:L25 L51:L342 L348:L388 L394:L442 L448:L1048576" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L17:L25 L48:L339 L345:L385 L391:L439 L445:L1048576" type="list">
       <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -49020,541 +48914,541 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="7.23"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="69" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="69" width="57.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="68" width="7.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="68" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="68" width="57.87"/>
   </cols>
   <sheetData>
-    <row r="1" s="72" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="70" t="s">
+    <row r="1" s="71" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="69" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="69" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="70"/>
+    </row>
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="73"/>
+    </row>
+    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="72" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="73"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="73"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="73"/>
+    </row>
+    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="E6" s="73"/>
+    </row>
+    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="B7" s="72" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="C7" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="72" t="s">
         <v>186</v>
       </c>
-      <c r="E1" s="71"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="73" t="n">
+      <c r="E7" s="73"/>
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="73"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="73"/>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="73"/>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="73"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="73"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="75"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="75"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="73"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="72" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="73"/>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="72" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="73"/>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="72" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="73"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="72" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="73"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="72" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="72" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" s="73"/>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="72" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="72" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" s="73"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" s="73"/>
+    </row>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="72" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="72" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="73"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="72" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="73"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="76"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="72" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="E34" s="73"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" s="72" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="73"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="73"/>
+    </row>
+    <row r="37" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="72" t="s">
+        <v>227</v>
+      </c>
+      <c r="E37" s="73"/>
+    </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="72" t="s">
+        <v>229</v>
+      </c>
+      <c r="E38" s="73"/>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" s="73"/>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="72" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="73"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="72" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="72" t="s">
+        <v>235</v>
+      </c>
+      <c r="E41" s="73"/>
+    </row>
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="72" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="72" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="73"/>
+    </row>
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="C2" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="E2" s="74"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" s="74"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="73" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="74"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="74"/>
-    </row>
-    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>198</v>
-      </c>
-      <c r="E6" s="74"/>
-    </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="73" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>200</v>
-      </c>
-      <c r="E7" s="74"/>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="E8" s="74"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="74"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="n">
-        <v>15</v>
-      </c>
-      <c r="B10" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>208</v>
-      </c>
-      <c r="E10" s="74"/>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="E11" s="74"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="75"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="74"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="76"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="76"/>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="76"/>
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="77" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="73" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="73" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="E18" s="74"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="73" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="73" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="73" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="74"/>
-    </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="73" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="73" t="s">
-        <v>217</v>
-      </c>
-      <c r="C20" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="74"/>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="73" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="73" t="s">
-        <v>219</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D21" s="73" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" s="74"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="73" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D22" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="E22" s="74"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="73" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" s="73" t="s">
-        <v>223</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D23" s="73" t="s">
-        <v>224</v>
-      </c>
-      <c r="E23" s="74"/>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="73" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="73" t="s">
-        <v>225</v>
-      </c>
-      <c r="C24" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D24" s="73" t="s">
-        <v>226</v>
-      </c>
-      <c r="E24" s="74"/>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="73" t="n">
-        <v>8</v>
-      </c>
-      <c r="B25" s="73" t="s">
-        <v>227</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="E25" s="74"/>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="73" t="n">
-        <v>7</v>
-      </c>
-      <c r="B26" s="73" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="73" t="s">
-        <v>230</v>
-      </c>
-      <c r="E26" s="74"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="73" t="s">
-        <v>231</v>
-      </c>
-      <c r="B27" s="73" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D27" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="E27" s="74"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="73" t="s">
-        <v>234</v>
-      </c>
-      <c r="B34" s="73" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="D34" s="73" t="s">
-        <v>235</v>
-      </c>
-      <c r="E34" s="74"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="B35" s="73" t="s">
-        <v>237</v>
-      </c>
-      <c r="C35" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="73" t="s">
+      <c r="B43" s="72" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="74"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="73" t="s">
+      <c r="C43" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="72" t="s">
         <v>239</v>
       </c>
-      <c r="B36" s="73" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D36" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" s="74"/>
-    </row>
-    <row r="37" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="73" t="s">
-        <v>240</v>
-      </c>
-      <c r="C37" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D37" s="73" t="s">
-        <v>241</v>
-      </c>
-      <c r="E37" s="74"/>
-    </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="73" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="C38" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D38" s="73" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" s="74"/>
-    </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="73" t="s">
-        <v>244</v>
-      </c>
-      <c r="C39" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D39" s="73" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="74"/>
-    </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="B40" s="73" t="s">
-        <v>246</v>
-      </c>
-      <c r="C40" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" s="73" t="s">
-        <v>247</v>
-      </c>
-      <c r="E40" s="74"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="C41" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" s="73" t="s">
-        <v>249</v>
-      </c>
-      <c r="E41" s="74"/>
-    </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="73" t="s">
-        <v>250</v>
-      </c>
-      <c r="C42" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D42" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="E42" s="74"/>
-    </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" s="73" t="s">
-        <v>252</v>
-      </c>
-      <c r="C43" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D43" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="E43" s="74"/>
+      <c r="E43" s="73"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="75"/>
-      <c r="B44" s="75"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="74"/>
+      <c r="A44" s="74"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="73"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="76"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
+      <c r="A45" s="75"/>
+      <c r="B45" s="75"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="75"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="76"/>
-      <c r="B46" s="76"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
+      <c r="A46" s="75"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="75"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="76"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
+      <c r="A47" s="75"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -49579,1314 +49473,1314 @@
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="40.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="69" width="77.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="69" width="99.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="69" width="89.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="69" width="86.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="69" width="36.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="69" width="60.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="69" width="68.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="69" width="30.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="69" width="21.98"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="69" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="69" width="44.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="68" width="40.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="68" width="77.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="68" width="99.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="68" width="89.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="68" width="86.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="68" width="36.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="68" width="60.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="68" width="68.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="68" width="30.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="68" width="21.98"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="68" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="68" width="44.79"/>
   </cols>
   <sheetData>
-    <row r="1" s="78" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="77" t="s">
+    <row r="1" s="77" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+    </row>
+    <row r="2" s="79" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="78"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="H3" s="72" t="s">
+        <v>242</v>
+      </c>
+      <c r="I3" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="73"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="H4" s="72" t="s">
+        <v>244</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="73"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="74"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="H5" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="I5" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="73"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="74"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" s="73"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="74"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>250</v>
+      </c>
+      <c r="I7" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="N7" s="73"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="74"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>251</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="72" t="s">
+        <v>97</v>
+      </c>
+      <c r="N8" s="73"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="74"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="72" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>253</v>
+      </c>
+      <c r="H9" s="72" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-    </row>
-    <row r="2" s="80" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="70" t="s">
+      <c r="I9" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="73"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="74"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>255</v>
+      </c>
+      <c r="H10" s="72" t="s">
+        <v>256</v>
+      </c>
+      <c r="I10" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="72" t="s">
+        <v>106</v>
+      </c>
+      <c r="N10" s="73"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="74"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="72" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="H11" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="N11" s="73"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="D12" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="H12" s="72" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="N12" s="73"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="72" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" s="72" t="s">
+        <v>262</v>
+      </c>
+      <c r="I13" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="N13" s="73"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="72" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="72" t="s">
+        <v>263</v>
+      </c>
+      <c r="H14" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="I14" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="N14" s="73"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="74"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="D15" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" s="72" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="H15" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="I15" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="72" t="s">
+        <v>270</v>
+      </c>
+      <c r="N15" s="73"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="74"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="72" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>271</v>
+      </c>
+      <c r="G16" s="72" t="s">
+        <v>272</v>
+      </c>
+      <c r="H16" s="72" t="s">
+        <v>273</v>
+      </c>
+      <c r="I16" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="72" t="s">
+        <v>274</v>
+      </c>
+      <c r="N16" s="73"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="74"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="72" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="I17" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="K17" s="74"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="N17" s="73"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="74"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="72" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" s="72" t="s">
+        <v>279</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="I18" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="K18" s="74"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="N18" s="73"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="74"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="D19" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="E19" s="72" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" s="72" t="s">
+        <v>286</v>
+      </c>
+      <c r="I19" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="N19" s="73"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="74"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="72" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" s="72" t="s">
+        <v>288</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>289</v>
+      </c>
+      <c r="H20" s="72" t="s">
+        <v>290</v>
+      </c>
+      <c r="I20" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>291</v>
+      </c>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="72" t="s">
+        <v>292</v>
+      </c>
+      <c r="N20" s="73"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="74"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="72" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>293</v>
+      </c>
+      <c r="G21" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="H21" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="I21" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J21" s="72" t="s">
+        <v>291</v>
+      </c>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="72" t="s">
+        <v>296</v>
+      </c>
+      <c r="N21" s="73"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="70" t="s">
+      <c r="D22" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="72" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="N22" s="73"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="74"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="72" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="72" t="s">
+        <v>297</v>
+      </c>
+      <c r="H23" s="72" t="s">
+        <v>298</v>
+      </c>
+      <c r="I23" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="74"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="N23" s="73"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="74"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="72" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>299</v>
+      </c>
+      <c r="H24" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="I24" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="N24" s="73"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="74"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="72" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>302</v>
+      </c>
+      <c r="I25" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="N25" s="73"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="74"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="72" t="s">
+        <v>303</v>
+      </c>
+      <c r="H26" s="72" t="s">
+        <v>304</v>
+      </c>
+      <c r="I26" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="72" t="s">
+        <v>147</v>
+      </c>
+      <c r="N26" s="73"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="74"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="72" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>305</v>
+      </c>
+      <c r="H27" s="72" t="s">
+        <v>306</v>
+      </c>
+      <c r="I27" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="N27" s="73"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="74"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="72" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="79"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="H3" s="73" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="N3" s="74"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="75"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="73" t="s">
-        <v>257</v>
-      </c>
-      <c r="H4" s="73" t="s">
-        <v>258</v>
-      </c>
-      <c r="I4" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="73" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4" s="74"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="75"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>259</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>260</v>
-      </c>
-      <c r="I5" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" s="74"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="75"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="73" t="s">
-        <v>261</v>
-      </c>
-      <c r="H6" s="73" t="s">
-        <v>262</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="74"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="75"/>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="73" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="73" t="s">
-        <v>263</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>264</v>
-      </c>
-      <c r="I7" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="N7" s="74"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="75"/>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>266</v>
-      </c>
-      <c r="I8" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="N8" s="74"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75"/>
-      <c r="B9" s="75"/>
-      <c r="C9" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="73" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="H9" s="73" t="s">
-        <v>268</v>
-      </c>
-      <c r="I9" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="73" t="s">
-        <v>102</v>
-      </c>
-      <c r="N9" s="74"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="75"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="73" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="73" t="s">
-        <v>269</v>
-      </c>
-      <c r="H10" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="I10" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="N10" s="74"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="75"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="73" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>271</v>
-      </c>
-      <c r="H11" s="73" t="s">
-        <v>272</v>
-      </c>
-      <c r="I11" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="N11" s="74"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="75"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="73" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" s="73" t="s">
-        <v>273</v>
-      </c>
-      <c r="H12" s="73" t="s">
-        <v>274</v>
-      </c>
-      <c r="I12" s="73" t="s">
+      <c r="D28" s="72" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="72" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="72" t="s">
+        <v>307</v>
+      </c>
+      <c r="H28" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="I28" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="N12" s="74"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="75"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="73" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" s="73" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="73" t="s">
-        <v>275</v>
-      </c>
-      <c r="H13" s="73" t="s">
-        <v>276</v>
-      </c>
-      <c r="I13" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="73" t="s">
-        <v>120</v>
-      </c>
-      <c r="N13" s="74"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="75"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="73" t="n">
-        <v>12</v>
-      </c>
-      <c r="F14" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="73" t="s">
-        <v>277</v>
-      </c>
-      <c r="H14" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="I14" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="K14" s="75"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="73" t="s">
-        <v>124</v>
-      </c>
-      <c r="N14" s="74"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="75"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="73" t="s">
-        <v>279</v>
-      </c>
-      <c r="E15" s="73" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="73" t="s">
-        <v>281</v>
-      </c>
-      <c r="H15" s="73" t="s">
-        <v>282</v>
-      </c>
-      <c r="I15" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="73" t="s">
-        <v>284</v>
-      </c>
-      <c r="N15" s="74"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="75"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="73" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>285</v>
-      </c>
-      <c r="G16" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="H16" s="73" t="s">
-        <v>287</v>
-      </c>
-      <c r="I16" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="K16" s="75"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="73" t="s">
-        <v>288</v>
-      </c>
-      <c r="N16" s="74"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="75"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="73" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" s="73" t="s">
-        <v>289</v>
-      </c>
-      <c r="G17" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="H17" s="73" t="s">
-        <v>291</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="K17" s="75"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="73" t="s">
-        <v>292</v>
-      </c>
-      <c r="N17" s="74"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="75"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="73" t="n">
-        <v>16</v>
-      </c>
-      <c r="F18" s="73" t="s">
-        <v>293</v>
-      </c>
-      <c r="G18" s="73" t="s">
-        <v>294</v>
-      </c>
-      <c r="H18" s="73" t="s">
-        <v>295</v>
-      </c>
-      <c r="I18" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="K18" s="75"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="N18" s="74"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="75"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="73" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="73" t="n">
-        <v>17</v>
-      </c>
-      <c r="F19" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="G19" s="73" t="s">
-        <v>297</v>
-      </c>
-      <c r="H19" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="73" t="s">
-        <v>131</v>
-      </c>
-      <c r="N19" s="74"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="73" t="n">
-        <v>18</v>
-      </c>
-      <c r="F20" s="73" t="s">
-        <v>132</v>
-      </c>
-      <c r="G20" s="73" t="s">
-        <v>299</v>
-      </c>
-      <c r="H20" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="I20" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="N20" s="74"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="75"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="73" t="n">
-        <v>19</v>
-      </c>
-      <c r="F21" s="73" t="s">
-        <v>137</v>
-      </c>
-      <c r="G21" s="73" t="s">
-        <v>301</v>
-      </c>
-      <c r="H21" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="I21" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J21" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="73" t="s">
-        <v>140</v>
-      </c>
-      <c r="N21" s="74"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="75"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="73" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="73" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="I22" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="N22" s="74"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="75"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="73" t="n">
-        <v>21</v>
-      </c>
-      <c r="F23" s="73" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="73" t="s">
-        <v>303</v>
-      </c>
-      <c r="H23" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="I23" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J23" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K23" s="75"/>
-      <c r="L23" s="75"/>
-      <c r="M23" s="73" t="s">
-        <v>150</v>
-      </c>
-      <c r="N23" s="74"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="75"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="73" t="n">
-        <v>22</v>
-      </c>
-      <c r="F24" s="73" t="s">
-        <v>151</v>
-      </c>
-      <c r="G24" s="73" t="s">
-        <v>305</v>
-      </c>
-      <c r="H24" s="73" t="s">
-        <v>306</v>
-      </c>
-      <c r="I24" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J24" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="73" t="s">
-        <v>154</v>
-      </c>
-      <c r="N24" s="74"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="73" t="n">
-        <v>23</v>
-      </c>
-      <c r="F25" s="73" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" s="73" t="s">
-        <v>307</v>
-      </c>
-      <c r="H25" s="73" t="s">
-        <v>308</v>
-      </c>
-      <c r="I25" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="73" t="s">
+      <c r="J28" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="72" t="s">
         <v>158</v>
       </c>
-      <c r="N25" s="74"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="73" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" s="73" t="s">
-        <v>159</v>
-      </c>
-      <c r="G26" s="73" t="s">
+      <c r="N28" s="73"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="73"/>
+    </row>
+    <row r="31" s="80" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="75"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="76" t="s">
         <v>309</v>
       </c>
-      <c r="H26" s="73" t="s">
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76"/>
+      <c r="M34" s="76"/>
+      <c r="N34" s="77"/>
+    </row>
+    <row r="35" s="79" customFormat="true" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="I26" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="N26" s="74"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="73" t="n">
-        <v>25</v>
-      </c>
-      <c r="F27" s="73" t="s">
-        <v>163</v>
-      </c>
-      <c r="G27" s="73" t="s">
+      <c r="B35" s="69" t="s">
         <v>311</v>
       </c>
-      <c r="H27" s="73" t="s">
+      <c r="C35" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="I27" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="J27" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="N27" s="74"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="73" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="73" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="73" t="n">
-        <v>26</v>
-      </c>
-      <c r="F28" s="73" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="73" t="s">
+      <c r="D35" s="69" t="s">
         <v>313</v>
       </c>
-      <c r="H28" s="73" t="s">
+      <c r="E35" s="69" t="s">
         <v>314</v>
       </c>
-      <c r="I28" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="73" t="s">
-        <v>171</v>
-      </c>
-      <c r="K28" s="75"/>
-      <c r="L28" s="75"/>
-      <c r="M28" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="N28" s="74"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="75"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="75"/>
-      <c r="M29" s="75"/>
-      <c r="N29" s="74"/>
-    </row>
-    <row r="31" s="81" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="77" t="s">
+      <c r="F35" s="78"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="81"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
-      <c r="L34" s="77"/>
-      <c r="M34" s="77"/>
-      <c r="N34" s="78"/>
-    </row>
-    <row r="35" s="80" customFormat="true" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="70" t="s">
+      <c r="B36" s="72" t="s">
         <v>316</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="C36" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="D36" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="D35" s="70" t="s">
+      <c r="E36" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="E35" s="70" t="s">
+      <c r="F36" s="73"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F35" s="79"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="82"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="73" t="s">
+      <c r="B37" s="72" t="s">
         <v>321</v>
       </c>
-      <c r="B36" s="73" t="s">
+      <c r="C37" s="72" t="s">
         <v>322</v>
       </c>
-      <c r="C36" s="73" t="s">
+      <c r="D37" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="D36" s="73" t="s">
+      <c r="E37" s="72" t="s">
         <v>324</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="F37" s="73"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="F36" s="74"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="73" t="s">
+      <c r="B38" s="72" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="73" t="s">
+      <c r="C38" s="72" t="s">
         <v>327</v>
       </c>
-      <c r="C37" s="73" t="s">
+      <c r="D38" s="72" t="s">
         <v>328</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="E38" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="F38" s="73"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="F37" s="74"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="73" t="s">
+      <c r="B39" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="B38" s="73" t="s">
+      <c r="C39" s="72" t="s">
         <v>332</v>
       </c>
-      <c r="C38" s="73" t="s">
+      <c r="D39" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="D38" s="73" t="s">
+      <c r="E39" s="72" t="s">
         <v>334</v>
       </c>
-      <c r="E38" s="73" t="s">
+      <c r="F39" s="73"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="72" t="s">
         <v>335</v>
       </c>
-      <c r="F38" s="74"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="73" t="s">
+      <c r="B40" s="72" t="s">
         <v>336</v>
       </c>
-      <c r="B39" s="73" t="s">
+      <c r="C40" s="72" t="s">
         <v>337</v>
       </c>
-      <c r="C39" s="73" t="s">
+      <c r="D40" s="72" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="73" t="s">
+      <c r="E40" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="F40" s="73"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="72" t="s">
         <v>340</v>
       </c>
-      <c r="F39" s="74"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="73" t="s">
+      <c r="B41" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="B40" s="73" t="s">
+      <c r="C41" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="C40" s="73" t="s">
+      <c r="D41" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="D40" s="73" t="s">
+      <c r="E41" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="F41" s="73"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="F40" s="74"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="73" t="s">
+      <c r="D42" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="B41" s="73" t="s">
+      <c r="E42" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="73"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="72" t="s">
         <v>347</v>
       </c>
-      <c r="C41" s="73" t="s">
+      <c r="D43" s="72" t="s">
         <v>348</v>
       </c>
-      <c r="D41" s="73" t="s">
+      <c r="E43" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="73"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="72" t="s">
         <v>349</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="D44" s="72" t="s">
         <v>350</v>
       </c>
-      <c r="F41" s="74"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="73" t="s">
+      <c r="E44" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="73"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="72" t="s">
         <v>351</v>
       </c>
-      <c r="D42" s="73" t="s">
+      <c r="C45" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="E42" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="74"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="73" t="s">
+      <c r="D45" s="72" t="s">
         <v>353</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="E45" s="72" t="s">
         <v>354</v>
       </c>
-      <c r="E43" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="F43" s="74"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="73" t="s">
+      <c r="F45" s="73"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="72" t="s">
         <v>355</v>
       </c>
-      <c r="D44" s="73" t="s">
+      <c r="B46" s="72" t="s">
         <v>356</v>
       </c>
-      <c r="E44" s="73" t="s">
-        <v>69</v>
-      </c>
-      <c r="F44" s="74"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="73" t="s">
+      <c r="C46" s="72" t="s">
         <v>357</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="D46" s="72" t="s">
         <v>358</v>
       </c>
-      <c r="D45" s="73" t="s">
+      <c r="E46" s="72" t="s">
         <v>359</v>
       </c>
-      <c r="E45" s="73" t="s">
+      <c r="F46" s="73"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="72" t="s">
         <v>360</v>
       </c>
-      <c r="F45" s="74"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="73" t="s">
+      <c r="B47" s="72" t="s">
         <v>361</v>
       </c>
-      <c r="B46" s="73" t="s">
+      <c r="C47" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="C46" s="73" t="s">
+      <c r="D47" s="72" t="s">
         <v>363</v>
       </c>
-      <c r="D46" s="73" t="s">
+      <c r="E47" s="72" t="s">
         <v>364</v>
       </c>
-      <c r="E46" s="73" t="s">
+      <c r="F47" s="73"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="72" t="s">
         <v>365</v>
       </c>
-      <c r="F46" s="74"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="73" t="s">
+      <c r="B48" s="72" t="s">
         <v>366</v>
       </c>
-      <c r="B47" s="73" t="s">
+      <c r="C48" s="72" t="s">
         <v>367</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="D48" s="72" t="s">
         <v>368</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="E48" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="F48" s="73"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="72" t="s">
         <v>370</v>
       </c>
-      <c r="F47" s="74"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="73" t="s">
+      <c r="B49" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="B48" s="73" t="s">
+      <c r="C49" s="72" t="s">
         <v>372</v>
       </c>
-      <c r="C48" s="73" t="s">
+      <c r="D49" s="72" t="s">
         <v>373</v>
       </c>
-      <c r="D48" s="73" t="s">
+      <c r="E49" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="E48" s="73" t="s">
+      <c r="F49" s="73"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="72" t="s">
         <v>375</v>
       </c>
-      <c r="F48" s="74"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="73" t="s">
+      <c r="C50" s="72" t="s">
         <v>376</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="D50" s="72" t="s">
         <v>377</v>
       </c>
-      <c r="C49" s="73" t="s">
+      <c r="E50" s="72" t="s">
         <v>378</v>
       </c>
-      <c r="D49" s="73" t="s">
+      <c r="F50" s="73"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="72" t="s">
         <v>379</v>
       </c>
-      <c r="E49" s="73" t="s">
+      <c r="B51" s="72" t="s">
         <v>380</v>
       </c>
-      <c r="F49" s="74"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="73" t="s">
+      <c r="C51" s="72" t="s">
         <v>381</v>
       </c>
-      <c r="C50" s="73" t="s">
+      <c r="D51" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="D50" s="73" t="s">
+      <c r="E51" s="72" t="s">
         <v>383</v>
       </c>
-      <c r="E50" s="73" t="s">
+      <c r="F51" s="73"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="72" t="s">
         <v>384</v>
       </c>
-      <c r="F50" s="74"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="73" t="s">
+      <c r="B52" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="72" t="s">
         <v>385</v>
       </c>
-      <c r="B51" s="73" t="s">
+      <c r="D52" s="72" t="s">
         <v>386</v>
       </c>
-      <c r="C51" s="73" t="s">
+      <c r="E52" s="72" t="s">
         <v>387</v>
       </c>
-      <c r="D51" s="73" t="s">
+      <c r="F52" s="73"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="72" t="s">
         <v>388</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="B53" s="72" t="s">
         <v>389</v>
       </c>
-      <c r="F51" s="74"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="73" t="s">
+      <c r="C53" s="72" t="s">
         <v>390</v>
       </c>
-      <c r="B52" s="73" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" s="73" t="s">
+      <c r="D53" s="72" t="s">
         <v>391</v>
       </c>
-      <c r="D52" s="73" t="s">
+      <c r="E53" s="72" t="s">
         <v>392</v>
       </c>
-      <c r="E52" s="73" t="s">
+      <c r="F53" s="73"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="72" t="s">
         <v>393</v>
       </c>
-      <c r="F52" s="74"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="73" t="s">
+      <c r="B54" s="72" t="s">
         <v>394</v>
       </c>
-      <c r="B53" s="73" t="s">
+      <c r="C54" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="C53" s="73" t="s">
+      <c r="D54" s="72" t="s">
         <v>396</v>
       </c>
-      <c r="D53" s="73" t="s">
+      <c r="E54" s="72" t="s">
         <v>397</v>
       </c>
-      <c r="E53" s="73" t="s">
-        <v>398</v>
-      </c>
-      <c r="F53" s="74"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="73" t="s">
-        <v>399</v>
-      </c>
-      <c r="B54" s="73" t="s">
-        <v>400</v>
-      </c>
-      <c r="C54" s="73" t="s">
-        <v>401</v>
-      </c>
-      <c r="D54" s="73" t="s">
-        <v>402</v>
-      </c>
-      <c r="E54" s="73" t="s">
-        <v>403</v>
-      </c>
-      <c r="F54" s="74"/>
+      <c r="F54" s="73"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="75"/>
-      <c r="B55" s="75"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="74"/>
+      <c r="A55" s="74"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/plan_phase/majid/tp_miim_tx.xlsx
+++ b/plan_phase/majid/tp_miim_tx.xlsx
@@ -21,16 +21,12 @@
     <definedName name="Scrolling_Increment">#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="399">
   <si>
     <t>Section no.</t>
   </si>
@@ -1745,10 +1741,10 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -11179,7 +11175,9 @@
       <c r="I29" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="34"/>
+      <c r="J29" s="34" t="s">
+        <v>398</v>
+      </c>
       <c r="K29" s="34"/>
       <c r="L29" s="23" t="s">
         <v>18</v>
@@ -11209,7 +11207,9 @@
       <c r="I30" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="34"/>
+      <c r="J30" s="34" t="s">
+        <v>398</v>
+      </c>
       <c r="K30" s="34"/>
       <c r="L30" s="23" t="s">
         <v>18</v>
@@ -14894,7 +14894,7 @@
       <c r="A439" s="76"/>
       <c r="B439" s="77"/>
       <c r="C439" s="78"/>
-      <c r="D439" s="73"/>
+      <c r="D439" s="74"/>
       <c r="E439" s="17"/>
       <c r="F439" s="17"/>
       <c r="G439" s="17"/>
@@ -14903,7 +14903,7 @@
       <c r="A440" s="76"/>
       <c r="B440" s="77"/>
       <c r="C440" s="78"/>
-      <c r="D440" s="73"/>
+      <c r="D440" s="74"/>
       <c r="E440" s="17"/>
       <c r="F440" s="17"/>
       <c r="G440" s="17"/>
@@ -14912,7 +14912,7 @@
       <c r="A441" s="76"/>
       <c r="B441" s="77"/>
       <c r="C441" s="78"/>
-      <c r="D441" s="73"/>
+      <c r="D441" s="74"/>
       <c r="E441" s="17"/>
       <c r="F441" s="17"/>
       <c r="G441" s="17"/>
@@ -14921,7 +14921,7 @@
       <c r="A442" s="76"/>
       <c r="B442" s="77"/>
       <c r="C442" s="78"/>
-      <c r="D442" s="73"/>
+      <c r="D442" s="74"/>
       <c r="E442" s="17"/>
       <c r="F442" s="17"/>
       <c r="G442" s="17"/>
@@ -14930,7 +14930,7 @@
       <c r="A443" s="76"/>
       <c r="B443" s="77"/>
       <c r="C443" s="78"/>
-      <c r="D443" s="73"/>
+      <c r="D443" s="74"/>
       <c r="E443" s="17"/>
       <c r="F443" s="17"/>
       <c r="G443" s="17"/>
@@ -14939,7 +14939,7 @@
       <c r="A444" s="76"/>
       <c r="B444" s="77"/>
       <c r="C444" s="78"/>
-      <c r="D444" s="73"/>
+      <c r="D444" s="74"/>
       <c r="E444" s="17"/>
       <c r="F444" s="17"/>
       <c r="G444" s="17"/>
@@ -14948,7 +14948,7 @@
       <c r="A445" s="76"/>
       <c r="B445" s="77"/>
       <c r="C445" s="78"/>
-      <c r="D445" s="73"/>
+      <c r="D445" s="74"/>
       <c r="E445" s="17"/>
       <c r="F445" s="17"/>
       <c r="G445" s="17"/>
@@ -14957,7 +14957,7 @@
       <c r="A446" s="76"/>
       <c r="B446" s="77"/>
       <c r="C446" s="78"/>
-      <c r="D446" s="73"/>
+      <c r="D446" s="74"/>
       <c r="E446" s="17"/>
       <c r="F446" s="17"/>
       <c r="G446" s="17"/>
@@ -14966,7 +14966,7 @@
       <c r="A447" s="76"/>
       <c r="B447" s="77"/>
       <c r="C447" s="78"/>
-      <c r="D447" s="73"/>
+      <c r="D447" s="74"/>
       <c r="E447" s="17"/>
       <c r="F447" s="17"/>
       <c r="G447" s="17"/>
@@ -14975,7 +14975,7 @@
       <c r="A448" s="76"/>
       <c r="B448" s="77"/>
       <c r="C448" s="78"/>
-      <c r="D448" s="73"/>
+      <c r="D448" s="74"/>
       <c r="E448" s="17"/>
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
@@ -14984,7 +14984,7 @@
       <c r="A449" s="76"/>
       <c r="B449" s="77"/>
       <c r="C449" s="78"/>
-      <c r="D449" s="73"/>
+      <c r="D449" s="74"/>
       <c r="E449" s="17"/>
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
@@ -14993,7 +14993,7 @@
       <c r="A450" s="76"/>
       <c r="B450" s="77"/>
       <c r="C450" s="78"/>
-      <c r="D450" s="73"/>
+      <c r="D450" s="74"/>
       <c r="E450" s="17"/>
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
@@ -15002,7 +15002,7 @@
       <c r="A451" s="76"/>
       <c r="B451" s="77"/>
       <c r="C451" s="78"/>
-      <c r="D451" s="73"/>
+      <c r="D451" s="74"/>
       <c r="E451" s="17"/>
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
@@ -15011,7 +15011,7 @@
       <c r="A452" s="76"/>
       <c r="B452" s="77"/>
       <c r="C452" s="78"/>
-      <c r="D452" s="73"/>
+      <c r="D452" s="74"/>
       <c r="E452" s="17"/>
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
@@ -15020,7 +15020,7 @@
       <c r="A453" s="76"/>
       <c r="B453" s="77"/>
       <c r="C453" s="78"/>
-      <c r="D453" s="73"/>
+      <c r="D453" s="74"/>
       <c r="E453" s="17"/>
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
@@ -15029,7 +15029,7 @@
       <c r="A454" s="76"/>
       <c r="B454" s="77"/>
       <c r="C454" s="78"/>
-      <c r="D454" s="73"/>
+      <c r="D454" s="74"/>
       <c r="E454" s="17"/>
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
@@ -15038,7 +15038,7 @@
       <c r="A455" s="76"/>
       <c r="B455" s="77"/>
       <c r="C455" s="78"/>
-      <c r="D455" s="73"/>
+      <c r="D455" s="74"/>
       <c r="E455" s="17"/>
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
@@ -15047,7 +15047,7 @@
       <c r="A456" s="76"/>
       <c r="B456" s="77"/>
       <c r="C456" s="78"/>
-      <c r="D456" s="73"/>
+      <c r="D456" s="74"/>
       <c r="E456" s="17"/>
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
@@ -15056,7 +15056,7 @@
       <c r="A457" s="76"/>
       <c r="B457" s="77"/>
       <c r="C457" s="78"/>
-      <c r="D457" s="73"/>
+      <c r="D457" s="74"/>
       <c r="E457" s="17"/>
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
@@ -15065,7 +15065,7 @@
       <c r="A458" s="76"/>
       <c r="B458" s="77"/>
       <c r="C458" s="78"/>
-      <c r="D458" s="73"/>
+      <c r="D458" s="74"/>
       <c r="E458" s="17"/>
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
@@ -15074,7 +15074,7 @@
       <c r="A459" s="76"/>
       <c r="B459" s="77"/>
       <c r="C459" s="78"/>
-      <c r="D459" s="73"/>
+      <c r="D459" s="74"/>
       <c r="E459" s="17"/>
       <c r="F459" s="17"/>
       <c r="G459" s="17"/>
@@ -15083,7 +15083,7 @@
       <c r="A460" s="76"/>
       <c r="B460" s="77"/>
       <c r="C460" s="78"/>
-      <c r="D460" s="73"/>
+      <c r="D460" s="74"/>
       <c r="E460" s="17"/>
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
@@ -15092,7 +15092,7 @@
       <c r="A461" s="76"/>
       <c r="B461" s="77"/>
       <c r="C461" s="78"/>
-      <c r="D461" s="73"/>
+      <c r="D461" s="74"/>
       <c r="E461" s="17"/>
       <c r="F461" s="17"/>
       <c r="G461" s="17"/>
@@ -15101,7 +15101,7 @@
       <c r="A462" s="76"/>
       <c r="B462" s="77"/>
       <c r="C462" s="78"/>
-      <c r="D462" s="73"/>
+      <c r="D462" s="74"/>
       <c r="E462" s="17"/>
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
@@ -15110,7 +15110,7 @@
       <c r="A463" s="76"/>
       <c r="B463" s="77"/>
       <c r="C463" s="78"/>
-      <c r="D463" s="73"/>
+      <c r="D463" s="74"/>
       <c r="E463" s="17"/>
       <c r="F463" s="17"/>
       <c r="G463" s="17"/>
@@ -15119,7 +15119,7 @@
       <c r="A464" s="76"/>
       <c r="B464" s="77"/>
       <c r="C464" s="78"/>
-      <c r="D464" s="73"/>
+      <c r="D464" s="74"/>
       <c r="E464" s="17"/>
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
@@ -15128,7 +15128,7 @@
       <c r="A465" s="76"/>
       <c r="B465" s="77"/>
       <c r="C465" s="78"/>
-      <c r="D465" s="73"/>
+      <c r="D465" s="74"/>
       <c r="E465" s="17"/>
       <c r="F465" s="17"/>
       <c r="G465" s="17"/>
@@ -15137,7 +15137,7 @@
       <c r="A466" s="76"/>
       <c r="B466" s="77"/>
       <c r="C466" s="78"/>
-      <c r="D466" s="73"/>
+      <c r="D466" s="74"/>
       <c r="E466" s="17"/>
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
@@ -15146,7 +15146,7 @@
       <c r="A467" s="76"/>
       <c r="B467" s="77"/>
       <c r="C467" s="78"/>
-      <c r="D467" s="73"/>
+      <c r="D467" s="74"/>
       <c r="E467" s="17"/>
       <c r="F467" s="17"/>
       <c r="G467" s="17"/>
@@ -15155,7 +15155,7 @@
       <c r="A468" s="76"/>
       <c r="B468" s="77"/>
       <c r="C468" s="78"/>
-      <c r="D468" s="73"/>
+      <c r="D468" s="74"/>
       <c r="E468" s="17"/>
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
@@ -15164,7 +15164,7 @@
       <c r="A469" s="76"/>
       <c r="B469" s="77"/>
       <c r="C469" s="78"/>
-      <c r="D469" s="73"/>
+      <c r="D469" s="74"/>
       <c r="E469" s="17"/>
       <c r="F469" s="17"/>
       <c r="G469" s="17"/>
@@ -15173,7 +15173,7 @@
       <c r="A470" s="76"/>
       <c r="B470" s="77"/>
       <c r="C470" s="78"/>
-      <c r="D470" s="73"/>
+      <c r="D470" s="74"/>
       <c r="E470" s="17"/>
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
@@ -15182,7 +15182,7 @@
       <c r="A471" s="76"/>
       <c r="B471" s="77"/>
       <c r="C471" s="78"/>
-      <c r="D471" s="73"/>
+      <c r="D471" s="74"/>
       <c r="E471" s="17"/>
       <c r="F471" s="17"/>
       <c r="G471" s="17"/>
@@ -15191,7 +15191,7 @@
       <c r="A472" s="76"/>
       <c r="B472" s="77"/>
       <c r="C472" s="78"/>
-      <c r="D472" s="73"/>
+      <c r="D472" s="74"/>
       <c r="E472" s="17"/>
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
@@ -15200,7 +15200,7 @@
       <c r="A473" s="76"/>
       <c r="B473" s="77"/>
       <c r="C473" s="78"/>
-      <c r="D473" s="73"/>
+      <c r="D473" s="74"/>
       <c r="E473" s="17"/>
       <c r="F473" s="17"/>
       <c r="G473" s="17"/>
@@ -15209,7 +15209,7 @@
       <c r="A474" s="76"/>
       <c r="B474" s="77"/>
       <c r="C474" s="78"/>
-      <c r="D474" s="73"/>
+      <c r="D474" s="74"/>
       <c r="E474" s="17"/>
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
@@ -15218,7 +15218,7 @@
       <c r="A475" s="76"/>
       <c r="B475" s="77"/>
       <c r="C475" s="78"/>
-      <c r="D475" s="73"/>
+      <c r="D475" s="74"/>
       <c r="E475" s="17"/>
       <c r="F475" s="17"/>
       <c r="G475" s="17"/>
@@ -15227,7 +15227,7 @@
       <c r="A476" s="76"/>
       <c r="B476" s="77"/>
       <c r="C476" s="78"/>
-      <c r="D476" s="73"/>
+      <c r="D476" s="74"/>
       <c r="E476" s="17"/>
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
@@ -15236,7 +15236,7 @@
       <c r="A477" s="76"/>
       <c r="B477" s="77"/>
       <c r="C477" s="78"/>
-      <c r="D477" s="73"/>
+      <c r="D477" s="74"/>
       <c r="E477" s="17"/>
       <c r="F477" s="17"/>
       <c r="G477" s="17"/>
@@ -15245,7 +15245,7 @@
       <c r="A478" s="76"/>
       <c r="B478" s="77"/>
       <c r="C478" s="78"/>
-      <c r="D478" s="73"/>
+      <c r="D478" s="74"/>
       <c r="E478" s="17"/>
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
@@ -15254,7 +15254,7 @@
       <c r="A479" s="76"/>
       <c r="B479" s="77"/>
       <c r="C479" s="78"/>
-      <c r="D479" s="73"/>
+      <c r="D479" s="74"/>
       <c r="E479" s="17"/>
       <c r="F479" s="17"/>
       <c r="G479" s="17"/>
@@ -15263,7 +15263,7 @@
       <c r="A480" s="76"/>
       <c r="B480" s="77"/>
       <c r="C480" s="78"/>
-      <c r="D480" s="73"/>
+      <c r="D480" s="74"/>
       <c r="E480" s="17"/>
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
@@ -15272,7 +15272,7 @@
       <c r="A481" s="76"/>
       <c r="B481" s="77"/>
       <c r="C481" s="78"/>
-      <c r="D481" s="73"/>
+      <c r="D481" s="74"/>
       <c r="E481" s="17"/>
       <c r="F481" s="17"/>
       <c r="G481" s="17"/>
@@ -15281,7 +15281,7 @@
       <c r="A482" s="76"/>
       <c r="B482" s="77"/>
       <c r="C482" s="78"/>
-      <c r="D482" s="73"/>
+      <c r="D482" s="74"/>
       <c r="E482" s="17"/>
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
@@ -15290,7 +15290,7 @@
       <c r="A483" s="76"/>
       <c r="B483" s="77"/>
       <c r="C483" s="78"/>
-      <c r="D483" s="73"/>
+      <c r="D483" s="74"/>
       <c r="E483" s="17"/>
       <c r="F483" s="17"/>
       <c r="G483" s="17"/>
@@ -15299,7 +15299,7 @@
       <c r="A484" s="76"/>
       <c r="B484" s="77"/>
       <c r="C484" s="78"/>
-      <c r="D484" s="73"/>
+      <c r="D484" s="74"/>
       <c r="E484" s="17"/>
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
@@ -15308,7 +15308,7 @@
       <c r="A485" s="76"/>
       <c r="B485" s="77"/>
       <c r="C485" s="78"/>
-      <c r="D485" s="73"/>
+      <c r="D485" s="74"/>
       <c r="E485" s="17"/>
       <c r="F485" s="17"/>
       <c r="G485" s="17"/>
@@ -15317,7 +15317,7 @@
       <c r="A486" s="76"/>
       <c r="B486" s="77"/>
       <c r="C486" s="78"/>
-      <c r="D486" s="73"/>
+      <c r="D486" s="74"/>
       <c r="E486" s="17"/>
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
@@ -15326,7 +15326,7 @@
       <c r="A487" s="76"/>
       <c r="B487" s="77"/>
       <c r="C487" s="78"/>
-      <c r="D487" s="73"/>
+      <c r="D487" s="74"/>
       <c r="E487" s="17"/>
       <c r="F487" s="17"/>
       <c r="G487" s="17"/>
@@ -15335,7 +15335,7 @@
       <c r="A488" s="76"/>
       <c r="B488" s="77"/>
       <c r="C488" s="78"/>
-      <c r="D488" s="73"/>
+      <c r="D488" s="74"/>
       <c r="E488" s="17"/>
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
@@ -15344,7 +15344,7 @@
       <c r="A489" s="76"/>
       <c r="B489" s="77"/>
       <c r="C489" s="78"/>
-      <c r="D489" s="73"/>
+      <c r="D489" s="74"/>
       <c r="E489" s="17"/>
       <c r="F489" s="17"/>
       <c r="G489" s="17"/>
@@ -15353,7 +15353,7 @@
       <c r="A490" s="76"/>
       <c r="B490" s="77"/>
       <c r="C490" s="78"/>
-      <c r="D490" s="73"/>
+      <c r="D490" s="74"/>
       <c r="E490" s="17"/>
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
@@ -15362,7 +15362,7 @@
       <c r="A491" s="76"/>
       <c r="B491" s="77"/>
       <c r="C491" s="78"/>
-      <c r="D491" s="73"/>
+      <c r="D491" s="74"/>
       <c r="E491" s="17"/>
       <c r="F491" s="17"/>
       <c r="G491" s="17"/>
@@ -15371,7 +15371,7 @@
       <c r="A492" s="76"/>
       <c r="B492" s="77"/>
       <c r="C492" s="78"/>
-      <c r="D492" s="73"/>
+      <c r="D492" s="74"/>
       <c r="E492" s="17"/>
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
@@ -15380,7 +15380,7 @@
       <c r="A493" s="76"/>
       <c r="B493" s="77"/>
       <c r="C493" s="78"/>
-      <c r="D493" s="73"/>
+      <c r="D493" s="74"/>
       <c r="E493" s="17"/>
       <c r="F493" s="17"/>
       <c r="G493" s="17"/>
@@ -15389,7 +15389,7 @@
       <c r="A494" s="76"/>
       <c r="B494" s="77"/>
       <c r="C494" s="78"/>
-      <c r="D494" s="73"/>
+      <c r="D494" s="74"/>
       <c r="E494" s="17"/>
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
@@ -15398,7 +15398,7 @@
       <c r="A495" s="76"/>
       <c r="B495" s="77"/>
       <c r="C495" s="78"/>
-      <c r="D495" s="73"/>
+      <c r="D495" s="74"/>
       <c r="E495" s="17"/>
       <c r="F495" s="17"/>
       <c r="G495" s="17"/>
@@ -15407,7 +15407,7 @@
       <c r="A496" s="76"/>
       <c r="B496" s="77"/>
       <c r="C496" s="78"/>
-      <c r="D496" s="73"/>
+      <c r="D496" s="74"/>
       <c r="E496" s="17"/>
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
@@ -15416,7 +15416,7 @@
       <c r="A497" s="76"/>
       <c r="B497" s="77"/>
       <c r="C497" s="78"/>
-      <c r="D497" s="73"/>
+      <c r="D497" s="74"/>
       <c r="E497" s="17"/>
       <c r="F497" s="17"/>
       <c r="G497" s="17"/>
@@ -15425,7 +15425,7 @@
       <c r="A498" s="76"/>
       <c r="B498" s="77"/>
       <c r="C498" s="78"/>
-      <c r="D498" s="73"/>
+      <c r="D498" s="74"/>
       <c r="E498" s="17"/>
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
@@ -15434,7 +15434,7 @@
       <c r="A499" s="76"/>
       <c r="B499" s="77"/>
       <c r="C499" s="78"/>
-      <c r="D499" s="73"/>
+      <c r="D499" s="74"/>
       <c r="E499" s="17"/>
       <c r="F499" s="17"/>
       <c r="G499" s="17"/>
@@ -15443,7 +15443,7 @@
       <c r="A500" s="76"/>
       <c r="B500" s="77"/>
       <c r="C500" s="78"/>
-      <c r="D500" s="73"/>
+      <c r="D500" s="74"/>
       <c r="E500" s="17"/>
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
@@ -15452,7 +15452,7 @@
       <c r="A501" s="76"/>
       <c r="B501" s="77"/>
       <c r="C501" s="78"/>
-      <c r="D501" s="73"/>
+      <c r="D501" s="74"/>
       <c r="E501" s="17"/>
       <c r="F501" s="17"/>
       <c r="G501" s="17"/>
@@ -15461,7 +15461,7 @@
       <c r="A502" s="76"/>
       <c r="B502" s="77"/>
       <c r="C502" s="78"/>
-      <c r="D502" s="73"/>
+      <c r="D502" s="74"/>
       <c r="E502" s="17"/>
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
@@ -15470,7 +15470,7 @@
       <c r="A503" s="76"/>
       <c r="B503" s="77"/>
       <c r="C503" s="78"/>
-      <c r="D503" s="73"/>
+      <c r="D503" s="74"/>
       <c r="E503" s="17"/>
       <c r="F503" s="17"/>
       <c r="G503" s="17"/>
@@ -15479,7 +15479,7 @@
       <c r="A504" s="76"/>
       <c r="B504" s="77"/>
       <c r="C504" s="78"/>
-      <c r="D504" s="73"/>
+      <c r="D504" s="74"/>
       <c r="E504" s="17"/>
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
@@ -15488,7 +15488,7 @@
       <c r="A505" s="76"/>
       <c r="B505" s="77"/>
       <c r="C505" s="78"/>
-      <c r="D505" s="73"/>
+      <c r="D505" s="74"/>
       <c r="E505" s="17"/>
       <c r="F505" s="17"/>
       <c r="G505" s="17"/>
@@ -15497,7 +15497,7 @@
       <c r="A506" s="76"/>
       <c r="B506" s="77"/>
       <c r="C506" s="78"/>
-      <c r="D506" s="73"/>
+      <c r="D506" s="74"/>
       <c r="E506" s="17"/>
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
@@ -15506,7 +15506,7 @@
       <c r="A507" s="76"/>
       <c r="B507" s="77"/>
       <c r="C507" s="78"/>
-      <c r="D507" s="73"/>
+      <c r="D507" s="74"/>
       <c r="E507" s="17"/>
       <c r="F507" s="17"/>
       <c r="G507" s="17"/>
@@ -15515,7 +15515,7 @@
       <c r="A508" s="76"/>
       <c r="B508" s="77"/>
       <c r="C508" s="78"/>
-      <c r="D508" s="73"/>
+      <c r="D508" s="74"/>
       <c r="E508" s="17"/>
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
@@ -15524,7 +15524,7 @@
       <c r="A509" s="76"/>
       <c r="B509" s="77"/>
       <c r="C509" s="78"/>
-      <c r="D509" s="73"/>
+      <c r="D509" s="74"/>
       <c r="E509" s="17"/>
       <c r="F509" s="17"/>
       <c r="G509" s="17"/>
@@ -15533,7 +15533,7 @@
       <c r="A510" s="76"/>
       <c r="B510" s="77"/>
       <c r="C510" s="78"/>
-      <c r="D510" s="73"/>
+      <c r="D510" s="74"/>
       <c r="E510" s="17"/>
       <c r="F510" s="17"/>
       <c r="G510" s="17"/>
@@ -15542,7 +15542,7 @@
       <c r="A511" s="76"/>
       <c r="B511" s="77"/>
       <c r="C511" s="78"/>
-      <c r="D511" s="73"/>
+      <c r="D511" s="74"/>
       <c r="E511" s="17"/>
       <c r="F511" s="17"/>
       <c r="G511" s="17"/>
@@ -15560,7 +15560,7 @@
       <c r="A513" s="76"/>
       <c r="B513" s="77"/>
       <c r="C513" s="78"/>
-      <c r="D513" s="73"/>
+      <c r="D513" s="74"/>
       <c r="E513" s="17"/>
       <c r="F513" s="17"/>
       <c r="G513" s="17"/>
@@ -15569,7 +15569,7 @@
       <c r="A514" s="76"/>
       <c r="B514" s="77"/>
       <c r="C514" s="78"/>
-      <c r="D514" s="73"/>
+      <c r="D514" s="74"/>
       <c r="E514" s="17"/>
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
@@ -15578,7 +15578,7 @@
       <c r="A515" s="76"/>
       <c r="B515" s="77"/>
       <c r="C515" s="78"/>
-      <c r="D515" s="73"/>
+      <c r="D515" s="74"/>
       <c r="E515" s="17"/>
       <c r="F515" s="17"/>
       <c r="G515" s="17"/>
@@ -15587,7 +15587,7 @@
       <c r="A516" s="76"/>
       <c r="B516" s="77"/>
       <c r="C516" s="78"/>
-      <c r="D516" s="73"/>
+      <c r="D516" s="74"/>
       <c r="E516" s="17"/>
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
@@ -15596,7 +15596,7 @@
       <c r="A517" s="76"/>
       <c r="B517" s="77"/>
       <c r="C517" s="78"/>
-      <c r="D517" s="73"/>
+      <c r="D517" s="74"/>
       <c r="E517" s="17"/>
       <c r="F517" s="17"/>
       <c r="G517" s="17"/>
@@ -15605,7 +15605,7 @@
       <c r="A518" s="76"/>
       <c r="B518" s="77"/>
       <c r="C518" s="78"/>
-      <c r="D518" s="73"/>
+      <c r="D518" s="74"/>
       <c r="E518" s="17"/>
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
@@ -15614,7 +15614,7 @@
       <c r="A519" s="76"/>
       <c r="B519" s="77"/>
       <c r="C519" s="78"/>
-      <c r="D519" s="73"/>
+      <c r="D519" s="74"/>
       <c r="E519" s="17"/>
       <c r="F519" s="17"/>
       <c r="G519" s="17"/>
@@ -15623,7 +15623,7 @@
       <c r="A520" s="76"/>
       <c r="B520" s="77"/>
       <c r="C520" s="78"/>
-      <c r="D520" s="73"/>
+      <c r="D520" s="74"/>
       <c r="E520" s="17"/>
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
@@ -15631,8 +15631,8 @@
     <row r="521" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="76"/>
       <c r="B521" s="77"/>
-      <c r="C521" s="74"/>
-      <c r="D521" s="73"/>
+      <c r="C521" s="73"/>
+      <c r="D521" s="74"/>
       <c r="E521" s="17"/>
       <c r="F521" s="17"/>
       <c r="G521" s="17"/>
@@ -15640,8 +15640,8 @@
     <row r="522" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="76"/>
       <c r="B522" s="77"/>
-      <c r="C522" s="74"/>
-      <c r="D522" s="73"/>
+      <c r="C522" s="73"/>
+      <c r="D522" s="74"/>
       <c r="E522" s="17"/>
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
@@ -15649,8 +15649,8 @@
     <row r="523" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="76"/>
       <c r="B523" s="77"/>
-      <c r="C523" s="74"/>
-      <c r="D523" s="73"/>
+      <c r="C523" s="73"/>
+      <c r="D523" s="74"/>
       <c r="E523" s="17"/>
       <c r="F523" s="17"/>
       <c r="G523" s="17"/>
@@ -15658,8 +15658,8 @@
     <row r="524" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="76"/>
       <c r="B524" s="77"/>
-      <c r="C524" s="74"/>
-      <c r="D524" s="73"/>
+      <c r="C524" s="73"/>
+      <c r="D524" s="74"/>
       <c r="E524" s="17"/>
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
@@ -15667,8 +15667,8 @@
     <row r="525" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="76"/>
       <c r="B525" s="77"/>
-      <c r="C525" s="74"/>
-      <c r="D525" s="73"/>
+      <c r="C525" s="73"/>
+      <c r="D525" s="74"/>
       <c r="E525" s="17"/>
       <c r="F525" s="17"/>
       <c r="G525" s="17"/>
@@ -15676,8 +15676,8 @@
     <row r="526" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="76"/>
       <c r="B526" s="77"/>
-      <c r="C526" s="74"/>
-      <c r="D526" s="73"/>
+      <c r="C526" s="73"/>
+      <c r="D526" s="74"/>
       <c r="E526" s="17"/>
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
@@ -15685,8 +15685,8 @@
     <row r="527" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="76"/>
       <c r="B527" s="77"/>
-      <c r="C527" s="74"/>
-      <c r="D527" s="73"/>
+      <c r="C527" s="73"/>
+      <c r="D527" s="74"/>
       <c r="E527" s="17"/>
       <c r="F527" s="17"/>
       <c r="G527" s="17"/>
@@ -15694,8 +15694,8 @@
     <row r="528" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="76"/>
       <c r="B528" s="77"/>
-      <c r="C528" s="74"/>
-      <c r="D528" s="73"/>
+      <c r="C528" s="73"/>
+      <c r="D528" s="74"/>
       <c r="E528" s="17"/>
       <c r="F528" s="17"/>
       <c r="G528" s="17"/>
@@ -15703,8 +15703,8 @@
     <row r="529" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="76"/>
       <c r="B529" s="77"/>
-      <c r="C529" s="74"/>
-      <c r="D529" s="73"/>
+      <c r="C529" s="73"/>
+      <c r="D529" s="74"/>
       <c r="E529" s="17"/>
       <c r="F529" s="17"/>
       <c r="G529" s="17"/>
@@ -15841,7 +15841,6 @@
     <mergeCell ref="C369:C370"/>
     <mergeCell ref="D369:D370"/>
     <mergeCell ref="C371:C374"/>
-    <mergeCell ref="C509:C511"/>
     <mergeCell ref="D509:D511"/>
     <mergeCell ref="C513:C520"/>
     <mergeCell ref="D371:D374"/>
@@ -15888,6 +15887,7 @@
     <mergeCell ref="D499:D503"/>
     <mergeCell ref="C504:C508"/>
     <mergeCell ref="D504:D508"/>
+    <mergeCell ref="C509:C511"/>
   </mergeCells>
   <conditionalFormatting sqref="J339:J379 J385:J433 J439:J1048576 J2:J4 J43:J333 J6:J20 J23:J40">
     <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="None">

--- a/plan_phase/majid/tp_miim_tx.xlsx
+++ b/plan_phase/majid/tp_miim_tx.xlsx
@@ -21,12 +21,11 @@
     <definedName name="Scrolling_Increment">#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="395">
   <si>
     <t>Section no.</t>
   </si>
@@ -346,9 +345,6 @@
     <t>tc_tx_huge_disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmit an oversized frame (&gt;1536B) with MODER.HUGEN = 0. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Core forcefully aborts transmission precisely at the max frame length boundary, deasserts MTxEn, and sets the error bit in the TX BD. </t>
   </si>
   <si>
@@ -541,21 +537,6 @@
     <t>FLOW CONTROL &amp; DEFERRAL</t>
   </si>
   <si>
-    <t>tc_tx_pause_frame_timer</t>
-  </si>
-  <si>
-    <t>Inject an incoming valid PAUSE control MAC frame into the RX path while a TX transmission sequence is currently pending.</t>
-  </si>
-  <si>
-    <t>The TX module instantly freezes transmission scheduling for the exact duration specified by the pause timer value × slot time.</t>
-  </si>
-  <si>
-    <t>Verifies IEEE 802.3x compliance.</t>
-  </si>
-  <si>
-    <t>tx_flow_cg</t>
-  </si>
-  <si>
     <t>tc_tx_slot_timer_alignment</t>
   </si>
   <si>
@@ -1256,6 +1237,12 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit an oversized frame with MODER.HUGEN = 0. </t>
+  </si>
+  <si>
+    <t>m_wr_cfg_cov</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1526,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1741,35 +1728,65 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1777,35 +1794,14 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1816,7 +1812,127 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="zHiddenText" xfId="2"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2137,7 +2253,7 @@
   <sheetPr>
     <tabColor rgb="FF4868E5"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048556"/>
+  <dimension ref="A1:XFD1048554"/>
   <sheetFormatPr defaultColWidth="37.6640625" defaultRowHeight="28.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" style="1" customWidth="1"/>
@@ -2208,10 +2324,10 @@
       <c r="W1"/>
     </row>
     <row r="2" spans="1:23 16384:16384" ht="145.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="91">
+      <c r="A2" s="77">
         <v>1</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="78" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="14">
@@ -2243,12 +2359,12 @@
       </c>
     </row>
     <row r="3" spans="1:23 16384:16384" ht="162.30000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="91"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="92">
+      <c r="A3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="79">
         <v>2</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="4">
@@ -2274,12 +2390,12 @@
       </c>
     </row>
     <row r="4" spans="1:23 16384:16384" ht="132.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="92">
+      <c r="A4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="79">
         <v>3</v>
       </c>
-      <c r="D4" s="89"/>
+      <c r="D4" s="80"/>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2303,12 +2419,12 @@
       </c>
     </row>
     <row r="5" spans="1:23 16384:16384" s="11" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="91"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="92">
+      <c r="A5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="79">
         <v>4</v>
       </c>
-      <c r="D5" s="89"/>
+      <c r="D5" s="80"/>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2339,12 +2455,12 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23 16384:16384" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="91"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="92">
+      <c r="A6" s="77"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="79">
         <v>3</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="80" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4">
@@ -2373,12 +2489,12 @@
       </c>
     </row>
     <row r="7" spans="1:23 16384:16384" ht="100.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="92">
+      <c r="A7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="79">
         <v>4</v>
       </c>
-      <c r="D7" s="89"/>
+      <c r="D7" s="80"/>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2402,12 +2518,12 @@
       </c>
     </row>
     <row r="8" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="91"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="92">
+      <c r="A8" s="77"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="79">
         <v>4</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="80" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="4">
@@ -2433,12 +2549,12 @@
       </c>
     </row>
     <row r="9" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="92">
+      <c r="A9" s="77"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79">
         <v>5</v>
       </c>
-      <c r="D9" s="89"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2460,12 +2576,12 @@
       </c>
     </row>
     <row r="10" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="92">
+      <c r="A10" s="77"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="79">
         <v>5</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="80" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="4">
@@ -2491,12 +2607,12 @@
       </c>
     </row>
     <row r="11" spans="1:23 16384:16384" ht="208.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="92">
+      <c r="A11" s="77"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="79">
         <v>6</v>
       </c>
-      <c r="D11" s="89"/>
+      <c r="D11" s="80"/>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2524,12 +2640,12 @@
       <c r="XFD11"/>
     </row>
     <row r="12" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="92">
+      <c r="A12" s="77"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="79">
         <v>7</v>
       </c>
-      <c r="D12" s="89"/>
+      <c r="D12" s="80"/>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2553,12 +2669,12 @@
       </c>
     </row>
     <row r="13" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="92">
+      <c r="A13" s="77"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79">
         <v>8</v>
       </c>
-      <c r="D13" s="89"/>
+      <c r="D13" s="80"/>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2582,12 +2698,12 @@
       </c>
     </row>
     <row r="14" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="91"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="92">
+      <c r="A14" s="77"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="79">
         <v>6</v>
       </c>
-      <c r="D14" s="89" t="s">
+      <c r="D14" s="80" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="4">
@@ -2613,10 +2729,10 @@
       </c>
     </row>
     <row r="15" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="91"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="89"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2640,10 +2756,10 @@
       </c>
     </row>
     <row r="16" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="91"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="89"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="80"/>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10932,20 +11048,20 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="91">
+      <c r="A22" s="77">
         <v>2</v>
       </c>
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="92">
+      <c r="C22" s="79">
         <v>1</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="80" t="s">
         <v>71</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" ref="E22:E42" si="1">ROW()-21</f>
+        <f t="shared" ref="E22:E40" si="1">ROW()-21</f>
         <v>1</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -10960,20 +11076,22 @@
       <c r="I22" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="34"/>
+      <c r="J22" s="34" t="s">
+        <v>392</v>
+      </c>
       <c r="K22" s="34"/>
       <c r="L22" s="23" t="s">
         <v>76</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="91"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="89"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
       <c r="E23" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -10996,14 +11114,14 @@
         <v>18</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="91"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="89"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
       <c r="E24" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -11026,14 +11144,14 @@
         <v>18</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="91"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="89"/>
+      <c r="A25" s="77"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
       <c r="E25" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -11056,15 +11174,15 @@
         <v>18</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="91"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="89"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
       <c r="E26" s="4">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -11081,20 +11199,22 @@
       <c r="I26" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="34"/>
+      <c r="J26" s="34" t="s">
+        <v>392</v>
+      </c>
       <c r="K26" s="34"/>
       <c r="L26" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="91"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="89"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
       <c r="E27" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -11103,207 +11223,213 @@
         <v>94</v>
       </c>
       <c r="G27" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="H27" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="I27" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="J27" s="34"/>
+      <c r="J27" s="34" t="s">
+        <v>392</v>
+      </c>
       <c r="K27" s="34"/>
       <c r="L27" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="91"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="92">
+      <c r="A28" s="77"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="79">
         <v>2</v>
       </c>
-      <c r="D28" s="89" t="s">
-        <v>98</v>
+      <c r="D28" s="80" t="s">
+        <v>97</v>
       </c>
       <c r="E28" s="4">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="F28" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="H28" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="I28" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="J28" s="34"/>
+      <c r="J28" s="34" t="s">
+        <v>392</v>
+      </c>
       <c r="K28" s="34"/>
       <c r="L28" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="91"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="89"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
       <c r="E29" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="F29" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="H29" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="I29" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>106</v>
-      </c>
       <c r="J29" s="34" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="91"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="89"/>
+      <c r="A30" s="77"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="80"/>
       <c r="E30" s="4">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F30" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="H30" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="I30" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="23" t="s">
-        <v>110</v>
-      </c>
       <c r="J30" s="34" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="K30" s="34"/>
       <c r="L30" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="91"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="92">
+      <c r="A31" s="77"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79">
         <v>3</v>
       </c>
-      <c r="D31" s="89" t="s">
-        <v>111</v>
+      <c r="D31" s="80" t="s">
+        <v>110</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="F31" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="H31" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="I31" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="I31" s="23" t="s">
-        <v>115</v>
-      </c>
       <c r="J31" s="72" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="23" t="s">
         <v>32</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
     </row>
     <row r="32" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="91"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="89"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="80"/>
       <c r="E32" s="4">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="F32" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="H32" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="I32" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="I32" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="J32" s="34"/>
+      <c r="J32" s="34" t="s">
+        <v>392</v>
+      </c>
       <c r="K32" s="34"/>
       <c r="L32" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="91"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="89"/>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="77"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
       <c r="E33" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F33" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="H33" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="I33" s="23" t="s">
         <v>123</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>124</v>
       </c>
       <c r="J33" s="34"/>
       <c r="K33" s="34"/>
@@ -11311,153 +11437,153 @@
         <v>18</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="91"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="92">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="77"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="79">
         <v>4</v>
       </c>
-      <c r="D34" s="93" t="s">
-        <v>125</v>
+      <c r="D34" s="81" t="s">
+        <v>124</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="F34" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="H34" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="I34" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="J34" s="34"/>
       <c r="K34" s="34"/>
       <c r="L34" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="M34" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="M34" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="91"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="93"/>
+    </row>
+    <row r="35" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="77"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="81"/>
       <c r="E35" s="4">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="F35" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="H35" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="I35" s="23" t="s">
         <v>134</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>135</v>
       </c>
       <c r="J35" s="34"/>
       <c r="K35" s="34"/>
       <c r="L35" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="M35" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="M35" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="91"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="92"/>
-      <c r="D36" s="93"/>
+    </row>
+    <row r="36" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="77"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="81"/>
       <c r="E36" s="4">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="F36" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="H36" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="I36" s="23" t="s">
         <v>138</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>139</v>
       </c>
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
       <c r="L36" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="M36" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="M36" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="91"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="93"/>
+    </row>
+    <row r="37" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="77"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="81"/>
       <c r="E37" s="4">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="F37" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="H37" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="I37" s="23" t="s">
         <v>142</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>143</v>
       </c>
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
       <c r="L37" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="M37" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="M37" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="91"/>
-      <c r="B38" s="82"/>
-      <c r="C38" s="92"/>
-      <c r="D38" s="93"/>
+    </row>
+    <row r="38" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="77"/>
+      <c r="B38" s="78"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="81"/>
       <c r="E38" s="4">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="F38" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="H38" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="I38" s="23" t="s">
         <v>146</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>147</v>
       </c>
       <c r="J38" s="34"/>
       <c r="K38" s="34"/>
@@ -11465,63 +11591,61 @@
         <v>32</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="91"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="92"/>
-      <c r="D39" s="93"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="77"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="81"/>
       <c r="E39" s="4">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="F39" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="H39" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="H39" s="23" t="s">
+      <c r="I39" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>151</v>
       </c>
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
       <c r="L39" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A40" s="91"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="35">
-        <v>5</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>153</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="77"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="76" t="s">
+        <v>158</v>
       </c>
       <c r="E40" s="4">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J40" s="34"/>
       <c r="K40" s="34"/>
@@ -11529,105 +11653,89 @@
         <v>32</v>
       </c>
       <c r="M40" s="23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="91"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="92">
-        <v>6</v>
-      </c>
-      <c r="D41" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="I41" s="23" t="s">
         <v>163</v>
       </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+    </row>
+    <row r="41" spans="1:23" s="73" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
-      <c r="L41" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="91"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="4">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="P41" s="62"/>
+      <c r="Q41" s="62"/>
+      <c r="V41" s="62"/>
+      <c r="W41" s="62"/>
+    </row>
+    <row r="42" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="H42" s="15"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+    </row>
+    <row r="43" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="4"/>
       <c r="H43" s="15"/>
-    </row>
-    <row r="44" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+    </row>
+    <row r="44" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
       <c r="H44" s="15"/>
-    </row>
-    <row r="45" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+    </row>
+    <row r="45" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="13"/>
       <c r="C45" s="14"/>
       <c r="H45" s="15"/>
-    </row>
-    <row r="46" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+    </row>
+    <row r="46" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12"/>
       <c r="B46" s="13"/>
       <c r="C46" s="14"/>
       <c r="H46" s="15"/>
-    </row>
-    <row r="47" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+    </row>
+    <row r="47" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
       <c r="B47" s="13"/>
       <c r="C47" s="14"/>
       <c r="H47" s="15"/>
     </row>
-    <row r="48" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48" s="13"/>
       <c r="C48" s="14"/>
@@ -11828,13 +11936,21 @@
     <row r="81" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="13"/>
-      <c r="C81" s="14"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
       <c r="H81" s="15"/>
     </row>
     <row r="82" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12"/>
       <c r="B82" s="13"/>
-      <c r="C82" s="14"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
       <c r="H82" s="15"/>
     </row>
     <row r="83" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -11877,7 +11993,7 @@
       <c r="G86" s="22"/>
       <c r="H86" s="15"/>
     </row>
-    <row r="87" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12"/>
       <c r="B87" s="13"/>
       <c r="C87" s="37"/>
@@ -11897,7 +12013,7 @@
       <c r="G88" s="22"/>
       <c r="H88" s="15"/>
     </row>
-    <row r="89" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12"/>
       <c r="B89" s="13"/>
       <c r="C89" s="37"/>
@@ -11968,3755 +12084,3892 @@
       <c r="H95" s="15"/>
     </row>
     <row r="96" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="12"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="37"/>
+      <c r="A96" s="82"/>
+      <c r="B96" s="78"/>
+      <c r="C96" s="4"/>
       <c r="D96" s="38"/>
       <c r="E96" s="22"/>
       <c r="F96" s="22"/>
       <c r="G96" s="22"/>
-      <c r="H96" s="15"/>
-    </row>
-    <row r="97" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="12"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="37"/>
+    </row>
+    <row r="97" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="82"/>
+      <c r="B97" s="78"/>
+      <c r="C97" s="4"/>
       <c r="D97" s="38"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
       <c r="G97" s="22"/>
-      <c r="H97" s="15"/>
-    </row>
-    <row r="98" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="81"/>
-      <c r="B98" s="82"/>
+    </row>
+    <row r="98" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="82"/>
+      <c r="B98" s="78"/>
       <c r="C98" s="4"/>
       <c r="D98" s="38"/>
       <c r="E98" s="22"/>
       <c r="F98" s="22"/>
       <c r="G98" s="22"/>
     </row>
-    <row r="99" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="81"/>
-      <c r="B99" s="82"/>
+    <row r="99" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="82"/>
+      <c r="B99" s="78"/>
       <c r="C99" s="4"/>
       <c r="D99" s="38"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
       <c r="G99" s="22"/>
     </row>
-    <row r="100" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="81"/>
-      <c r="B100" s="82"/>
+    <row r="100" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="82"/>
+      <c r="B100" s="78"/>
       <c r="C100" s="4"/>
       <c r="D100" s="38"/>
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="22"/>
     </row>
-    <row r="101" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="81"/>
-      <c r="B101" s="82"/>
+    <row r="101" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="82"/>
+      <c r="B101" s="78"/>
       <c r="C101" s="4"/>
       <c r="D101" s="38"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
       <c r="G101" s="22"/>
     </row>
-    <row r="102" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="81"/>
-      <c r="B102" s="82"/>
+    <row r="102" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="82"/>
+      <c r="B102" s="78"/>
       <c r="C102" s="4"/>
       <c r="D102" s="38"/>
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="22"/>
     </row>
-    <row r="103" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="81"/>
-      <c r="B103" s="82"/>
+    <row r="103" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="82"/>
+      <c r="B103" s="78"/>
       <c r="C103" s="4"/>
       <c r="D103" s="38"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
       <c r="G103" s="22"/>
     </row>
-    <row r="104" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="81"/>
-      <c r="B104" s="82"/>
+    <row r="104" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="82"/>
+      <c r="B104" s="78"/>
       <c r="C104" s="4"/>
       <c r="D104" s="38"/>
       <c r="E104" s="22"/>
       <c r="F104" s="22"/>
       <c r="G104" s="22"/>
     </row>
-    <row r="105" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="81"/>
-      <c r="B105" s="82"/>
+    <row r="105" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="82"/>
+      <c r="B105" s="78"/>
       <c r="C105" s="4"/>
       <c r="D105" s="38"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
       <c r="G105" s="22"/>
     </row>
-    <row r="106" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="81"/>
-      <c r="B106" s="82"/>
+    <row r="106" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="82"/>
+      <c r="B106" s="78"/>
       <c r="C106" s="4"/>
       <c r="D106" s="38"/>
       <c r="E106" s="22"/>
       <c r="F106" s="22"/>
       <c r="G106" s="22"/>
     </row>
-    <row r="107" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="81"/>
-      <c r="B107" s="82"/>
+    <row r="107" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="82"/>
+      <c r="B107" s="78"/>
       <c r="C107" s="4"/>
       <c r="D107" s="38"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
       <c r="G107" s="22"/>
     </row>
-    <row r="108" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="81"/>
-      <c r="B108" s="82"/>
+    <row r="108" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="82"/>
+      <c r="B108" s="78"/>
       <c r="C108" s="4"/>
       <c r="D108" s="38"/>
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="22"/>
     </row>
-    <row r="109" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="81"/>
-      <c r="B109" s="82"/>
+    <row r="109" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="82"/>
+      <c r="B109" s="78"/>
       <c r="C109" s="4"/>
       <c r="D109" s="38"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
       <c r="G109" s="22"/>
     </row>
-    <row r="110" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="81"/>
-      <c r="B110" s="82"/>
+    <row r="110" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="82"/>
+      <c r="B110" s="78"/>
       <c r="C110" s="4"/>
       <c r="D110" s="38"/>
       <c r="E110" s="22"/>
       <c r="F110" s="22"/>
       <c r="G110" s="22"/>
     </row>
-    <row r="111" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="81"/>
-      <c r="B111" s="82"/>
+    <row r="111" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="82"/>
+      <c r="B111" s="78"/>
       <c r="C111" s="4"/>
       <c r="D111" s="38"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
       <c r="G111" s="22"/>
     </row>
-    <row r="112" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="81"/>
-      <c r="B112" s="82"/>
+    <row r="112" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="82"/>
+      <c r="B112" s="78"/>
       <c r="C112" s="4"/>
-      <c r="D112" s="38"/>
       <c r="E112" s="22"/>
       <c r="F112" s="22"/>
       <c r="G112" s="22"/>
     </row>
     <row r="113" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="81"/>
-      <c r="B113" s="82"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="38"/>
+      <c r="A113" s="82"/>
+      <c r="B113" s="78"/>
+      <c r="C113" s="83"/>
+      <c r="D113" s="80"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
       <c r="G113" s="22"/>
     </row>
     <row r="114" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="81"/>
-      <c r="B114" s="82"/>
-      <c r="C114" s="4"/>
+      <c r="A114" s="82"/>
+      <c r="B114" s="78"/>
+      <c r="C114" s="83"/>
+      <c r="D114" s="80"/>
       <c r="E114" s="22"/>
       <c r="F114" s="22"/>
       <c r="G114" s="22"/>
     </row>
     <row r="115" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="81"/>
-      <c r="B115" s="82"/>
-      <c r="C115" s="90"/>
-      <c r="D115" s="89"/>
+      <c r="A115" s="82"/>
+      <c r="B115" s="78"/>
+      <c r="C115" s="4"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
       <c r="G115" s="22"/>
     </row>
     <row r="116" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="81"/>
-      <c r="B116" s="82"/>
-      <c r="C116" s="90"/>
-      <c r="D116" s="89"/>
+      <c r="A116" s="82"/>
+      <c r="B116" s="78"/>
+      <c r="C116" s="83"/>
+      <c r="D116" s="80"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="22"/>
     </row>
     <row r="117" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="81"/>
-      <c r="B117" s="82"/>
-      <c r="C117" s="4"/>
+      <c r="A117" s="82"/>
+      <c r="B117" s="78"/>
+      <c r="C117" s="83"/>
+      <c r="D117" s="80"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
       <c r="G117" s="22"/>
     </row>
     <row r="118" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="81"/>
-      <c r="B118" s="82"/>
-      <c r="C118" s="90"/>
-      <c r="D118" s="89"/>
+      <c r="A118" s="82"/>
+      <c r="B118" s="78"/>
+      <c r="C118" s="83"/>
+      <c r="D118" s="80"/>
       <c r="E118" s="22"/>
       <c r="F118" s="22"/>
       <c r="G118" s="22"/>
     </row>
     <row r="119" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="81"/>
-      <c r="B119" s="82"/>
-      <c r="C119" s="90"/>
-      <c r="D119" s="89"/>
+      <c r="A119" s="82"/>
+      <c r="B119" s="78"/>
+      <c r="C119" s="83"/>
+      <c r="D119" s="80"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
       <c r="G119" s="22"/>
     </row>
     <row r="120" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="81"/>
-      <c r="B120" s="82"/>
-      <c r="C120" s="90"/>
-      <c r="D120" s="89"/>
+      <c r="A120" s="82"/>
+      <c r="B120" s="78"/>
+      <c r="C120" s="83"/>
+      <c r="D120" s="80"/>
       <c r="E120" s="22"/>
       <c r="F120" s="22"/>
       <c r="G120" s="22"/>
     </row>
     <row r="121" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="81"/>
-      <c r="B121" s="82"/>
-      <c r="C121" s="90"/>
-      <c r="D121" s="89"/>
+      <c r="A121" s="82"/>
+      <c r="B121" s="78"/>
+      <c r="C121" s="83"/>
+      <c r="D121" s="80"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
       <c r="G121" s="22"/>
     </row>
     <row r="122" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="81"/>
-      <c r="B122" s="82"/>
-      <c r="C122" s="90"/>
-      <c r="D122" s="89"/>
+      <c r="A122" s="82"/>
+      <c r="B122" s="78"/>
+      <c r="C122" s="83"/>
+      <c r="D122" s="80"/>
       <c r="E122" s="22"/>
       <c r="F122" s="22"/>
       <c r="G122" s="22"/>
     </row>
     <row r="123" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="81"/>
-      <c r="B123" s="82"/>
-      <c r="C123" s="90"/>
-      <c r="D123" s="89"/>
+      <c r="A123" s="82"/>
+      <c r="B123" s="78"/>
+      <c r="C123" s="83"/>
+      <c r="D123" s="80"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
       <c r="G123" s="22"/>
     </row>
     <row r="124" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="81"/>
-      <c r="B124" s="82"/>
-      <c r="C124" s="90"/>
-      <c r="D124" s="89"/>
+      <c r="A124" s="82"/>
+      <c r="B124" s="78"/>
+      <c r="C124" s="83"/>
+      <c r="D124" s="80"/>
       <c r="E124" s="22"/>
       <c r="F124" s="22"/>
       <c r="G124" s="22"/>
     </row>
     <row r="125" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="81"/>
-      <c r="B125" s="82"/>
-      <c r="C125" s="90"/>
-      <c r="D125" s="89"/>
+      <c r="A125" s="82"/>
+      <c r="B125" s="78"/>
+      <c r="C125" s="83"/>
+      <c r="D125" s="80"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
       <c r="G125" s="22"/>
     </row>
     <row r="126" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="81"/>
-      <c r="B126" s="82"/>
-      <c r="C126" s="90"/>
-      <c r="D126" s="89"/>
+      <c r="A126" s="82"/>
+      <c r="B126" s="78"/>
+      <c r="C126" s="83"/>
+      <c r="D126" s="80"/>
       <c r="E126" s="22"/>
       <c r="F126" s="22"/>
       <c r="G126" s="22"/>
     </row>
     <row r="127" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="81"/>
-      <c r="B127" s="82"/>
-      <c r="C127" s="90"/>
-      <c r="D127" s="89"/>
+      <c r="A127" s="82"/>
+      <c r="B127" s="78"/>
+      <c r="C127" s="83"/>
+      <c r="D127" s="80"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
       <c r="G127" s="22"/>
     </row>
     <row r="128" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="81"/>
-      <c r="B128" s="82"/>
-      <c r="C128" s="90"/>
-      <c r="D128" s="89"/>
+      <c r="A128" s="82"/>
+      <c r="B128" s="78"/>
+      <c r="C128" s="83"/>
+      <c r="D128" s="80"/>
       <c r="E128" s="22"/>
       <c r="F128" s="22"/>
       <c r="G128" s="22"/>
     </row>
     <row r="129" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="81"/>
-      <c r="B129" s="82"/>
-      <c r="C129" s="90"/>
-      <c r="D129" s="89"/>
+      <c r="A129" s="82"/>
+      <c r="B129" s="78"/>
+      <c r="C129" s="83"/>
+      <c r="D129" s="80"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
       <c r="G129" s="22"/>
     </row>
     <row r="130" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="81"/>
-      <c r="B130" s="82"/>
-      <c r="C130" s="90"/>
-      <c r="D130" s="89"/>
+      <c r="A130" s="82"/>
+      <c r="B130" s="78"/>
+      <c r="C130" s="83"/>
+      <c r="D130" s="80"/>
       <c r="E130" s="22"/>
       <c r="F130" s="22"/>
       <c r="G130" s="22"/>
     </row>
     <row r="131" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="81"/>
-      <c r="B131" s="82"/>
-      <c r="C131" s="90"/>
-      <c r="D131" s="89"/>
+      <c r="A131" s="82"/>
+      <c r="B131" s="78"/>
+      <c r="C131" s="83"/>
+      <c r="D131" s="80"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
       <c r="G131" s="22"/>
     </row>
     <row r="132" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="81"/>
-      <c r="B132" s="82"/>
-      <c r="C132" s="90"/>
-      <c r="D132" s="89"/>
+      <c r="A132" s="82"/>
+      <c r="B132" s="78"/>
+      <c r="C132" s="83"/>
+      <c r="D132" s="80"/>
       <c r="E132" s="22"/>
       <c r="F132" s="22"/>
       <c r="G132" s="22"/>
     </row>
     <row r="133" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="81"/>
-      <c r="B133" s="82"/>
-      <c r="C133" s="90"/>
-      <c r="D133" s="89"/>
+      <c r="A133" s="82"/>
+      <c r="B133" s="78"/>
+      <c r="C133" s="83"/>
+      <c r="D133" s="80"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
       <c r="G133" s="22"/>
     </row>
     <row r="134" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="81"/>
-      <c r="B134" s="82"/>
-      <c r="C134" s="90"/>
-      <c r="D134" s="89"/>
+      <c r="A134" s="82"/>
+      <c r="B134" s="78"/>
+      <c r="C134" s="83"/>
+      <c r="D134" s="80"/>
       <c r="E134" s="22"/>
       <c r="F134" s="22"/>
       <c r="G134" s="22"/>
     </row>
     <row r="135" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="81"/>
-      <c r="B135" s="82"/>
-      <c r="C135" s="90"/>
-      <c r="D135" s="89"/>
+      <c r="A135" s="82"/>
+      <c r="B135" s="78"/>
+      <c r="C135" s="83"/>
+      <c r="D135" s="80"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
       <c r="G135" s="22"/>
     </row>
     <row r="136" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="81"/>
-      <c r="B136" s="82"/>
-      <c r="C136" s="90"/>
-      <c r="D136" s="89"/>
+      <c r="A136" s="82"/>
+      <c r="B136" s="78"/>
+      <c r="C136" s="83"/>
+      <c r="D136" s="80"/>
       <c r="E136" s="22"/>
       <c r="F136" s="22"/>
       <c r="G136" s="22"/>
     </row>
     <row r="137" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="81"/>
-      <c r="B137" s="82"/>
-      <c r="C137" s="90"/>
-      <c r="D137" s="89"/>
+      <c r="A137" s="82"/>
+      <c r="B137" s="78"/>
+      <c r="C137" s="83"/>
+      <c r="D137" s="80"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="22"/>
     </row>
     <row r="138" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="81"/>
-      <c r="B138" s="82"/>
-      <c r="C138" s="90"/>
-      <c r="D138" s="89"/>
+      <c r="A138" s="82"/>
+      <c r="B138" s="78"/>
+      <c r="C138" s="83"/>
+      <c r="D138" s="80"/>
       <c r="E138" s="22"/>
       <c r="F138" s="22"/>
       <c r="G138" s="22"/>
     </row>
     <row r="139" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="81"/>
-      <c r="B139" s="82"/>
-      <c r="C139" s="90"/>
-      <c r="D139" s="89"/>
+      <c r="A139" s="82"/>
+      <c r="B139" s="78"/>
+      <c r="C139" s="83"/>
+      <c r="D139" s="80"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
       <c r="G139" s="22"/>
     </row>
     <row r="140" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="81"/>
-      <c r="B140" s="82"/>
-      <c r="C140" s="90"/>
-      <c r="D140" s="89"/>
+      <c r="A140" s="82"/>
+      <c r="B140" s="78"/>
+      <c r="C140" s="83"/>
+      <c r="D140" s="80"/>
       <c r="E140" s="22"/>
       <c r="F140" s="22"/>
       <c r="G140" s="22"/>
     </row>
     <row r="141" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="81"/>
-      <c r="B141" s="82"/>
-      <c r="C141" s="90"/>
-      <c r="D141" s="89"/>
+      <c r="A141" s="82"/>
+      <c r="B141" s="78"/>
+      <c r="C141" s="83"/>
+      <c r="D141" s="80"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
       <c r="G141" s="22"/>
     </row>
     <row r="142" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="81"/>
-      <c r="B142" s="82"/>
-      <c r="C142" s="90"/>
-      <c r="D142" s="89"/>
+      <c r="A142" s="82"/>
+      <c r="B142" s="78"/>
+      <c r="C142" s="83"/>
+      <c r="D142" s="80"/>
       <c r="E142" s="22"/>
       <c r="F142" s="22"/>
       <c r="G142" s="22"/>
     </row>
     <row r="143" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="81"/>
-      <c r="B143" s="82"/>
-      <c r="C143" s="90"/>
-      <c r="D143" s="89"/>
+      <c r="A143" s="82"/>
+      <c r="B143" s="78"/>
+      <c r="C143" s="83"/>
+      <c r="D143" s="80"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
       <c r="G143" s="22"/>
     </row>
     <row r="144" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="81"/>
-      <c r="B144" s="82"/>
-      <c r="C144" s="90"/>
-      <c r="D144" s="89"/>
+      <c r="A144" s="82"/>
+      <c r="B144" s="78"/>
+      <c r="C144" s="83"/>
+      <c r="D144" s="80"/>
       <c r="E144" s="22"/>
       <c r="F144" s="22"/>
       <c r="G144" s="22"/>
     </row>
     <row r="145" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="81"/>
-      <c r="B145" s="82"/>
-      <c r="C145" s="90"/>
-      <c r="D145" s="89"/>
+      <c r="A145" s="82"/>
+      <c r="B145" s="78"/>
+      <c r="C145" s="83"/>
+      <c r="D145" s="80"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="22"/>
     </row>
     <row r="146" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="81"/>
-      <c r="B146" s="82"/>
-      <c r="C146" s="90"/>
-      <c r="D146" s="89"/>
+      <c r="A146" s="82"/>
+      <c r="B146" s="78"/>
+      <c r="C146" s="83"/>
+      <c r="D146" s="80"/>
       <c r="E146" s="22"/>
       <c r="F146" s="22"/>
       <c r="G146" s="22"/>
     </row>
     <row r="147" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="81"/>
-      <c r="B147" s="82"/>
-      <c r="C147" s="90"/>
-      <c r="D147" s="89"/>
+      <c r="A147" s="82"/>
+      <c r="B147" s="78"/>
+      <c r="C147" s="83"/>
+      <c r="D147" s="80"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
       <c r="G147" s="22"/>
     </row>
     <row r="148" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="81"/>
-      <c r="B148" s="82"/>
-      <c r="C148" s="90"/>
-      <c r="D148" s="89"/>
+      <c r="A148" s="82"/>
+      <c r="B148" s="78"/>
+      <c r="C148" s="83"/>
+      <c r="D148" s="80"/>
       <c r="E148" s="22"/>
       <c r="F148" s="22"/>
       <c r="G148" s="22"/>
     </row>
     <row r="149" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="81"/>
-      <c r="B149" s="82"/>
-      <c r="C149" s="90"/>
-      <c r="D149" s="89"/>
+      <c r="A149" s="82"/>
+      <c r="B149" s="78"/>
+      <c r="C149" s="83"/>
+      <c r="D149" s="80"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
       <c r="G149" s="22"/>
     </row>
     <row r="150" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="81"/>
-      <c r="B150" s="82"/>
-      <c r="C150" s="90"/>
-      <c r="D150" s="89"/>
+      <c r="A150" s="82"/>
+      <c r="B150" s="78"/>
+      <c r="C150" s="83"/>
+      <c r="D150" s="80"/>
       <c r="E150" s="22"/>
       <c r="F150" s="22"/>
       <c r="G150" s="22"/>
     </row>
     <row r="151" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="81"/>
-      <c r="B151" s="82"/>
-      <c r="C151" s="90"/>
-      <c r="D151" s="89"/>
+      <c r="A151" s="82"/>
+      <c r="B151" s="78"/>
+      <c r="C151" s="83"/>
+      <c r="D151" s="80"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
       <c r="G151" s="22"/>
     </row>
     <row r="152" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="81"/>
-      <c r="B152" s="82"/>
-      <c r="C152" s="90"/>
-      <c r="D152" s="89"/>
+      <c r="A152" s="82"/>
+      <c r="B152" s="78"/>
+      <c r="C152" s="83"/>
+      <c r="D152" s="80"/>
       <c r="E152" s="22"/>
       <c r="F152" s="22"/>
       <c r="G152" s="22"/>
     </row>
     <row r="153" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="81"/>
-      <c r="B153" s="82"/>
-      <c r="C153" s="90"/>
-      <c r="D153" s="89"/>
+      <c r="A153" s="82"/>
+      <c r="B153" s="78"/>
+      <c r="C153" s="83"/>
+      <c r="D153" s="80"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="22"/>
     </row>
     <row r="154" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="81"/>
-      <c r="B154" s="82"/>
-      <c r="C154" s="90"/>
-      <c r="D154" s="89"/>
+      <c r="A154" s="82"/>
+      <c r="B154" s="78"/>
+      <c r="C154" s="83"/>
+      <c r="D154" s="80"/>
       <c r="E154" s="22"/>
       <c r="F154" s="22"/>
       <c r="G154" s="22"/>
     </row>
     <row r="155" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="81"/>
-      <c r="B155" s="82"/>
-      <c r="C155" s="90"/>
-      <c r="D155" s="89"/>
+      <c r="A155" s="82"/>
+      <c r="B155" s="78"/>
+      <c r="C155" s="83"/>
+      <c r="D155" s="80"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
       <c r="G155" s="22"/>
     </row>
     <row r="156" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="81"/>
-      <c r="B156" s="82"/>
-      <c r="C156" s="90"/>
-      <c r="D156" s="89"/>
+      <c r="A156" s="82"/>
+      <c r="B156" s="78"/>
+      <c r="C156" s="83"/>
+      <c r="D156" s="80"/>
       <c r="E156" s="22"/>
       <c r="F156" s="22"/>
       <c r="G156" s="22"/>
     </row>
     <row r="157" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="81"/>
-      <c r="B157" s="82"/>
-      <c r="C157" s="90"/>
-      <c r="D157" s="89"/>
+      <c r="A157" s="82"/>
+      <c r="B157" s="78"/>
+      <c r="C157" s="83"/>
+      <c r="D157" s="80"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
       <c r="G157" s="22"/>
     </row>
     <row r="158" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="81"/>
-      <c r="B158" s="82"/>
-      <c r="C158" s="90"/>
-      <c r="D158" s="89"/>
+      <c r="A158" s="82"/>
+      <c r="B158" s="78"/>
+      <c r="C158" s="83"/>
+      <c r="D158" s="80"/>
       <c r="E158" s="22"/>
       <c r="F158" s="22"/>
       <c r="G158" s="22"/>
     </row>
     <row r="159" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="81"/>
-      <c r="B159" s="82"/>
-      <c r="C159" s="90"/>
-      <c r="D159" s="89"/>
+      <c r="A159" s="82"/>
+      <c r="B159" s="78"/>
+      <c r="C159" s="83"/>
+      <c r="D159" s="80"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
       <c r="G159" s="22"/>
     </row>
     <row r="160" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="81"/>
-      <c r="B160" s="82"/>
-      <c r="C160" s="90"/>
-      <c r="D160" s="89"/>
+      <c r="A160" s="82"/>
+      <c r="B160" s="78"/>
+      <c r="C160" s="83"/>
+      <c r="D160" s="80"/>
       <c r="E160" s="22"/>
       <c r="F160" s="22"/>
       <c r="G160" s="22"/>
     </row>
     <row r="161" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="81"/>
-      <c r="B161" s="82"/>
-      <c r="C161" s="90"/>
-      <c r="D161" s="89"/>
+      <c r="A161" s="82"/>
+      <c r="B161" s="78"/>
+      <c r="C161" s="83"/>
+      <c r="D161" s="80"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="22"/>
     </row>
     <row r="162" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="81"/>
-      <c r="B162" s="82"/>
-      <c r="C162" s="90"/>
-      <c r="D162" s="89"/>
+      <c r="A162" s="82"/>
+      <c r="B162" s="78"/>
+      <c r="C162" s="83"/>
+      <c r="D162" s="80"/>
       <c r="E162" s="22"/>
       <c r="F162" s="22"/>
       <c r="G162" s="22"/>
     </row>
     <row r="163" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="81"/>
-      <c r="B163" s="82"/>
-      <c r="C163" s="90"/>
-      <c r="D163" s="89"/>
+      <c r="A163" s="82"/>
+      <c r="B163" s="78"/>
+      <c r="C163" s="83"/>
+      <c r="D163" s="80"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
       <c r="G163" s="22"/>
     </row>
     <row r="164" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="81"/>
-      <c r="B164" s="82"/>
-      <c r="C164" s="90"/>
-      <c r="D164" s="89"/>
+      <c r="A164" s="82"/>
+      <c r="B164" s="78"/>
+      <c r="C164" s="83"/>
+      <c r="D164" s="80"/>
       <c r="E164" s="22"/>
       <c r="F164" s="22"/>
       <c r="G164" s="22"/>
     </row>
     <row r="165" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="81"/>
-      <c r="B165" s="82"/>
-      <c r="C165" s="90"/>
-      <c r="D165" s="89"/>
+      <c r="A165" s="82"/>
+      <c r="B165" s="78"/>
+      <c r="C165" s="83"/>
+      <c r="D165" s="80"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
       <c r="G165" s="22"/>
     </row>
     <row r="166" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="81"/>
-      <c r="B166" s="82"/>
-      <c r="C166" s="90"/>
-      <c r="D166" s="89"/>
+      <c r="A166" s="82"/>
+      <c r="B166" s="78"/>
+      <c r="C166" s="83"/>
+      <c r="D166" s="80"/>
       <c r="E166" s="22"/>
       <c r="F166" s="22"/>
       <c r="G166" s="22"/>
     </row>
     <row r="167" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="81"/>
-      <c r="B167" s="82"/>
-      <c r="C167" s="90"/>
-      <c r="D167" s="89"/>
+      <c r="A167" s="82"/>
+      <c r="B167" s="78"/>
+      <c r="C167" s="83"/>
+      <c r="D167" s="80"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
       <c r="G167" s="22"/>
     </row>
     <row r="168" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="81"/>
-      <c r="B168" s="82"/>
-      <c r="C168" s="90"/>
-      <c r="D168" s="89"/>
+      <c r="A168" s="82"/>
+      <c r="B168" s="78"/>
+      <c r="C168" s="83"/>
+      <c r="D168" s="80"/>
       <c r="E168" s="22"/>
       <c r="F168" s="22"/>
       <c r="G168" s="22"/>
     </row>
     <row r="169" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="81"/>
-      <c r="B169" s="82"/>
-      <c r="C169" s="90"/>
-      <c r="D169" s="89"/>
+      <c r="A169" s="82"/>
+      <c r="B169" s="78"/>
+      <c r="C169" s="83"/>
+      <c r="D169" s="80"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
       <c r="G169" s="22"/>
     </row>
     <row r="170" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="81"/>
-      <c r="B170" s="82"/>
-      <c r="C170" s="90"/>
-      <c r="D170" s="89"/>
+      <c r="A170" s="82"/>
+      <c r="B170" s="78"/>
+      <c r="C170" s="83"/>
+      <c r="D170" s="80"/>
       <c r="E170" s="22"/>
       <c r="F170" s="22"/>
       <c r="G170" s="22"/>
     </row>
     <row r="171" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="81"/>
-      <c r="B171" s="82"/>
-      <c r="C171" s="90"/>
-      <c r="D171" s="89"/>
+      <c r="A171" s="82"/>
+      <c r="B171" s="78"/>
+      <c r="C171" s="83"/>
+      <c r="D171" s="80"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
       <c r="G171" s="22"/>
     </row>
     <row r="172" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="81"/>
-      <c r="B172" s="82"/>
-      <c r="C172" s="90"/>
-      <c r="D172" s="89"/>
+      <c r="A172" s="82"/>
+      <c r="B172" s="78"/>
+      <c r="C172" s="83"/>
+      <c r="D172" s="80"/>
       <c r="E172" s="22"/>
       <c r="F172" s="22"/>
       <c r="G172" s="22"/>
     </row>
     <row r="173" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="81"/>
-      <c r="B173" s="82"/>
-      <c r="C173" s="90"/>
-      <c r="D173" s="89"/>
+      <c r="A173" s="82"/>
+      <c r="B173" s="78"/>
+      <c r="C173" s="83"/>
+      <c r="D173" s="80"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
       <c r="G173" s="22"/>
     </row>
     <row r="174" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="81"/>
-      <c r="B174" s="82"/>
-      <c r="C174" s="90"/>
-      <c r="D174" s="89"/>
+      <c r="A174" s="82"/>
+      <c r="B174" s="78"/>
+      <c r="C174" s="83"/>
+      <c r="D174" s="80"/>
       <c r="E174" s="22"/>
       <c r="F174" s="22"/>
       <c r="G174" s="22"/>
     </row>
     <row r="175" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="81"/>
-      <c r="B175" s="82"/>
-      <c r="C175" s="90"/>
-      <c r="D175" s="89"/>
+      <c r="A175" s="82"/>
+      <c r="B175" s="78"/>
+      <c r="C175" s="83"/>
+      <c r="D175" s="80"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
       <c r="G175" s="22"/>
     </row>
     <row r="176" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="81"/>
-      <c r="B176" s="82"/>
-      <c r="C176" s="90"/>
-      <c r="D176" s="89"/>
+      <c r="A176" s="82"/>
+      <c r="B176" s="78"/>
+      <c r="C176" s="83"/>
+      <c r="D176" s="80"/>
       <c r="E176" s="22"/>
       <c r="F176" s="22"/>
       <c r="G176" s="22"/>
     </row>
     <row r="177" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="81"/>
-      <c r="B177" s="82"/>
-      <c r="C177" s="90"/>
-      <c r="D177" s="89"/>
+      <c r="A177" s="82"/>
+      <c r="B177" s="78"/>
+      <c r="C177" s="83"/>
+      <c r="D177" s="80"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="22"/>
     </row>
     <row r="178" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="81"/>
-      <c r="B178" s="82"/>
-      <c r="C178" s="90"/>
-      <c r="D178" s="89"/>
+      <c r="A178" s="82"/>
+      <c r="B178" s="78"/>
+      <c r="C178" s="83"/>
+      <c r="D178" s="80"/>
       <c r="E178" s="22"/>
       <c r="F178" s="22"/>
       <c r="G178" s="22"/>
     </row>
     <row r="179" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="81"/>
-      <c r="B179" s="82"/>
-      <c r="C179" s="90"/>
-      <c r="D179" s="89"/>
+      <c r="A179" s="82"/>
+      <c r="B179" s="78"/>
+      <c r="C179" s="83"/>
+      <c r="D179" s="80"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
       <c r="G179" s="22"/>
     </row>
     <row r="180" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="81"/>
-      <c r="B180" s="82"/>
-      <c r="C180" s="90"/>
-      <c r="D180" s="89"/>
+      <c r="A180" s="82"/>
+      <c r="B180" s="78"/>
+      <c r="C180" s="83"/>
+      <c r="D180" s="80"/>
       <c r="E180" s="22"/>
       <c r="F180" s="22"/>
       <c r="G180" s="22"/>
     </row>
     <row r="181" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="81"/>
-      <c r="B181" s="82"/>
-      <c r="C181" s="90"/>
-      <c r="D181" s="89"/>
+      <c r="A181" s="82"/>
+      <c r="B181" s="78"/>
+      <c r="C181" s="83"/>
+      <c r="D181" s="80"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
       <c r="G181" s="22"/>
     </row>
     <row r="182" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="81"/>
-      <c r="B182" s="82"/>
-      <c r="C182" s="90"/>
-      <c r="D182" s="89"/>
+      <c r="A182" s="82"/>
+      <c r="B182" s="78"/>
+      <c r="C182" s="83"/>
+      <c r="D182" s="80"/>
       <c r="E182" s="22"/>
       <c r="F182" s="22"/>
       <c r="G182" s="22"/>
     </row>
     <row r="183" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="81"/>
-      <c r="B183" s="82"/>
-      <c r="C183" s="90"/>
-      <c r="D183" s="89"/>
+      <c r="A183" s="82"/>
+      <c r="B183" s="78"/>
+      <c r="C183" s="83"/>
+      <c r="D183" s="80"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
       <c r="G183" s="22"/>
     </row>
     <row r="184" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="81"/>
-      <c r="B184" s="82"/>
-      <c r="C184" s="90"/>
-      <c r="D184" s="89"/>
+      <c r="A184" s="82"/>
+      <c r="B184" s="78"/>
+      <c r="C184" s="83"/>
+      <c r="D184" s="80"/>
       <c r="E184" s="22"/>
       <c r="F184" s="22"/>
       <c r="G184" s="22"/>
     </row>
     <row r="185" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="81"/>
-      <c r="B185" s="82"/>
-      <c r="C185" s="90"/>
-      <c r="D185" s="89"/>
+      <c r="A185" s="82"/>
+      <c r="B185" s="78"/>
+      <c r="C185" s="83"/>
+      <c r="D185" s="80"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="22"/>
     </row>
     <row r="186" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="81"/>
-      <c r="B186" s="82"/>
-      <c r="C186" s="90"/>
-      <c r="D186" s="89"/>
+      <c r="A186" s="82"/>
+      <c r="B186" s="78"/>
+      <c r="C186" s="83"/>
+      <c r="D186" s="80"/>
       <c r="E186" s="22"/>
       <c r="F186" s="22"/>
       <c r="G186" s="22"/>
     </row>
     <row r="187" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="81"/>
-      <c r="B187" s="82"/>
-      <c r="C187" s="90"/>
-      <c r="D187" s="89"/>
+      <c r="A187" s="82"/>
+      <c r="B187" s="78"/>
+      <c r="C187" s="83"/>
+      <c r="D187" s="80"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
       <c r="G187" s="22"/>
     </row>
     <row r="188" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="81"/>
-      <c r="B188" s="82"/>
-      <c r="C188" s="90"/>
-      <c r="D188" s="89"/>
+      <c r="A188" s="82"/>
+      <c r="B188" s="78"/>
+      <c r="C188" s="83"/>
+      <c r="D188" s="80"/>
       <c r="E188" s="22"/>
       <c r="F188" s="22"/>
       <c r="G188" s="22"/>
     </row>
     <row r="189" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="81"/>
-      <c r="B189" s="82"/>
-      <c r="C189" s="90"/>
-      <c r="D189" s="89"/>
+      <c r="A189" s="82"/>
+      <c r="B189" s="78"/>
+      <c r="C189" s="83"/>
+      <c r="D189" s="80"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
       <c r="G189" s="22"/>
     </row>
     <row r="190" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="81"/>
-      <c r="B190" s="82"/>
-      <c r="C190" s="90"/>
-      <c r="D190" s="89"/>
+      <c r="A190" s="82"/>
+      <c r="B190" s="78"/>
+      <c r="C190" s="83"/>
+      <c r="D190" s="80"/>
       <c r="E190" s="22"/>
       <c r="F190" s="22"/>
       <c r="G190" s="22"/>
     </row>
     <row r="191" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="81"/>
-      <c r="B191" s="82"/>
-      <c r="C191" s="90"/>
-      <c r="D191" s="89"/>
+      <c r="A191" s="82"/>
+      <c r="B191" s="78"/>
+      <c r="C191" s="83"/>
+      <c r="D191" s="80"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
       <c r="G191" s="22"/>
     </row>
     <row r="192" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="81"/>
-      <c r="B192" s="82"/>
-      <c r="C192" s="90"/>
-      <c r="D192" s="89"/>
+      <c r="A192" s="82"/>
+      <c r="B192" s="78"/>
+      <c r="C192" s="83"/>
+      <c r="D192" s="80"/>
       <c r="E192" s="22"/>
       <c r="F192" s="22"/>
       <c r="G192" s="22"/>
     </row>
     <row r="193" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="81"/>
-      <c r="B193" s="82"/>
-      <c r="C193" s="90"/>
-      <c r="D193" s="89"/>
+      <c r="A193" s="82"/>
+      <c r="B193" s="78"/>
+      <c r="C193" s="83"/>
+      <c r="D193" s="80"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
       <c r="G193" s="22"/>
     </row>
     <row r="194" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="81"/>
-      <c r="B194" s="82"/>
-      <c r="C194" s="90"/>
-      <c r="D194" s="89"/>
+      <c r="A194" s="82"/>
+      <c r="B194" s="78"/>
+      <c r="C194" s="83"/>
+      <c r="D194" s="80"/>
       <c r="E194" s="22"/>
       <c r="F194" s="22"/>
       <c r="G194" s="22"/>
     </row>
     <row r="195" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="81"/>
-      <c r="B195" s="82"/>
-      <c r="C195" s="90"/>
-      <c r="D195" s="89"/>
+      <c r="A195" s="82"/>
+      <c r="B195" s="78"/>
+      <c r="C195" s="83"/>
+      <c r="D195" s="80"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
       <c r="G195" s="22"/>
     </row>
     <row r="196" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="81"/>
-      <c r="B196" s="82"/>
-      <c r="C196" s="90"/>
-      <c r="D196" s="89"/>
+      <c r="A196" s="82"/>
+      <c r="B196" s="78"/>
+      <c r="C196" s="83"/>
+      <c r="D196" s="80"/>
       <c r="E196" s="22"/>
       <c r="F196" s="22"/>
       <c r="G196" s="22"/>
     </row>
     <row r="197" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="81"/>
-      <c r="B197" s="82"/>
-      <c r="C197" s="90"/>
-      <c r="D197" s="89"/>
+      <c r="A197" s="82"/>
+      <c r="B197" s="78"/>
+      <c r="C197" s="83"/>
+      <c r="D197" s="80"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
       <c r="G197" s="22"/>
     </row>
     <row r="198" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="81"/>
-      <c r="B198" s="82"/>
-      <c r="C198" s="90"/>
-      <c r="D198" s="89"/>
+      <c r="A198" s="82"/>
+      <c r="B198" s="78"/>
+      <c r="C198" s="83"/>
+      <c r="D198" s="80"/>
       <c r="E198" s="22"/>
       <c r="F198" s="22"/>
       <c r="G198" s="22"/>
     </row>
     <row r="199" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="81"/>
-      <c r="B199" s="82"/>
-      <c r="C199" s="90"/>
-      <c r="D199" s="89"/>
+      <c r="A199" s="82"/>
+      <c r="B199" s="78"/>
+      <c r="C199" s="83"/>
+      <c r="D199" s="80"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
       <c r="G199" s="22"/>
     </row>
     <row r="200" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="81"/>
-      <c r="B200" s="82"/>
-      <c r="C200" s="90"/>
-      <c r="D200" s="89"/>
+      <c r="A200" s="82"/>
+      <c r="B200" s="78"/>
+      <c r="C200" s="83"/>
+      <c r="D200" s="80"/>
       <c r="E200" s="22"/>
       <c r="F200" s="22"/>
       <c r="G200" s="22"/>
     </row>
     <row r="201" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="81"/>
-      <c r="B201" s="82"/>
-      <c r="C201" s="90"/>
-      <c r="D201" s="89"/>
+      <c r="A201" s="82"/>
+      <c r="B201" s="78"/>
+      <c r="C201" s="83"/>
+      <c r="D201" s="80"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="22"/>
     </row>
     <row r="202" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="81"/>
-      <c r="B202" s="82"/>
-      <c r="C202" s="90"/>
-      <c r="D202" s="89"/>
+      <c r="A202" s="82"/>
+      <c r="B202" s="78"/>
+      <c r="C202" s="83"/>
+      <c r="D202" s="80"/>
       <c r="E202" s="22"/>
       <c r="F202" s="22"/>
       <c r="G202" s="22"/>
     </row>
     <row r="203" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="81"/>
-      <c r="B203" s="82"/>
-      <c r="C203" s="90"/>
-      <c r="D203" s="89"/>
+      <c r="A203" s="82"/>
+      <c r="B203" s="78"/>
+      <c r="C203" s="83"/>
+      <c r="D203" s="80"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
       <c r="G203" s="22"/>
     </row>
     <row r="204" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="81"/>
-      <c r="B204" s="82"/>
-      <c r="C204" s="90"/>
-      <c r="D204" s="89"/>
+      <c r="A204" s="82"/>
+      <c r="B204" s="78"/>
+      <c r="C204" s="83"/>
+      <c r="D204" s="80"/>
       <c r="E204" s="22"/>
       <c r="F204" s="22"/>
       <c r="G204" s="22"/>
     </row>
     <row r="205" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="81"/>
-      <c r="B205" s="82"/>
-      <c r="C205" s="90"/>
-      <c r="D205" s="89"/>
+      <c r="A205" s="82"/>
+      <c r="B205" s="78"/>
+      <c r="C205" s="83"/>
+      <c r="D205" s="80"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
       <c r="G205" s="22"/>
     </row>
     <row r="206" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="81"/>
-      <c r="B206" s="82"/>
-      <c r="C206" s="90"/>
-      <c r="D206" s="89"/>
+      <c r="A206" s="82"/>
+      <c r="B206" s="78"/>
+      <c r="C206" s="83"/>
+      <c r="D206" s="80"/>
       <c r="E206" s="22"/>
       <c r="F206" s="22"/>
       <c r="G206" s="22"/>
     </row>
     <row r="207" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="81"/>
-      <c r="B207" s="82"/>
-      <c r="C207" s="90"/>
-      <c r="D207" s="89"/>
+      <c r="A207" s="82"/>
+      <c r="B207" s="78"/>
+      <c r="C207" s="83"/>
+      <c r="D207" s="80"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
       <c r="G207" s="22"/>
     </row>
     <row r="208" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="81"/>
-      <c r="B208" s="82"/>
-      <c r="C208" s="90"/>
-      <c r="D208" s="89"/>
+      <c r="A208" s="82"/>
+      <c r="B208" s="78"/>
+      <c r="C208" s="83"/>
+      <c r="D208" s="80"/>
       <c r="E208" s="22"/>
       <c r="F208" s="22"/>
       <c r="G208" s="22"/>
     </row>
     <row r="209" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="81"/>
-      <c r="B209" s="82"/>
-      <c r="C209" s="90"/>
-      <c r="D209" s="89"/>
+      <c r="A209" s="82"/>
+      <c r="B209" s="78"/>
+      <c r="C209" s="83"/>
+      <c r="D209" s="80"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="22"/>
     </row>
     <row r="210" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="81"/>
-      <c r="B210" s="82"/>
-      <c r="C210" s="90"/>
-      <c r="D210" s="89"/>
+      <c r="A210" s="82"/>
+      <c r="B210" s="78"/>
+      <c r="C210" s="83"/>
+      <c r="D210" s="80"/>
       <c r="E210" s="22"/>
       <c r="F210" s="22"/>
       <c r="G210" s="22"/>
     </row>
     <row r="211" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="81"/>
-      <c r="B211" s="82"/>
-      <c r="C211" s="90"/>
-      <c r="D211" s="89"/>
+      <c r="A211" s="82"/>
+      <c r="B211" s="78"/>
+      <c r="C211" s="83"/>
+      <c r="D211" s="80"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
       <c r="G211" s="22"/>
     </row>
     <row r="212" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="81"/>
-      <c r="B212" s="82"/>
-      <c r="C212" s="90"/>
-      <c r="D212" s="89"/>
+      <c r="A212" s="82"/>
+      <c r="B212" s="78"/>
+      <c r="C212" s="83"/>
+      <c r="D212" s="80"/>
       <c r="E212" s="22"/>
       <c r="F212" s="22"/>
       <c r="G212" s="22"/>
     </row>
     <row r="213" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="81"/>
-      <c r="B213" s="82"/>
-      <c r="C213" s="90"/>
-      <c r="D213" s="89"/>
+      <c r="A213" s="82"/>
+      <c r="B213" s="78"/>
+      <c r="C213" s="83"/>
+      <c r="D213" s="80"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
       <c r="G213" s="22"/>
     </row>
     <row r="214" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="81"/>
-      <c r="B214" s="82"/>
-      <c r="C214" s="90"/>
-      <c r="D214" s="89"/>
+      <c r="A214" s="82"/>
+      <c r="B214" s="78"/>
+      <c r="C214" s="83"/>
+      <c r="D214" s="80"/>
       <c r="E214" s="22"/>
       <c r="F214" s="22"/>
       <c r="G214" s="22"/>
     </row>
     <row r="215" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="81"/>
-      <c r="B215" s="82"/>
-      <c r="C215" s="90"/>
-      <c r="D215" s="89"/>
+      <c r="A215" s="82"/>
+      <c r="B215" s="78"/>
+      <c r="C215" s="83"/>
+      <c r="D215" s="80"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
       <c r="G215" s="22"/>
     </row>
     <row r="216" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="81"/>
-      <c r="B216" s="82"/>
-      <c r="C216" s="90"/>
-      <c r="D216" s="89"/>
+      <c r="A216" s="82"/>
+      <c r="B216" s="78"/>
+      <c r="C216" s="83"/>
+      <c r="D216" s="80"/>
       <c r="E216" s="22"/>
       <c r="F216" s="22"/>
       <c r="G216" s="22"/>
     </row>
     <row r="217" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="81"/>
-      <c r="B217" s="82"/>
-      <c r="C217" s="90"/>
-      <c r="D217" s="89"/>
+      <c r="A217" s="82"/>
+      <c r="B217" s="78"/>
+      <c r="C217" s="83"/>
+      <c r="D217" s="80"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="22"/>
     </row>
     <row r="218" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="81"/>
-      <c r="B218" s="82"/>
-      <c r="C218" s="90"/>
-      <c r="D218" s="89"/>
+      <c r="A218" s="82"/>
+      <c r="B218" s="78"/>
+      <c r="C218" s="83"/>
+      <c r="D218" s="80"/>
       <c r="E218" s="22"/>
       <c r="F218" s="22"/>
       <c r="G218" s="22"/>
     </row>
     <row r="219" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="81"/>
-      <c r="B219" s="82"/>
-      <c r="C219" s="90"/>
-      <c r="D219" s="89"/>
+      <c r="A219" s="82"/>
+      <c r="B219" s="78"/>
+      <c r="C219" s="83"/>
+      <c r="D219" s="80"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
       <c r="G219" s="22"/>
     </row>
     <row r="220" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="81"/>
-      <c r="B220" s="82"/>
-      <c r="C220" s="90"/>
-      <c r="D220" s="89"/>
+      <c r="A220" s="82"/>
+      <c r="B220" s="78"/>
+      <c r="C220" s="83"/>
+      <c r="D220" s="80"/>
       <c r="E220" s="22"/>
       <c r="F220" s="22"/>
       <c r="G220" s="22"/>
     </row>
     <row r="221" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="81"/>
-      <c r="B221" s="82"/>
-      <c r="C221" s="90"/>
-      <c r="D221" s="89"/>
+      <c r="A221" s="82"/>
+      <c r="B221" s="78"/>
+      <c r="C221" s="83"/>
+      <c r="D221" s="80"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
       <c r="G221" s="22"/>
     </row>
     <row r="222" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="81"/>
-      <c r="B222" s="82"/>
-      <c r="C222" s="90"/>
-      <c r="D222" s="89"/>
+      <c r="A222" s="82"/>
+      <c r="B222" s="78"/>
+      <c r="C222" s="83"/>
+      <c r="D222" s="80"/>
       <c r="E222" s="22"/>
       <c r="F222" s="22"/>
       <c r="G222" s="22"/>
     </row>
     <row r="223" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="81"/>
-      <c r="B223" s="82"/>
-      <c r="C223" s="90"/>
-      <c r="D223" s="89"/>
+      <c r="A223" s="82"/>
+      <c r="B223" s="78"/>
+      <c r="C223" s="83"/>
+      <c r="D223" s="80"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
       <c r="G223" s="22"/>
     </row>
     <row r="224" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="81"/>
-      <c r="B224" s="82"/>
-      <c r="C224" s="90"/>
-      <c r="D224" s="89"/>
+      <c r="A224" s="82"/>
+      <c r="B224" s="78"/>
+      <c r="C224" s="83"/>
+      <c r="D224" s="80"/>
       <c r="E224" s="22"/>
       <c r="F224" s="22"/>
       <c r="G224" s="22"/>
     </row>
-    <row r="225" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="81"/>
-      <c r="B225" s="82"/>
-      <c r="C225" s="90"/>
-      <c r="D225" s="89"/>
+    <row r="225" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="82"/>
+      <c r="B225" s="78"/>
+      <c r="C225" s="83"/>
+      <c r="D225" s="80"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="22"/>
     </row>
-    <row r="226" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="81"/>
-      <c r="B226" s="82"/>
-      <c r="C226" s="90"/>
-      <c r="D226" s="89"/>
+    <row r="226" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="82"/>
+      <c r="B226" s="78"/>
+      <c r="C226" s="83"/>
+      <c r="D226" s="80"/>
       <c r="E226" s="22"/>
       <c r="F226" s="22"/>
       <c r="G226" s="22"/>
     </row>
-    <row r="227" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="81"/>
-      <c r="B227" s="82"/>
-      <c r="C227" s="90"/>
-      <c r="D227" s="89"/>
+    <row r="227" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="82"/>
+      <c r="B227" s="78"/>
+      <c r="C227" s="83"/>
+      <c r="D227" s="80"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
       <c r="G227" s="22"/>
     </row>
-    <row r="228" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="81"/>
-      <c r="B228" s="82"/>
-      <c r="C228" s="90"/>
-      <c r="D228" s="89"/>
+    <row r="228" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="82"/>
+      <c r="B228" s="78"/>
+      <c r="C228" s="83"/>
+      <c r="D228" s="80"/>
       <c r="E228" s="22"/>
       <c r="F228" s="22"/>
       <c r="G228" s="22"/>
     </row>
-    <row r="229" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="81"/>
-      <c r="B229" s="82"/>
-      <c r="C229" s="90"/>
-      <c r="D229" s="89"/>
+    <row r="229" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="82"/>
+      <c r="B229" s="78"/>
+      <c r="C229" s="83"/>
+      <c r="D229" s="80"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
       <c r="G229" s="22"/>
     </row>
-    <row r="230" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="81"/>
-      <c r="B230" s="82"/>
-      <c r="C230" s="90"/>
-      <c r="D230" s="89"/>
+    <row r="230" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="82"/>
+      <c r="B230" s="78"/>
+      <c r="C230" s="83"/>
+      <c r="D230" s="80"/>
       <c r="E230" s="22"/>
       <c r="F230" s="22"/>
       <c r="G230" s="22"/>
     </row>
-    <row r="231" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="81"/>
-      <c r="B231" s="82"/>
-      <c r="C231" s="90"/>
-      <c r="D231" s="89"/>
+    <row r="231" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="82"/>
+      <c r="B231" s="78"/>
+      <c r="C231" s="83"/>
+      <c r="D231" s="80"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
       <c r="G231" s="22"/>
     </row>
-    <row r="232" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="81"/>
-      <c r="B232" s="82"/>
-      <c r="C232" s="90"/>
-      <c r="D232" s="89"/>
+    <row r="232" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="82"/>
+      <c r="B232" s="78"/>
+      <c r="C232" s="83"/>
+      <c r="D232" s="80"/>
       <c r="E232" s="22"/>
       <c r="F232" s="22"/>
       <c r="G232" s="22"/>
     </row>
-    <row r="233" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="81"/>
-      <c r="B233" s="82"/>
-      <c r="C233" s="90"/>
-      <c r="D233" s="89"/>
+    <row r="233" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="82"/>
+      <c r="B233" s="78"/>
+      <c r="C233" s="83"/>
+      <c r="D233" s="80"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
       <c r="G233" s="22"/>
     </row>
-    <row r="234" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="81"/>
-      <c r="B234" s="82"/>
-      <c r="C234" s="90"/>
-      <c r="D234" s="89"/>
+    <row r="234" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="82"/>
+      <c r="B234" s="78"/>
+      <c r="C234" s="83"/>
+      <c r="D234" s="80"/>
       <c r="E234" s="22"/>
       <c r="F234" s="22"/>
       <c r="G234" s="22"/>
     </row>
-    <row r="235" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="81"/>
-      <c r="B235" s="82"/>
-      <c r="C235" s="90"/>
-      <c r="D235" s="89"/>
+    <row r="235" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="82"/>
+      <c r="B235" s="78"/>
+      <c r="C235" s="83"/>
+      <c r="D235" s="80"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
       <c r="G235" s="22"/>
     </row>
-    <row r="236" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="81"/>
-      <c r="B236" s="82"/>
-      <c r="C236" s="90"/>
-      <c r="D236" s="89"/>
+    <row r="236" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="82"/>
+      <c r="B236" s="78"/>
+      <c r="C236" s="83"/>
+      <c r="D236" s="80"/>
       <c r="E236" s="22"/>
       <c r="F236" s="22"/>
       <c r="G236" s="22"/>
     </row>
-    <row r="237" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="81"/>
-      <c r="B237" s="82"/>
-      <c r="C237" s="90"/>
-      <c r="D237" s="89"/>
+    <row r="237" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="82"/>
+      <c r="B237" s="78"/>
+      <c r="C237" s="83"/>
+      <c r="D237" s="80"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
       <c r="G237" s="22"/>
     </row>
-    <row r="238" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="81"/>
-      <c r="B238" s="82"/>
-      <c r="C238" s="90"/>
-      <c r="D238" s="89"/>
+    <row r="238" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="82"/>
+      <c r="B238" s="78"/>
+      <c r="C238" s="83"/>
+      <c r="D238" s="80"/>
       <c r="E238" s="22"/>
       <c r="F238" s="22"/>
       <c r="G238" s="22"/>
     </row>
-    <row r="239" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="81"/>
-      <c r="B239" s="82"/>
-      <c r="C239" s="90"/>
-      <c r="D239" s="89"/>
+    <row r="239" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="82"/>
+      <c r="B239" s="78"/>
+      <c r="C239" s="83"/>
+      <c r="D239" s="80"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
       <c r="G239" s="22"/>
     </row>
-    <row r="240" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="81"/>
-      <c r="B240" s="82"/>
-      <c r="C240" s="90"/>
-      <c r="D240" s="89"/>
-      <c r="E240" s="22"/>
-      <c r="F240" s="22"/>
-      <c r="G240" s="22"/>
-    </row>
-    <row r="241" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="81"/>
-      <c r="B241" s="82"/>
-      <c r="C241" s="90"/>
-      <c r="D241" s="89"/>
-      <c r="E241" s="22"/>
-      <c r="F241" s="22"/>
-      <c r="G241" s="22"/>
-    </row>
-    <row r="242" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="39"/>
-      <c r="B242" s="40"/>
-      <c r="C242" s="41"/>
-      <c r="D242" s="42"/>
-      <c r="E242" s="43"/>
-      <c r="F242" s="43"/>
-      <c r="G242" s="43"/>
-      <c r="H242" s="41"/>
-      <c r="J242" s="44"/>
-      <c r="K242" s="44"/>
-      <c r="L242" s="41"/>
-      <c r="M242" s="41"/>
-    </row>
-    <row r="243" spans="1:13" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="87"/>
-      <c r="B243" s="82"/>
-      <c r="C243" s="88"/>
-      <c r="D243" s="89"/>
-    </row>
-    <row r="244" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="87"/>
-      <c r="B244" s="82"/>
-      <c r="C244" s="88"/>
-      <c r="D244" s="89"/>
-    </row>
-    <row r="245" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="87"/>
-      <c r="B245" s="82"/>
-      <c r="C245" s="88"/>
-      <c r="D245" s="89"/>
-    </row>
-    <row r="246" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="87"/>
-      <c r="B246" s="82"/>
-      <c r="C246" s="88"/>
-      <c r="D246" s="89"/>
-    </row>
-    <row r="247" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="87"/>
-      <c r="B247" s="82"/>
-      <c r="C247" s="88"/>
-      <c r="D247" s="89"/>
-    </row>
-    <row r="248" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="87"/>
-      <c r="B248" s="82"/>
-      <c r="C248" s="88"/>
-      <c r="D248" s="89"/>
-    </row>
-    <row r="249" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="87"/>
-      <c r="B249" s="82"/>
-      <c r="C249" s="88"/>
-      <c r="D249" s="89"/>
-    </row>
-    <row r="250" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="87"/>
-      <c r="B250" s="82"/>
-      <c r="C250" s="88"/>
-      <c r="D250" s="89"/>
-    </row>
-    <row r="251" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="87"/>
-      <c r="B251" s="82"/>
-      <c r="C251" s="88"/>
-      <c r="D251" s="89"/>
-    </row>
-    <row r="252" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="87"/>
-      <c r="B252" s="82"/>
-      <c r="C252" s="88"/>
-      <c r="D252" s="89"/>
-    </row>
-    <row r="253" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="87"/>
-      <c r="B253" s="82"/>
-      <c r="C253" s="88"/>
-      <c r="D253" s="89"/>
-    </row>
-    <row r="254" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="87"/>
-      <c r="B254" s="82"/>
-      <c r="C254" s="88"/>
-      <c r="D254" s="89"/>
-    </row>
-    <row r="255" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="87"/>
-      <c r="B255" s="82"/>
-      <c r="C255" s="88"/>
-      <c r="D255" s="89"/>
-    </row>
-    <row r="256" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="87"/>
-      <c r="B256" s="82"/>
-      <c r="C256" s="88"/>
-      <c r="D256" s="89"/>
+    <row r="240" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="39"/>
+      <c r="B240" s="40"/>
+      <c r="C240" s="41"/>
+      <c r="D240" s="42"/>
+      <c r="E240" s="43"/>
+      <c r="F240" s="43"/>
+      <c r="G240" s="43"/>
+      <c r="H240" s="41"/>
+      <c r="J240" s="44"/>
+      <c r="K240" s="44"/>
+      <c r="L240" s="41"/>
+      <c r="M240" s="41"/>
+    </row>
+    <row r="241" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="84"/>
+      <c r="B241" s="78"/>
+      <c r="C241" s="85"/>
+      <c r="D241" s="80"/>
+    </row>
+    <row r="242" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="84"/>
+      <c r="B242" s="78"/>
+      <c r="C242" s="85"/>
+      <c r="D242" s="80"/>
+    </row>
+    <row r="243" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="84"/>
+      <c r="B243" s="78"/>
+      <c r="C243" s="85"/>
+      <c r="D243" s="80"/>
+    </row>
+    <row r="244" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="84"/>
+      <c r="B244" s="78"/>
+      <c r="C244" s="85"/>
+      <c r="D244" s="80"/>
+    </row>
+    <row r="245" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="84"/>
+      <c r="B245" s="78"/>
+      <c r="C245" s="85"/>
+      <c r="D245" s="80"/>
+    </row>
+    <row r="246" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="84"/>
+      <c r="B246" s="78"/>
+      <c r="C246" s="85"/>
+      <c r="D246" s="80"/>
+    </row>
+    <row r="247" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="84"/>
+      <c r="B247" s="78"/>
+      <c r="C247" s="85"/>
+      <c r="D247" s="80"/>
+    </row>
+    <row r="248" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="84"/>
+      <c r="B248" s="78"/>
+      <c r="C248" s="85"/>
+      <c r="D248" s="80"/>
+    </row>
+    <row r="249" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="84"/>
+      <c r="B249" s="78"/>
+      <c r="C249" s="85"/>
+      <c r="D249" s="80"/>
+    </row>
+    <row r="250" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="84"/>
+      <c r="B250" s="78"/>
+      <c r="C250" s="85"/>
+      <c r="D250" s="80"/>
+    </row>
+    <row r="251" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="84"/>
+      <c r="B251" s="78"/>
+      <c r="C251" s="85"/>
+      <c r="D251" s="80"/>
+    </row>
+    <row r="252" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="84"/>
+      <c r="B252" s="78"/>
+      <c r="C252" s="85"/>
+      <c r="D252" s="80"/>
+    </row>
+    <row r="253" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="84"/>
+      <c r="B253" s="78"/>
+      <c r="C253" s="85"/>
+      <c r="D253" s="80"/>
+    </row>
+    <row r="254" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="84"/>
+      <c r="B254" s="78"/>
+      <c r="C254" s="85"/>
+      <c r="D254" s="80"/>
+    </row>
+    <row r="255" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="84"/>
+      <c r="B255" s="78"/>
+      <c r="C255" s="85"/>
+      <c r="D255" s="80"/>
+    </row>
+    <row r="256" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="84"/>
+      <c r="B256" s="78"/>
+      <c r="C256" s="85"/>
+      <c r="D256" s="80"/>
     </row>
     <row r="257" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="87"/>
-      <c r="B257" s="82"/>
-      <c r="C257" s="88"/>
-      <c r="D257" s="89"/>
+      <c r="A257" s="84"/>
+      <c r="B257" s="78"/>
+      <c r="C257" s="85"/>
+      <c r="D257" s="80"/>
     </row>
     <row r="258" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="87"/>
-      <c r="B258" s="82"/>
-      <c r="C258" s="88"/>
-      <c r="D258" s="89"/>
+      <c r="A258" s="84"/>
+      <c r="B258" s="78"/>
+      <c r="C258" s="85"/>
+      <c r="D258" s="80"/>
     </row>
     <row r="259" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="87"/>
-      <c r="B259" s="82"/>
-      <c r="C259" s="88"/>
-      <c r="D259" s="89"/>
+      <c r="A259" s="84"/>
+      <c r="B259" s="78"/>
+      <c r="C259" s="85"/>
+      <c r="D259" s="80"/>
     </row>
     <row r="260" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="87"/>
-      <c r="B260" s="82"/>
-      <c r="C260" s="88"/>
-      <c r="D260" s="89"/>
+      <c r="A260" s="84"/>
+      <c r="B260" s="78"/>
+      <c r="C260" s="85"/>
+      <c r="D260" s="80"/>
     </row>
     <row r="261" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="87"/>
-      <c r="B261" s="82"/>
-      <c r="C261" s="88"/>
-      <c r="D261" s="89"/>
+      <c r="A261" s="84"/>
+      <c r="B261" s="78"/>
+      <c r="C261" s="85"/>
+      <c r="D261" s="80"/>
     </row>
     <row r="262" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="87"/>
-      <c r="B262" s="82"/>
-      <c r="C262" s="88"/>
-      <c r="D262" s="89"/>
+      <c r="A262" s="84"/>
+      <c r="B262" s="78"/>
+      <c r="C262" s="85"/>
+      <c r="D262" s="80"/>
     </row>
     <row r="263" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="87"/>
-      <c r="B263" s="82"/>
-      <c r="C263" s="88"/>
-      <c r="D263" s="89"/>
+      <c r="A263" s="84"/>
+      <c r="B263" s="78"/>
+      <c r="C263" s="85"/>
+      <c r="D263" s="80"/>
     </row>
     <row r="264" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="87"/>
-      <c r="B264" s="82"/>
-      <c r="C264" s="88"/>
-      <c r="D264" s="89"/>
+      <c r="A264" s="84"/>
+      <c r="B264" s="78"/>
+      <c r="C264" s="85"/>
+      <c r="D264" s="80"/>
     </row>
     <row r="265" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="87"/>
-      <c r="B265" s="82"/>
-      <c r="C265" s="88"/>
-      <c r="D265" s="89"/>
+      <c r="A265" s="84"/>
+      <c r="B265" s="78"/>
+      <c r="C265" s="85"/>
+      <c r="D265" s="80"/>
     </row>
     <row r="266" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="87"/>
-      <c r="B266" s="82"/>
-      <c r="C266" s="88"/>
-      <c r="D266" s="89"/>
+      <c r="A266" s="84"/>
+      <c r="B266" s="78"/>
+      <c r="C266" s="85"/>
+      <c r="D266" s="80"/>
     </row>
     <row r="267" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="87"/>
-      <c r="B267" s="82"/>
-      <c r="C267" s="88"/>
-      <c r="D267" s="89"/>
+      <c r="A267" s="84"/>
+      <c r="B267" s="78"/>
+      <c r="C267" s="85"/>
+      <c r="D267" s="80"/>
     </row>
     <row r="268" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="87"/>
-      <c r="B268" s="82"/>
-      <c r="C268" s="88"/>
-      <c r="D268" s="89"/>
+      <c r="A268" s="84"/>
+      <c r="B268" s="78"/>
+      <c r="C268" s="85"/>
+      <c r="D268" s="80"/>
     </row>
     <row r="269" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="87"/>
-      <c r="B269" s="82"/>
-      <c r="C269" s="88"/>
-      <c r="D269" s="89"/>
+      <c r="A269" s="84"/>
+      <c r="B269" s="78"/>
+      <c r="C269" s="85"/>
+      <c r="D269" s="80"/>
     </row>
     <row r="270" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="87"/>
-      <c r="B270" s="82"/>
-      <c r="C270" s="88"/>
-      <c r="D270" s="89"/>
+      <c r="A270" s="84"/>
+      <c r="B270" s="78"/>
+      <c r="C270" s="85"/>
+      <c r="D270" s="80"/>
     </row>
     <row r="271" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="87"/>
-      <c r="B271" s="82"/>
-      <c r="C271" s="88"/>
-      <c r="D271" s="89"/>
+      <c r="A271" s="84"/>
+      <c r="B271" s="78"/>
+      <c r="C271" s="85"/>
+      <c r="D271" s="80"/>
     </row>
     <row r="272" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="87"/>
-      <c r="B272" s="82"/>
-      <c r="C272" s="88"/>
-      <c r="D272" s="89"/>
+      <c r="A272" s="84"/>
+      <c r="B272" s="78"/>
+      <c r="C272" s="85"/>
+      <c r="D272" s="80"/>
     </row>
     <row r="273" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="87"/>
-      <c r="B273" s="82"/>
-      <c r="C273" s="88"/>
-      <c r="D273" s="89"/>
+      <c r="A273" s="84"/>
+      <c r="B273" s="78"/>
+      <c r="C273" s="85"/>
+      <c r="D273" s="80"/>
     </row>
     <row r="274" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="87"/>
-      <c r="B274" s="82"/>
-      <c r="C274" s="88"/>
-      <c r="D274" s="89"/>
+      <c r="A274" s="84"/>
+      <c r="B274" s="78"/>
+      <c r="C274" s="85"/>
+      <c r="D274" s="80"/>
     </row>
     <row r="275" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="87"/>
-      <c r="B275" s="82"/>
-      <c r="C275" s="88"/>
-      <c r="D275" s="89"/>
+      <c r="A275" s="84"/>
+      <c r="B275" s="78"/>
+      <c r="C275" s="85"/>
+      <c r="D275" s="80"/>
     </row>
     <row r="276" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="87"/>
-      <c r="B276" s="82"/>
-      <c r="C276" s="88"/>
-      <c r="D276" s="89"/>
+      <c r="A276" s="84"/>
+      <c r="B276" s="78"/>
+      <c r="C276" s="85"/>
+      <c r="D276" s="80"/>
     </row>
     <row r="277" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="87"/>
-      <c r="B277" s="82"/>
-      <c r="C277" s="88"/>
-      <c r="D277" s="89"/>
+      <c r="A277" s="84"/>
+      <c r="B277" s="78"/>
+      <c r="C277" s="85"/>
+      <c r="D277" s="80"/>
     </row>
     <row r="278" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="87"/>
-      <c r="B278" s="82"/>
-      <c r="C278" s="88"/>
-      <c r="D278" s="89"/>
+      <c r="A278" s="84"/>
+      <c r="B278" s="78"/>
+      <c r="C278" s="85"/>
+      <c r="D278" s="80"/>
     </row>
     <row r="279" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="87"/>
-      <c r="B279" s="82"/>
-      <c r="C279" s="88"/>
-      <c r="D279" s="89"/>
+      <c r="A279" s="84"/>
+      <c r="B279" s="78"/>
+      <c r="C279" s="85"/>
+      <c r="D279" s="80"/>
     </row>
     <row r="280" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="87"/>
-      <c r="B280" s="82"/>
-      <c r="C280" s="88"/>
-      <c r="D280" s="89"/>
+      <c r="A280" s="84"/>
+      <c r="B280" s="78"/>
+      <c r="C280" s="85"/>
+      <c r="D280" s="80"/>
     </row>
     <row r="281" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="87"/>
-      <c r="B281" s="82"/>
-      <c r="C281" s="88"/>
-      <c r="D281" s="89"/>
+      <c r="A281" s="84"/>
+      <c r="B281" s="78"/>
+      <c r="C281" s="85"/>
+      <c r="D281" s="80"/>
     </row>
     <row r="282" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="87"/>
-      <c r="B282" s="82"/>
-      <c r="C282" s="88"/>
-      <c r="D282" s="89"/>
+      <c r="A282" s="84"/>
+      <c r="B282" s="78"/>
+      <c r="C282" s="85"/>
+      <c r="D282" s="80"/>
     </row>
     <row r="283" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="87"/>
-      <c r="B283" s="82"/>
-      <c r="C283" s="88"/>
-      <c r="D283" s="89"/>
+      <c r="A283" s="84"/>
+      <c r="B283" s="78"/>
+      <c r="C283" s="85"/>
+      <c r="D283" s="80"/>
     </row>
     <row r="284" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="87"/>
-      <c r="B284" s="82"/>
-      <c r="C284" s="88"/>
-      <c r="D284" s="89"/>
+      <c r="A284" s="84"/>
+      <c r="B284" s="78"/>
+      <c r="C284" s="85"/>
+      <c r="D284" s="80"/>
     </row>
     <row r="285" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="87"/>
-      <c r="B285" s="82"/>
-      <c r="C285" s="88"/>
-      <c r="D285" s="89"/>
+      <c r="A285" s="84"/>
+      <c r="B285" s="78"/>
+      <c r="C285" s="85"/>
+      <c r="D285" s="80"/>
     </row>
     <row r="286" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="87"/>
-      <c r="B286" s="82"/>
-      <c r="C286" s="88"/>
-      <c r="D286" s="89"/>
+      <c r="A286" s="84"/>
+      <c r="B286" s="78"/>
+      <c r="C286" s="85"/>
+      <c r="D286" s="80"/>
     </row>
     <row r="287" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="87"/>
-      <c r="B287" s="82"/>
-      <c r="C287" s="88"/>
-      <c r="D287" s="89"/>
+      <c r="A287" s="84"/>
+      <c r="B287" s="78"/>
+      <c r="C287" s="85"/>
+      <c r="D287" s="80"/>
     </row>
     <row r="288" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="87"/>
-      <c r="B288" s="82"/>
-      <c r="C288" s="88"/>
-      <c r="D288" s="89"/>
+      <c r="A288" s="84"/>
+      <c r="B288" s="78"/>
+      <c r="C288" s="85"/>
+      <c r="D288" s="80"/>
     </row>
     <row r="289" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="87"/>
-      <c r="B289" s="82"/>
-      <c r="C289" s="88"/>
-      <c r="D289" s="89"/>
+      <c r="A289" s="84"/>
+      <c r="B289" s="78"/>
+      <c r="C289" s="85"/>
+      <c r="D289" s="80"/>
     </row>
     <row r="290" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="87"/>
-      <c r="B290" s="82"/>
-      <c r="C290" s="88"/>
-      <c r="D290" s="89"/>
+      <c r="A290" s="84"/>
+      <c r="B290" s="78"/>
+      <c r="C290" s="85"/>
+      <c r="D290" s="80"/>
     </row>
     <row r="291" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="87"/>
-      <c r="B291" s="82"/>
-      <c r="C291" s="88"/>
-      <c r="D291" s="89"/>
+      <c r="A291" s="84"/>
+      <c r="B291" s="78"/>
+      <c r="C291" s="85"/>
+      <c r="D291" s="80"/>
     </row>
     <row r="292" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="87"/>
-      <c r="B292" s="82"/>
-      <c r="C292" s="88"/>
-      <c r="D292" s="89"/>
+      <c r="A292" s="84"/>
+      <c r="B292" s="78"/>
+      <c r="C292" s="85"/>
+      <c r="D292" s="80"/>
     </row>
     <row r="293" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="87"/>
-      <c r="B293" s="82"/>
-      <c r="C293" s="88"/>
-      <c r="D293" s="89"/>
+      <c r="A293" s="84"/>
+      <c r="B293" s="78"/>
+      <c r="C293" s="85"/>
+      <c r="D293" s="80"/>
     </row>
     <row r="294" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="87"/>
-      <c r="B294" s="82"/>
-      <c r="C294" s="88"/>
-      <c r="D294" s="89"/>
+      <c r="A294" s="84"/>
+      <c r="B294" s="78"/>
+      <c r="C294" s="85"/>
+      <c r="D294" s="80"/>
     </row>
     <row r="295" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="87"/>
-      <c r="B295" s="82"/>
-      <c r="C295" s="88"/>
-      <c r="D295" s="89"/>
+      <c r="A295" s="84"/>
+      <c r="B295" s="78"/>
+      <c r="C295" s="85"/>
+      <c r="D295" s="80"/>
     </row>
     <row r="296" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="87"/>
-      <c r="B296" s="82"/>
-      <c r="C296" s="88"/>
-      <c r="D296" s="89"/>
+      <c r="A296" s="84"/>
+      <c r="B296" s="78"/>
+      <c r="C296" s="85"/>
+      <c r="D296" s="80"/>
     </row>
     <row r="297" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="87"/>
-      <c r="B297" s="82"/>
-      <c r="C297" s="88"/>
-      <c r="D297" s="89"/>
+      <c r="A297" s="84"/>
+      <c r="B297" s="78"/>
+      <c r="C297" s="85"/>
+      <c r="D297" s="80"/>
     </row>
     <row r="298" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="87"/>
-      <c r="B298" s="82"/>
-      <c r="C298" s="88"/>
-      <c r="D298" s="89"/>
+      <c r="A298" s="84"/>
+      <c r="B298" s="78"/>
+      <c r="C298" s="85"/>
+      <c r="D298" s="80"/>
     </row>
     <row r="299" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="87"/>
-      <c r="B299" s="82"/>
-      <c r="C299" s="88"/>
-      <c r="D299" s="89"/>
+      <c r="A299" s="84"/>
+      <c r="B299" s="78"/>
+      <c r="C299" s="85"/>
+      <c r="D299" s="80"/>
     </row>
     <row r="300" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="87"/>
-      <c r="B300" s="82"/>
-      <c r="C300" s="88"/>
-      <c r="D300" s="89"/>
-    </row>
-    <row r="301" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="87"/>
-      <c r="B301" s="82"/>
-      <c r="C301" s="88"/>
-      <c r="D301" s="89"/>
-    </row>
-    <row r="302" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="87"/>
-      <c r="B302" s="82"/>
-      <c r="C302" s="88"/>
-      <c r="D302" s="89"/>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A303" s="45"/>
-      <c r="B303" s="40"/>
-      <c r="C303" s="46"/>
-      <c r="D303" s="42"/>
-      <c r="E303" s="47"/>
-      <c r="F303" s="47"/>
-      <c r="G303" s="48"/>
-      <c r="H303" s="41"/>
-      <c r="J303" s="44"/>
-      <c r="K303" s="44"/>
-      <c r="L303" s="41"/>
-      <c r="M303" s="41"/>
+      <c r="A300" s="84"/>
+      <c r="B300" s="78"/>
+      <c r="C300" s="85"/>
+      <c r="D300" s="80"/>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301" s="45"/>
+      <c r="B301" s="40"/>
+      <c r="C301" s="46"/>
+      <c r="D301" s="42"/>
+      <c r="E301" s="47"/>
+      <c r="F301" s="47"/>
+      <c r="G301" s="48"/>
+      <c r="H301" s="41"/>
+      <c r="J301" s="44"/>
+      <c r="K301" s="44"/>
+      <c r="L301" s="41"/>
+      <c r="M301" s="41"/>
+    </row>
+    <row r="302" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="84"/>
+      <c r="B302" s="78"/>
+      <c r="C302" s="85"/>
+      <c r="D302" s="80"/>
+    </row>
+    <row r="303" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="84"/>
+      <c r="B303" s="78"/>
+      <c r="C303" s="85"/>
+      <c r="D303" s="80"/>
     </row>
     <row r="304" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="87"/>
-      <c r="B304" s="82"/>
-      <c r="C304" s="88"/>
-      <c r="D304" s="89"/>
+      <c r="A304" s="84"/>
+      <c r="B304" s="78"/>
+      <c r="C304" s="85"/>
+      <c r="D304" s="80"/>
     </row>
     <row r="305" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="87"/>
-      <c r="B305" s="82"/>
-      <c r="C305" s="88"/>
-      <c r="D305" s="89"/>
+      <c r="A305" s="84"/>
+      <c r="B305" s="78"/>
+      <c r="C305" s="85"/>
+      <c r="D305" s="80"/>
     </row>
     <row r="306" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="87"/>
-      <c r="B306" s="82"/>
-      <c r="C306" s="88"/>
-      <c r="D306" s="89"/>
+      <c r="A306" s="84"/>
+      <c r="B306" s="78"/>
+      <c r="C306" s="85"/>
+      <c r="D306" s="80"/>
     </row>
     <row r="307" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="87"/>
-      <c r="B307" s="82"/>
-      <c r="C307" s="88"/>
-      <c r="D307" s="89"/>
+      <c r="A307" s="84"/>
+      <c r="B307" s="78"/>
+      <c r="C307" s="85"/>
+      <c r="D307" s="80"/>
     </row>
     <row r="308" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="87"/>
-      <c r="B308" s="82"/>
-      <c r="C308" s="88"/>
-      <c r="D308" s="89"/>
+      <c r="A308" s="84"/>
+      <c r="B308" s="78"/>
+      <c r="C308" s="85"/>
+      <c r="D308" s="80"/>
     </row>
     <row r="309" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="87"/>
-      <c r="B309" s="82"/>
-      <c r="C309" s="88"/>
-      <c r="D309" s="89"/>
+      <c r="A309" s="84"/>
+      <c r="B309" s="78"/>
+      <c r="C309" s="85"/>
+      <c r="D309" s="80"/>
     </row>
     <row r="310" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="87"/>
-      <c r="B310" s="82"/>
-      <c r="C310" s="88"/>
-      <c r="D310" s="89"/>
+      <c r="A310" s="84"/>
+      <c r="B310" s="78"/>
+      <c r="C310" s="85"/>
+      <c r="D310" s="80"/>
     </row>
     <row r="311" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="87"/>
-      <c r="B311" s="82"/>
-      <c r="C311" s="88"/>
-      <c r="D311" s="89"/>
+      <c r="A311" s="84"/>
+      <c r="B311" s="78"/>
+      <c r="C311" s="85"/>
+      <c r="D311" s="80"/>
     </row>
     <row r="312" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="87"/>
-      <c r="B312" s="82"/>
-      <c r="C312" s="88"/>
-      <c r="D312" s="89"/>
+      <c r="A312" s="84"/>
+      <c r="B312" s="78"/>
+      <c r="C312" s="85"/>
+      <c r="D312" s="80"/>
     </row>
     <row r="313" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="87"/>
-      <c r="B313" s="82"/>
-      <c r="C313" s="88"/>
-      <c r="D313" s="89"/>
+      <c r="A313" s="84"/>
+      <c r="B313" s="78"/>
+      <c r="C313" s="85"/>
+      <c r="D313" s="80"/>
     </row>
     <row r="314" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="87"/>
-      <c r="B314" s="82"/>
-      <c r="C314" s="88"/>
-      <c r="D314" s="89"/>
+      <c r="A314" s="84"/>
+      <c r="B314" s="78"/>
+      <c r="C314" s="85"/>
+      <c r="D314" s="80"/>
     </row>
     <row r="315" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="87"/>
-      <c r="B315" s="82"/>
-      <c r="C315" s="88"/>
-      <c r="D315" s="89"/>
+      <c r="A315" s="84"/>
+      <c r="B315" s="78"/>
+      <c r="C315" s="85"/>
+      <c r="D315" s="80"/>
     </row>
     <row r="316" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A316" s="87"/>
-      <c r="B316" s="82"/>
-      <c r="C316" s="88"/>
-      <c r="D316" s="89"/>
+      <c r="A316" s="84"/>
+      <c r="B316" s="78"/>
+      <c r="C316" s="85"/>
+      <c r="D316" s="80"/>
     </row>
     <row r="317" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="87"/>
-      <c r="B317" s="82"/>
-      <c r="C317" s="88"/>
-      <c r="D317" s="89"/>
+      <c r="A317" s="84"/>
+      <c r="B317" s="78"/>
+      <c r="C317" s="85"/>
+      <c r="D317" s="80"/>
     </row>
     <row r="318" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="87"/>
-      <c r="B318" s="82"/>
-      <c r="C318" s="88"/>
-      <c r="D318" s="89"/>
+      <c r="A318" s="84"/>
+      <c r="B318" s="78"/>
+      <c r="C318" s="85"/>
+      <c r="D318" s="80"/>
     </row>
     <row r="319" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="87"/>
-      <c r="B319" s="82"/>
-      <c r="C319" s="88"/>
-      <c r="D319" s="89"/>
+      <c r="A319" s="84"/>
+      <c r="B319" s="78"/>
+      <c r="C319" s="85"/>
+      <c r="D319" s="80"/>
     </row>
     <row r="320" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="87"/>
-      <c r="B320" s="82"/>
-      <c r="C320" s="88"/>
-      <c r="D320" s="89"/>
+      <c r="A320" s="84"/>
+      <c r="B320" s="78"/>
+      <c r="C320" s="85"/>
+      <c r="D320" s="80"/>
     </row>
     <row r="321" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="87"/>
-      <c r="B321" s="82"/>
-      <c r="C321" s="88"/>
-      <c r="D321" s="89"/>
+      <c r="A321" s="84"/>
+      <c r="B321" s="78"/>
+      <c r="C321" s="85"/>
+      <c r="D321" s="80"/>
     </row>
     <row r="322" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="87"/>
-      <c r="B322" s="82"/>
-      <c r="C322" s="88"/>
-      <c r="D322" s="89"/>
+      <c r="A322" s="84"/>
+      <c r="B322" s="78"/>
+      <c r="C322" s="85"/>
+      <c r="D322" s="80"/>
     </row>
     <row r="323" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="87"/>
-      <c r="B323" s="82"/>
-      <c r="C323" s="88"/>
-      <c r="D323" s="89"/>
+      <c r="A323" s="84"/>
+      <c r="B323" s="78"/>
+      <c r="C323" s="85"/>
+      <c r="D323" s="80"/>
     </row>
     <row r="324" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="87"/>
-      <c r="B324" s="82"/>
-      <c r="C324" s="88"/>
-      <c r="D324" s="89"/>
+      <c r="A324" s="84"/>
+      <c r="B324" s="78"/>
+      <c r="C324" s="85"/>
+      <c r="D324" s="80"/>
     </row>
     <row r="325" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="87"/>
-      <c r="B325" s="82"/>
-      <c r="C325" s="88"/>
-      <c r="D325" s="89"/>
+      <c r="A325" s="84"/>
+      <c r="B325" s="78"/>
+      <c r="C325" s="85"/>
+      <c r="D325" s="80"/>
     </row>
     <row r="326" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="87"/>
-      <c r="B326" s="82"/>
-      <c r="C326" s="88"/>
-      <c r="D326" s="89"/>
+      <c r="A326" s="84"/>
+      <c r="B326" s="78"/>
+      <c r="C326" s="85"/>
+      <c r="D326" s="80"/>
     </row>
     <row r="327" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="87"/>
-      <c r="B327" s="82"/>
-      <c r="C327" s="88"/>
-      <c r="D327" s="89"/>
+      <c r="A327" s="84"/>
+      <c r="B327" s="78"/>
+      <c r="C327" s="85"/>
+      <c r="D327" s="80"/>
     </row>
     <row r="328" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="87"/>
-      <c r="B328" s="82"/>
-      <c r="C328" s="88"/>
-      <c r="D328" s="89"/>
+      <c r="A328" s="84"/>
+      <c r="B328" s="78"/>
+      <c r="C328" s="85"/>
+      <c r="D328" s="80"/>
     </row>
     <row r="329" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="87"/>
-      <c r="B329" s="82"/>
-      <c r="C329" s="88"/>
-      <c r="D329" s="89"/>
+      <c r="A329" s="84"/>
+      <c r="B329" s="78"/>
+      <c r="C329" s="85"/>
+      <c r="D329" s="80"/>
     </row>
     <row r="330" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="87"/>
-      <c r="B330" s="82"/>
-      <c r="C330" s="88"/>
-      <c r="D330" s="89"/>
+      <c r="A330" s="84"/>
+      <c r="B330" s="78"/>
+      <c r="C330" s="85"/>
+      <c r="D330" s="80"/>
     </row>
     <row r="331" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="87"/>
-      <c r="B331" s="82"/>
-      <c r="C331" s="88"/>
-      <c r="D331" s="89"/>
-    </row>
-    <row r="332" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A332" s="87"/>
-      <c r="B332" s="82"/>
-      <c r="C332" s="88"/>
-      <c r="D332" s="89"/>
-    </row>
-    <row r="333" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A333" s="87"/>
-      <c r="B333" s="82"/>
-      <c r="C333" s="88"/>
-      <c r="D333" s="89"/>
+      <c r="A331" s="84"/>
+      <c r="B331" s="78"/>
+      <c r="C331" s="85"/>
+      <c r="D331" s="80"/>
+    </row>
+    <row r="332" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A332" s="86"/>
+      <c r="B332" s="86"/>
+      <c r="C332" s="86"/>
+      <c r="D332" s="86"/>
+      <c r="E332" s="86"/>
+      <c r="F332" s="86"/>
+      <c r="G332" s="86"/>
+      <c r="H332" s="86"/>
+      <c r="I332" s="86"/>
+      <c r="J332" s="86"/>
+      <c r="K332" s="86"/>
+      <c r="L332" s="86"/>
+      <c r="M332" s="49"/>
+    </row>
+    <row r="333" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A333" s="86"/>
+      <c r="B333" s="86"/>
+      <c r="C333" s="86"/>
+      <c r="D333" s="86"/>
+      <c r="E333" s="86"/>
+      <c r="F333" s="86"/>
+      <c r="G333" s="86"/>
+      <c r="H333" s="86"/>
+      <c r="I333" s="86"/>
+      <c r="J333" s="86"/>
+      <c r="K333" s="86"/>
+      <c r="L333" s="86"/>
+      <c r="M333" s="49"/>
     </row>
     <row r="334" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A334" s="75"/>
-      <c r="B334" s="75"/>
-      <c r="C334" s="75"/>
-      <c r="D334" s="75"/>
-      <c r="E334" s="75"/>
-      <c r="F334" s="75"/>
-      <c r="G334" s="75"/>
-      <c r="H334" s="75"/>
-      <c r="I334" s="75"/>
-      <c r="J334" s="75"/>
-      <c r="K334" s="75"/>
-      <c r="L334" s="75"/>
+      <c r="A334" s="86"/>
+      <c r="B334" s="86"/>
+      <c r="C334" s="86"/>
+      <c r="D334" s="86"/>
+      <c r="E334" s="86"/>
+      <c r="F334" s="86"/>
+      <c r="G334" s="86"/>
+      <c r="H334" s="86"/>
+      <c r="I334" s="86"/>
+      <c r="J334" s="86"/>
+      <c r="K334" s="86"/>
+      <c r="L334" s="86"/>
       <c r="M334" s="49"/>
     </row>
     <row r="335" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A335" s="75"/>
-      <c r="B335" s="75"/>
-      <c r="C335" s="75"/>
-      <c r="D335" s="75"/>
-      <c r="E335" s="75"/>
-      <c r="F335" s="75"/>
-      <c r="G335" s="75"/>
-      <c r="H335" s="75"/>
-      <c r="I335" s="75"/>
-      <c r="J335" s="75"/>
-      <c r="K335" s="75"/>
-      <c r="L335" s="75"/>
+      <c r="A335" s="86"/>
+      <c r="B335" s="86"/>
+      <c r="C335" s="86"/>
+      <c r="D335" s="86"/>
+      <c r="E335" s="86"/>
+      <c r="F335" s="86"/>
+      <c r="G335" s="86"/>
+      <c r="H335" s="86"/>
+      <c r="I335" s="86"/>
+      <c r="J335" s="86"/>
+      <c r="K335" s="86"/>
+      <c r="L335" s="86"/>
       <c r="M335" s="49"/>
     </row>
     <row r="336" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A336" s="75"/>
-      <c r="B336" s="75"/>
-      <c r="C336" s="75"/>
-      <c r="D336" s="75"/>
-      <c r="E336" s="75"/>
-      <c r="F336" s="75"/>
-      <c r="G336" s="75"/>
-      <c r="H336" s="75"/>
-      <c r="I336" s="75"/>
-      <c r="J336" s="75"/>
-      <c r="K336" s="75"/>
-      <c r="L336" s="75"/>
+      <c r="A336" s="86"/>
+      <c r="B336" s="86"/>
+      <c r="C336" s="86"/>
+      <c r="D336" s="86"/>
+      <c r="E336" s="86"/>
+      <c r="F336" s="86"/>
+      <c r="G336" s="86"/>
+      <c r="H336" s="86"/>
+      <c r="I336" s="86"/>
+      <c r="J336" s="86"/>
+      <c r="K336" s="86"/>
+      <c r="L336" s="86"/>
       <c r="M336" s="49"/>
     </row>
-    <row r="337" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A337" s="75"/>
-      <c r="B337" s="75"/>
-      <c r="C337" s="75"/>
-      <c r="D337" s="75"/>
-      <c r="E337" s="75"/>
-      <c r="F337" s="75"/>
-      <c r="G337" s="75"/>
-      <c r="H337" s="75"/>
-      <c r="I337" s="75"/>
-      <c r="J337" s="75"/>
-      <c r="K337" s="75"/>
-      <c r="L337" s="75"/>
-      <c r="M337" s="49"/>
-    </row>
-    <row r="338" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A338" s="75"/>
-      <c r="B338" s="75"/>
-      <c r="C338" s="75"/>
-      <c r="D338" s="75"/>
-      <c r="E338" s="75"/>
-      <c r="F338" s="75"/>
-      <c r="G338" s="75"/>
-      <c r="H338" s="75"/>
-      <c r="I338" s="75"/>
-      <c r="J338" s="75"/>
-      <c r="K338" s="75"/>
-      <c r="L338" s="75"/>
-      <c r="M338" s="49"/>
-    </row>
-    <row r="339" spans="1:15" ht="126.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="85"/>
-      <c r="B339" s="86"/>
-      <c r="C339" s="80"/>
-      <c r="D339" s="79"/>
+    <row r="337" spans="1:15" ht="126.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A337" s="87"/>
+      <c r="B337" s="88"/>
+      <c r="C337" s="89"/>
+      <c r="D337" s="90"/>
+      <c r="E337" s="52"/>
+      <c r="F337" s="52"/>
+      <c r="G337" s="53"/>
+      <c r="I337" s="54"/>
+      <c r="N337" s="55"/>
+      <c r="O337" s="55"/>
+    </row>
+    <row r="338" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A338" s="87"/>
+      <c r="B338" s="88"/>
+      <c r="C338" s="89"/>
+      <c r="D338" s="90"/>
+      <c r="E338" s="52"/>
+      <c r="F338" s="52"/>
+      <c r="G338" s="53"/>
+      <c r="I338" s="56"/>
+      <c r="N338" s="55"/>
+      <c r="O338" s="55"/>
+    </row>
+    <row r="339" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A339" s="87"/>
+      <c r="B339" s="88"/>
+      <c r="C339" s="89"/>
+      <c r="D339" s="90"/>
       <c r="E339" s="52"/>
       <c r="F339" s="52"/>
       <c r="G339" s="53"/>
-      <c r="I339" s="54"/>
-      <c r="N339" s="55"/>
-      <c r="O339" s="55"/>
     </row>
     <row r="340" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A340" s="85"/>
-      <c r="B340" s="86"/>
-      <c r="C340" s="80"/>
-      <c r="D340" s="79"/>
+      <c r="A340" s="87"/>
+      <c r="B340" s="88"/>
+      <c r="C340" s="89"/>
+      <c r="D340" s="90"/>
       <c r="E340" s="52"/>
       <c r="F340" s="52"/>
       <c r="G340" s="53"/>
-      <c r="I340" s="56"/>
-      <c r="N340" s="55"/>
-      <c r="O340" s="55"/>
     </row>
     <row r="341" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A341" s="85"/>
-      <c r="B341" s="86"/>
-      <c r="C341" s="80"/>
-      <c r="D341" s="79"/>
+      <c r="A341" s="87"/>
+      <c r="B341" s="88"/>
+      <c r="C341" s="89"/>
+      <c r="D341" s="90"/>
       <c r="E341" s="52"/>
       <c r="F341" s="52"/>
       <c r="G341" s="53"/>
     </row>
     <row r="342" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A342" s="85"/>
-      <c r="B342" s="86"/>
-      <c r="C342" s="80"/>
-      <c r="D342" s="79"/>
+      <c r="A342" s="87"/>
+      <c r="B342" s="88"/>
+      <c r="C342" s="89"/>
+      <c r="D342" s="90"/>
       <c r="E342" s="52"/>
       <c r="F342" s="52"/>
       <c r="G342" s="53"/>
     </row>
     <row r="343" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A343" s="85"/>
-      <c r="B343" s="86"/>
-      <c r="C343" s="80"/>
-      <c r="D343" s="79"/>
+      <c r="A343" s="87"/>
+      <c r="B343" s="88"/>
+      <c r="C343" s="89"/>
+      <c r="D343" s="90"/>
       <c r="E343" s="52"/>
       <c r="F343" s="52"/>
       <c r="G343" s="53"/>
     </row>
     <row r="344" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A344" s="85"/>
-      <c r="B344" s="86"/>
-      <c r="C344" s="80"/>
-      <c r="D344" s="79"/>
+      <c r="A344" s="87"/>
+      <c r="B344" s="88"/>
+      <c r="C344" s="89"/>
+      <c r="D344" s="90"/>
       <c r="E344" s="52"/>
       <c r="F344" s="52"/>
       <c r="G344" s="53"/>
     </row>
     <row r="345" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A345" s="85"/>
-      <c r="B345" s="86"/>
-      <c r="C345" s="80"/>
-      <c r="D345" s="79"/>
+      <c r="A345" s="87"/>
+      <c r="B345" s="88"/>
+      <c r="C345" s="89"/>
+      <c r="D345" s="90"/>
       <c r="E345" s="52"/>
       <c r="F345" s="52"/>
       <c r="G345" s="53"/>
     </row>
     <row r="346" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A346" s="85"/>
-      <c r="B346" s="86"/>
-      <c r="C346" s="80"/>
-      <c r="D346" s="79"/>
+      <c r="A346" s="87"/>
+      <c r="B346" s="88"/>
+      <c r="C346" s="89"/>
+      <c r="D346" s="90"/>
       <c r="E346" s="52"/>
       <c r="F346" s="52"/>
       <c r="G346" s="53"/>
     </row>
     <row r="347" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A347" s="85"/>
-      <c r="B347" s="86"/>
-      <c r="C347" s="80"/>
-      <c r="D347" s="79"/>
+      <c r="A347" s="87"/>
+      <c r="B347" s="88"/>
+      <c r="C347" s="89"/>
+      <c r="D347" s="90"/>
       <c r="E347" s="52"/>
       <c r="F347" s="52"/>
       <c r="G347" s="53"/>
     </row>
     <row r="348" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A348" s="85"/>
-      <c r="B348" s="86"/>
-      <c r="C348" s="80"/>
-      <c r="D348" s="79"/>
+      <c r="A348" s="87"/>
+      <c r="B348" s="88"/>
+      <c r="C348" s="89"/>
+      <c r="D348" s="90"/>
       <c r="E348" s="52"/>
       <c r="F348" s="52"/>
       <c r="G348" s="53"/>
     </row>
     <row r="349" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A349" s="85"/>
-      <c r="B349" s="86"/>
-      <c r="C349" s="80"/>
-      <c r="D349" s="79"/>
+      <c r="A349" s="87"/>
+      <c r="B349" s="88"/>
+      <c r="C349" s="89"/>
+      <c r="D349" s="90"/>
       <c r="E349" s="52"/>
       <c r="F349" s="52"/>
       <c r="G349" s="53"/>
     </row>
     <row r="350" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A350" s="85"/>
-      <c r="B350" s="86"/>
-      <c r="C350" s="80"/>
-      <c r="D350" s="79"/>
+      <c r="A350" s="87"/>
+      <c r="B350" s="88"/>
+      <c r="C350" s="89"/>
+      <c r="D350" s="90"/>
       <c r="E350" s="52"/>
       <c r="F350" s="52"/>
       <c r="G350" s="53"/>
     </row>
     <row r="351" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A351" s="85"/>
-      <c r="B351" s="86"/>
-      <c r="C351" s="80"/>
-      <c r="D351" s="79"/>
+      <c r="A351" s="87"/>
+      <c r="B351" s="88"/>
+      <c r="C351" s="89"/>
+      <c r="D351" s="90"/>
       <c r="E351" s="52"/>
       <c r="F351" s="52"/>
       <c r="G351" s="53"/>
     </row>
     <row r="352" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A352" s="85"/>
-      <c r="B352" s="86"/>
-      <c r="C352" s="80"/>
-      <c r="D352" s="79"/>
+      <c r="A352" s="87"/>
+      <c r="B352" s="88"/>
+      <c r="C352" s="89"/>
+      <c r="D352" s="90"/>
       <c r="E352" s="52"/>
       <c r="F352" s="52"/>
       <c r="G352" s="53"/>
     </row>
     <row r="353" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A353" s="85"/>
-      <c r="B353" s="86"/>
-      <c r="C353" s="80"/>
-      <c r="D353" s="79"/>
+      <c r="A353" s="87"/>
+      <c r="B353" s="88"/>
+      <c r="C353" s="89"/>
+      <c r="D353" s="90"/>
       <c r="E353" s="52"/>
       <c r="F353" s="52"/>
       <c r="G353" s="53"/>
     </row>
     <row r="354" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A354" s="85"/>
-      <c r="B354" s="86"/>
-      <c r="C354" s="80"/>
-      <c r="D354" s="79"/>
+      <c r="A354" s="87"/>
+      <c r="B354" s="88"/>
+      <c r="C354" s="89"/>
+      <c r="D354" s="90"/>
       <c r="E354" s="52"/>
       <c r="F354" s="52"/>
       <c r="G354" s="53"/>
     </row>
     <row r="355" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A355" s="85"/>
-      <c r="B355" s="86"/>
-      <c r="C355" s="80"/>
-      <c r="D355" s="79"/>
+      <c r="A355" s="87"/>
+      <c r="B355" s="88"/>
+      <c r="C355" s="89"/>
+      <c r="D355" s="90"/>
       <c r="E355" s="52"/>
       <c r="F355" s="52"/>
       <c r="G355" s="53"/>
     </row>
     <row r="356" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A356" s="85"/>
-      <c r="B356" s="86"/>
-      <c r="C356" s="80"/>
-      <c r="D356" s="79"/>
+      <c r="A356" s="87"/>
+      <c r="B356" s="88"/>
+      <c r="C356" s="89"/>
+      <c r="D356" s="90"/>
       <c r="E356" s="52"/>
       <c r="F356" s="52"/>
       <c r="G356" s="53"/>
     </row>
     <row r="357" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A357" s="85"/>
-      <c r="B357" s="86"/>
-      <c r="C357" s="80"/>
-      <c r="D357" s="79"/>
+      <c r="A357" s="87"/>
+      <c r="B357" s="88"/>
+      <c r="C357" s="89"/>
+      <c r="D357" s="90"/>
       <c r="E357" s="52"/>
       <c r="F357" s="52"/>
       <c r="G357" s="53"/>
     </row>
     <row r="358" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A358" s="85"/>
-      <c r="B358" s="86"/>
-      <c r="C358" s="80"/>
-      <c r="D358" s="79"/>
+      <c r="A358" s="87"/>
+      <c r="B358" s="88"/>
+      <c r="C358" s="89"/>
+      <c r="D358" s="90"/>
       <c r="E358" s="52"/>
       <c r="F358" s="52"/>
       <c r="G358" s="53"/>
     </row>
     <row r="359" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A359" s="85"/>
-      <c r="B359" s="86"/>
-      <c r="C359" s="80"/>
-      <c r="D359" s="79"/>
+      <c r="A359" s="87"/>
+      <c r="B359" s="88"/>
+      <c r="C359" s="89"/>
+      <c r="D359" s="90"/>
       <c r="E359" s="52"/>
       <c r="F359" s="52"/>
       <c r="G359" s="53"/>
     </row>
     <row r="360" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A360" s="85"/>
-      <c r="B360" s="86"/>
-      <c r="C360" s="80"/>
-      <c r="D360" s="79"/>
+      <c r="A360" s="87"/>
+      <c r="B360" s="88"/>
+      <c r="C360" s="89"/>
+      <c r="D360" s="90"/>
       <c r="E360" s="52"/>
       <c r="F360" s="52"/>
       <c r="G360" s="53"/>
     </row>
     <row r="361" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A361" s="85"/>
-      <c r="B361" s="86"/>
-      <c r="C361" s="80"/>
-      <c r="D361" s="79"/>
+      <c r="A361" s="87"/>
+      <c r="B361" s="88"/>
+      <c r="C361" s="89"/>
+      <c r="D361" s="90"/>
       <c r="E361" s="52"/>
       <c r="F361" s="52"/>
       <c r="G361" s="53"/>
     </row>
     <row r="362" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A362" s="85"/>
-      <c r="B362" s="86"/>
-      <c r="C362" s="80"/>
-      <c r="D362" s="79"/>
+      <c r="A362" s="87"/>
+      <c r="B362" s="88"/>
+      <c r="C362" s="89"/>
+      <c r="D362" s="90"/>
       <c r="E362" s="52"/>
       <c r="F362" s="52"/>
       <c r="G362" s="53"/>
     </row>
     <row r="363" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A363" s="85"/>
-      <c r="B363" s="86"/>
-      <c r="C363" s="80"/>
-      <c r="D363" s="79"/>
+      <c r="A363" s="87"/>
+      <c r="B363" s="88"/>
+      <c r="C363" s="89"/>
+      <c r="D363" s="90"/>
       <c r="E363" s="52"/>
       <c r="F363" s="52"/>
       <c r="G363" s="53"/>
     </row>
     <row r="364" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A364" s="85"/>
-      <c r="B364" s="86"/>
-      <c r="C364" s="80"/>
-      <c r="D364" s="79"/>
+      <c r="A364" s="87"/>
+      <c r="B364" s="88"/>
+      <c r="C364" s="89"/>
+      <c r="D364" s="90"/>
       <c r="E364" s="52"/>
       <c r="F364" s="52"/>
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A365" s="85"/>
-      <c r="B365" s="86"/>
-      <c r="C365" s="80"/>
-      <c r="D365" s="79"/>
+    <row r="365" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A365" s="87"/>
+      <c r="B365" s="88"/>
+      <c r="C365" s="50"/>
+      <c r="D365" s="51"/>
       <c r="E365" s="52"/>
       <c r="F365" s="52"/>
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A366" s="85"/>
-      <c r="B366" s="86"/>
-      <c r="C366" s="80"/>
-      <c r="D366" s="79"/>
+    <row r="366" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A366" s="87"/>
+      <c r="B366" s="88"/>
+      <c r="C366" s="50"/>
+      <c r="D366" s="51"/>
       <c r="E366" s="52"/>
       <c r="F366" s="52"/>
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A367" s="85"/>
-      <c r="B367" s="86"/>
-      <c r="C367" s="50"/>
-      <c r="D367" s="51"/>
+    <row r="367" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A367" s="87"/>
+      <c r="B367" s="88"/>
+      <c r="C367" s="89"/>
+      <c r="D367" s="90"/>
       <c r="E367" s="52"/>
       <c r="F367" s="52"/>
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A368" s="85"/>
-      <c r="B368" s="86"/>
-      <c r="C368" s="50"/>
-      <c r="D368" s="51"/>
+    <row r="368" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A368" s="87"/>
+      <c r="B368" s="88"/>
+      <c r="C368" s="89"/>
+      <c r="D368" s="90"/>
       <c r="E368" s="52"/>
       <c r="F368" s="52"/>
       <c r="G368" s="53"/>
     </row>
     <row r="369" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A369" s="85"/>
-      <c r="B369" s="86"/>
-      <c r="C369" s="80"/>
-      <c r="D369" s="79"/>
+      <c r="A369" s="87"/>
+      <c r="B369" s="88"/>
+      <c r="C369" s="89"/>
+      <c r="D369" s="90"/>
       <c r="E369" s="52"/>
       <c r="F369" s="52"/>
       <c r="G369" s="53"/>
     </row>
     <row r="370" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A370" s="85"/>
-      <c r="B370" s="86"/>
-      <c r="C370" s="80"/>
-      <c r="D370" s="79"/>
+      <c r="A370" s="87"/>
+      <c r="B370" s="88"/>
+      <c r="C370" s="89"/>
+      <c r="D370" s="90"/>
       <c r="E370" s="52"/>
       <c r="F370" s="52"/>
       <c r="G370" s="53"/>
     </row>
     <row r="371" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A371" s="85"/>
-      <c r="B371" s="86"/>
-      <c r="C371" s="80"/>
-      <c r="D371" s="79"/>
+      <c r="A371" s="87"/>
+      <c r="B371" s="88"/>
+      <c r="C371" s="89"/>
+      <c r="D371" s="90"/>
       <c r="E371" s="52"/>
       <c r="F371" s="52"/>
       <c r="G371" s="53"/>
     </row>
     <row r="372" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A372" s="85"/>
-      <c r="B372" s="86"/>
-      <c r="C372" s="80"/>
-      <c r="D372" s="79"/>
+      <c r="A372" s="87"/>
+      <c r="B372" s="88"/>
+      <c r="C372" s="89"/>
+      <c r="D372" s="90"/>
       <c r="E372" s="52"/>
       <c r="F372" s="52"/>
       <c r="G372" s="53"/>
     </row>
     <row r="373" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A373" s="85"/>
-      <c r="B373" s="86"/>
-      <c r="C373" s="80"/>
-      <c r="D373" s="79"/>
+      <c r="A373" s="87"/>
+      <c r="B373" s="88"/>
+      <c r="C373" s="89"/>
+      <c r="D373" s="90"/>
       <c r="E373" s="52"/>
       <c r="F373" s="52"/>
       <c r="G373" s="53"/>
     </row>
     <row r="374" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A374" s="85"/>
-      <c r="B374" s="86"/>
-      <c r="C374" s="80"/>
-      <c r="D374" s="79"/>
+      <c r="A374" s="87"/>
+      <c r="B374" s="88"/>
+      <c r="C374" s="89"/>
+      <c r="D374" s="90"/>
       <c r="E374" s="52"/>
       <c r="F374" s="52"/>
       <c r="G374" s="53"/>
     </row>
     <row r="375" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A375" s="85"/>
-      <c r="B375" s="86"/>
-      <c r="C375" s="80"/>
-      <c r="D375" s="79"/>
+      <c r="A375" s="87"/>
+      <c r="B375" s="88"/>
+      <c r="C375" s="89"/>
+      <c r="D375" s="90"/>
       <c r="E375" s="52"/>
       <c r="F375" s="52"/>
       <c r="G375" s="53"/>
     </row>
     <row r="376" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A376" s="85"/>
-      <c r="B376" s="86"/>
-      <c r="C376" s="80"/>
-      <c r="D376" s="79"/>
+      <c r="A376" s="87"/>
+      <c r="B376" s="88"/>
+      <c r="C376" s="89"/>
+      <c r="D376" s="90"/>
       <c r="E376" s="52"/>
       <c r="F376" s="52"/>
       <c r="G376" s="53"/>
     </row>
     <row r="377" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A377" s="85"/>
-      <c r="B377" s="86"/>
-      <c r="C377" s="80"/>
-      <c r="D377" s="79"/>
+      <c r="A377" s="87"/>
+      <c r="B377" s="88"/>
+      <c r="C377" s="89"/>
+      <c r="D377" s="90"/>
       <c r="E377" s="52"/>
       <c r="F377" s="52"/>
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A378" s="85"/>
+    <row r="378" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="86"/>
       <c r="B378" s="86"/>
-      <c r="C378" s="80"/>
-      <c r="D378" s="79"/>
-      <c r="E378" s="52"/>
-      <c r="F378" s="52"/>
-      <c r="G378" s="53"/>
-    </row>
-    <row r="379" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A379" s="85"/>
+      <c r="C378" s="86"/>
+      <c r="D378" s="86"/>
+      <c r="E378" s="86"/>
+      <c r="F378" s="86"/>
+      <c r="G378" s="86"/>
+      <c r="H378" s="86"/>
+      <c r="I378" s="86"/>
+      <c r="J378" s="86"/>
+      <c r="K378" s="86"/>
+      <c r="L378" s="86"/>
+      <c r="M378" s="49"/>
+    </row>
+    <row r="379" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="86"/>
       <c r="B379" s="86"/>
-      <c r="C379" s="80"/>
-      <c r="D379" s="79"/>
-      <c r="E379" s="52"/>
-      <c r="F379" s="52"/>
-      <c r="G379" s="53"/>
+      <c r="C379" s="86"/>
+      <c r="D379" s="86"/>
+      <c r="E379" s="86"/>
+      <c r="F379" s="86"/>
+      <c r="G379" s="86"/>
+      <c r="H379" s="86"/>
+      <c r="I379" s="86"/>
+      <c r="J379" s="86"/>
+      <c r="K379" s="86"/>
+      <c r="L379" s="86"/>
+      <c r="M379" s="49"/>
     </row>
     <row r="380" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="75"/>
-      <c r="B380" s="75"/>
-      <c r="C380" s="75"/>
-      <c r="D380" s="75"/>
-      <c r="E380" s="75"/>
-      <c r="F380" s="75"/>
-      <c r="G380" s="75"/>
-      <c r="H380" s="75"/>
-      <c r="I380" s="75"/>
-      <c r="J380" s="75"/>
-      <c r="K380" s="75"/>
-      <c r="L380" s="75"/>
+      <c r="A380" s="86"/>
+      <c r="B380" s="86"/>
+      <c r="C380" s="86"/>
+      <c r="D380" s="86"/>
+      <c r="E380" s="86"/>
+      <c r="F380" s="86"/>
+      <c r="G380" s="86"/>
+      <c r="H380" s="86"/>
+      <c r="I380" s="86"/>
+      <c r="J380" s="86"/>
+      <c r="K380" s="86"/>
+      <c r="L380" s="86"/>
       <c r="M380" s="49"/>
     </row>
     <row r="381" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="75"/>
-      <c r="B381" s="75"/>
-      <c r="C381" s="75"/>
-      <c r="D381" s="75"/>
-      <c r="E381" s="75"/>
-      <c r="F381" s="75"/>
-      <c r="G381" s="75"/>
-      <c r="H381" s="75"/>
-      <c r="I381" s="75"/>
-      <c r="J381" s="75"/>
-      <c r="K381" s="75"/>
-      <c r="L381" s="75"/>
+      <c r="A381" s="86"/>
+      <c r="B381" s="86"/>
+      <c r="C381" s="86"/>
+      <c r="D381" s="86"/>
+      <c r="E381" s="86"/>
+      <c r="F381" s="86"/>
+      <c r="G381" s="86"/>
+      <c r="H381" s="86"/>
+      <c r="I381" s="86"/>
+      <c r="J381" s="86"/>
+      <c r="K381" s="86"/>
+      <c r="L381" s="86"/>
       <c r="M381" s="49"/>
     </row>
     <row r="382" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="75"/>
-      <c r="B382" s="75"/>
-      <c r="C382" s="75"/>
-      <c r="D382" s="75"/>
-      <c r="E382" s="75"/>
-      <c r="F382" s="75"/>
-      <c r="G382" s="75"/>
-      <c r="H382" s="75"/>
-      <c r="I382" s="75"/>
-      <c r="J382" s="75"/>
-      <c r="K382" s="75"/>
-      <c r="L382" s="75"/>
+      <c r="A382" s="86"/>
+      <c r="B382" s="86"/>
+      <c r="C382" s="86"/>
+      <c r="D382" s="86"/>
+      <c r="E382" s="86"/>
+      <c r="F382" s="86"/>
+      <c r="G382" s="86"/>
+      <c r="H382" s="86"/>
+      <c r="I382" s="86"/>
+      <c r="J382" s="86"/>
+      <c r="K382" s="86"/>
+      <c r="L382" s="86"/>
       <c r="M382" s="49"/>
     </row>
-    <row r="383" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="75"/>
-      <c r="B383" s="75"/>
-      <c r="C383" s="75"/>
-      <c r="D383" s="75"/>
-      <c r="E383" s="75"/>
-      <c r="F383" s="75"/>
-      <c r="G383" s="75"/>
-      <c r="H383" s="75"/>
-      <c r="I383" s="75"/>
-      <c r="J383" s="75"/>
-      <c r="K383" s="75"/>
-      <c r="L383" s="75"/>
-      <c r="M383" s="49"/>
-    </row>
-    <row r="384" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="75"/>
-      <c r="B384" s="75"/>
-      <c r="C384" s="75"/>
-      <c r="D384" s="75"/>
-      <c r="E384" s="75"/>
-      <c r="F384" s="75"/>
-      <c r="G384" s="75"/>
-      <c r="H384" s="75"/>
-      <c r="I384" s="75"/>
-      <c r="J384" s="75"/>
-      <c r="K384" s="75"/>
-      <c r="L384" s="75"/>
-      <c r="M384" s="49"/>
+    <row r="383" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="82"/>
+      <c r="B383" s="78"/>
+      <c r="C383" s="93"/>
+      <c r="D383" s="94"/>
+      <c r="E383" s="15"/>
+      <c r="F383" s="15"/>
+      <c r="G383" s="15"/>
+    </row>
+    <row r="384" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="82"/>
+      <c r="B384" s="78"/>
+      <c r="C384" s="93"/>
+      <c r="D384" s="94"/>
+      <c r="E384" s="15"/>
+      <c r="F384" s="15"/>
+      <c r="G384" s="15"/>
     </row>
     <row r="385" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="81"/>
-      <c r="B385" s="82"/>
-      <c r="C385" s="83"/>
-      <c r="D385" s="84"/>
+      <c r="A385" s="82"/>
+      <c r="B385" s="78"/>
+      <c r="C385" s="93"/>
+      <c r="D385" s="94"/>
       <c r="E385" s="15"/>
       <c r="F385" s="15"/>
       <c r="G385" s="15"/>
     </row>
     <row r="386" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="81"/>
-      <c r="B386" s="82"/>
-      <c r="C386" s="83"/>
-      <c r="D386" s="84"/>
+      <c r="A386" s="82"/>
+      <c r="B386" s="78"/>
+      <c r="C386" s="93"/>
+      <c r="D386" s="94"/>
       <c r="E386" s="15"/>
       <c r="F386" s="15"/>
       <c r="G386" s="15"/>
     </row>
     <row r="387" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="81"/>
-      <c r="B387" s="82"/>
-      <c r="C387" s="83"/>
-      <c r="D387" s="84"/>
+      <c r="A387" s="82"/>
+      <c r="B387" s="78"/>
+      <c r="C387" s="93"/>
+      <c r="D387" s="94"/>
       <c r="E387" s="15"/>
       <c r="F387" s="15"/>
       <c r="G387" s="15"/>
     </row>
     <row r="388" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="81"/>
-      <c r="B388" s="82"/>
-      <c r="C388" s="83"/>
-      <c r="D388" s="84"/>
+      <c r="A388" s="82"/>
+      <c r="B388" s="78"/>
+      <c r="C388" s="93"/>
+      <c r="D388" s="94"/>
       <c r="E388" s="15"/>
       <c r="F388" s="15"/>
       <c r="G388" s="15"/>
     </row>
     <row r="389" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="81"/>
-      <c r="B389" s="82"/>
-      <c r="C389" s="83"/>
-      <c r="D389" s="84"/>
+      <c r="A389" s="82"/>
+      <c r="B389" s="78"/>
+      <c r="C389" s="93"/>
+      <c r="D389" s="94"/>
       <c r="E389" s="15"/>
       <c r="F389" s="15"/>
       <c r="G389" s="15"/>
     </row>
     <row r="390" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="81"/>
-      <c r="B390" s="82"/>
-      <c r="C390" s="83"/>
-      <c r="D390" s="84"/>
+      <c r="A390" s="82"/>
+      <c r="B390" s="78"/>
+      <c r="C390" s="93"/>
+      <c r="D390" s="94"/>
       <c r="E390" s="15"/>
       <c r="F390" s="15"/>
       <c r="G390" s="15"/>
     </row>
     <row r="391" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="81"/>
-      <c r="B391" s="82"/>
-      <c r="C391" s="83"/>
-      <c r="D391" s="84"/>
+      <c r="A391" s="82"/>
+      <c r="B391" s="78"/>
+      <c r="C391" s="93"/>
+      <c r="D391" s="94"/>
       <c r="E391" s="15"/>
       <c r="F391" s="15"/>
       <c r="G391" s="15"/>
     </row>
     <row r="392" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="81"/>
-      <c r="B392" s="82"/>
-      <c r="C392" s="83"/>
-      <c r="D392" s="84"/>
+      <c r="A392" s="82"/>
+      <c r="B392" s="78"/>
+      <c r="C392" s="93"/>
+      <c r="D392" s="94"/>
       <c r="E392" s="15"/>
       <c r="F392" s="15"/>
       <c r="G392" s="15"/>
     </row>
     <row r="393" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="81"/>
-      <c r="B393" s="82"/>
-      <c r="C393" s="83"/>
-      <c r="D393" s="84"/>
+      <c r="A393" s="82"/>
+      <c r="B393" s="78"/>
+      <c r="C393" s="93"/>
+      <c r="D393" s="94"/>
       <c r="E393" s="15"/>
       <c r="F393" s="15"/>
       <c r="G393" s="15"/>
     </row>
     <row r="394" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="81"/>
-      <c r="B394" s="82"/>
-      <c r="C394" s="83"/>
-      <c r="D394" s="84"/>
+      <c r="A394" s="82"/>
+      <c r="B394" s="78"/>
+      <c r="C394" s="93"/>
+      <c r="D394" s="94"/>
       <c r="E394" s="15"/>
       <c r="F394" s="15"/>
       <c r="G394" s="15"/>
     </row>
     <row r="395" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="81"/>
-      <c r="B395" s="82"/>
-      <c r="C395" s="83"/>
-      <c r="D395" s="84"/>
+      <c r="A395" s="82"/>
+      <c r="B395" s="78"/>
+      <c r="C395" s="93"/>
+      <c r="D395" s="94"/>
       <c r="E395" s="15"/>
       <c r="F395" s="15"/>
       <c r="G395" s="15"/>
     </row>
     <row r="396" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="81"/>
-      <c r="B396" s="82"/>
-      <c r="C396" s="83"/>
-      <c r="D396" s="84"/>
+      <c r="A396" s="82"/>
+      <c r="B396" s="78"/>
+      <c r="C396" s="93"/>
+      <c r="D396" s="94"/>
       <c r="E396" s="15"/>
       <c r="F396" s="15"/>
       <c r="G396" s="15"/>
     </row>
     <row r="397" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="81"/>
-      <c r="B397" s="82"/>
-      <c r="C397" s="83"/>
-      <c r="D397" s="84"/>
+      <c r="A397" s="82"/>
+      <c r="B397" s="78"/>
+      <c r="C397" s="93"/>
+      <c r="D397" s="94"/>
       <c r="E397" s="15"/>
       <c r="F397" s="15"/>
       <c r="G397" s="15"/>
     </row>
     <row r="398" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="81"/>
-      <c r="B398" s="82"/>
-      <c r="C398" s="83"/>
-      <c r="D398" s="84"/>
+      <c r="A398" s="82"/>
+      <c r="B398" s="78"/>
+      <c r="C398" s="93"/>
+      <c r="D398" s="94"/>
       <c r="E398" s="15"/>
       <c r="F398" s="15"/>
       <c r="G398" s="15"/>
     </row>
     <row r="399" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="81"/>
-      <c r="B399" s="82"/>
-      <c r="C399" s="83"/>
-      <c r="D399" s="84"/>
+      <c r="A399" s="82"/>
+      <c r="B399" s="78"/>
+      <c r="C399" s="93"/>
+      <c r="D399" s="94"/>
       <c r="E399" s="15"/>
       <c r="F399" s="15"/>
       <c r="G399" s="15"/>
     </row>
     <row r="400" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="81"/>
-      <c r="B400" s="82"/>
-      <c r="C400" s="83"/>
-      <c r="D400" s="84"/>
+      <c r="A400" s="82"/>
+      <c r="B400" s="78"/>
+      <c r="C400" s="93"/>
+      <c r="D400" s="94"/>
       <c r="E400" s="15"/>
       <c r="F400" s="15"/>
       <c r="G400" s="15"/>
     </row>
     <row r="401" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="81"/>
-      <c r="B401" s="82"/>
-      <c r="C401" s="83"/>
-      <c r="D401" s="84"/>
+      <c r="A401" s="82"/>
+      <c r="B401" s="78"/>
+      <c r="C401" s="93"/>
+      <c r="D401" s="94"/>
       <c r="E401" s="15"/>
       <c r="F401" s="15"/>
       <c r="G401" s="15"/>
     </row>
     <row r="402" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="81"/>
-      <c r="B402" s="82"/>
-      <c r="C402" s="83"/>
-      <c r="D402" s="84"/>
+      <c r="A402" s="82"/>
+      <c r="B402" s="78"/>
+      <c r="C402" s="93"/>
+      <c r="D402" s="94"/>
       <c r="E402" s="15"/>
       <c r="F402" s="15"/>
       <c r="G402" s="15"/>
     </row>
     <row r="403" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="81"/>
-      <c r="B403" s="82"/>
-      <c r="C403" s="83"/>
-      <c r="D403" s="84"/>
+      <c r="A403" s="82"/>
+      <c r="B403" s="78"/>
+      <c r="C403" s="93"/>
+      <c r="D403" s="94"/>
       <c r="E403" s="15"/>
       <c r="F403" s="15"/>
       <c r="G403" s="15"/>
     </row>
     <row r="404" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="81"/>
-      <c r="B404" s="82"/>
-      <c r="C404" s="83"/>
-      <c r="D404" s="84"/>
+      <c r="A404" s="82"/>
+      <c r="B404" s="78"/>
+      <c r="C404" s="93"/>
+      <c r="D404" s="94"/>
       <c r="E404" s="15"/>
       <c r="F404" s="15"/>
       <c r="G404" s="15"/>
     </row>
     <row r="405" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="81"/>
-      <c r="B405" s="82"/>
-      <c r="C405" s="83"/>
-      <c r="D405" s="84"/>
+      <c r="A405" s="82"/>
+      <c r="B405" s="78"/>
+      <c r="C405" s="93"/>
+      <c r="D405" s="94"/>
       <c r="E405" s="15"/>
       <c r="F405" s="15"/>
       <c r="G405" s="15"/>
     </row>
     <row r="406" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="81"/>
-      <c r="B406" s="82"/>
-      <c r="C406" s="83"/>
-      <c r="D406" s="84"/>
+      <c r="A406" s="82"/>
+      <c r="B406" s="78"/>
+      <c r="C406" s="93"/>
+      <c r="D406" s="94"/>
       <c r="E406" s="15"/>
       <c r="F406" s="15"/>
       <c r="G406" s="15"/>
     </row>
     <row r="407" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="81"/>
-      <c r="B407" s="82"/>
-      <c r="C407" s="83"/>
-      <c r="D407" s="84"/>
+      <c r="A407" s="82"/>
+      <c r="B407" s="78"/>
+      <c r="C407" s="93"/>
+      <c r="D407" s="94"/>
       <c r="E407" s="15"/>
       <c r="F407" s="15"/>
       <c r="G407" s="15"/>
     </row>
     <row r="408" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="81"/>
-      <c r="B408" s="82"/>
-      <c r="C408" s="83"/>
-      <c r="D408" s="84"/>
+      <c r="A408" s="82"/>
+      <c r="B408" s="78"/>
+      <c r="C408" s="93"/>
+      <c r="D408" s="94"/>
       <c r="E408" s="15"/>
       <c r="F408" s="15"/>
       <c r="G408" s="15"/>
     </row>
     <row r="409" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="81"/>
-      <c r="B409" s="82"/>
-      <c r="C409" s="83"/>
-      <c r="D409" s="84"/>
+      <c r="A409" s="82"/>
+      <c r="B409" s="78"/>
+      <c r="C409" s="93"/>
+      <c r="D409" s="94"/>
       <c r="E409" s="15"/>
       <c r="F409" s="15"/>
       <c r="G409" s="15"/>
     </row>
     <row r="410" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="81"/>
-      <c r="B410" s="82"/>
-      <c r="C410" s="83"/>
-      <c r="D410" s="84"/>
+      <c r="A410" s="82"/>
+      <c r="B410" s="78"/>
+      <c r="C410" s="93"/>
+      <c r="D410" s="94"/>
       <c r="E410" s="15"/>
       <c r="F410" s="15"/>
       <c r="G410" s="15"/>
     </row>
     <row r="411" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="81"/>
-      <c r="B411" s="82"/>
-      <c r="C411" s="83"/>
-      <c r="D411" s="84"/>
+      <c r="A411" s="82"/>
+      <c r="B411" s="78"/>
+      <c r="C411" s="93"/>
+      <c r="D411" s="94"/>
       <c r="E411" s="15"/>
       <c r="F411" s="15"/>
       <c r="G411" s="15"/>
     </row>
     <row r="412" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="81"/>
-      <c r="B412" s="82"/>
-      <c r="C412" s="83"/>
-      <c r="D412" s="84"/>
+      <c r="A412" s="82"/>
+      <c r="B412" s="78"/>
+      <c r="C412" s="93"/>
+      <c r="D412" s="94"/>
       <c r="E412" s="15"/>
       <c r="F412" s="15"/>
       <c r="G412" s="15"/>
     </row>
     <row r="413" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="81"/>
-      <c r="B413" s="82"/>
-      <c r="C413" s="83"/>
-      <c r="D413" s="84"/>
+      <c r="A413" s="82"/>
+      <c r="B413" s="78"/>
+      <c r="C413" s="93"/>
+      <c r="D413" s="94"/>
       <c r="E413" s="15"/>
       <c r="F413" s="15"/>
       <c r="G413" s="15"/>
     </row>
     <row r="414" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="81"/>
-      <c r="B414" s="82"/>
-      <c r="C414" s="83"/>
-      <c r="D414" s="84"/>
+      <c r="A414" s="82"/>
+      <c r="B414" s="78"/>
+      <c r="C414" s="93"/>
+      <c r="D414" s="94"/>
       <c r="E414" s="15"/>
       <c r="F414" s="15"/>
       <c r="G414" s="15"/>
     </row>
     <row r="415" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="81"/>
-      <c r="B415" s="82"/>
-      <c r="C415" s="83"/>
-      <c r="D415" s="84"/>
+      <c r="A415" s="82"/>
+      <c r="B415" s="78"/>
+      <c r="C415" s="93"/>
+      <c r="D415" s="94"/>
       <c r="E415" s="15"/>
       <c r="F415" s="15"/>
       <c r="G415" s="15"/>
     </row>
     <row r="416" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="81"/>
-      <c r="B416" s="82"/>
-      <c r="C416" s="83"/>
-      <c r="D416" s="84"/>
+      <c r="A416" s="82"/>
+      <c r="B416" s="78"/>
+      <c r="C416" s="93"/>
+      <c r="D416" s="94"/>
       <c r="E416" s="15"/>
       <c r="F416" s="15"/>
       <c r="G416" s="15"/>
     </row>
-    <row r="417" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="81"/>
-      <c r="B417" s="82"/>
-      <c r="C417" s="83"/>
-      <c r="D417" s="84"/>
+    <row r="417" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="82"/>
+      <c r="B417" s="78"/>
+      <c r="C417" s="93"/>
+      <c r="D417" s="94"/>
       <c r="E417" s="15"/>
       <c r="F417" s="15"/>
       <c r="G417" s="15"/>
     </row>
-    <row r="418" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="81"/>
-      <c r="B418" s="82"/>
-      <c r="C418" s="83"/>
-      <c r="D418" s="84"/>
+    <row r="418" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="82"/>
+      <c r="B418" s="78"/>
+      <c r="C418" s="93"/>
+      <c r="D418" s="94"/>
       <c r="E418" s="15"/>
       <c r="F418" s="15"/>
       <c r="G418" s="15"/>
     </row>
-    <row r="419" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="81"/>
-      <c r="B419" s="82"/>
-      <c r="C419" s="83"/>
-      <c r="D419" s="84"/>
+    <row r="419" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="82"/>
+      <c r="B419" s="78"/>
+      <c r="C419" s="93"/>
+      <c r="D419" s="94"/>
       <c r="E419" s="15"/>
       <c r="F419" s="15"/>
       <c r="G419" s="15"/>
     </row>
-    <row r="420" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="81"/>
-      <c r="B420" s="82"/>
-      <c r="C420" s="83"/>
-      <c r="D420" s="84"/>
+    <row r="420" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="82"/>
+      <c r="B420" s="78"/>
+      <c r="C420" s="93"/>
+      <c r="D420" s="94"/>
       <c r="E420" s="15"/>
       <c r="F420" s="15"/>
       <c r="G420" s="15"/>
     </row>
-    <row r="421" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="81"/>
-      <c r="B421" s="82"/>
-      <c r="C421" s="83"/>
-      <c r="D421" s="84"/>
+    <row r="421" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="82"/>
+      <c r="B421" s="78"/>
+      <c r="C421" s="93"/>
+      <c r="D421" s="94"/>
       <c r="E421" s="15"/>
       <c r="F421" s="15"/>
       <c r="G421" s="15"/>
     </row>
-    <row r="422" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="81"/>
-      <c r="B422" s="82"/>
-      <c r="C422" s="83"/>
-      <c r="D422" s="84"/>
+    <row r="422" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="82"/>
+      <c r="B422" s="78"/>
+      <c r="C422" s="93"/>
+      <c r="D422" s="94"/>
       <c r="E422" s="15"/>
       <c r="F422" s="15"/>
       <c r="G422" s="15"/>
     </row>
-    <row r="423" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="81"/>
-      <c r="B423" s="82"/>
-      <c r="C423" s="83"/>
-      <c r="D423" s="84"/>
+    <row r="423" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A423" s="82"/>
+      <c r="B423" s="78"/>
+      <c r="C423" s="93"/>
+      <c r="D423" s="94"/>
       <c r="E423" s="15"/>
       <c r="F423" s="15"/>
       <c r="G423" s="15"/>
     </row>
-    <row r="424" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="81"/>
-      <c r="B424" s="82"/>
-      <c r="C424" s="83"/>
-      <c r="D424" s="84"/>
+    <row r="424" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A424" s="82"/>
+      <c r="B424" s="78"/>
+      <c r="C424" s="93"/>
+      <c r="D424" s="94"/>
       <c r="E424" s="15"/>
       <c r="F424" s="15"/>
       <c r="G424" s="15"/>
     </row>
-    <row r="425" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="81"/>
-      <c r="B425" s="82"/>
-      <c r="C425" s="83"/>
-      <c r="D425" s="84"/>
+    <row r="425" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="82"/>
+      <c r="B425" s="78"/>
+      <c r="C425" s="93"/>
+      <c r="D425" s="94"/>
       <c r="E425" s="15"/>
       <c r="F425" s="15"/>
       <c r="G425" s="15"/>
     </row>
-    <row r="426" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="81"/>
-      <c r="B426" s="82"/>
-      <c r="C426" s="83"/>
-      <c r="D426" s="84"/>
+    <row r="426" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="82"/>
+      <c r="B426" s="78"/>
+      <c r="C426" s="93"/>
+      <c r="D426" s="94"/>
       <c r="E426" s="15"/>
       <c r="F426" s="15"/>
       <c r="G426" s="15"/>
     </row>
-    <row r="427" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="81"/>
-      <c r="B427" s="82"/>
-      <c r="C427" s="83"/>
-      <c r="D427" s="84"/>
+    <row r="427" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A427" s="82"/>
+      <c r="B427" s="78"/>
+      <c r="C427" s="93"/>
+      <c r="D427" s="94"/>
       <c r="E427" s="15"/>
       <c r="F427" s="15"/>
       <c r="G427" s="15"/>
     </row>
-    <row r="428" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="81"/>
-      <c r="B428" s="82"/>
-      <c r="C428" s="83"/>
-      <c r="D428" s="84"/>
+    <row r="428" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="82"/>
+      <c r="B428" s="78"/>
+      <c r="C428" s="93"/>
+      <c r="D428" s="94"/>
       <c r="E428" s="15"/>
       <c r="F428" s="15"/>
       <c r="G428" s="15"/>
     </row>
-    <row r="429" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="81"/>
-      <c r="B429" s="82"/>
-      <c r="C429" s="83"/>
-      <c r="D429" s="84"/>
+    <row r="429" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="82"/>
+      <c r="B429" s="78"/>
+      <c r="C429" s="93"/>
+      <c r="D429" s="94"/>
       <c r="E429" s="15"/>
       <c r="F429" s="15"/>
       <c r="G429" s="15"/>
     </row>
-    <row r="430" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="81"/>
-      <c r="B430" s="82"/>
-      <c r="C430" s="83"/>
-      <c r="D430" s="84"/>
+    <row r="430" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="82"/>
+      <c r="B430" s="78"/>
+      <c r="C430" s="93"/>
+      <c r="D430" s="94"/>
       <c r="E430" s="15"/>
       <c r="F430" s="15"/>
       <c r="G430" s="15"/>
     </row>
-    <row r="431" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="81"/>
-      <c r="B431" s="82"/>
-      <c r="C431" s="83"/>
-      <c r="D431" s="84"/>
+    <row r="431" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A431" s="82"/>
+      <c r="B431" s="78"/>
+      <c r="C431" s="93"/>
+      <c r="D431" s="94"/>
       <c r="E431" s="15"/>
       <c r="F431" s="15"/>
       <c r="G431" s="15"/>
     </row>
-    <row r="432" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="81"/>
-      <c r="B432" s="82"/>
-      <c r="C432" s="83"/>
-      <c r="D432" s="84"/>
-      <c r="E432" s="15"/>
-      <c r="F432" s="15"/>
-      <c r="G432" s="15"/>
-    </row>
-    <row r="433" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="81"/>
-      <c r="B433" s="82"/>
-      <c r="C433" s="83"/>
-      <c r="D433" s="84"/>
-      <c r="E433" s="15"/>
-      <c r="F433" s="15"/>
-      <c r="G433" s="15"/>
+    <row r="432" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A432" s="86"/>
+      <c r="B432" s="86"/>
+      <c r="C432" s="86"/>
+      <c r="D432" s="86"/>
+      <c r="E432" s="86"/>
+      <c r="F432" s="86"/>
+      <c r="G432" s="86"/>
+      <c r="H432" s="86"/>
+      <c r="I432" s="86"/>
+      <c r="J432" s="86"/>
+      <c r="K432" s="86"/>
+      <c r="L432" s="86"/>
+      <c r="M432" s="49"/>
+    </row>
+    <row r="433" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A433" s="86"/>
+      <c r="B433" s="86"/>
+      <c r="C433" s="86"/>
+      <c r="D433" s="86"/>
+      <c r="E433" s="86"/>
+      <c r="F433" s="86"/>
+      <c r="G433" s="86"/>
+      <c r="H433" s="86"/>
+      <c r="I433" s="86"/>
+      <c r="J433" s="86"/>
+      <c r="K433" s="86"/>
+      <c r="L433" s="86"/>
+      <c r="M433" s="49"/>
     </row>
     <row r="434" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A434" s="75"/>
-      <c r="B434" s="75"/>
-      <c r="C434" s="75"/>
-      <c r="D434" s="75"/>
-      <c r="E434" s="75"/>
-      <c r="F434" s="75"/>
-      <c r="G434" s="75"/>
-      <c r="H434" s="75"/>
-      <c r="I434" s="75"/>
-      <c r="J434" s="75"/>
-      <c r="K434" s="75"/>
-      <c r="L434" s="75"/>
+      <c r="A434" s="86"/>
+      <c r="B434" s="86"/>
+      <c r="C434" s="86"/>
+      <c r="D434" s="86"/>
+      <c r="E434" s="86"/>
+      <c r="F434" s="86"/>
+      <c r="G434" s="86"/>
+      <c r="H434" s="86"/>
+      <c r="I434" s="86"/>
+      <c r="J434" s="86"/>
+      <c r="K434" s="86"/>
+      <c r="L434" s="86"/>
       <c r="M434" s="49"/>
     </row>
     <row r="435" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A435" s="75"/>
-      <c r="B435" s="75"/>
-      <c r="C435" s="75"/>
-      <c r="D435" s="75"/>
-      <c r="E435" s="75"/>
-      <c r="F435" s="75"/>
-      <c r="G435" s="75"/>
-      <c r="H435" s="75"/>
-      <c r="I435" s="75"/>
-      <c r="J435" s="75"/>
-      <c r="K435" s="75"/>
-      <c r="L435" s="75"/>
+      <c r="A435" s="86"/>
+      <c r="B435" s="86"/>
+      <c r="C435" s="86"/>
+      <c r="D435" s="86"/>
+      <c r="E435" s="86"/>
+      <c r="F435" s="86"/>
+      <c r="G435" s="86"/>
+      <c r="H435" s="86"/>
+      <c r="I435" s="86"/>
+      <c r="J435" s="86"/>
+      <c r="K435" s="86"/>
+      <c r="L435" s="86"/>
       <c r="M435" s="49"/>
     </row>
     <row r="436" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A436" s="75"/>
-      <c r="B436" s="75"/>
-      <c r="C436" s="75"/>
-      <c r="D436" s="75"/>
-      <c r="E436" s="75"/>
-      <c r="F436" s="75"/>
-      <c r="G436" s="75"/>
-      <c r="H436" s="75"/>
-      <c r="I436" s="75"/>
-      <c r="J436" s="75"/>
-      <c r="K436" s="75"/>
-      <c r="L436" s="75"/>
+      <c r="A436" s="86"/>
+      <c r="B436" s="86"/>
+      <c r="C436" s="86"/>
+      <c r="D436" s="86"/>
+      <c r="E436" s="86"/>
+      <c r="F436" s="86"/>
+      <c r="G436" s="86"/>
+      <c r="H436" s="86"/>
+      <c r="I436" s="86"/>
+      <c r="J436" s="86"/>
+      <c r="K436" s="86"/>
+      <c r="L436" s="86"/>
       <c r="M436" s="49"/>
     </row>
-    <row r="437" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A437" s="75"/>
-      <c r="B437" s="75"/>
-      <c r="C437" s="75"/>
-      <c r="D437" s="75"/>
-      <c r="E437" s="75"/>
-      <c r="F437" s="75"/>
-      <c r="G437" s="75"/>
-      <c r="H437" s="75"/>
-      <c r="I437" s="75"/>
-      <c r="J437" s="75"/>
-      <c r="K437" s="75"/>
-      <c r="L437" s="75"/>
-      <c r="M437" s="49"/>
-    </row>
-    <row r="438" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A438" s="75"/>
-      <c r="B438" s="75"/>
-      <c r="C438" s="75"/>
-      <c r="D438" s="75"/>
-      <c r="E438" s="75"/>
-      <c r="F438" s="75"/>
-      <c r="G438" s="75"/>
-      <c r="H438" s="75"/>
-      <c r="I438" s="75"/>
-      <c r="J438" s="75"/>
-      <c r="K438" s="75"/>
-      <c r="L438" s="75"/>
-      <c r="M438" s="49"/>
+    <row r="437" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A437" s="96"/>
+      <c r="B437" s="97"/>
+      <c r="C437" s="92"/>
+      <c r="D437" s="91"/>
+      <c r="E437" s="17"/>
+      <c r="F437" s="17"/>
+      <c r="G437" s="17"/>
+    </row>
+    <row r="438" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A438" s="96"/>
+      <c r="B438" s="97"/>
+      <c r="C438" s="92"/>
+      <c r="D438" s="91"/>
+      <c r="E438" s="17"/>
+      <c r="F438" s="17"/>
+      <c r="G438" s="17"/>
     </row>
     <row r="439" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="76"/>
-      <c r="B439" s="77"/>
-      <c r="C439" s="78"/>
-      <c r="D439" s="74"/>
+      <c r="A439" s="96"/>
+      <c r="B439" s="97"/>
+      <c r="C439" s="92"/>
+      <c r="D439" s="91"/>
       <c r="E439" s="17"/>
       <c r="F439" s="17"/>
       <c r="G439" s="17"/>
     </row>
     <row r="440" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="76"/>
-      <c r="B440" s="77"/>
-      <c r="C440" s="78"/>
-      <c r="D440" s="74"/>
+      <c r="A440" s="96"/>
+      <c r="B440" s="97"/>
+      <c r="C440" s="92"/>
+      <c r="D440" s="91"/>
       <c r="E440" s="17"/>
       <c r="F440" s="17"/>
       <c r="G440" s="17"/>
     </row>
     <row r="441" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="76"/>
-      <c r="B441" s="77"/>
-      <c r="C441" s="78"/>
-      <c r="D441" s="74"/>
+      <c r="A441" s="96"/>
+      <c r="B441" s="97"/>
+      <c r="C441" s="92"/>
+      <c r="D441" s="91"/>
       <c r="E441" s="17"/>
       <c r="F441" s="17"/>
       <c r="G441" s="17"/>
     </row>
     <row r="442" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="76"/>
-      <c r="B442" s="77"/>
-      <c r="C442" s="78"/>
-      <c r="D442" s="74"/>
+      <c r="A442" s="96"/>
+      <c r="B442" s="97"/>
+      <c r="C442" s="92"/>
+      <c r="D442" s="91"/>
       <c r="E442" s="17"/>
       <c r="F442" s="17"/>
       <c r="G442" s="17"/>
     </row>
     <row r="443" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="76"/>
-      <c r="B443" s="77"/>
-      <c r="C443" s="78"/>
-      <c r="D443" s="74"/>
+      <c r="A443" s="96"/>
+      <c r="B443" s="97"/>
+      <c r="C443" s="92"/>
+      <c r="D443" s="91"/>
       <c r="E443" s="17"/>
       <c r="F443" s="17"/>
       <c r="G443" s="17"/>
     </row>
     <row r="444" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="76"/>
-      <c r="B444" s="77"/>
-      <c r="C444" s="78"/>
-      <c r="D444" s="74"/>
+      <c r="A444" s="96"/>
+      <c r="B444" s="97"/>
+      <c r="C444" s="92"/>
+      <c r="D444" s="91"/>
       <c r="E444" s="17"/>
       <c r="F444" s="17"/>
       <c r="G444" s="17"/>
     </row>
     <row r="445" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="76"/>
-      <c r="B445" s="77"/>
-      <c r="C445" s="78"/>
-      <c r="D445" s="74"/>
+      <c r="A445" s="96"/>
+      <c r="B445" s="97"/>
+      <c r="C445" s="92"/>
+      <c r="D445" s="91"/>
       <c r="E445" s="17"/>
       <c r="F445" s="17"/>
       <c r="G445" s="17"/>
     </row>
     <row r="446" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="76"/>
-      <c r="B446" s="77"/>
-      <c r="C446" s="78"/>
-      <c r="D446" s="74"/>
+      <c r="A446" s="96"/>
+      <c r="B446" s="97"/>
+      <c r="C446" s="92"/>
+      <c r="D446" s="91"/>
       <c r="E446" s="17"/>
       <c r="F446" s="17"/>
       <c r="G446" s="17"/>
     </row>
     <row r="447" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="76"/>
-      <c r="B447" s="77"/>
-      <c r="C447" s="78"/>
-      <c r="D447" s="74"/>
+      <c r="A447" s="96"/>
+      <c r="B447" s="97"/>
+      <c r="C447" s="92"/>
+      <c r="D447" s="91"/>
       <c r="E447" s="17"/>
       <c r="F447" s="17"/>
       <c r="G447" s="17"/>
     </row>
     <row r="448" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="76"/>
-      <c r="B448" s="77"/>
-      <c r="C448" s="78"/>
-      <c r="D448" s="74"/>
+      <c r="A448" s="96"/>
+      <c r="B448" s="97"/>
+      <c r="C448" s="92"/>
+      <c r="D448" s="91"/>
       <c r="E448" s="17"/>
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
     </row>
     <row r="449" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="76"/>
-      <c r="B449" s="77"/>
-      <c r="C449" s="78"/>
-      <c r="D449" s="74"/>
+      <c r="A449" s="96"/>
+      <c r="B449" s="97"/>
+      <c r="C449" s="92"/>
+      <c r="D449" s="91"/>
       <c r="E449" s="17"/>
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
     </row>
     <row r="450" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="76"/>
-      <c r="B450" s="77"/>
-      <c r="C450" s="78"/>
-      <c r="D450" s="74"/>
+      <c r="A450" s="96"/>
+      <c r="B450" s="97"/>
+      <c r="C450" s="92"/>
+      <c r="D450" s="91"/>
       <c r="E450" s="17"/>
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
     </row>
     <row r="451" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="76"/>
-      <c r="B451" s="77"/>
-      <c r="C451" s="78"/>
-      <c r="D451" s="74"/>
+      <c r="A451" s="96"/>
+      <c r="B451" s="97"/>
+      <c r="C451" s="92"/>
+      <c r="D451" s="91"/>
       <c r="E451" s="17"/>
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
     </row>
     <row r="452" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="76"/>
-      <c r="B452" s="77"/>
-      <c r="C452" s="78"/>
-      <c r="D452" s="74"/>
+      <c r="A452" s="96"/>
+      <c r="B452" s="97"/>
+      <c r="C452" s="92"/>
+      <c r="D452" s="91"/>
       <c r="E452" s="17"/>
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
     </row>
     <row r="453" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="76"/>
-      <c r="B453" s="77"/>
-      <c r="C453" s="78"/>
-      <c r="D453" s="74"/>
+      <c r="A453" s="96"/>
+      <c r="B453" s="97"/>
+      <c r="C453" s="92"/>
+      <c r="D453" s="91"/>
       <c r="E453" s="17"/>
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
     </row>
     <row r="454" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="76"/>
-      <c r="B454" s="77"/>
-      <c r="C454" s="78"/>
-      <c r="D454" s="74"/>
+      <c r="A454" s="96"/>
+      <c r="B454" s="97"/>
+      <c r="C454" s="92"/>
+      <c r="D454" s="91"/>
       <c r="E454" s="17"/>
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
     </row>
     <row r="455" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="76"/>
-      <c r="B455" s="77"/>
-      <c r="C455" s="78"/>
-      <c r="D455" s="74"/>
+      <c r="A455" s="96"/>
+      <c r="B455" s="97"/>
+      <c r="C455" s="92"/>
+      <c r="D455" s="91"/>
       <c r="E455" s="17"/>
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
     </row>
     <row r="456" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="76"/>
-      <c r="B456" s="77"/>
-      <c r="C456" s="78"/>
-      <c r="D456" s="74"/>
+      <c r="A456" s="96"/>
+      <c r="B456" s="97"/>
+      <c r="C456" s="92"/>
+      <c r="D456" s="91"/>
       <c r="E456" s="17"/>
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
     </row>
     <row r="457" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="76"/>
-      <c r="B457" s="77"/>
-      <c r="C457" s="78"/>
-      <c r="D457" s="74"/>
+      <c r="A457" s="96"/>
+      <c r="B457" s="97"/>
+      <c r="C457" s="92"/>
+      <c r="D457" s="91"/>
       <c r="E457" s="17"/>
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
     </row>
     <row r="458" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="76"/>
-      <c r="B458" s="77"/>
-      <c r="C458" s="78"/>
-      <c r="D458" s="74"/>
+      <c r="A458" s="96"/>
+      <c r="B458" s="97"/>
+      <c r="C458" s="92"/>
+      <c r="D458" s="91"/>
       <c r="E458" s="17"/>
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
     </row>
     <row r="459" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="76"/>
-      <c r="B459" s="77"/>
-      <c r="C459" s="78"/>
-      <c r="D459" s="74"/>
+      <c r="A459" s="96"/>
+      <c r="B459" s="97"/>
+      <c r="C459" s="92"/>
+      <c r="D459" s="91"/>
       <c r="E459" s="17"/>
       <c r="F459" s="17"/>
       <c r="G459" s="17"/>
     </row>
     <row r="460" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="76"/>
-      <c r="B460" s="77"/>
-      <c r="C460" s="78"/>
-      <c r="D460" s="74"/>
+      <c r="A460" s="96"/>
+      <c r="B460" s="97"/>
+      <c r="C460" s="92"/>
+      <c r="D460" s="91"/>
       <c r="E460" s="17"/>
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
     </row>
     <row r="461" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="76"/>
-      <c r="B461" s="77"/>
-      <c r="C461" s="78"/>
-      <c r="D461" s="74"/>
+      <c r="A461" s="96"/>
+      <c r="B461" s="97"/>
+      <c r="C461" s="92"/>
+      <c r="D461" s="91"/>
       <c r="E461" s="17"/>
       <c r="F461" s="17"/>
       <c r="G461" s="17"/>
     </row>
     <row r="462" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="76"/>
-      <c r="B462" s="77"/>
-      <c r="C462" s="78"/>
-      <c r="D462" s="74"/>
+      <c r="A462" s="96"/>
+      <c r="B462" s="97"/>
+      <c r="C462" s="92"/>
+      <c r="D462" s="91"/>
       <c r="E462" s="17"/>
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
     </row>
     <row r="463" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="76"/>
-      <c r="B463" s="77"/>
-      <c r="C463" s="78"/>
-      <c r="D463" s="74"/>
+      <c r="A463" s="96"/>
+      <c r="B463" s="97"/>
+      <c r="C463" s="92"/>
+      <c r="D463" s="91"/>
       <c r="E463" s="17"/>
       <c r="F463" s="17"/>
       <c r="G463" s="17"/>
     </row>
     <row r="464" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="76"/>
-      <c r="B464" s="77"/>
-      <c r="C464" s="78"/>
-      <c r="D464" s="74"/>
+      <c r="A464" s="96"/>
+      <c r="B464" s="97"/>
+      <c r="C464" s="92"/>
+      <c r="D464" s="91"/>
       <c r="E464" s="17"/>
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
     </row>
     <row r="465" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="76"/>
-      <c r="B465" s="77"/>
-      <c r="C465" s="78"/>
-      <c r="D465" s="74"/>
+      <c r="A465" s="96"/>
+      <c r="B465" s="97"/>
+      <c r="C465" s="92"/>
+      <c r="D465" s="91"/>
       <c r="E465" s="17"/>
       <c r="F465" s="17"/>
       <c r="G465" s="17"/>
     </row>
     <row r="466" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="76"/>
-      <c r="B466" s="77"/>
-      <c r="C466" s="78"/>
-      <c r="D466" s="74"/>
+      <c r="A466" s="96"/>
+      <c r="B466" s="97"/>
+      <c r="C466" s="92"/>
+      <c r="D466" s="91"/>
       <c r="E466" s="17"/>
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
     </row>
     <row r="467" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="76"/>
-      <c r="B467" s="77"/>
-      <c r="C467" s="78"/>
-      <c r="D467" s="74"/>
+      <c r="A467" s="96"/>
+      <c r="B467" s="97"/>
+      <c r="C467" s="92"/>
+      <c r="D467" s="91"/>
       <c r="E467" s="17"/>
       <c r="F467" s="17"/>
       <c r="G467" s="17"/>
     </row>
     <row r="468" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="76"/>
-      <c r="B468" s="77"/>
-      <c r="C468" s="78"/>
-      <c r="D468" s="74"/>
+      <c r="A468" s="96"/>
+      <c r="B468" s="97"/>
+      <c r="C468" s="92"/>
+      <c r="D468" s="91"/>
       <c r="E468" s="17"/>
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
     </row>
     <row r="469" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="76"/>
-      <c r="B469" s="77"/>
-      <c r="C469" s="78"/>
-      <c r="D469" s="74"/>
+      <c r="A469" s="96"/>
+      <c r="B469" s="97"/>
+      <c r="C469" s="92"/>
+      <c r="D469" s="91"/>
       <c r="E469" s="17"/>
       <c r="F469" s="17"/>
       <c r="G469" s="17"/>
     </row>
     <row r="470" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="76"/>
-      <c r="B470" s="77"/>
-      <c r="C470" s="78"/>
-      <c r="D470" s="74"/>
+      <c r="A470" s="96"/>
+      <c r="B470" s="97"/>
+      <c r="C470" s="92"/>
+      <c r="D470" s="91"/>
       <c r="E470" s="17"/>
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
     </row>
     <row r="471" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="76"/>
-      <c r="B471" s="77"/>
-      <c r="C471" s="78"/>
-      <c r="D471" s="74"/>
+      <c r="A471" s="96"/>
+      <c r="B471" s="97"/>
+      <c r="C471" s="92"/>
+      <c r="D471" s="91"/>
       <c r="E471" s="17"/>
       <c r="F471" s="17"/>
       <c r="G471" s="17"/>
     </row>
     <row r="472" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="76"/>
-      <c r="B472" s="77"/>
-      <c r="C472" s="78"/>
-      <c r="D472" s="74"/>
+      <c r="A472" s="96"/>
+      <c r="B472" s="97"/>
+      <c r="C472" s="92"/>
+      <c r="D472" s="91"/>
       <c r="E472" s="17"/>
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
     </row>
     <row r="473" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="76"/>
-      <c r="B473" s="77"/>
-      <c r="C473" s="78"/>
-      <c r="D473" s="74"/>
+      <c r="A473" s="96"/>
+      <c r="B473" s="97"/>
+      <c r="C473" s="92"/>
+      <c r="D473" s="91"/>
       <c r="E473" s="17"/>
       <c r="F473" s="17"/>
       <c r="G473" s="17"/>
     </row>
     <row r="474" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="76"/>
-      <c r="B474" s="77"/>
-      <c r="C474" s="78"/>
-      <c r="D474" s="74"/>
+      <c r="A474" s="96"/>
+      <c r="B474" s="97"/>
+      <c r="C474" s="92"/>
+      <c r="D474" s="91"/>
       <c r="E474" s="17"/>
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
     </row>
     <row r="475" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="76"/>
-      <c r="B475" s="77"/>
-      <c r="C475" s="78"/>
-      <c r="D475" s="74"/>
+      <c r="A475" s="96"/>
+      <c r="B475" s="97"/>
+      <c r="C475" s="92"/>
+      <c r="D475" s="91"/>
       <c r="E475" s="17"/>
       <c r="F475" s="17"/>
       <c r="G475" s="17"/>
     </row>
     <row r="476" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="76"/>
-      <c r="B476" s="77"/>
-      <c r="C476" s="78"/>
-      <c r="D476" s="74"/>
+      <c r="A476" s="96"/>
+      <c r="B476" s="97"/>
+      <c r="C476" s="92"/>
+      <c r="D476" s="91"/>
       <c r="E476" s="17"/>
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
     </row>
     <row r="477" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="76"/>
-      <c r="B477" s="77"/>
-      <c r="C477" s="78"/>
-      <c r="D477" s="74"/>
+      <c r="A477" s="96"/>
+      <c r="B477" s="97"/>
+      <c r="C477" s="92"/>
+      <c r="D477" s="91"/>
       <c r="E477" s="17"/>
       <c r="F477" s="17"/>
       <c r="G477" s="17"/>
     </row>
     <row r="478" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A478" s="76"/>
-      <c r="B478" s="77"/>
-      <c r="C478" s="78"/>
-      <c r="D478" s="74"/>
+      <c r="A478" s="96"/>
+      <c r="B478" s="97"/>
+      <c r="C478" s="92"/>
+      <c r="D478" s="91"/>
       <c r="E478" s="17"/>
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
     </row>
     <row r="479" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A479" s="76"/>
-      <c r="B479" s="77"/>
-      <c r="C479" s="78"/>
-      <c r="D479" s="74"/>
+      <c r="A479" s="96"/>
+      <c r="B479" s="97"/>
+      <c r="C479" s="92"/>
+      <c r="D479" s="91"/>
       <c r="E479" s="17"/>
       <c r="F479" s="17"/>
       <c r="G479" s="17"/>
     </row>
     <row r="480" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A480" s="76"/>
-      <c r="B480" s="77"/>
-      <c r="C480" s="78"/>
-      <c r="D480" s="74"/>
+      <c r="A480" s="96"/>
+      <c r="B480" s="97"/>
+      <c r="C480" s="92"/>
+      <c r="D480" s="91"/>
       <c r="E480" s="17"/>
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
     </row>
     <row r="481" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="76"/>
-      <c r="B481" s="77"/>
-      <c r="C481" s="78"/>
-      <c r="D481" s="74"/>
+      <c r="A481" s="96"/>
+      <c r="B481" s="97"/>
+      <c r="C481" s="92"/>
+      <c r="D481" s="91"/>
       <c r="E481" s="17"/>
       <c r="F481" s="17"/>
       <c r="G481" s="17"/>
     </row>
     <row r="482" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="76"/>
-      <c r="B482" s="77"/>
-      <c r="C482" s="78"/>
-      <c r="D482" s="74"/>
+      <c r="A482" s="96"/>
+      <c r="B482" s="97"/>
+      <c r="C482" s="92"/>
+      <c r="D482" s="91"/>
       <c r="E482" s="17"/>
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
     </row>
     <row r="483" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A483" s="76"/>
-      <c r="B483" s="77"/>
-      <c r="C483" s="78"/>
-      <c r="D483" s="74"/>
+      <c r="A483" s="96"/>
+      <c r="B483" s="97"/>
+      <c r="C483" s="92"/>
+      <c r="D483" s="91"/>
       <c r="E483" s="17"/>
       <c r="F483" s="17"/>
       <c r="G483" s="17"/>
     </row>
     <row r="484" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="76"/>
-      <c r="B484" s="77"/>
-      <c r="C484" s="78"/>
-      <c r="D484" s="74"/>
+      <c r="A484" s="96"/>
+      <c r="B484" s="97"/>
+      <c r="C484" s="92"/>
+      <c r="D484" s="91"/>
       <c r="E484" s="17"/>
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
     </row>
     <row r="485" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="76"/>
-      <c r="B485" s="77"/>
-      <c r="C485" s="78"/>
-      <c r="D485" s="74"/>
+      <c r="A485" s="96"/>
+      <c r="B485" s="97"/>
+      <c r="C485" s="92"/>
+      <c r="D485" s="91"/>
       <c r="E485" s="17"/>
       <c r="F485" s="17"/>
       <c r="G485" s="17"/>
     </row>
     <row r="486" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="76"/>
-      <c r="B486" s="77"/>
-      <c r="C486" s="78"/>
-      <c r="D486" s="74"/>
+      <c r="A486" s="96"/>
+      <c r="B486" s="97"/>
+      <c r="C486" s="92"/>
+      <c r="D486" s="91"/>
       <c r="E486" s="17"/>
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
     </row>
     <row r="487" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="76"/>
-      <c r="B487" s="77"/>
-      <c r="C487" s="78"/>
-      <c r="D487" s="74"/>
+      <c r="A487" s="96"/>
+      <c r="B487" s="97"/>
+      <c r="C487" s="92"/>
+      <c r="D487" s="91"/>
       <c r="E487" s="17"/>
       <c r="F487" s="17"/>
       <c r="G487" s="17"/>
     </row>
     <row r="488" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="76"/>
-      <c r="B488" s="77"/>
-      <c r="C488" s="78"/>
-      <c r="D488" s="74"/>
+      <c r="A488" s="96"/>
+      <c r="B488" s="97"/>
+      <c r="C488" s="92"/>
+      <c r="D488" s="91"/>
       <c r="E488" s="17"/>
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
     </row>
     <row r="489" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A489" s="76"/>
-      <c r="B489" s="77"/>
-      <c r="C489" s="78"/>
-      <c r="D489" s="74"/>
+      <c r="A489" s="96"/>
+      <c r="B489" s="97"/>
+      <c r="C489" s="92"/>
+      <c r="D489" s="91"/>
       <c r="E489" s="17"/>
       <c r="F489" s="17"/>
       <c r="G489" s="17"/>
     </row>
     <row r="490" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="76"/>
-      <c r="B490" s="77"/>
-      <c r="C490" s="78"/>
-      <c r="D490" s="74"/>
+      <c r="A490" s="96"/>
+      <c r="B490" s="97"/>
+      <c r="C490" s="92"/>
+      <c r="D490" s="91"/>
       <c r="E490" s="17"/>
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
     </row>
     <row r="491" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="76"/>
-      <c r="B491" s="77"/>
-      <c r="C491" s="78"/>
-      <c r="D491" s="74"/>
+      <c r="A491" s="96"/>
+      <c r="B491" s="97"/>
+      <c r="C491" s="92"/>
+      <c r="D491" s="91"/>
       <c r="E491" s="17"/>
       <c r="F491" s="17"/>
       <c r="G491" s="17"/>
     </row>
     <row r="492" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="76"/>
-      <c r="B492" s="77"/>
-      <c r="C492" s="78"/>
-      <c r="D492" s="74"/>
+      <c r="A492" s="96"/>
+      <c r="B492" s="97"/>
+      <c r="C492" s="92"/>
+      <c r="D492" s="91"/>
       <c r="E492" s="17"/>
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
     </row>
     <row r="493" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="76"/>
-      <c r="B493" s="77"/>
-      <c r="C493" s="78"/>
-      <c r="D493" s="74"/>
+      <c r="A493" s="96"/>
+      <c r="B493" s="97"/>
+      <c r="C493" s="92"/>
+      <c r="D493" s="91"/>
       <c r="E493" s="17"/>
       <c r="F493" s="17"/>
       <c r="G493" s="17"/>
     </row>
     <row r="494" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="76"/>
-      <c r="B494" s="77"/>
-      <c r="C494" s="78"/>
-      <c r="D494" s="74"/>
+      <c r="A494" s="96"/>
+      <c r="B494" s="97"/>
+      <c r="C494" s="92"/>
+      <c r="D494" s="91"/>
       <c r="E494" s="17"/>
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
     </row>
     <row r="495" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="76"/>
-      <c r="B495" s="77"/>
-      <c r="C495" s="78"/>
-      <c r="D495" s="74"/>
+      <c r="A495" s="96"/>
+      <c r="B495" s="97"/>
+      <c r="C495" s="92"/>
+      <c r="D495" s="91"/>
       <c r="E495" s="17"/>
       <c r="F495" s="17"/>
       <c r="G495" s="17"/>
     </row>
     <row r="496" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="76"/>
-      <c r="B496" s="77"/>
-      <c r="C496" s="78"/>
-      <c r="D496" s="74"/>
+      <c r="A496" s="96"/>
+      <c r="B496" s="97"/>
+      <c r="C496" s="92"/>
+      <c r="D496" s="91"/>
       <c r="E496" s="17"/>
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
     </row>
     <row r="497" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="76"/>
-      <c r="B497" s="77"/>
-      <c r="C497" s="78"/>
-      <c r="D497" s="74"/>
+      <c r="A497" s="96"/>
+      <c r="B497" s="97"/>
+      <c r="C497" s="92"/>
+      <c r="D497" s="91"/>
       <c r="E497" s="17"/>
       <c r="F497" s="17"/>
       <c r="G497" s="17"/>
     </row>
     <row r="498" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A498" s="76"/>
-      <c r="B498" s="77"/>
-      <c r="C498" s="78"/>
-      <c r="D498" s="74"/>
+      <c r="A498" s="96"/>
+      <c r="B498" s="97"/>
+      <c r="C498" s="92"/>
+      <c r="D498" s="91"/>
       <c r="E498" s="17"/>
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
     </row>
     <row r="499" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="76"/>
-      <c r="B499" s="77"/>
-      <c r="C499" s="78"/>
-      <c r="D499" s="74"/>
+      <c r="A499" s="96"/>
+      <c r="B499" s="97"/>
+      <c r="C499" s="92"/>
+      <c r="D499" s="91"/>
       <c r="E499" s="17"/>
       <c r="F499" s="17"/>
       <c r="G499" s="17"/>
     </row>
     <row r="500" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="76"/>
-      <c r="B500" s="77"/>
-      <c r="C500" s="78"/>
-      <c r="D500" s="74"/>
+      <c r="A500" s="96"/>
+      <c r="B500" s="97"/>
+      <c r="C500" s="92"/>
+      <c r="D500" s="91"/>
       <c r="E500" s="17"/>
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
     </row>
     <row r="501" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="76"/>
-      <c r="B501" s="77"/>
-      <c r="C501" s="78"/>
-      <c r="D501" s="74"/>
+      <c r="A501" s="96"/>
+      <c r="B501" s="97"/>
+      <c r="C501" s="92"/>
+      <c r="D501" s="91"/>
       <c r="E501" s="17"/>
       <c r="F501" s="17"/>
       <c r="G501" s="17"/>
     </row>
     <row r="502" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="76"/>
-      <c r="B502" s="77"/>
-      <c r="C502" s="78"/>
-      <c r="D502" s="74"/>
+      <c r="A502" s="96"/>
+      <c r="B502" s="97"/>
+      <c r="C502" s="92"/>
+      <c r="D502" s="91"/>
       <c r="E502" s="17"/>
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
     </row>
     <row r="503" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="76"/>
-      <c r="B503" s="77"/>
-      <c r="C503" s="78"/>
-      <c r="D503" s="74"/>
+      <c r="A503" s="96"/>
+      <c r="B503" s="97"/>
+      <c r="C503" s="92"/>
+      <c r="D503" s="91"/>
       <c r="E503" s="17"/>
       <c r="F503" s="17"/>
       <c r="G503" s="17"/>
     </row>
     <row r="504" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="76"/>
-      <c r="B504" s="77"/>
-      <c r="C504" s="78"/>
-      <c r="D504" s="74"/>
+      <c r="A504" s="96"/>
+      <c r="B504" s="97"/>
+      <c r="C504" s="92"/>
+      <c r="D504" s="91"/>
       <c r="E504" s="17"/>
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
     </row>
     <row r="505" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A505" s="76"/>
-      <c r="B505" s="77"/>
-      <c r="C505" s="78"/>
-      <c r="D505" s="74"/>
+      <c r="A505" s="96"/>
+      <c r="B505" s="97"/>
+      <c r="C505" s="92"/>
+      <c r="D505" s="91"/>
       <c r="E505" s="17"/>
       <c r="F505" s="17"/>
       <c r="G505" s="17"/>
     </row>
     <row r="506" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A506" s="76"/>
-      <c r="B506" s="77"/>
-      <c r="C506" s="78"/>
-      <c r="D506" s="74"/>
+      <c r="A506" s="96"/>
+      <c r="B506" s="97"/>
+      <c r="C506" s="92"/>
+      <c r="D506" s="91"/>
       <c r="E506" s="17"/>
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
     </row>
     <row r="507" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A507" s="76"/>
-      <c r="B507" s="77"/>
-      <c r="C507" s="78"/>
-      <c r="D507" s="74"/>
+      <c r="A507" s="96"/>
+      <c r="B507" s="97"/>
+      <c r="C507" s="92"/>
+      <c r="D507" s="91"/>
       <c r="E507" s="17"/>
       <c r="F507" s="17"/>
       <c r="G507" s="17"/>
     </row>
     <row r="508" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A508" s="76"/>
-      <c r="B508" s="77"/>
-      <c r="C508" s="78"/>
-      <c r="D508" s="74"/>
+      <c r="A508" s="96"/>
+      <c r="B508" s="97"/>
+      <c r="C508" s="92"/>
+      <c r="D508" s="91"/>
       <c r="E508" s="17"/>
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
     </row>
     <row r="509" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A509" s="76"/>
-      <c r="B509" s="77"/>
-      <c r="C509" s="78"/>
-      <c r="D509" s="74"/>
+      <c r="A509" s="96"/>
+      <c r="B509" s="97"/>
+      <c r="C509" s="92"/>
+      <c r="D509" s="91"/>
       <c r="E509" s="17"/>
       <c r="F509" s="17"/>
       <c r="G509" s="17"/>
     </row>
     <row r="510" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A510" s="76"/>
-      <c r="B510" s="77"/>
-      <c r="C510" s="78"/>
-      <c r="D510" s="74"/>
+      <c r="A510" s="96"/>
+      <c r="B510" s="97"/>
+      <c r="C510" s="57"/>
+      <c r="D510" s="58"/>
       <c r="E510" s="17"/>
       <c r="F510" s="17"/>
       <c r="G510" s="17"/>
     </row>
     <row r="511" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A511" s="76"/>
-      <c r="B511" s="77"/>
-      <c r="C511" s="78"/>
-      <c r="D511" s="74"/>
+      <c r="A511" s="96"/>
+      <c r="B511" s="97"/>
+      <c r="C511" s="92"/>
+      <c r="D511" s="91"/>
       <c r="E511" s="17"/>
       <c r="F511" s="17"/>
       <c r="G511" s="17"/>
     </row>
     <row r="512" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A512" s="76"/>
-      <c r="B512" s="77"/>
-      <c r="C512" s="57"/>
-      <c r="D512" s="58"/>
+      <c r="A512" s="96"/>
+      <c r="B512" s="97"/>
+      <c r="C512" s="92"/>
+      <c r="D512" s="91"/>
       <c r="E512" s="17"/>
       <c r="F512" s="17"/>
       <c r="G512" s="17"/>
     </row>
     <row r="513" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A513" s="76"/>
-      <c r="B513" s="77"/>
-      <c r="C513" s="78"/>
-      <c r="D513" s="74"/>
+      <c r="A513" s="96"/>
+      <c r="B513" s="97"/>
+      <c r="C513" s="92"/>
+      <c r="D513" s="91"/>
       <c r="E513" s="17"/>
       <c r="F513" s="17"/>
       <c r="G513" s="17"/>
     </row>
     <row r="514" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A514" s="76"/>
-      <c r="B514" s="77"/>
-      <c r="C514" s="78"/>
-      <c r="D514" s="74"/>
+      <c r="A514" s="96"/>
+      <c r="B514" s="97"/>
+      <c r="C514" s="92"/>
+      <c r="D514" s="91"/>
       <c r="E514" s="17"/>
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
     </row>
     <row r="515" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A515" s="76"/>
-      <c r="B515" s="77"/>
-      <c r="C515" s="78"/>
-      <c r="D515" s="74"/>
+      <c r="A515" s="96"/>
+      <c r="B515" s="97"/>
+      <c r="C515" s="92"/>
+      <c r="D515" s="91"/>
       <c r="E515" s="17"/>
       <c r="F515" s="17"/>
       <c r="G515" s="17"/>
     </row>
     <row r="516" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A516" s="76"/>
-      <c r="B516" s="77"/>
-      <c r="C516" s="78"/>
-      <c r="D516" s="74"/>
+      <c r="A516" s="96"/>
+      <c r="B516" s="97"/>
+      <c r="C516" s="92"/>
+      <c r="D516" s="91"/>
       <c r="E516" s="17"/>
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
     </row>
     <row r="517" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A517" s="76"/>
-      <c r="B517" s="77"/>
-      <c r="C517" s="78"/>
-      <c r="D517" s="74"/>
+      <c r="A517" s="96"/>
+      <c r="B517" s="97"/>
+      <c r="C517" s="92"/>
+      <c r="D517" s="91"/>
       <c r="E517" s="17"/>
       <c r="F517" s="17"/>
       <c r="G517" s="17"/>
     </row>
     <row r="518" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A518" s="76"/>
-      <c r="B518" s="77"/>
-      <c r="C518" s="78"/>
-      <c r="D518" s="74"/>
+      <c r="A518" s="96"/>
+      <c r="B518" s="97"/>
+      <c r="C518" s="92"/>
+      <c r="D518" s="91"/>
       <c r="E518" s="17"/>
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
     </row>
     <row r="519" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A519" s="76"/>
-      <c r="B519" s="77"/>
-      <c r="C519" s="78"/>
-      <c r="D519" s="74"/>
+      <c r="A519" s="96"/>
+      <c r="B519" s="97"/>
+      <c r="C519" s="95"/>
+      <c r="D519" s="91"/>
       <c r="E519" s="17"/>
       <c r="F519" s="17"/>
       <c r="G519" s="17"/>
     </row>
     <row r="520" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="76"/>
-      <c r="B520" s="77"/>
-      <c r="C520" s="78"/>
-      <c r="D520" s="74"/>
+      <c r="A520" s="96"/>
+      <c r="B520" s="97"/>
+      <c r="C520" s="95"/>
+      <c r="D520" s="91"/>
       <c r="E520" s="17"/>
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
     </row>
     <row r="521" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="76"/>
-      <c r="B521" s="77"/>
-      <c r="C521" s="73"/>
-      <c r="D521" s="74"/>
+      <c r="A521" s="96"/>
+      <c r="B521" s="97"/>
+      <c r="C521" s="95"/>
+      <c r="D521" s="91"/>
       <c r="E521" s="17"/>
       <c r="F521" s="17"/>
       <c r="G521" s="17"/>
     </row>
     <row r="522" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="76"/>
-      <c r="B522" s="77"/>
-      <c r="C522" s="73"/>
-      <c r="D522" s="74"/>
+      <c r="A522" s="96"/>
+      <c r="B522" s="97"/>
+      <c r="C522" s="95"/>
+      <c r="D522" s="91"/>
       <c r="E522" s="17"/>
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
     </row>
     <row r="523" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="76"/>
-      <c r="B523" s="77"/>
-      <c r="C523" s="73"/>
-      <c r="D523" s="74"/>
+      <c r="A523" s="96"/>
+      <c r="B523" s="97"/>
+      <c r="C523" s="95"/>
+      <c r="D523" s="91"/>
       <c r="E523" s="17"/>
       <c r="F523" s="17"/>
       <c r="G523" s="17"/>
     </row>
     <row r="524" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="76"/>
-      <c r="B524" s="77"/>
-      <c r="C524" s="73"/>
-      <c r="D524" s="74"/>
+      <c r="A524" s="96"/>
+      <c r="B524" s="97"/>
+      <c r="C524" s="95"/>
+      <c r="D524" s="91"/>
       <c r="E524" s="17"/>
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
     </row>
     <row r="525" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="76"/>
-      <c r="B525" s="77"/>
-      <c r="C525" s="73"/>
-      <c r="D525" s="74"/>
+      <c r="A525" s="96"/>
+      <c r="B525" s="97"/>
+      <c r="C525" s="95"/>
+      <c r="D525" s="91"/>
       <c r="E525" s="17"/>
       <c r="F525" s="17"/>
       <c r="G525" s="17"/>
     </row>
     <row r="526" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="76"/>
-      <c r="B526" s="77"/>
-      <c r="C526" s="73"/>
-      <c r="D526" s="74"/>
+      <c r="A526" s="96"/>
+      <c r="B526" s="97"/>
+      <c r="C526" s="95"/>
+      <c r="D526" s="91"/>
       <c r="E526" s="17"/>
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
     </row>
     <row r="527" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="76"/>
-      <c r="B527" s="77"/>
-      <c r="C527" s="73"/>
-      <c r="D527" s="74"/>
+      <c r="A527" s="96"/>
+      <c r="B527" s="97"/>
+      <c r="C527" s="95"/>
+      <c r="D527" s="91"/>
       <c r="E527" s="17"/>
       <c r="F527" s="17"/>
       <c r="G527" s="17"/>
     </row>
-    <row r="528" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A528" s="76"/>
-      <c r="B528" s="77"/>
-      <c r="C528" s="73"/>
-      <c r="D528" s="74"/>
-      <c r="E528" s="17"/>
-      <c r="F528" s="17"/>
-      <c r="G528" s="17"/>
-    </row>
-    <row r="529" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A529" s="76"/>
-      <c r="B529" s="77"/>
-      <c r="C529" s="73"/>
-      <c r="D529" s="74"/>
-      <c r="E529" s="17"/>
-      <c r="F529" s="17"/>
-      <c r="G529" s="17"/>
-    </row>
-    <row r="1048556" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E1048556" s="4">
+    <row r="1048554" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E1048554" s="4">
         <f>COUNT(E1:E9)</f>
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="171">
+  <mergeCells count="169">
+    <mergeCell ref="C519:C527"/>
+    <mergeCell ref="D519:D527"/>
+    <mergeCell ref="A432:L436"/>
+    <mergeCell ref="A437:A527"/>
+    <mergeCell ref="B437:B527"/>
+    <mergeCell ref="C437:C457"/>
+    <mergeCell ref="D437:D457"/>
+    <mergeCell ref="C458:C464"/>
+    <mergeCell ref="D458:D464"/>
+    <mergeCell ref="C465:C470"/>
+    <mergeCell ref="D465:D470"/>
+    <mergeCell ref="C471:C479"/>
+    <mergeCell ref="D471:D479"/>
+    <mergeCell ref="C480:C482"/>
+    <mergeCell ref="D480:D482"/>
+    <mergeCell ref="C483:C488"/>
+    <mergeCell ref="D483:D488"/>
+    <mergeCell ref="C489:C496"/>
+    <mergeCell ref="D489:D496"/>
+    <mergeCell ref="C497:C501"/>
+    <mergeCell ref="D497:D501"/>
+    <mergeCell ref="C502:C506"/>
+    <mergeCell ref="D502:D506"/>
+    <mergeCell ref="C507:C509"/>
+    <mergeCell ref="D507:D509"/>
+    <mergeCell ref="C511:C518"/>
+    <mergeCell ref="D369:D372"/>
+    <mergeCell ref="C373:C375"/>
+    <mergeCell ref="D373:D375"/>
+    <mergeCell ref="C376:C377"/>
+    <mergeCell ref="D376:D377"/>
+    <mergeCell ref="A378:L382"/>
+    <mergeCell ref="A383:A431"/>
+    <mergeCell ref="B383:B431"/>
+    <mergeCell ref="C383:C392"/>
+    <mergeCell ref="D383:D392"/>
+    <mergeCell ref="C393:C399"/>
+    <mergeCell ref="D393:D399"/>
+    <mergeCell ref="C400:C410"/>
+    <mergeCell ref="D400:D410"/>
+    <mergeCell ref="C411:C415"/>
+    <mergeCell ref="D411:D415"/>
+    <mergeCell ref="C416:C425"/>
+    <mergeCell ref="D416:D425"/>
+    <mergeCell ref="C426:C431"/>
+    <mergeCell ref="D426:D431"/>
+    <mergeCell ref="D511:D518"/>
+    <mergeCell ref="A332:L336"/>
+    <mergeCell ref="A337:A377"/>
+    <mergeCell ref="B337:B377"/>
+    <mergeCell ref="C337:C341"/>
+    <mergeCell ref="D337:D341"/>
+    <mergeCell ref="C342:C343"/>
+    <mergeCell ref="D342:D343"/>
+    <mergeCell ref="C344:C345"/>
+    <mergeCell ref="D344:D345"/>
+    <mergeCell ref="C346:C348"/>
+    <mergeCell ref="D346:D348"/>
+    <mergeCell ref="C349:C353"/>
+    <mergeCell ref="D349:D353"/>
+    <mergeCell ref="C354:C358"/>
+    <mergeCell ref="D354:D358"/>
+    <mergeCell ref="C359:C360"/>
+    <mergeCell ref="D359:D360"/>
+    <mergeCell ref="C361:C362"/>
+    <mergeCell ref="D361:D362"/>
+    <mergeCell ref="C363:C364"/>
+    <mergeCell ref="D363:D364"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="D367:D368"/>
+    <mergeCell ref="C369:C372"/>
+    <mergeCell ref="A302:A331"/>
+    <mergeCell ref="B302:B331"/>
+    <mergeCell ref="C302:C307"/>
+    <mergeCell ref="D302:D307"/>
+    <mergeCell ref="C308:C315"/>
+    <mergeCell ref="D308:D315"/>
+    <mergeCell ref="C316:C319"/>
+    <mergeCell ref="D316:D319"/>
+    <mergeCell ref="C320:C327"/>
+    <mergeCell ref="D320:D327"/>
+    <mergeCell ref="C328:C331"/>
+    <mergeCell ref="D328:D331"/>
+    <mergeCell ref="A241:A300"/>
+    <mergeCell ref="B241:B300"/>
+    <mergeCell ref="C241:C248"/>
+    <mergeCell ref="D241:D248"/>
+    <mergeCell ref="C249:C255"/>
+    <mergeCell ref="D249:D255"/>
+    <mergeCell ref="C256:C260"/>
+    <mergeCell ref="D256:D260"/>
+    <mergeCell ref="C261:C266"/>
+    <mergeCell ref="D261:D266"/>
+    <mergeCell ref="C267:C275"/>
+    <mergeCell ref="D267:D275"/>
+    <mergeCell ref="C276:C281"/>
+    <mergeCell ref="D276:D281"/>
+    <mergeCell ref="C282:C288"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="C289:C295"/>
+    <mergeCell ref="D289:D295"/>
+    <mergeCell ref="C296:C300"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="C212:C218"/>
+    <mergeCell ref="D212:D218"/>
+    <mergeCell ref="C219:C226"/>
+    <mergeCell ref="D219:D226"/>
+    <mergeCell ref="C227:C231"/>
+    <mergeCell ref="D227:D231"/>
+    <mergeCell ref="C232:C235"/>
+    <mergeCell ref="D232:D235"/>
+    <mergeCell ref="C236:C239"/>
+    <mergeCell ref="D236:D239"/>
+    <mergeCell ref="C169:C174"/>
+    <mergeCell ref="D169:D174"/>
+    <mergeCell ref="C175:C180"/>
+    <mergeCell ref="D175:D180"/>
+    <mergeCell ref="C181:C187"/>
+    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="C188:C199"/>
+    <mergeCell ref="D188:D199"/>
+    <mergeCell ref="C200:C211"/>
+    <mergeCell ref="D200:D211"/>
+    <mergeCell ref="A96:A239"/>
+    <mergeCell ref="B96:B239"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="C119:C122"/>
+    <mergeCell ref="D119:D122"/>
+    <mergeCell ref="C123:C128"/>
+    <mergeCell ref="D123:D128"/>
+    <mergeCell ref="C129:C135"/>
+    <mergeCell ref="D129:D135"/>
+    <mergeCell ref="C136:C143"/>
+    <mergeCell ref="D136:D143"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C150:C155"/>
+    <mergeCell ref="D150:D155"/>
+    <mergeCell ref="C156:C162"/>
+    <mergeCell ref="D156:D162"/>
+    <mergeCell ref="C163:C168"/>
+    <mergeCell ref="D163:D168"/>
+    <mergeCell ref="A22:A40"/>
+    <mergeCell ref="B22:B40"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="D34:D39"/>
     <mergeCell ref="A2:A16"/>
     <mergeCell ref="B2:B16"/>
     <mergeCell ref="C3:C5"/>
@@ -15729,204 +15982,61 @@
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A22:A42"/>
-    <mergeCell ref="B22:B42"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A98:A241"/>
-    <mergeCell ref="B98:B241"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="C121:C124"/>
-    <mergeCell ref="D121:D124"/>
-    <mergeCell ref="C125:C130"/>
-    <mergeCell ref="D125:D130"/>
-    <mergeCell ref="C131:C137"/>
-    <mergeCell ref="D131:D137"/>
-    <mergeCell ref="C138:C145"/>
-    <mergeCell ref="D138:D145"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="C148:C151"/>
-    <mergeCell ref="D148:D151"/>
-    <mergeCell ref="C152:C157"/>
-    <mergeCell ref="D152:D157"/>
-    <mergeCell ref="C158:C164"/>
-    <mergeCell ref="D158:D164"/>
-    <mergeCell ref="C165:C170"/>
-    <mergeCell ref="D165:D170"/>
-    <mergeCell ref="C171:C176"/>
-    <mergeCell ref="D171:D176"/>
-    <mergeCell ref="C177:C182"/>
-    <mergeCell ref="D177:D182"/>
-    <mergeCell ref="C183:C189"/>
-    <mergeCell ref="D183:D189"/>
-    <mergeCell ref="C190:C201"/>
-    <mergeCell ref="D190:D201"/>
-    <mergeCell ref="C202:C213"/>
-    <mergeCell ref="D202:D213"/>
-    <mergeCell ref="C214:C220"/>
-    <mergeCell ref="D214:D220"/>
-    <mergeCell ref="C221:C228"/>
-    <mergeCell ref="D221:D228"/>
-    <mergeCell ref="C229:C233"/>
-    <mergeCell ref="D229:D233"/>
-    <mergeCell ref="C234:C237"/>
-    <mergeCell ref="D234:D237"/>
-    <mergeCell ref="C238:C241"/>
-    <mergeCell ref="D238:D241"/>
-    <mergeCell ref="A243:A302"/>
-    <mergeCell ref="B243:B302"/>
-    <mergeCell ref="C243:C250"/>
-    <mergeCell ref="D243:D250"/>
-    <mergeCell ref="C251:C257"/>
-    <mergeCell ref="D251:D257"/>
-    <mergeCell ref="C258:C262"/>
-    <mergeCell ref="D258:D262"/>
-    <mergeCell ref="C263:C268"/>
-    <mergeCell ref="D263:D268"/>
-    <mergeCell ref="C269:C277"/>
-    <mergeCell ref="D269:D277"/>
-    <mergeCell ref="C278:C283"/>
-    <mergeCell ref="D278:D283"/>
-    <mergeCell ref="C284:C290"/>
-    <mergeCell ref="D284:D290"/>
-    <mergeCell ref="C291:C297"/>
-    <mergeCell ref="D291:D297"/>
-    <mergeCell ref="C298:C302"/>
-    <mergeCell ref="D298:D302"/>
-    <mergeCell ref="A304:A333"/>
-    <mergeCell ref="B304:B333"/>
-    <mergeCell ref="C304:C309"/>
-    <mergeCell ref="D304:D309"/>
-    <mergeCell ref="C310:C317"/>
-    <mergeCell ref="D310:D317"/>
-    <mergeCell ref="C318:C321"/>
-    <mergeCell ref="D318:D321"/>
-    <mergeCell ref="C322:C329"/>
-    <mergeCell ref="D322:D329"/>
-    <mergeCell ref="C330:C333"/>
-    <mergeCell ref="D330:D333"/>
-    <mergeCell ref="A334:L338"/>
-    <mergeCell ref="A339:A379"/>
-    <mergeCell ref="B339:B379"/>
-    <mergeCell ref="C339:C343"/>
-    <mergeCell ref="D339:D343"/>
-    <mergeCell ref="C344:C345"/>
-    <mergeCell ref="D344:D345"/>
-    <mergeCell ref="C346:C347"/>
-    <mergeCell ref="D346:D347"/>
-    <mergeCell ref="C348:C350"/>
-    <mergeCell ref="D348:D350"/>
-    <mergeCell ref="C351:C355"/>
-    <mergeCell ref="D351:D355"/>
-    <mergeCell ref="C356:C360"/>
-    <mergeCell ref="D356:D360"/>
-    <mergeCell ref="C361:C362"/>
-    <mergeCell ref="D361:D362"/>
-    <mergeCell ref="C363:C364"/>
-    <mergeCell ref="D363:D364"/>
-    <mergeCell ref="C365:C366"/>
-    <mergeCell ref="D365:D366"/>
-    <mergeCell ref="C369:C370"/>
-    <mergeCell ref="D369:D370"/>
-    <mergeCell ref="C371:C374"/>
-    <mergeCell ref="D509:D511"/>
-    <mergeCell ref="C513:C520"/>
-    <mergeCell ref="D371:D374"/>
-    <mergeCell ref="C375:C377"/>
-    <mergeCell ref="D375:D377"/>
-    <mergeCell ref="C378:C379"/>
-    <mergeCell ref="D378:D379"/>
-    <mergeCell ref="A380:L384"/>
-    <mergeCell ref="A385:A433"/>
-    <mergeCell ref="B385:B433"/>
-    <mergeCell ref="C385:C394"/>
-    <mergeCell ref="D385:D394"/>
-    <mergeCell ref="C395:C401"/>
-    <mergeCell ref="D395:D401"/>
-    <mergeCell ref="C402:C412"/>
-    <mergeCell ref="D402:D412"/>
-    <mergeCell ref="C413:C417"/>
-    <mergeCell ref="D413:D417"/>
-    <mergeCell ref="C418:C427"/>
-    <mergeCell ref="D418:D427"/>
-    <mergeCell ref="C428:C433"/>
-    <mergeCell ref="D428:D433"/>
-    <mergeCell ref="D513:D520"/>
-    <mergeCell ref="C521:C529"/>
-    <mergeCell ref="D521:D529"/>
-    <mergeCell ref="A434:L438"/>
-    <mergeCell ref="A439:A529"/>
-    <mergeCell ref="B439:B529"/>
-    <mergeCell ref="C439:C459"/>
-    <mergeCell ref="D439:D459"/>
-    <mergeCell ref="C460:C466"/>
-    <mergeCell ref="D460:D466"/>
-    <mergeCell ref="C467:C472"/>
-    <mergeCell ref="D467:D472"/>
-    <mergeCell ref="C473:C481"/>
-    <mergeCell ref="D473:D481"/>
-    <mergeCell ref="C482:C484"/>
-    <mergeCell ref="D482:D484"/>
-    <mergeCell ref="C485:C490"/>
-    <mergeCell ref="D485:D490"/>
-    <mergeCell ref="C491:C498"/>
-    <mergeCell ref="D491:D498"/>
-    <mergeCell ref="C499:C503"/>
-    <mergeCell ref="D499:D503"/>
-    <mergeCell ref="C504:C508"/>
-    <mergeCell ref="D504:D508"/>
-    <mergeCell ref="C509:C511"/>
   </mergeCells>
-  <conditionalFormatting sqref="J339:J379 J385:J433 J439:J1048576 J2:J4 J43:J333 J6:J20 J23:J40">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="None">
+  <conditionalFormatting sqref="J337:J377 J383:J431 J437:J1048576 J2:J4 J42:J331 J6:J20 J23:J39">
+    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="None">
       <formula>NOT(ISERROR(SEARCH("None",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J339:J379 J385:J433 J439:J1048576 J2:J4 J43:J333 J6:J20 J23:J40">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Completed">
+  <conditionalFormatting sqref="J337:J377 J383:J431 J437:J1048576 J2:J4 J42:J331 J6:J20 J23:J39">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="ongoing">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="ongoing">
       <formula>NOT(ISERROR(SEARCH("ongoing",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Not started">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J339:J379 J385:J433 J439:J1048576 J2:J4 J43:J333 J6:J20 J23:J40">
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="fail">
+  <conditionalFormatting sqref="J337:J377 J383:J431 J437:J1048576 J2:J4 J42:J331 J6:J20 J23:J39">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="fail">
       <formula>NOT(ISERROR(SEARCH("fail",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="pass">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="pass">
       <formula>NOT(ISERROR(SEARCH("pass",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J18:J20 J43:J333 J339:J379 J385:J433 J439:J1048576">
+  <conditionalFormatting sqref="J41">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="None">
+      <formula>NOT(ISERROR(SEARCH("None",J41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Completed">
+      <formula>NOT(ISERROR(SEARCH("Completed",J41)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="ongoing">
+      <formula>NOT(ISERROR(SEARCH("ongoing",J41)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Not started">
+      <formula>NOT(ISERROR(SEARCH("Not started",J41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="fail">
+      <formula>NOT(ISERROR(SEARCH("fail",J41)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="pass">
+      <formula>NOT(ISERROR(SEARCH("pass",J41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J18:J20 J437:J1048576 J337:J377 J383:J431 J42:J331">
       <formula1>"Not started,ongoing,Completed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L17:L20 L43:L241 L243:L302 L304:L333">
-      <formula1>#REF!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H98:H241 H243:H297">
-      <formula1>#REF!</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:K20 K43:K333 K339:K379 K385:K433 K439:K1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L302:L331 L241:L300 L42:L239 K17:L20 K437:K1048576 K337:K377 K383:K431 K42:K331 H96:H239 H241:H295">
       <formula1>#REF!</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15948,16 +16058,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="62" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E1" s="61"/>
     </row>
@@ -15966,13 +16076,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E2" s="64"/>
     </row>
@@ -15981,13 +16091,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E3" s="64"/>
     </row>
@@ -15996,13 +16106,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E4" s="64"/>
     </row>
@@ -16011,13 +16121,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E5" s="64"/>
     </row>
@@ -16026,13 +16136,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E6" s="64"/>
     </row>
@@ -16041,13 +16151,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E7" s="64"/>
     </row>
@@ -16056,28 +16166,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E9" s="64"/>
     </row>
@@ -16086,28 +16196,28 @@
         <v>15</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E10" s="64"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E11" s="64"/>
     </row>
@@ -16137,25 +16247,25 @@
       <c r="D15" s="66"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="95" t="s">
-        <v>198</v>
-      </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
+      <c r="A17" s="98" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="63">
         <v>15</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E18" s="64"/>
     </row>
@@ -16164,13 +16274,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E19" s="64"/>
     </row>
@@ -16179,13 +16289,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E20" s="64"/>
     </row>
@@ -16194,13 +16304,13 @@
         <v>12</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E21" s="64"/>
     </row>
@@ -16209,13 +16319,13 @@
         <v>11</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E22" s="64"/>
     </row>
@@ -16224,13 +16334,13 @@
         <v>10</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E23" s="64"/>
     </row>
@@ -16239,13 +16349,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E24" s="64"/>
     </row>
@@ -16254,13 +16364,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E25" s="64"/>
     </row>
@@ -16269,81 +16379,81 @@
         <v>7</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E26" s="64"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="63" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E27" s="64"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="95" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="95"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="95"/>
+      <c r="A33" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="63" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B34" s="63" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E34" s="64"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="63" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D35" s="63" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E35" s="64"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E36" s="64"/>
     </row>
@@ -16352,13 +16462,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E37" s="64"/>
     </row>
@@ -16367,13 +16477,13 @@
         <v>5</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C38" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E38" s="64"/>
     </row>
@@ -16382,13 +16492,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D39" s="63" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E39" s="64"/>
     </row>
@@ -16397,13 +16507,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D40" s="63" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E40" s="64"/>
     </row>
@@ -16412,13 +16522,13 @@
         <v>2</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D41" s="63" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E41" s="64"/>
     </row>
@@ -16427,13 +16537,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="63" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E42" s="64"/>
     </row>
@@ -16442,13 +16552,13 @@
         <v>0</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E43" s="64"/>
     </row>
@@ -16511,21 +16621,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
-        <v>240</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
+      <c r="A1" s="98" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
     </row>
     <row r="2" spans="1:14" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="60" t="s">
@@ -16589,10 +16699,10 @@
         <v>72</v>
       </c>
       <c r="G3" s="63" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H3" s="63" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I3" s="63" t="s">
         <v>76</v>
@@ -16619,10 +16729,10 @@
         <v>78</v>
       </c>
       <c r="G4" s="63" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H4" s="63" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I4" s="63" t="s">
         <v>18</v>
@@ -16649,10 +16759,10 @@
         <v>82</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="H5" s="63" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I5" s="63" t="s">
         <v>18</v>
@@ -16679,10 +16789,10 @@
         <v>86</v>
       </c>
       <c r="G6" s="63" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H6" s="63" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I6" s="63" t="s">
         <v>18</v>
@@ -16709,10 +16819,10 @@
         <v>90</v>
       </c>
       <c r="G7" s="63" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H7" s="63" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I7" s="63" t="s">
         <v>18</v>
@@ -16739,10 +16849,10 @@
         <v>94</v>
       </c>
       <c r="G8" s="63" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H8" s="63" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I8" s="63" t="s">
         <v>18</v>
@@ -16753,7 +16863,7 @@
       <c r="K8" s="65"/>
       <c r="L8" s="65"/>
       <c r="M8" s="63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N8" s="64"/>
     </row>
@@ -16764,19 +16874,19 @@
         <v>2</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="63">
         <v>7</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I9" s="63" t="s">
         <v>18</v>
@@ -16787,7 +16897,7 @@
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
       <c r="M9" s="63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N9" s="64"/>
     </row>
@@ -16800,13 +16910,13 @@
         <v>8</v>
       </c>
       <c r="F10" s="63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="63" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H10" s="63" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I10" s="63" t="s">
         <v>18</v>
@@ -16817,7 +16927,7 @@
       <c r="K10" s="65"/>
       <c r="L10" s="65"/>
       <c r="M10" s="63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N10" s="64"/>
     </row>
@@ -16830,13 +16940,13 @@
         <v>9</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" s="63" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H11" s="63" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I11" s="63" t="s">
         <v>18</v>
@@ -16847,7 +16957,7 @@
       <c r="K11" s="65"/>
       <c r="L11" s="65"/>
       <c r="M11" s="63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N11" s="64"/>
     </row>
@@ -16858,19 +16968,19 @@
         <v>3</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E12" s="63">
         <v>10</v>
       </c>
       <c r="F12" s="63" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G12" s="63" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H12" s="63" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I12" s="63" t="s">
         <v>32</v>
@@ -16881,7 +16991,7 @@
       <c r="K12" s="65"/>
       <c r="L12" s="65"/>
       <c r="M12" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="64"/>
     </row>
@@ -16894,24 +17004,24 @@
         <v>11</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="63" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H13" s="63" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I13" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K13" s="65"/>
       <c r="L13" s="65"/>
       <c r="M13" s="63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N13" s="64"/>
     </row>
@@ -16924,24 +17034,24 @@
         <v>12</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="63" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I14" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="65"/>
       <c r="M14" s="63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N14" s="64"/>
     </row>
@@ -16952,30 +17062,30 @@
         <v>4</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E15" s="63">
         <v>13</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G15" s="63" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I15" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="63" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K15" s="65"/>
       <c r="L15" s="65"/>
       <c r="M15" s="63" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N15" s="64"/>
     </row>
@@ -16988,24 +17098,24 @@
         <v>14</v>
       </c>
       <c r="F16" s="63" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G16" s="63" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H16" s="63" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="I16" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J16" s="63" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K16" s="65"/>
       <c r="L16" s="65"/>
       <c r="M16" s="63" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N16" s="64"/>
     </row>
@@ -17018,24 +17128,24 @@
         <v>15</v>
       </c>
       <c r="F17" s="63" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I17" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="63" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K17" s="65"/>
       <c r="L17" s="65"/>
       <c r="M17" s="63" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="N17" s="64"/>
     </row>
@@ -17048,24 +17158,24 @@
         <v>16</v>
       </c>
       <c r="F18" s="63" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G18" s="63" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I18" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J18" s="63" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K18" s="65"/>
       <c r="L18" s="65"/>
       <c r="M18" s="63" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N18" s="64"/>
     </row>
@@ -17076,30 +17186,30 @@
         <v>5</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E19" s="63">
         <v>17</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G19" s="63" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J19" s="63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K19" s="65"/>
       <c r="L19" s="65"/>
       <c r="M19" s="63" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="N19" s="64"/>
     </row>
@@ -17112,24 +17222,24 @@
         <v>18</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G20" s="63" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="I20" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="63" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="K20" s="65"/>
       <c r="L20" s="65"/>
       <c r="M20" s="63" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="N20" s="64"/>
     </row>
@@ -17142,24 +17252,24 @@
         <v>19</v>
       </c>
       <c r="F21" s="63" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G21" s="63" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H21" s="63" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I21" s="63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J21" s="63" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="K21" s="65"/>
       <c r="L21" s="65"/>
       <c r="M21" s="63" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N21" s="64"/>
     </row>
@@ -17170,30 +17280,30 @@
         <v>6</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E22" s="63">
         <v>20</v>
       </c>
       <c r="F22" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="H22" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="63" t="s">
-        <v>128</v>
-      </c>
       <c r="I22" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="J22" s="63" t="s">
         <v>130</v>
-      </c>
-      <c r="J22" s="63" t="s">
-        <v>131</v>
       </c>
       <c r="K22" s="65"/>
       <c r="L22" s="65"/>
       <c r="M22" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N22" s="64"/>
     </row>
@@ -17206,24 +17316,24 @@
         <v>21</v>
       </c>
       <c r="F23" s="63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G23" s="63" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H23" s="63" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I23" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23" s="63" t="s">
         <v>130</v>
-      </c>
-      <c r="J23" s="63" t="s">
-        <v>131</v>
       </c>
       <c r="K23" s="65"/>
       <c r="L23" s="65"/>
       <c r="M23" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N23" s="64"/>
     </row>
@@ -17236,24 +17346,24 @@
         <v>22</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G24" s="63" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I24" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="63" t="s">
         <v>130</v>
-      </c>
-      <c r="J24" s="63" t="s">
-        <v>131</v>
       </c>
       <c r="K24" s="65"/>
       <c r="L24" s="65"/>
       <c r="M24" s="63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N24" s="64"/>
     </row>
@@ -17266,24 +17376,24 @@
         <v>23</v>
       </c>
       <c r="F25" s="63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G25" s="63" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I25" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="63" t="s">
         <v>130</v>
-      </c>
-      <c r="J25" s="63" t="s">
-        <v>131</v>
       </c>
       <c r="K25" s="65"/>
       <c r="L25" s="65"/>
       <c r="M25" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N25" s="64"/>
     </row>
@@ -17296,24 +17406,24 @@
         <v>24</v>
       </c>
       <c r="F26" s="63" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" s="63" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I26" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K26" s="65"/>
       <c r="L26" s="65"/>
       <c r="M26" s="63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N26" s="64"/>
     </row>
@@ -17326,24 +17436,24 @@
         <v>25</v>
       </c>
       <c r="F27" s="63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G27" s="63" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I27" s="63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J27" s="63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K27" s="65"/>
       <c r="L27" s="65"/>
       <c r="M27" s="63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N27" s="64"/>
     </row>
@@ -17354,30 +17464,30 @@
         <v>7</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E28" s="63">
         <v>26</v>
       </c>
       <c r="F28" s="63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G28" s="63" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H28" s="63" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I28" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J28" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K28" s="65"/>
       <c r="L28" s="65"/>
       <c r="M28" s="63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N28" s="64"/>
     </row>
@@ -17413,38 +17523,38 @@
       <c r="M31" s="66"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="95" t="s">
-        <v>309</v>
-      </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="95"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="95"/>
-      <c r="J34" s="95"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="95"/>
-      <c r="M34" s="95"/>
+      <c r="A34" s="98" t="s">
+        <v>303</v>
+      </c>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
       <c r="N34" s="67"/>
     </row>
     <row r="35" spans="1:14" s="69" customFormat="1" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="60" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E35" s="60" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F35" s="68"/>
       <c r="G35" s="71"/>
@@ -17457,109 +17567,109 @@
     </row>
     <row r="36" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E36" s="63" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F36" s="64"/>
     </row>
     <row r="37" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="63" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E37" s="63" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F37" s="64"/>
     </row>
     <row r="38" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="63" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C38" s="63" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E38" s="63" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F38" s="64"/>
     </row>
     <row r="39" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="63" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D39" s="63" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E39" s="63" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F39" s="64"/>
     </row>
     <row r="40" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="63" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D40" s="63" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E40" s="63" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F40" s="64"/>
     </row>
     <row r="41" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="63" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D41" s="63" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E41" s="63" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F41" s="64"/>
     </row>
@@ -17571,10 +17681,10 @@
         <v>62</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E42" s="63" t="s">
         <v>63</v>
@@ -17589,10 +17699,10 @@
         <v>65</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E43" s="63" t="s">
         <v>66</v>
@@ -17607,10 +17717,10 @@
         <v>68</v>
       </c>
       <c r="C44" s="63" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D44" s="63" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E44" s="63" t="s">
         <v>69</v>
@@ -17622,88 +17732,88 @@
         <v>54</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C45" s="63" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D45" s="63" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E45" s="63" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F45" s="64"/>
     </row>
     <row r="46" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="63" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B46" s="63" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C46" s="63" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D46" s="63" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E46" s="63" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F46" s="64"/>
     </row>
     <row r="47" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="63" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B47" s="63" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D47" s="63" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F47" s="64"/>
     </row>
     <row r="48" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="63" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D48" s="63" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E48" s="63" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="F48" s="64"/>
     </row>
     <row r="49" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="63" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B49" s="63" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C49" s="63" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D49" s="63" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E49" s="63" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F49" s="64"/>
     </row>
@@ -17712,88 +17822,88 @@
         <v>43</v>
       </c>
       <c r="B50" s="63" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C50" s="63" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D50" s="63" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E50" s="63" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="F50" s="64"/>
     </row>
     <row r="51" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="63" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B51" s="63" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C51" s="63" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D51" s="63" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E51" s="63" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F51" s="64"/>
     </row>
     <row r="52" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="63" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B52" s="63" t="s">
         <v>58</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D52" s="63" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E52" s="63" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F52" s="64"/>
     </row>
     <row r="53" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="63" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B53" s="63" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C53" s="63" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D53" s="63" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E53" s="63" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F53" s="64"/>
     </row>
     <row r="54" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="63" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B54" s="63" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C54" s="63" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D54" s="63" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E54" s="63" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F54" s="64"/>
     </row>

--- a/plan_phase/majid/tp_miim_tx.xlsx
+++ b/plan_phase/majid/tp_miim_tx.xlsx
@@ -20,12 +20,12 @@
     <definedName name="Project_Start">#REF!</definedName>
     <definedName name="Scrolling_Increment">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="393">
   <si>
     <t>Section no.</t>
   </si>
@@ -333,9 +333,6 @@
     <t>tc_tx_huge_frame</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmit a massive frame exceeding standard limits (&gt;1536B) with MODER.HUGEN = 1. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Transmission completes fully on the MII path without being prematurely truncated or generating core exceptions. </t>
   </si>
   <si>
@@ -522,12 +519,6 @@
     <t>tc_tx_loopback</t>
   </si>
   <si>
-    <t xml:space="preserve">Turn on core loopback execution by setting MODER.LOOPBCK = 1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitted data sequences are internally switched straight into the receive logic; scoreboard confirms a direct bit-level match. </t>
-  </si>
-  <si>
     <t>Bypasses PHY layer for localized verification.</t>
   </si>
   <si>
@@ -1243,6 +1234,9 @@
   </si>
   <si>
     <t>m_wr_cfg_cov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit a massive frame exceeding maxfl with MODER.HUGEN = 1. </t>
   </si>
 </sst>
 </file>
@@ -1740,26 +1734,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1767,41 +1782,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1812,67 +1806,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="zHiddenText" xfId="2"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2324,10 +2258,10 @@
       <c r="W1"/>
     </row>
     <row r="2" spans="1:23 16384:16384" ht="145.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="77">
+      <c r="A2" s="95">
         <v>1</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="86" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="14">
@@ -2359,12 +2293,12 @@
       </c>
     </row>
     <row r="3" spans="1:23 16384:16384" ht="162.30000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="79">
+      <c r="A3" s="95"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="96">
         <v>2</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="93" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="4">
@@ -2390,12 +2324,12 @@
       </c>
     </row>
     <row r="4" spans="1:23 16384:16384" ht="132.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="79">
+      <c r="A4" s="95"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="96">
         <v>3</v>
       </c>
-      <c r="D4" s="80"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2419,12 +2353,12 @@
       </c>
     </row>
     <row r="5" spans="1:23 16384:16384" s="11" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="77"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79">
+      <c r="A5" s="95"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="96">
         <v>4</v>
       </c>
-      <c r="D5" s="80"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2455,12 +2389,12 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23 16384:16384" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="77"/>
-      <c r="B6" s="78"/>
-      <c r="C6" s="79">
+      <c r="A6" s="95"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="96">
         <v>3</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="93" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4">
@@ -2489,12 +2423,12 @@
       </c>
     </row>
     <row r="7" spans="1:23 16384:16384" ht="100.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="79">
+      <c r="A7" s="95"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="96">
         <v>4</v>
       </c>
-      <c r="D7" s="80"/>
+      <c r="D7" s="93"/>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2518,12 +2452,12 @@
       </c>
     </row>
     <row r="8" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="77"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="79">
+      <c r="A8" s="95"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="96">
         <v>4</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="93" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="4">
@@ -2549,12 +2483,12 @@
       </c>
     </row>
     <row r="9" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="77"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="79">
+      <c r="A9" s="95"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="96">
         <v>5</v>
       </c>
-      <c r="D9" s="80"/>
+      <c r="D9" s="93"/>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2576,12 +2510,12 @@
       </c>
     </row>
     <row r="10" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="79">
+      <c r="A10" s="95"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="96">
         <v>5</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="93" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="4">
@@ -2607,12 +2541,12 @@
       </c>
     </row>
     <row r="11" spans="1:23 16384:16384" ht="208.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="79">
+      <c r="A11" s="95"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="96">
         <v>6</v>
       </c>
-      <c r="D11" s="80"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2640,12 +2574,12 @@
       <c r="XFD11"/>
     </row>
     <row r="12" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="79">
+      <c r="A12" s="95"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="96">
         <v>7</v>
       </c>
-      <c r="D12" s="80"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2669,12 +2603,12 @@
       </c>
     </row>
     <row r="13" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79">
+      <c r="A13" s="95"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="96">
         <v>8</v>
       </c>
-      <c r="D13" s="80"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2698,12 +2632,12 @@
       </c>
     </row>
     <row r="14" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="79">
+      <c r="A14" s="95"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="96">
         <v>6</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D14" s="93" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="4">
@@ -2729,10 +2663,10 @@
       </c>
     </row>
     <row r="15" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
+      <c r="A15" s="95"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="93"/>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2756,10 +2690,10 @@
       </c>
     </row>
     <row r="16" spans="1:23 16384:16384" ht="57.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="80"/>
+      <c r="A16" s="95"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11048,16 +10982,16 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="77">
+      <c r="A22" s="95">
         <v>2</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="96">
         <v>1</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="93" t="s">
         <v>71</v>
       </c>
       <c r="E22" s="4">
@@ -11077,21 +11011,21 @@
         <v>75</v>
       </c>
       <c r="J22" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K22" s="34"/>
       <c r="L22" s="23" t="s">
         <v>76</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="93"/>
       <c r="E23" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -11114,14 +11048,14 @@
         <v>18</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="80"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="93"/>
       <c r="E24" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -11138,20 +11072,22 @@
       <c r="I24" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="J24" s="34"/>
+      <c r="J24" s="34" t="s">
+        <v>389</v>
+      </c>
       <c r="K24" s="34"/>
       <c r="L24" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="93"/>
       <c r="E25" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -11168,21 +11104,23 @@
       <c r="I25" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="J25" s="34"/>
+      <c r="J25" s="34" t="s">
+        <v>389</v>
+      </c>
       <c r="K25" s="34"/>
       <c r="L25" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="77"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="4">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -11191,245 +11129,245 @@
         <v>90</v>
       </c>
       <c r="G26" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="H26" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="I26" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>93</v>
-      </c>
       <c r="J26" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K26" s="34"/>
       <c r="L26" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="77"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="F27" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="H27" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="G27" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="H27" s="23" t="s">
+      <c r="I27" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>96</v>
-      </c>
       <c r="J27" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K27" s="34"/>
       <c r="L27" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="77"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="79">
+      <c r="A28" s="95"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="96">
         <v>2</v>
       </c>
-      <c r="D28" s="80" t="s">
-        <v>97</v>
+      <c r="D28" s="93" t="s">
+        <v>96</v>
       </c>
       <c r="E28" s="4">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="F28" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="H28" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="I28" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>101</v>
-      </c>
       <c r="J28" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K28" s="34"/>
       <c r="L28" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="77"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="93"/>
       <c r="E29" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="F29" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="H29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="I29" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>105</v>
-      </c>
       <c r="J29" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="77"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="93"/>
       <c r="E30" s="4">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F30" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="H30" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="I30" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="I30" s="23" t="s">
-        <v>109</v>
-      </c>
       <c r="J30" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K30" s="34"/>
       <c r="L30" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="77"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="79">
+      <c r="A31" s="95"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="96">
         <v>3</v>
       </c>
-      <c r="D31" s="80" t="s">
-        <v>110</v>
+      <c r="D31" s="93" t="s">
+        <v>109</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="F31" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="H31" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="I31" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="I31" s="23" t="s">
-        <v>114</v>
-      </c>
       <c r="J31" s="72" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="23" t="s">
         <v>32</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="77"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="93"/>
       <c r="E32" s="4">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="F32" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="H32" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="I32" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I32" s="23" t="s">
-        <v>118</v>
-      </c>
       <c r="J32" s="34" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K32" s="34"/>
       <c r="L32" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="77"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="80"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="93"/>
       <c r="E33" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F33" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="H33" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="I33" s="23" t="s">
         <v>122</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>123</v>
       </c>
       <c r="J33" s="34"/>
       <c r="K33" s="34"/>
@@ -11437,153 +11375,153 @@
         <v>18</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="77"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="79">
+      <c r="A34" s="95"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="96">
         <v>4</v>
       </c>
-      <c r="D34" s="81" t="s">
-        <v>124</v>
+      <c r="D34" s="97" t="s">
+        <v>123</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="F34" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="H34" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="I34" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>128</v>
       </c>
       <c r="J34" s="34"/>
       <c r="K34" s="34"/>
       <c r="L34" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="M34" s="23" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="35" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="77"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="81"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="97"/>
       <c r="E35" s="4">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="F35" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="H35" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="I35" s="23" t="s">
         <v>133</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>134</v>
       </c>
       <c r="J35" s="34"/>
       <c r="K35" s="34"/>
       <c r="L35" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M35" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="M35" s="23" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="36" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="77"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="81"/>
+      <c r="A36" s="95"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="4">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="F36" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="H36" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="I36" s="23" t="s">
         <v>137</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>138</v>
       </c>
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
       <c r="L36" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M36" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="M36" s="23" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="37" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="77"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="81"/>
+      <c r="A37" s="95"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="4">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="F37" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="H37" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="I37" s="23" t="s">
         <v>141</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>142</v>
       </c>
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
       <c r="L37" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M37" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="M37" s="23" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="38" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="77"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="81"/>
+      <c r="A38" s="95"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="4">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="F38" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G38" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="H38" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="I38" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>146</v>
       </c>
       <c r="J38" s="34"/>
       <c r="K38" s="34"/>
@@ -11591,61 +11529,61 @@
         <v>32</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="77"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="81"/>
+      <c r="A39" s="95"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="97"/>
       <c r="E39" s="4">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="F39" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="H39" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="H39" s="23" t="s">
+      <c r="I39" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>150</v>
       </c>
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
       <c r="L39" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="77"/>
-      <c r="B40" s="78"/>
+      <c r="A40" s="95"/>
+      <c r="B40" s="86"/>
       <c r="C40" s="75"/>
       <c r="D40" s="76" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E40" s="4">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="F40" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="23" t="s">
         <v>159</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>162</v>
       </c>
       <c r="J40" s="34"/>
       <c r="K40" s="34"/>
@@ -11653,7 +11591,7 @@
         <v>32</v>
       </c>
       <c r="M40" s="23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -12084,8 +12022,8 @@
       <c r="H95" s="15"/>
     </row>
     <row r="96" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="82"/>
-      <c r="B96" s="78"/>
+      <c r="A96" s="85"/>
+      <c r="B96" s="86"/>
       <c r="C96" s="4"/>
       <c r="D96" s="38"/>
       <c r="E96" s="22"/>
@@ -12093,8 +12031,8 @@
       <c r="G96" s="22"/>
     </row>
     <row r="97" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="82"/>
-      <c r="B97" s="78"/>
+      <c r="A97" s="85"/>
+      <c r="B97" s="86"/>
       <c r="C97" s="4"/>
       <c r="D97" s="38"/>
       <c r="E97" s="22"/>
@@ -12102,8 +12040,8 @@
       <c r="G97" s="22"/>
     </row>
     <row r="98" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="82"/>
-      <c r="B98" s="78"/>
+      <c r="A98" s="85"/>
+      <c r="B98" s="86"/>
       <c r="C98" s="4"/>
       <c r="D98" s="38"/>
       <c r="E98" s="22"/>
@@ -12111,8 +12049,8 @@
       <c r="G98" s="22"/>
     </row>
     <row r="99" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="82"/>
-      <c r="B99" s="78"/>
+      <c r="A99" s="85"/>
+      <c r="B99" s="86"/>
       <c r="C99" s="4"/>
       <c r="D99" s="38"/>
       <c r="E99" s="22"/>
@@ -12120,8 +12058,8 @@
       <c r="G99" s="22"/>
     </row>
     <row r="100" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="82"/>
-      <c r="B100" s="78"/>
+      <c r="A100" s="85"/>
+      <c r="B100" s="86"/>
       <c r="C100" s="4"/>
       <c r="D100" s="38"/>
       <c r="E100" s="22"/>
@@ -12129,8 +12067,8 @@
       <c r="G100" s="22"/>
     </row>
     <row r="101" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="82"/>
-      <c r="B101" s="78"/>
+      <c r="A101" s="85"/>
+      <c r="B101" s="86"/>
       <c r="C101" s="4"/>
       <c r="D101" s="38"/>
       <c r="E101" s="22"/>
@@ -12138,8 +12076,8 @@
       <c r="G101" s="22"/>
     </row>
     <row r="102" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="82"/>
-      <c r="B102" s="78"/>
+      <c r="A102" s="85"/>
+      <c r="B102" s="86"/>
       <c r="C102" s="4"/>
       <c r="D102" s="38"/>
       <c r="E102" s="22"/>
@@ -12147,8 +12085,8 @@
       <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="82"/>
-      <c r="B103" s="78"/>
+      <c r="A103" s="85"/>
+      <c r="B103" s="86"/>
       <c r="C103" s="4"/>
       <c r="D103" s="38"/>
       <c r="E103" s="22"/>
@@ -12156,8 +12094,8 @@
       <c r="G103" s="22"/>
     </row>
     <row r="104" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="82"/>
-      <c r="B104" s="78"/>
+      <c r="A104" s="85"/>
+      <c r="B104" s="86"/>
       <c r="C104" s="4"/>
       <c r="D104" s="38"/>
       <c r="E104" s="22"/>
@@ -12165,8 +12103,8 @@
       <c r="G104" s="22"/>
     </row>
     <row r="105" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="82"/>
-      <c r="B105" s="78"/>
+      <c r="A105" s="85"/>
+      <c r="B105" s="86"/>
       <c r="C105" s="4"/>
       <c r="D105" s="38"/>
       <c r="E105" s="22"/>
@@ -12174,8 +12112,8 @@
       <c r="G105" s="22"/>
     </row>
     <row r="106" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="82"/>
-      <c r="B106" s="78"/>
+      <c r="A106" s="85"/>
+      <c r="B106" s="86"/>
       <c r="C106" s="4"/>
       <c r="D106" s="38"/>
       <c r="E106" s="22"/>
@@ -12183,8 +12121,8 @@
       <c r="G106" s="22"/>
     </row>
     <row r="107" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="82"/>
-      <c r="B107" s="78"/>
+      <c r="A107" s="85"/>
+      <c r="B107" s="86"/>
       <c r="C107" s="4"/>
       <c r="D107" s="38"/>
       <c r="E107" s="22"/>
@@ -12192,8 +12130,8 @@
       <c r="G107" s="22"/>
     </row>
     <row r="108" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="82"/>
-      <c r="B108" s="78"/>
+      <c r="A108" s="85"/>
+      <c r="B108" s="86"/>
       <c r="C108" s="4"/>
       <c r="D108" s="38"/>
       <c r="E108" s="22"/>
@@ -12201,8 +12139,8 @@
       <c r="G108" s="22"/>
     </row>
     <row r="109" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="82"/>
-      <c r="B109" s="78"/>
+      <c r="A109" s="85"/>
+      <c r="B109" s="86"/>
       <c r="C109" s="4"/>
       <c r="D109" s="38"/>
       <c r="E109" s="22"/>
@@ -12210,8 +12148,8 @@
       <c r="G109" s="22"/>
     </row>
     <row r="110" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="82"/>
-      <c r="B110" s="78"/>
+      <c r="A110" s="85"/>
+      <c r="B110" s="86"/>
       <c r="C110" s="4"/>
       <c r="D110" s="38"/>
       <c r="E110" s="22"/>
@@ -12219,8 +12157,8 @@
       <c r="G110" s="22"/>
     </row>
     <row r="111" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="82"/>
-      <c r="B111" s="78"/>
+      <c r="A111" s="85"/>
+      <c r="B111" s="86"/>
       <c r="C111" s="4"/>
       <c r="D111" s="38"/>
       <c r="E111" s="22"/>
@@ -12228,1151 +12166,1151 @@
       <c r="G111" s="22"/>
     </row>
     <row r="112" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="82"/>
-      <c r="B112" s="78"/>
+      <c r="A112" s="85"/>
+      <c r="B112" s="86"/>
       <c r="C112" s="4"/>
       <c r="E112" s="22"/>
       <c r="F112" s="22"/>
       <c r="G112" s="22"/>
     </row>
     <row r="113" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="82"/>
-      <c r="B113" s="78"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="80"/>
+      <c r="A113" s="85"/>
+      <c r="B113" s="86"/>
+      <c r="C113" s="94"/>
+      <c r="D113" s="93"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
       <c r="G113" s="22"/>
     </row>
     <row r="114" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="82"/>
-      <c r="B114" s="78"/>
-      <c r="C114" s="83"/>
-      <c r="D114" s="80"/>
+      <c r="A114" s="85"/>
+      <c r="B114" s="86"/>
+      <c r="C114" s="94"/>
+      <c r="D114" s="93"/>
       <c r="E114" s="22"/>
       <c r="F114" s="22"/>
       <c r="G114" s="22"/>
     </row>
     <row r="115" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="82"/>
-      <c r="B115" s="78"/>
+      <c r="A115" s="85"/>
+      <c r="B115" s="86"/>
       <c r="C115" s="4"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
       <c r="G115" s="22"/>
     </row>
     <row r="116" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="82"/>
-      <c r="B116" s="78"/>
-      <c r="C116" s="83"/>
-      <c r="D116" s="80"/>
+      <c r="A116" s="85"/>
+      <c r="B116" s="86"/>
+      <c r="C116" s="94"/>
+      <c r="D116" s="93"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="22"/>
     </row>
     <row r="117" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="82"/>
-      <c r="B117" s="78"/>
-      <c r="C117" s="83"/>
-      <c r="D117" s="80"/>
+      <c r="A117" s="85"/>
+      <c r="B117" s="86"/>
+      <c r="C117" s="94"/>
+      <c r="D117" s="93"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
       <c r="G117" s="22"/>
     </row>
     <row r="118" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="82"/>
-      <c r="B118" s="78"/>
-      <c r="C118" s="83"/>
-      <c r="D118" s="80"/>
+      <c r="A118" s="85"/>
+      <c r="B118" s="86"/>
+      <c r="C118" s="94"/>
+      <c r="D118" s="93"/>
       <c r="E118" s="22"/>
       <c r="F118" s="22"/>
       <c r="G118" s="22"/>
     </row>
     <row r="119" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="82"/>
-      <c r="B119" s="78"/>
-      <c r="C119" s="83"/>
-      <c r="D119" s="80"/>
+      <c r="A119" s="85"/>
+      <c r="B119" s="86"/>
+      <c r="C119" s="94"/>
+      <c r="D119" s="93"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
       <c r="G119" s="22"/>
     </row>
     <row r="120" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="82"/>
-      <c r="B120" s="78"/>
-      <c r="C120" s="83"/>
-      <c r="D120" s="80"/>
+      <c r="A120" s="85"/>
+      <c r="B120" s="86"/>
+      <c r="C120" s="94"/>
+      <c r="D120" s="93"/>
       <c r="E120" s="22"/>
       <c r="F120" s="22"/>
       <c r="G120" s="22"/>
     </row>
     <row r="121" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="82"/>
-      <c r="B121" s="78"/>
-      <c r="C121" s="83"/>
-      <c r="D121" s="80"/>
+      <c r="A121" s="85"/>
+      <c r="B121" s="86"/>
+      <c r="C121" s="94"/>
+      <c r="D121" s="93"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
       <c r="G121" s="22"/>
     </row>
     <row r="122" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="82"/>
-      <c r="B122" s="78"/>
-      <c r="C122" s="83"/>
-      <c r="D122" s="80"/>
+      <c r="A122" s="85"/>
+      <c r="B122" s="86"/>
+      <c r="C122" s="94"/>
+      <c r="D122" s="93"/>
       <c r="E122" s="22"/>
       <c r="F122" s="22"/>
       <c r="G122" s="22"/>
     </row>
     <row r="123" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="82"/>
-      <c r="B123" s="78"/>
-      <c r="C123" s="83"/>
-      <c r="D123" s="80"/>
+      <c r="A123" s="85"/>
+      <c r="B123" s="86"/>
+      <c r="C123" s="94"/>
+      <c r="D123" s="93"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
       <c r="G123" s="22"/>
     </row>
     <row r="124" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="82"/>
-      <c r="B124" s="78"/>
-      <c r="C124" s="83"/>
-      <c r="D124" s="80"/>
+      <c r="A124" s="85"/>
+      <c r="B124" s="86"/>
+      <c r="C124" s="94"/>
+      <c r="D124" s="93"/>
       <c r="E124" s="22"/>
       <c r="F124" s="22"/>
       <c r="G124" s="22"/>
     </row>
     <row r="125" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="82"/>
-      <c r="B125" s="78"/>
-      <c r="C125" s="83"/>
-      <c r="D125" s="80"/>
+      <c r="A125" s="85"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="94"/>
+      <c r="D125" s="93"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
       <c r="G125" s="22"/>
     </row>
     <row r="126" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="82"/>
-      <c r="B126" s="78"/>
-      <c r="C126" s="83"/>
-      <c r="D126" s="80"/>
+      <c r="A126" s="85"/>
+      <c r="B126" s="86"/>
+      <c r="C126" s="94"/>
+      <c r="D126" s="93"/>
       <c r="E126" s="22"/>
       <c r="F126" s="22"/>
       <c r="G126" s="22"/>
     </row>
     <row r="127" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="82"/>
-      <c r="B127" s="78"/>
-      <c r="C127" s="83"/>
-      <c r="D127" s="80"/>
+      <c r="A127" s="85"/>
+      <c r="B127" s="86"/>
+      <c r="C127" s="94"/>
+      <c r="D127" s="93"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
       <c r="G127" s="22"/>
     </row>
     <row r="128" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="82"/>
-      <c r="B128" s="78"/>
-      <c r="C128" s="83"/>
-      <c r="D128" s="80"/>
+      <c r="A128" s="85"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="94"/>
+      <c r="D128" s="93"/>
       <c r="E128" s="22"/>
       <c r="F128" s="22"/>
       <c r="G128" s="22"/>
     </row>
     <row r="129" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="82"/>
-      <c r="B129" s="78"/>
-      <c r="C129" s="83"/>
-      <c r="D129" s="80"/>
+      <c r="A129" s="85"/>
+      <c r="B129" s="86"/>
+      <c r="C129" s="94"/>
+      <c r="D129" s="93"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
       <c r="G129" s="22"/>
     </row>
     <row r="130" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="82"/>
-      <c r="B130" s="78"/>
-      <c r="C130" s="83"/>
-      <c r="D130" s="80"/>
+      <c r="A130" s="85"/>
+      <c r="B130" s="86"/>
+      <c r="C130" s="94"/>
+      <c r="D130" s="93"/>
       <c r="E130" s="22"/>
       <c r="F130" s="22"/>
       <c r="G130" s="22"/>
     </row>
     <row r="131" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="82"/>
-      <c r="B131" s="78"/>
-      <c r="C131" s="83"/>
-      <c r="D131" s="80"/>
+      <c r="A131" s="85"/>
+      <c r="B131" s="86"/>
+      <c r="C131" s="94"/>
+      <c r="D131" s="93"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
       <c r="G131" s="22"/>
     </row>
     <row r="132" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="82"/>
-      <c r="B132" s="78"/>
-      <c r="C132" s="83"/>
-      <c r="D132" s="80"/>
+      <c r="A132" s="85"/>
+      <c r="B132" s="86"/>
+      <c r="C132" s="94"/>
+      <c r="D132" s="93"/>
       <c r="E132" s="22"/>
       <c r="F132" s="22"/>
       <c r="G132" s="22"/>
     </row>
     <row r="133" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="82"/>
-      <c r="B133" s="78"/>
-      <c r="C133" s="83"/>
-      <c r="D133" s="80"/>
+      <c r="A133" s="85"/>
+      <c r="B133" s="86"/>
+      <c r="C133" s="94"/>
+      <c r="D133" s="93"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
       <c r="G133" s="22"/>
     </row>
     <row r="134" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="82"/>
-      <c r="B134" s="78"/>
-      <c r="C134" s="83"/>
-      <c r="D134" s="80"/>
+      <c r="A134" s="85"/>
+      <c r="B134" s="86"/>
+      <c r="C134" s="94"/>
+      <c r="D134" s="93"/>
       <c r="E134" s="22"/>
       <c r="F134" s="22"/>
       <c r="G134" s="22"/>
     </row>
     <row r="135" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="82"/>
-      <c r="B135" s="78"/>
-      <c r="C135" s="83"/>
-      <c r="D135" s="80"/>
+      <c r="A135" s="85"/>
+      <c r="B135" s="86"/>
+      <c r="C135" s="94"/>
+      <c r="D135" s="93"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
       <c r="G135" s="22"/>
     </row>
     <row r="136" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="82"/>
-      <c r="B136" s="78"/>
-      <c r="C136" s="83"/>
-      <c r="D136" s="80"/>
+      <c r="A136" s="85"/>
+      <c r="B136" s="86"/>
+      <c r="C136" s="94"/>
+      <c r="D136" s="93"/>
       <c r="E136" s="22"/>
       <c r="F136" s="22"/>
       <c r="G136" s="22"/>
     </row>
     <row r="137" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="82"/>
-      <c r="B137" s="78"/>
-      <c r="C137" s="83"/>
-      <c r="D137" s="80"/>
+      <c r="A137" s="85"/>
+      <c r="B137" s="86"/>
+      <c r="C137" s="94"/>
+      <c r="D137" s="93"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="22"/>
     </row>
     <row r="138" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="82"/>
-      <c r="B138" s="78"/>
-      <c r="C138" s="83"/>
-      <c r="D138" s="80"/>
+      <c r="A138" s="85"/>
+      <c r="B138" s="86"/>
+      <c r="C138" s="94"/>
+      <c r="D138" s="93"/>
       <c r="E138" s="22"/>
       <c r="F138" s="22"/>
       <c r="G138" s="22"/>
     </row>
     <row r="139" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="82"/>
-      <c r="B139" s="78"/>
-      <c r="C139" s="83"/>
-      <c r="D139" s="80"/>
+      <c r="A139" s="85"/>
+      <c r="B139" s="86"/>
+      <c r="C139" s="94"/>
+      <c r="D139" s="93"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
       <c r="G139" s="22"/>
     </row>
     <row r="140" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="82"/>
-      <c r="B140" s="78"/>
-      <c r="C140" s="83"/>
-      <c r="D140" s="80"/>
+      <c r="A140" s="85"/>
+      <c r="B140" s="86"/>
+      <c r="C140" s="94"/>
+      <c r="D140" s="93"/>
       <c r="E140" s="22"/>
       <c r="F140" s="22"/>
       <c r="G140" s="22"/>
     </row>
     <row r="141" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="82"/>
-      <c r="B141" s="78"/>
-      <c r="C141" s="83"/>
-      <c r="D141" s="80"/>
+      <c r="A141" s="85"/>
+      <c r="B141" s="86"/>
+      <c r="C141" s="94"/>
+      <c r="D141" s="93"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
       <c r="G141" s="22"/>
     </row>
     <row r="142" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="82"/>
-      <c r="B142" s="78"/>
-      <c r="C142" s="83"/>
-      <c r="D142" s="80"/>
+      <c r="A142" s="85"/>
+      <c r="B142" s="86"/>
+      <c r="C142" s="94"/>
+      <c r="D142" s="93"/>
       <c r="E142" s="22"/>
       <c r="F142" s="22"/>
       <c r="G142" s="22"/>
     </row>
     <row r="143" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="82"/>
-      <c r="B143" s="78"/>
-      <c r="C143" s="83"/>
-      <c r="D143" s="80"/>
+      <c r="A143" s="85"/>
+      <c r="B143" s="86"/>
+      <c r="C143" s="94"/>
+      <c r="D143" s="93"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
       <c r="G143" s="22"/>
     </row>
     <row r="144" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="82"/>
-      <c r="B144" s="78"/>
-      <c r="C144" s="83"/>
-      <c r="D144" s="80"/>
+      <c r="A144" s="85"/>
+      <c r="B144" s="86"/>
+      <c r="C144" s="94"/>
+      <c r="D144" s="93"/>
       <c r="E144" s="22"/>
       <c r="F144" s="22"/>
       <c r="G144" s="22"/>
     </row>
     <row r="145" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="82"/>
-      <c r="B145" s="78"/>
-      <c r="C145" s="83"/>
-      <c r="D145" s="80"/>
+      <c r="A145" s="85"/>
+      <c r="B145" s="86"/>
+      <c r="C145" s="94"/>
+      <c r="D145" s="93"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="22"/>
     </row>
     <row r="146" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="82"/>
-      <c r="B146" s="78"/>
-      <c r="C146" s="83"/>
-      <c r="D146" s="80"/>
+      <c r="A146" s="85"/>
+      <c r="B146" s="86"/>
+      <c r="C146" s="94"/>
+      <c r="D146" s="93"/>
       <c r="E146" s="22"/>
       <c r="F146" s="22"/>
       <c r="G146" s="22"/>
     </row>
     <row r="147" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="82"/>
-      <c r="B147" s="78"/>
-      <c r="C147" s="83"/>
-      <c r="D147" s="80"/>
+      <c r="A147" s="85"/>
+      <c r="B147" s="86"/>
+      <c r="C147" s="94"/>
+      <c r="D147" s="93"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
       <c r="G147" s="22"/>
     </row>
     <row r="148" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="82"/>
-      <c r="B148" s="78"/>
-      <c r="C148" s="83"/>
-      <c r="D148" s="80"/>
+      <c r="A148" s="85"/>
+      <c r="B148" s="86"/>
+      <c r="C148" s="94"/>
+      <c r="D148" s="93"/>
       <c r="E148" s="22"/>
       <c r="F148" s="22"/>
       <c r="G148" s="22"/>
     </row>
     <row r="149" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="82"/>
-      <c r="B149" s="78"/>
-      <c r="C149" s="83"/>
-      <c r="D149" s="80"/>
+      <c r="A149" s="85"/>
+      <c r="B149" s="86"/>
+      <c r="C149" s="94"/>
+      <c r="D149" s="93"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
       <c r="G149" s="22"/>
     </row>
     <row r="150" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="82"/>
-      <c r="B150" s="78"/>
-      <c r="C150" s="83"/>
-      <c r="D150" s="80"/>
+      <c r="A150" s="85"/>
+      <c r="B150" s="86"/>
+      <c r="C150" s="94"/>
+      <c r="D150" s="93"/>
       <c r="E150" s="22"/>
       <c r="F150" s="22"/>
       <c r="G150" s="22"/>
     </row>
     <row r="151" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="82"/>
-      <c r="B151" s="78"/>
-      <c r="C151" s="83"/>
-      <c r="D151" s="80"/>
+      <c r="A151" s="85"/>
+      <c r="B151" s="86"/>
+      <c r="C151" s="94"/>
+      <c r="D151" s="93"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
       <c r="G151" s="22"/>
     </row>
     <row r="152" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="82"/>
-      <c r="B152" s="78"/>
-      <c r="C152" s="83"/>
-      <c r="D152" s="80"/>
+      <c r="A152" s="85"/>
+      <c r="B152" s="86"/>
+      <c r="C152" s="94"/>
+      <c r="D152" s="93"/>
       <c r="E152" s="22"/>
       <c r="F152" s="22"/>
       <c r="G152" s="22"/>
     </row>
     <row r="153" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="82"/>
-      <c r="B153" s="78"/>
-      <c r="C153" s="83"/>
-      <c r="D153" s="80"/>
+      <c r="A153" s="85"/>
+      <c r="B153" s="86"/>
+      <c r="C153" s="94"/>
+      <c r="D153" s="93"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="22"/>
     </row>
     <row r="154" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="82"/>
-      <c r="B154" s="78"/>
-      <c r="C154" s="83"/>
-      <c r="D154" s="80"/>
+      <c r="A154" s="85"/>
+      <c r="B154" s="86"/>
+      <c r="C154" s="94"/>
+      <c r="D154" s="93"/>
       <c r="E154" s="22"/>
       <c r="F154" s="22"/>
       <c r="G154" s="22"/>
     </row>
     <row r="155" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="82"/>
-      <c r="B155" s="78"/>
-      <c r="C155" s="83"/>
-      <c r="D155" s="80"/>
+      <c r="A155" s="85"/>
+      <c r="B155" s="86"/>
+      <c r="C155" s="94"/>
+      <c r="D155" s="93"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
       <c r="G155" s="22"/>
     </row>
     <row r="156" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="82"/>
-      <c r="B156" s="78"/>
-      <c r="C156" s="83"/>
-      <c r="D156" s="80"/>
+      <c r="A156" s="85"/>
+      <c r="B156" s="86"/>
+      <c r="C156" s="94"/>
+      <c r="D156" s="93"/>
       <c r="E156" s="22"/>
       <c r="F156" s="22"/>
       <c r="G156" s="22"/>
     </row>
     <row r="157" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="82"/>
-      <c r="B157" s="78"/>
-      <c r="C157" s="83"/>
-      <c r="D157" s="80"/>
+      <c r="A157" s="85"/>
+      <c r="B157" s="86"/>
+      <c r="C157" s="94"/>
+      <c r="D157" s="93"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
       <c r="G157" s="22"/>
     </row>
     <row r="158" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="82"/>
-      <c r="B158" s="78"/>
-      <c r="C158" s="83"/>
-      <c r="D158" s="80"/>
+      <c r="A158" s="85"/>
+      <c r="B158" s="86"/>
+      <c r="C158" s="94"/>
+      <c r="D158" s="93"/>
       <c r="E158" s="22"/>
       <c r="F158" s="22"/>
       <c r="G158" s="22"/>
     </row>
     <row r="159" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="82"/>
-      <c r="B159" s="78"/>
-      <c r="C159" s="83"/>
-      <c r="D159" s="80"/>
+      <c r="A159" s="85"/>
+      <c r="B159" s="86"/>
+      <c r="C159" s="94"/>
+      <c r="D159" s="93"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
       <c r="G159" s="22"/>
     </row>
     <row r="160" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="82"/>
-      <c r="B160" s="78"/>
-      <c r="C160" s="83"/>
-      <c r="D160" s="80"/>
+      <c r="A160" s="85"/>
+      <c r="B160" s="86"/>
+      <c r="C160" s="94"/>
+      <c r="D160" s="93"/>
       <c r="E160" s="22"/>
       <c r="F160" s="22"/>
       <c r="G160" s="22"/>
     </row>
     <row r="161" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="82"/>
-      <c r="B161" s="78"/>
-      <c r="C161" s="83"/>
-      <c r="D161" s="80"/>
+      <c r="A161" s="85"/>
+      <c r="B161" s="86"/>
+      <c r="C161" s="94"/>
+      <c r="D161" s="93"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="22"/>
     </row>
     <row r="162" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="82"/>
-      <c r="B162" s="78"/>
-      <c r="C162" s="83"/>
-      <c r="D162" s="80"/>
+      <c r="A162" s="85"/>
+      <c r="B162" s="86"/>
+      <c r="C162" s="94"/>
+      <c r="D162" s="93"/>
       <c r="E162" s="22"/>
       <c r="F162" s="22"/>
       <c r="G162" s="22"/>
     </row>
     <row r="163" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="82"/>
-      <c r="B163" s="78"/>
-      <c r="C163" s="83"/>
-      <c r="D163" s="80"/>
+      <c r="A163" s="85"/>
+      <c r="B163" s="86"/>
+      <c r="C163" s="94"/>
+      <c r="D163" s="93"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
       <c r="G163" s="22"/>
     </row>
     <row r="164" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="82"/>
-      <c r="B164" s="78"/>
-      <c r="C164" s="83"/>
-      <c r="D164" s="80"/>
+      <c r="A164" s="85"/>
+      <c r="B164" s="86"/>
+      <c r="C164" s="94"/>
+      <c r="D164" s="93"/>
       <c r="E164" s="22"/>
       <c r="F164" s="22"/>
       <c r="G164" s="22"/>
     </row>
     <row r="165" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="82"/>
-      <c r="B165" s="78"/>
-      <c r="C165" s="83"/>
-      <c r="D165" s="80"/>
+      <c r="A165" s="85"/>
+      <c r="B165" s="86"/>
+      <c r="C165" s="94"/>
+      <c r="D165" s="93"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
       <c r="G165" s="22"/>
     </row>
     <row r="166" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="82"/>
-      <c r="B166" s="78"/>
-      <c r="C166" s="83"/>
-      <c r="D166" s="80"/>
+      <c r="A166" s="85"/>
+      <c r="B166" s="86"/>
+      <c r="C166" s="94"/>
+      <c r="D166" s="93"/>
       <c r="E166" s="22"/>
       <c r="F166" s="22"/>
       <c r="G166" s="22"/>
     </row>
     <row r="167" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="82"/>
-      <c r="B167" s="78"/>
-      <c r="C167" s="83"/>
-      <c r="D167" s="80"/>
+      <c r="A167" s="85"/>
+      <c r="B167" s="86"/>
+      <c r="C167" s="94"/>
+      <c r="D167" s="93"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
       <c r="G167" s="22"/>
     </row>
     <row r="168" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="82"/>
-      <c r="B168" s="78"/>
-      <c r="C168" s="83"/>
-      <c r="D168" s="80"/>
+      <c r="A168" s="85"/>
+      <c r="B168" s="86"/>
+      <c r="C168" s="94"/>
+      <c r="D168" s="93"/>
       <c r="E168" s="22"/>
       <c r="F168" s="22"/>
       <c r="G168" s="22"/>
     </row>
     <row r="169" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="82"/>
-      <c r="B169" s="78"/>
-      <c r="C169" s="83"/>
-      <c r="D169" s="80"/>
+      <c r="A169" s="85"/>
+      <c r="B169" s="86"/>
+      <c r="C169" s="94"/>
+      <c r="D169" s="93"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
       <c r="G169" s="22"/>
     </row>
     <row r="170" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="82"/>
-      <c r="B170" s="78"/>
-      <c r="C170" s="83"/>
-      <c r="D170" s="80"/>
+      <c r="A170" s="85"/>
+      <c r="B170" s="86"/>
+      <c r="C170" s="94"/>
+      <c r="D170" s="93"/>
       <c r="E170" s="22"/>
       <c r="F170" s="22"/>
       <c r="G170" s="22"/>
     </row>
     <row r="171" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="82"/>
-      <c r="B171" s="78"/>
-      <c r="C171" s="83"/>
-      <c r="D171" s="80"/>
+      <c r="A171" s="85"/>
+      <c r="B171" s="86"/>
+      <c r="C171" s="94"/>
+      <c r="D171" s="93"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
       <c r="G171" s="22"/>
     </row>
     <row r="172" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="82"/>
-      <c r="B172" s="78"/>
-      <c r="C172" s="83"/>
-      <c r="D172" s="80"/>
+      <c r="A172" s="85"/>
+      <c r="B172" s="86"/>
+      <c r="C172" s="94"/>
+      <c r="D172" s="93"/>
       <c r="E172" s="22"/>
       <c r="F172" s="22"/>
       <c r="G172" s="22"/>
     </row>
     <row r="173" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="82"/>
-      <c r="B173" s="78"/>
-      <c r="C173" s="83"/>
-      <c r="D173" s="80"/>
+      <c r="A173" s="85"/>
+      <c r="B173" s="86"/>
+      <c r="C173" s="94"/>
+      <c r="D173" s="93"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
       <c r="G173" s="22"/>
     </row>
     <row r="174" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="82"/>
-      <c r="B174" s="78"/>
-      <c r="C174" s="83"/>
-      <c r="D174" s="80"/>
+      <c r="A174" s="85"/>
+      <c r="B174" s="86"/>
+      <c r="C174" s="94"/>
+      <c r="D174" s="93"/>
       <c r="E174" s="22"/>
       <c r="F174" s="22"/>
       <c r="G174" s="22"/>
     </row>
     <row r="175" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="82"/>
-      <c r="B175" s="78"/>
-      <c r="C175" s="83"/>
-      <c r="D175" s="80"/>
+      <c r="A175" s="85"/>
+      <c r="B175" s="86"/>
+      <c r="C175" s="94"/>
+      <c r="D175" s="93"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
       <c r="G175" s="22"/>
     </row>
     <row r="176" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="82"/>
-      <c r="B176" s="78"/>
-      <c r="C176" s="83"/>
-      <c r="D176" s="80"/>
+      <c r="A176" s="85"/>
+      <c r="B176" s="86"/>
+      <c r="C176" s="94"/>
+      <c r="D176" s="93"/>
       <c r="E176" s="22"/>
       <c r="F176" s="22"/>
       <c r="G176" s="22"/>
     </row>
     <row r="177" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="82"/>
-      <c r="B177" s="78"/>
-      <c r="C177" s="83"/>
-      <c r="D177" s="80"/>
+      <c r="A177" s="85"/>
+      <c r="B177" s="86"/>
+      <c r="C177" s="94"/>
+      <c r="D177" s="93"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="22"/>
     </row>
     <row r="178" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="82"/>
-      <c r="B178" s="78"/>
-      <c r="C178" s="83"/>
-      <c r="D178" s="80"/>
+      <c r="A178" s="85"/>
+      <c r="B178" s="86"/>
+      <c r="C178" s="94"/>
+      <c r="D178" s="93"/>
       <c r="E178" s="22"/>
       <c r="F178" s="22"/>
       <c r="G178" s="22"/>
     </row>
     <row r="179" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="82"/>
-      <c r="B179" s="78"/>
-      <c r="C179" s="83"/>
-      <c r="D179" s="80"/>
+      <c r="A179" s="85"/>
+      <c r="B179" s="86"/>
+      <c r="C179" s="94"/>
+      <c r="D179" s="93"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
       <c r="G179" s="22"/>
     </row>
     <row r="180" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="82"/>
-      <c r="B180" s="78"/>
-      <c r="C180" s="83"/>
-      <c r="D180" s="80"/>
+      <c r="A180" s="85"/>
+      <c r="B180" s="86"/>
+      <c r="C180" s="94"/>
+      <c r="D180" s="93"/>
       <c r="E180" s="22"/>
       <c r="F180" s="22"/>
       <c r="G180" s="22"/>
     </row>
     <row r="181" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="82"/>
-      <c r="B181" s="78"/>
-      <c r="C181" s="83"/>
-      <c r="D181" s="80"/>
+      <c r="A181" s="85"/>
+      <c r="B181" s="86"/>
+      <c r="C181" s="94"/>
+      <c r="D181" s="93"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
       <c r="G181" s="22"/>
     </row>
     <row r="182" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="82"/>
-      <c r="B182" s="78"/>
-      <c r="C182" s="83"/>
-      <c r="D182" s="80"/>
+      <c r="A182" s="85"/>
+      <c r="B182" s="86"/>
+      <c r="C182" s="94"/>
+      <c r="D182" s="93"/>
       <c r="E182" s="22"/>
       <c r="F182" s="22"/>
       <c r="G182" s="22"/>
     </row>
     <row r="183" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="82"/>
-      <c r="B183" s="78"/>
-      <c r="C183" s="83"/>
-      <c r="D183" s="80"/>
+      <c r="A183" s="85"/>
+      <c r="B183" s="86"/>
+      <c r="C183" s="94"/>
+      <c r="D183" s="93"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
       <c r="G183" s="22"/>
     </row>
     <row r="184" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="82"/>
-      <c r="B184" s="78"/>
-      <c r="C184" s="83"/>
-      <c r="D184" s="80"/>
+      <c r="A184" s="85"/>
+      <c r="B184" s="86"/>
+      <c r="C184" s="94"/>
+      <c r="D184" s="93"/>
       <c r="E184" s="22"/>
       <c r="F184" s="22"/>
       <c r="G184" s="22"/>
     </row>
     <row r="185" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="82"/>
-      <c r="B185" s="78"/>
-      <c r="C185" s="83"/>
-      <c r="D185" s="80"/>
+      <c r="A185" s="85"/>
+      <c r="B185" s="86"/>
+      <c r="C185" s="94"/>
+      <c r="D185" s="93"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="22"/>
     </row>
     <row r="186" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="82"/>
-      <c r="B186" s="78"/>
-      <c r="C186" s="83"/>
-      <c r="D186" s="80"/>
+      <c r="A186" s="85"/>
+      <c r="B186" s="86"/>
+      <c r="C186" s="94"/>
+      <c r="D186" s="93"/>
       <c r="E186" s="22"/>
       <c r="F186" s="22"/>
       <c r="G186" s="22"/>
     </row>
     <row r="187" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="82"/>
-      <c r="B187" s="78"/>
-      <c r="C187" s="83"/>
-      <c r="D187" s="80"/>
+      <c r="A187" s="85"/>
+      <c r="B187" s="86"/>
+      <c r="C187" s="94"/>
+      <c r="D187" s="93"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
       <c r="G187" s="22"/>
     </row>
     <row r="188" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="82"/>
-      <c r="B188" s="78"/>
-      <c r="C188" s="83"/>
-      <c r="D188" s="80"/>
+      <c r="A188" s="85"/>
+      <c r="B188" s="86"/>
+      <c r="C188" s="94"/>
+      <c r="D188" s="93"/>
       <c r="E188" s="22"/>
       <c r="F188" s="22"/>
       <c r="G188" s="22"/>
     </row>
     <row r="189" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="82"/>
-      <c r="B189" s="78"/>
-      <c r="C189" s="83"/>
-      <c r="D189" s="80"/>
+      <c r="A189" s="85"/>
+      <c r="B189" s="86"/>
+      <c r="C189" s="94"/>
+      <c r="D189" s="93"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
       <c r="G189" s="22"/>
     </row>
     <row r="190" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="82"/>
-      <c r="B190" s="78"/>
-      <c r="C190" s="83"/>
-      <c r="D190" s="80"/>
+      <c r="A190" s="85"/>
+      <c r="B190" s="86"/>
+      <c r="C190" s="94"/>
+      <c r="D190" s="93"/>
       <c r="E190" s="22"/>
       <c r="F190" s="22"/>
       <c r="G190" s="22"/>
     </row>
     <row r="191" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="82"/>
-      <c r="B191" s="78"/>
-      <c r="C191" s="83"/>
-      <c r="D191" s="80"/>
+      <c r="A191" s="85"/>
+      <c r="B191" s="86"/>
+      <c r="C191" s="94"/>
+      <c r="D191" s="93"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
       <c r="G191" s="22"/>
     </row>
     <row r="192" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="82"/>
-      <c r="B192" s="78"/>
-      <c r="C192" s="83"/>
-      <c r="D192" s="80"/>
+      <c r="A192" s="85"/>
+      <c r="B192" s="86"/>
+      <c r="C192" s="94"/>
+      <c r="D192" s="93"/>
       <c r="E192" s="22"/>
       <c r="F192" s="22"/>
       <c r="G192" s="22"/>
     </row>
     <row r="193" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="82"/>
-      <c r="B193" s="78"/>
-      <c r="C193" s="83"/>
-      <c r="D193" s="80"/>
+      <c r="A193" s="85"/>
+      <c r="B193" s="86"/>
+      <c r="C193" s="94"/>
+      <c r="D193" s="93"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
       <c r="G193" s="22"/>
     </row>
     <row r="194" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="82"/>
-      <c r="B194" s="78"/>
-      <c r="C194" s="83"/>
-      <c r="D194" s="80"/>
+      <c r="A194" s="85"/>
+      <c r="B194" s="86"/>
+      <c r="C194" s="94"/>
+      <c r="D194" s="93"/>
       <c r="E194" s="22"/>
       <c r="F194" s="22"/>
       <c r="G194" s="22"/>
     </row>
     <row r="195" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="82"/>
-      <c r="B195" s="78"/>
-      <c r="C195" s="83"/>
-      <c r="D195" s="80"/>
+      <c r="A195" s="85"/>
+      <c r="B195" s="86"/>
+      <c r="C195" s="94"/>
+      <c r="D195" s="93"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
       <c r="G195" s="22"/>
     </row>
     <row r="196" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="82"/>
-      <c r="B196" s="78"/>
-      <c r="C196" s="83"/>
-      <c r="D196" s="80"/>
+      <c r="A196" s="85"/>
+      <c r="B196" s="86"/>
+      <c r="C196" s="94"/>
+      <c r="D196" s="93"/>
       <c r="E196" s="22"/>
       <c r="F196" s="22"/>
       <c r="G196" s="22"/>
     </row>
     <row r="197" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="82"/>
-      <c r="B197" s="78"/>
-      <c r="C197" s="83"/>
-      <c r="D197" s="80"/>
+      <c r="A197" s="85"/>
+      <c r="B197" s="86"/>
+      <c r="C197" s="94"/>
+      <c r="D197" s="93"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
       <c r="G197" s="22"/>
     </row>
     <row r="198" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="82"/>
-      <c r="B198" s="78"/>
-      <c r="C198" s="83"/>
-      <c r="D198" s="80"/>
+      <c r="A198" s="85"/>
+      <c r="B198" s="86"/>
+      <c r="C198" s="94"/>
+      <c r="D198" s="93"/>
       <c r="E198" s="22"/>
       <c r="F198" s="22"/>
       <c r="G198" s="22"/>
     </row>
     <row r="199" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="82"/>
-      <c r="B199" s="78"/>
-      <c r="C199" s="83"/>
-      <c r="D199" s="80"/>
+      <c r="A199" s="85"/>
+      <c r="B199" s="86"/>
+      <c r="C199" s="94"/>
+      <c r="D199" s="93"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
       <c r="G199" s="22"/>
     </row>
     <row r="200" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="82"/>
-      <c r="B200" s="78"/>
-      <c r="C200" s="83"/>
-      <c r="D200" s="80"/>
+      <c r="A200" s="85"/>
+      <c r="B200" s="86"/>
+      <c r="C200" s="94"/>
+      <c r="D200" s="93"/>
       <c r="E200" s="22"/>
       <c r="F200" s="22"/>
       <c r="G200" s="22"/>
     </row>
     <row r="201" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="82"/>
-      <c r="B201" s="78"/>
-      <c r="C201" s="83"/>
-      <c r="D201" s="80"/>
+      <c r="A201" s="85"/>
+      <c r="B201" s="86"/>
+      <c r="C201" s="94"/>
+      <c r="D201" s="93"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="22"/>
     </row>
     <row r="202" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="82"/>
-      <c r="B202" s="78"/>
-      <c r="C202" s="83"/>
-      <c r="D202" s="80"/>
+      <c r="A202" s="85"/>
+      <c r="B202" s="86"/>
+      <c r="C202" s="94"/>
+      <c r="D202" s="93"/>
       <c r="E202" s="22"/>
       <c r="F202" s="22"/>
       <c r="G202" s="22"/>
     </row>
     <row r="203" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="82"/>
-      <c r="B203" s="78"/>
-      <c r="C203" s="83"/>
-      <c r="D203" s="80"/>
+      <c r="A203" s="85"/>
+      <c r="B203" s="86"/>
+      <c r="C203" s="94"/>
+      <c r="D203" s="93"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
       <c r="G203" s="22"/>
     </row>
     <row r="204" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="82"/>
-      <c r="B204" s="78"/>
-      <c r="C204" s="83"/>
-      <c r="D204" s="80"/>
+      <c r="A204" s="85"/>
+      <c r="B204" s="86"/>
+      <c r="C204" s="94"/>
+      <c r="D204" s="93"/>
       <c r="E204" s="22"/>
       <c r="F204" s="22"/>
       <c r="G204" s="22"/>
     </row>
     <row r="205" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="82"/>
-      <c r="B205" s="78"/>
-      <c r="C205" s="83"/>
-      <c r="D205" s="80"/>
+      <c r="A205" s="85"/>
+      <c r="B205" s="86"/>
+      <c r="C205" s="94"/>
+      <c r="D205" s="93"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
       <c r="G205" s="22"/>
     </row>
     <row r="206" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="82"/>
-      <c r="B206" s="78"/>
-      <c r="C206" s="83"/>
-      <c r="D206" s="80"/>
+      <c r="A206" s="85"/>
+      <c r="B206" s="86"/>
+      <c r="C206" s="94"/>
+      <c r="D206" s="93"/>
       <c r="E206" s="22"/>
       <c r="F206" s="22"/>
       <c r="G206" s="22"/>
     </row>
     <row r="207" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="82"/>
-      <c r="B207" s="78"/>
-      <c r="C207" s="83"/>
-      <c r="D207" s="80"/>
+      <c r="A207" s="85"/>
+      <c r="B207" s="86"/>
+      <c r="C207" s="94"/>
+      <c r="D207" s="93"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
       <c r="G207" s="22"/>
     </row>
     <row r="208" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="82"/>
-      <c r="B208" s="78"/>
-      <c r="C208" s="83"/>
-      <c r="D208" s="80"/>
+      <c r="A208" s="85"/>
+      <c r="B208" s="86"/>
+      <c r="C208" s="94"/>
+      <c r="D208" s="93"/>
       <c r="E208" s="22"/>
       <c r="F208" s="22"/>
       <c r="G208" s="22"/>
     </row>
     <row r="209" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="82"/>
-      <c r="B209" s="78"/>
-      <c r="C209" s="83"/>
-      <c r="D209" s="80"/>
+      <c r="A209" s="85"/>
+      <c r="B209" s="86"/>
+      <c r="C209" s="94"/>
+      <c r="D209" s="93"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="22"/>
     </row>
     <row r="210" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="82"/>
-      <c r="B210" s="78"/>
-      <c r="C210" s="83"/>
-      <c r="D210" s="80"/>
+      <c r="A210" s="85"/>
+      <c r="B210" s="86"/>
+      <c r="C210" s="94"/>
+      <c r="D210" s="93"/>
       <c r="E210" s="22"/>
       <c r="F210" s="22"/>
       <c r="G210" s="22"/>
     </row>
     <row r="211" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="82"/>
-      <c r="B211" s="78"/>
-      <c r="C211" s="83"/>
-      <c r="D211" s="80"/>
+      <c r="A211" s="85"/>
+      <c r="B211" s="86"/>
+      <c r="C211" s="94"/>
+      <c r="D211" s="93"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
       <c r="G211" s="22"/>
     </row>
     <row r="212" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="82"/>
-      <c r="B212" s="78"/>
-      <c r="C212" s="83"/>
-      <c r="D212" s="80"/>
+      <c r="A212" s="85"/>
+      <c r="B212" s="86"/>
+      <c r="C212" s="94"/>
+      <c r="D212" s="93"/>
       <c r="E212" s="22"/>
       <c r="F212" s="22"/>
       <c r="G212" s="22"/>
     </row>
     <row r="213" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="82"/>
-      <c r="B213" s="78"/>
-      <c r="C213" s="83"/>
-      <c r="D213" s="80"/>
+      <c r="A213" s="85"/>
+      <c r="B213" s="86"/>
+      <c r="C213" s="94"/>
+      <c r="D213" s="93"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
       <c r="G213" s="22"/>
     </row>
     <row r="214" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="82"/>
-      <c r="B214" s="78"/>
-      <c r="C214" s="83"/>
-      <c r="D214" s="80"/>
+      <c r="A214" s="85"/>
+      <c r="B214" s="86"/>
+      <c r="C214" s="94"/>
+      <c r="D214" s="93"/>
       <c r="E214" s="22"/>
       <c r="F214" s="22"/>
       <c r="G214" s="22"/>
     </row>
     <row r="215" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="82"/>
-      <c r="B215" s="78"/>
-      <c r="C215" s="83"/>
-      <c r="D215" s="80"/>
+      <c r="A215" s="85"/>
+      <c r="B215" s="86"/>
+      <c r="C215" s="94"/>
+      <c r="D215" s="93"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
       <c r="G215" s="22"/>
     </row>
     <row r="216" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="82"/>
-      <c r="B216" s="78"/>
-      <c r="C216" s="83"/>
-      <c r="D216" s="80"/>
+      <c r="A216" s="85"/>
+      <c r="B216" s="86"/>
+      <c r="C216" s="94"/>
+      <c r="D216" s="93"/>
       <c r="E216" s="22"/>
       <c r="F216" s="22"/>
       <c r="G216" s="22"/>
     </row>
     <row r="217" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="82"/>
-      <c r="B217" s="78"/>
-      <c r="C217" s="83"/>
-      <c r="D217" s="80"/>
+      <c r="A217" s="85"/>
+      <c r="B217" s="86"/>
+      <c r="C217" s="94"/>
+      <c r="D217" s="93"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="22"/>
     </row>
     <row r="218" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="82"/>
-      <c r="B218" s="78"/>
-      <c r="C218" s="83"/>
-      <c r="D218" s="80"/>
+      <c r="A218" s="85"/>
+      <c r="B218" s="86"/>
+      <c r="C218" s="94"/>
+      <c r="D218" s="93"/>
       <c r="E218" s="22"/>
       <c r="F218" s="22"/>
       <c r="G218" s="22"/>
     </row>
     <row r="219" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="82"/>
-      <c r="B219" s="78"/>
-      <c r="C219" s="83"/>
-      <c r="D219" s="80"/>
+      <c r="A219" s="85"/>
+      <c r="B219" s="86"/>
+      <c r="C219" s="94"/>
+      <c r="D219" s="93"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
       <c r="G219" s="22"/>
     </row>
     <row r="220" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="82"/>
-      <c r="B220" s="78"/>
-      <c r="C220" s="83"/>
-      <c r="D220" s="80"/>
+      <c r="A220" s="85"/>
+      <c r="B220" s="86"/>
+      <c r="C220" s="94"/>
+      <c r="D220" s="93"/>
       <c r="E220" s="22"/>
       <c r="F220" s="22"/>
       <c r="G220" s="22"/>
     </row>
     <row r="221" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="82"/>
-      <c r="B221" s="78"/>
-      <c r="C221" s="83"/>
-      <c r="D221" s="80"/>
+      <c r="A221" s="85"/>
+      <c r="B221" s="86"/>
+      <c r="C221" s="94"/>
+      <c r="D221" s="93"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
       <c r="G221" s="22"/>
     </row>
     <row r="222" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="82"/>
-      <c r="B222" s="78"/>
-      <c r="C222" s="83"/>
-      <c r="D222" s="80"/>
+      <c r="A222" s="85"/>
+      <c r="B222" s="86"/>
+      <c r="C222" s="94"/>
+      <c r="D222" s="93"/>
       <c r="E222" s="22"/>
       <c r="F222" s="22"/>
       <c r="G222" s="22"/>
     </row>
     <row r="223" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="82"/>
-      <c r="B223" s="78"/>
-      <c r="C223" s="83"/>
-      <c r="D223" s="80"/>
+      <c r="A223" s="85"/>
+      <c r="B223" s="86"/>
+      <c r="C223" s="94"/>
+      <c r="D223" s="93"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
       <c r="G223" s="22"/>
     </row>
     <row r="224" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="82"/>
-      <c r="B224" s="78"/>
-      <c r="C224" s="83"/>
-      <c r="D224" s="80"/>
+      <c r="A224" s="85"/>
+      <c r="B224" s="86"/>
+      <c r="C224" s="94"/>
+      <c r="D224" s="93"/>
       <c r="E224" s="22"/>
       <c r="F224" s="22"/>
       <c r="G224" s="22"/>
     </row>
     <row r="225" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="82"/>
-      <c r="B225" s="78"/>
-      <c r="C225" s="83"/>
-      <c r="D225" s="80"/>
+      <c r="A225" s="85"/>
+      <c r="B225" s="86"/>
+      <c r="C225" s="94"/>
+      <c r="D225" s="93"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="22"/>
     </row>
     <row r="226" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="82"/>
-      <c r="B226" s="78"/>
-      <c r="C226" s="83"/>
-      <c r="D226" s="80"/>
+      <c r="A226" s="85"/>
+      <c r="B226" s="86"/>
+      <c r="C226" s="94"/>
+      <c r="D226" s="93"/>
       <c r="E226" s="22"/>
       <c r="F226" s="22"/>
       <c r="G226" s="22"/>
     </row>
     <row r="227" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="82"/>
-      <c r="B227" s="78"/>
-      <c r="C227" s="83"/>
-      <c r="D227" s="80"/>
+      <c r="A227" s="85"/>
+      <c r="B227" s="86"/>
+      <c r="C227" s="94"/>
+      <c r="D227" s="93"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
       <c r="G227" s="22"/>
     </row>
     <row r="228" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="82"/>
-      <c r="B228" s="78"/>
-      <c r="C228" s="83"/>
-      <c r="D228" s="80"/>
+      <c r="A228" s="85"/>
+      <c r="B228" s="86"/>
+      <c r="C228" s="94"/>
+      <c r="D228" s="93"/>
       <c r="E228" s="22"/>
       <c r="F228" s="22"/>
       <c r="G228" s="22"/>
     </row>
     <row r="229" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="82"/>
-      <c r="B229" s="78"/>
-      <c r="C229" s="83"/>
-      <c r="D229" s="80"/>
+      <c r="A229" s="85"/>
+      <c r="B229" s="86"/>
+      <c r="C229" s="94"/>
+      <c r="D229" s="93"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
       <c r="G229" s="22"/>
     </row>
     <row r="230" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="82"/>
-      <c r="B230" s="78"/>
-      <c r="C230" s="83"/>
-      <c r="D230" s="80"/>
+      <c r="A230" s="85"/>
+      <c r="B230" s="86"/>
+      <c r="C230" s="94"/>
+      <c r="D230" s="93"/>
       <c r="E230" s="22"/>
       <c r="F230" s="22"/>
       <c r="G230" s="22"/>
     </row>
     <row r="231" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="82"/>
-      <c r="B231" s="78"/>
-      <c r="C231" s="83"/>
-      <c r="D231" s="80"/>
+      <c r="A231" s="85"/>
+      <c r="B231" s="86"/>
+      <c r="C231" s="94"/>
+      <c r="D231" s="93"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
       <c r="G231" s="22"/>
     </row>
     <row r="232" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="82"/>
-      <c r="B232" s="78"/>
-      <c r="C232" s="83"/>
-      <c r="D232" s="80"/>
+      <c r="A232" s="85"/>
+      <c r="B232" s="86"/>
+      <c r="C232" s="94"/>
+      <c r="D232" s="93"/>
       <c r="E232" s="22"/>
       <c r="F232" s="22"/>
       <c r="G232" s="22"/>
     </row>
     <row r="233" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="82"/>
-      <c r="B233" s="78"/>
-      <c r="C233" s="83"/>
-      <c r="D233" s="80"/>
+      <c r="A233" s="85"/>
+      <c r="B233" s="86"/>
+      <c r="C233" s="94"/>
+      <c r="D233" s="93"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
       <c r="G233" s="22"/>
     </row>
     <row r="234" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="82"/>
-      <c r="B234" s="78"/>
-      <c r="C234" s="83"/>
-      <c r="D234" s="80"/>
+      <c r="A234" s="85"/>
+      <c r="B234" s="86"/>
+      <c r="C234" s="94"/>
+      <c r="D234" s="93"/>
       <c r="E234" s="22"/>
       <c r="F234" s="22"/>
       <c r="G234" s="22"/>
     </row>
     <row r="235" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="82"/>
-      <c r="B235" s="78"/>
-      <c r="C235" s="83"/>
-      <c r="D235" s="80"/>
+      <c r="A235" s="85"/>
+      <c r="B235" s="86"/>
+      <c r="C235" s="94"/>
+      <c r="D235" s="93"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
       <c r="G235" s="22"/>
     </row>
     <row r="236" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="82"/>
-      <c r="B236" s="78"/>
-      <c r="C236" s="83"/>
-      <c r="D236" s="80"/>
+      <c r="A236" s="85"/>
+      <c r="B236" s="86"/>
+      <c r="C236" s="94"/>
+      <c r="D236" s="93"/>
       <c r="E236" s="22"/>
       <c r="F236" s="22"/>
       <c r="G236" s="22"/>
     </row>
     <row r="237" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="82"/>
-      <c r="B237" s="78"/>
-      <c r="C237" s="83"/>
-      <c r="D237" s="80"/>
+      <c r="A237" s="85"/>
+      <c r="B237" s="86"/>
+      <c r="C237" s="94"/>
+      <c r="D237" s="93"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
       <c r="G237" s="22"/>
     </row>
     <row r="238" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="82"/>
-      <c r="B238" s="78"/>
-      <c r="C238" s="83"/>
-      <c r="D238" s="80"/>
+      <c r="A238" s="85"/>
+      <c r="B238" s="86"/>
+      <c r="C238" s="94"/>
+      <c r="D238" s="93"/>
       <c r="E238" s="22"/>
       <c r="F238" s="22"/>
       <c r="G238" s="22"/>
     </row>
     <row r="239" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="82"/>
-      <c r="B239" s="78"/>
-      <c r="C239" s="83"/>
-      <c r="D239" s="80"/>
+      <c r="A239" s="85"/>
+      <c r="B239" s="86"/>
+      <c r="C239" s="94"/>
+      <c r="D239" s="93"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
       <c r="G239" s="22"/>
@@ -13392,364 +13330,364 @@
       <c r="M240" s="41"/>
     </row>
     <row r="241" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="84"/>
-      <c r="B241" s="78"/>
-      <c r="C241" s="85"/>
-      <c r="D241" s="80"/>
+      <c r="A241" s="91"/>
+      <c r="B241" s="86"/>
+      <c r="C241" s="92"/>
+      <c r="D241" s="93"/>
     </row>
     <row r="242" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="84"/>
-      <c r="B242" s="78"/>
-      <c r="C242" s="85"/>
-      <c r="D242" s="80"/>
+      <c r="A242" s="91"/>
+      <c r="B242" s="86"/>
+      <c r="C242" s="92"/>
+      <c r="D242" s="93"/>
     </row>
     <row r="243" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="84"/>
-      <c r="B243" s="78"/>
-      <c r="C243" s="85"/>
-      <c r="D243" s="80"/>
+      <c r="A243" s="91"/>
+      <c r="B243" s="86"/>
+      <c r="C243" s="92"/>
+      <c r="D243" s="93"/>
     </row>
     <row r="244" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="84"/>
-      <c r="B244" s="78"/>
-      <c r="C244" s="85"/>
-      <c r="D244" s="80"/>
+      <c r="A244" s="91"/>
+      <c r="B244" s="86"/>
+      <c r="C244" s="92"/>
+      <c r="D244" s="93"/>
     </row>
     <row r="245" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="84"/>
-      <c r="B245" s="78"/>
-      <c r="C245" s="85"/>
-      <c r="D245" s="80"/>
+      <c r="A245" s="91"/>
+      <c r="B245" s="86"/>
+      <c r="C245" s="92"/>
+      <c r="D245" s="93"/>
     </row>
     <row r="246" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="84"/>
-      <c r="B246" s="78"/>
-      <c r="C246" s="85"/>
-      <c r="D246" s="80"/>
+      <c r="A246" s="91"/>
+      <c r="B246" s="86"/>
+      <c r="C246" s="92"/>
+      <c r="D246" s="93"/>
     </row>
     <row r="247" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="84"/>
-      <c r="B247" s="78"/>
-      <c r="C247" s="85"/>
-      <c r="D247" s="80"/>
+      <c r="A247" s="91"/>
+      <c r="B247" s="86"/>
+      <c r="C247" s="92"/>
+      <c r="D247" s="93"/>
     </row>
     <row r="248" spans="1:4" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="84"/>
-      <c r="B248" s="78"/>
-      <c r="C248" s="85"/>
-      <c r="D248" s="80"/>
+      <c r="A248" s="91"/>
+      <c r="B248" s="86"/>
+      <c r="C248" s="92"/>
+      <c r="D248" s="93"/>
     </row>
     <row r="249" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="84"/>
-      <c r="B249" s="78"/>
-      <c r="C249" s="85"/>
-      <c r="D249" s="80"/>
+      <c r="A249" s="91"/>
+      <c r="B249" s="86"/>
+      <c r="C249" s="92"/>
+      <c r="D249" s="93"/>
     </row>
     <row r="250" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="84"/>
-      <c r="B250" s="78"/>
-      <c r="C250" s="85"/>
-      <c r="D250" s="80"/>
+      <c r="A250" s="91"/>
+      <c r="B250" s="86"/>
+      <c r="C250" s="92"/>
+      <c r="D250" s="93"/>
     </row>
     <row r="251" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="84"/>
-      <c r="B251" s="78"/>
-      <c r="C251" s="85"/>
-      <c r="D251" s="80"/>
+      <c r="A251" s="91"/>
+      <c r="B251" s="86"/>
+      <c r="C251" s="92"/>
+      <c r="D251" s="93"/>
     </row>
     <row r="252" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="84"/>
-      <c r="B252" s="78"/>
-      <c r="C252" s="85"/>
-      <c r="D252" s="80"/>
+      <c r="A252" s="91"/>
+      <c r="B252" s="86"/>
+      <c r="C252" s="92"/>
+      <c r="D252" s="93"/>
     </row>
     <row r="253" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="84"/>
-      <c r="B253" s="78"/>
-      <c r="C253" s="85"/>
-      <c r="D253" s="80"/>
+      <c r="A253" s="91"/>
+      <c r="B253" s="86"/>
+      <c r="C253" s="92"/>
+      <c r="D253" s="93"/>
     </row>
     <row r="254" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="84"/>
-      <c r="B254" s="78"/>
-      <c r="C254" s="85"/>
-      <c r="D254" s="80"/>
+      <c r="A254" s="91"/>
+      <c r="B254" s="86"/>
+      <c r="C254" s="92"/>
+      <c r="D254" s="93"/>
     </row>
     <row r="255" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="84"/>
-      <c r="B255" s="78"/>
-      <c r="C255" s="85"/>
-      <c r="D255" s="80"/>
+      <c r="A255" s="91"/>
+      <c r="B255" s="86"/>
+      <c r="C255" s="92"/>
+      <c r="D255" s="93"/>
     </row>
     <row r="256" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="84"/>
-      <c r="B256" s="78"/>
-      <c r="C256" s="85"/>
-      <c r="D256" s="80"/>
+      <c r="A256" s="91"/>
+      <c r="B256" s="86"/>
+      <c r="C256" s="92"/>
+      <c r="D256" s="93"/>
     </row>
     <row r="257" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="84"/>
-      <c r="B257" s="78"/>
-      <c r="C257" s="85"/>
-      <c r="D257" s="80"/>
+      <c r="A257" s="91"/>
+      <c r="B257" s="86"/>
+      <c r="C257" s="92"/>
+      <c r="D257" s="93"/>
     </row>
     <row r="258" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="84"/>
-      <c r="B258" s="78"/>
-      <c r="C258" s="85"/>
-      <c r="D258" s="80"/>
+      <c r="A258" s="91"/>
+      <c r="B258" s="86"/>
+      <c r="C258" s="92"/>
+      <c r="D258" s="93"/>
     </row>
     <row r="259" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="84"/>
-      <c r="B259" s="78"/>
-      <c r="C259" s="85"/>
-      <c r="D259" s="80"/>
+      <c r="A259" s="91"/>
+      <c r="B259" s="86"/>
+      <c r="C259" s="92"/>
+      <c r="D259" s="93"/>
     </row>
     <row r="260" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="84"/>
-      <c r="B260" s="78"/>
-      <c r="C260" s="85"/>
-      <c r="D260" s="80"/>
+      <c r="A260" s="91"/>
+      <c r="B260" s="86"/>
+      <c r="C260" s="92"/>
+      <c r="D260" s="93"/>
     </row>
     <row r="261" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="84"/>
-      <c r="B261" s="78"/>
-      <c r="C261" s="85"/>
-      <c r="D261" s="80"/>
+      <c r="A261" s="91"/>
+      <c r="B261" s="86"/>
+      <c r="C261" s="92"/>
+      <c r="D261" s="93"/>
     </row>
     <row r="262" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="84"/>
-      <c r="B262" s="78"/>
-      <c r="C262" s="85"/>
-      <c r="D262" s="80"/>
+      <c r="A262" s="91"/>
+      <c r="B262" s="86"/>
+      <c r="C262" s="92"/>
+      <c r="D262" s="93"/>
     </row>
     <row r="263" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="84"/>
-      <c r="B263" s="78"/>
-      <c r="C263" s="85"/>
-      <c r="D263" s="80"/>
+      <c r="A263" s="91"/>
+      <c r="B263" s="86"/>
+      <c r="C263" s="92"/>
+      <c r="D263" s="93"/>
     </row>
     <row r="264" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="84"/>
-      <c r="B264" s="78"/>
-      <c r="C264" s="85"/>
-      <c r="D264" s="80"/>
+      <c r="A264" s="91"/>
+      <c r="B264" s="86"/>
+      <c r="C264" s="92"/>
+      <c r="D264" s="93"/>
     </row>
     <row r="265" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="84"/>
-      <c r="B265" s="78"/>
-      <c r="C265" s="85"/>
-      <c r="D265" s="80"/>
+      <c r="A265" s="91"/>
+      <c r="B265" s="86"/>
+      <c r="C265" s="92"/>
+      <c r="D265" s="93"/>
     </row>
     <row r="266" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="84"/>
-      <c r="B266" s="78"/>
-      <c r="C266" s="85"/>
-      <c r="D266" s="80"/>
+      <c r="A266" s="91"/>
+      <c r="B266" s="86"/>
+      <c r="C266" s="92"/>
+      <c r="D266" s="93"/>
     </row>
     <row r="267" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="84"/>
-      <c r="B267" s="78"/>
-      <c r="C267" s="85"/>
-      <c r="D267" s="80"/>
+      <c r="A267" s="91"/>
+      <c r="B267" s="86"/>
+      <c r="C267" s="92"/>
+      <c r="D267" s="93"/>
     </row>
     <row r="268" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="84"/>
-      <c r="B268" s="78"/>
-      <c r="C268" s="85"/>
-      <c r="D268" s="80"/>
+      <c r="A268" s="91"/>
+      <c r="B268" s="86"/>
+      <c r="C268" s="92"/>
+      <c r="D268" s="93"/>
     </row>
     <row r="269" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="84"/>
-      <c r="B269" s="78"/>
-      <c r="C269" s="85"/>
-      <c r="D269" s="80"/>
+      <c r="A269" s="91"/>
+      <c r="B269" s="86"/>
+      <c r="C269" s="92"/>
+      <c r="D269" s="93"/>
     </row>
     <row r="270" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="84"/>
-      <c r="B270" s="78"/>
-      <c r="C270" s="85"/>
-      <c r="D270" s="80"/>
+      <c r="A270" s="91"/>
+      <c r="B270" s="86"/>
+      <c r="C270" s="92"/>
+      <c r="D270" s="93"/>
     </row>
     <row r="271" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="84"/>
-      <c r="B271" s="78"/>
-      <c r="C271" s="85"/>
-      <c r="D271" s="80"/>
+      <c r="A271" s="91"/>
+      <c r="B271" s="86"/>
+      <c r="C271" s="92"/>
+      <c r="D271" s="93"/>
     </row>
     <row r="272" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="84"/>
-      <c r="B272" s="78"/>
-      <c r="C272" s="85"/>
-      <c r="D272" s="80"/>
+      <c r="A272" s="91"/>
+      <c r="B272" s="86"/>
+      <c r="C272" s="92"/>
+      <c r="D272" s="93"/>
     </row>
     <row r="273" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="84"/>
-      <c r="B273" s="78"/>
-      <c r="C273" s="85"/>
-      <c r="D273" s="80"/>
+      <c r="A273" s="91"/>
+      <c r="B273" s="86"/>
+      <c r="C273" s="92"/>
+      <c r="D273" s="93"/>
     </row>
     <row r="274" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="84"/>
-      <c r="B274" s="78"/>
-      <c r="C274" s="85"/>
-      <c r="D274" s="80"/>
+      <c r="A274" s="91"/>
+      <c r="B274" s="86"/>
+      <c r="C274" s="92"/>
+      <c r="D274" s="93"/>
     </row>
     <row r="275" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="84"/>
-      <c r="B275" s="78"/>
-      <c r="C275" s="85"/>
-      <c r="D275" s="80"/>
+      <c r="A275" s="91"/>
+      <c r="B275" s="86"/>
+      <c r="C275" s="92"/>
+      <c r="D275" s="93"/>
     </row>
     <row r="276" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="84"/>
-      <c r="B276" s="78"/>
-      <c r="C276" s="85"/>
-      <c r="D276" s="80"/>
+      <c r="A276" s="91"/>
+      <c r="B276" s="86"/>
+      <c r="C276" s="92"/>
+      <c r="D276" s="93"/>
     </row>
     <row r="277" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="84"/>
-      <c r="B277" s="78"/>
-      <c r="C277" s="85"/>
-      <c r="D277" s="80"/>
+      <c r="A277" s="91"/>
+      <c r="B277" s="86"/>
+      <c r="C277" s="92"/>
+      <c r="D277" s="93"/>
     </row>
     <row r="278" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="84"/>
-      <c r="B278" s="78"/>
-      <c r="C278" s="85"/>
-      <c r="D278" s="80"/>
+      <c r="A278" s="91"/>
+      <c r="B278" s="86"/>
+      <c r="C278" s="92"/>
+      <c r="D278" s="93"/>
     </row>
     <row r="279" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="84"/>
-      <c r="B279" s="78"/>
-      <c r="C279" s="85"/>
-      <c r="D279" s="80"/>
+      <c r="A279" s="91"/>
+      <c r="B279" s="86"/>
+      <c r="C279" s="92"/>
+      <c r="D279" s="93"/>
     </row>
     <row r="280" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="84"/>
-      <c r="B280" s="78"/>
-      <c r="C280" s="85"/>
-      <c r="D280" s="80"/>
+      <c r="A280" s="91"/>
+      <c r="B280" s="86"/>
+      <c r="C280" s="92"/>
+      <c r="D280" s="93"/>
     </row>
     <row r="281" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="84"/>
-      <c r="B281" s="78"/>
-      <c r="C281" s="85"/>
-      <c r="D281" s="80"/>
+      <c r="A281" s="91"/>
+      <c r="B281" s="86"/>
+      <c r="C281" s="92"/>
+      <c r="D281" s="93"/>
     </row>
     <row r="282" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="84"/>
-      <c r="B282" s="78"/>
-      <c r="C282" s="85"/>
-      <c r="D282" s="80"/>
+      <c r="A282" s="91"/>
+      <c r="B282" s="86"/>
+      <c r="C282" s="92"/>
+      <c r="D282" s="93"/>
     </row>
     <row r="283" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="84"/>
-      <c r="B283" s="78"/>
-      <c r="C283" s="85"/>
-      <c r="D283" s="80"/>
+      <c r="A283" s="91"/>
+      <c r="B283" s="86"/>
+      <c r="C283" s="92"/>
+      <c r="D283" s="93"/>
     </row>
     <row r="284" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="84"/>
-      <c r="B284" s="78"/>
-      <c r="C284" s="85"/>
-      <c r="D284" s="80"/>
+      <c r="A284" s="91"/>
+      <c r="B284" s="86"/>
+      <c r="C284" s="92"/>
+      <c r="D284" s="93"/>
     </row>
     <row r="285" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="84"/>
-      <c r="B285" s="78"/>
-      <c r="C285" s="85"/>
-      <c r="D285" s="80"/>
+      <c r="A285" s="91"/>
+      <c r="B285" s="86"/>
+      <c r="C285" s="92"/>
+      <c r="D285" s="93"/>
     </row>
     <row r="286" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="84"/>
-      <c r="B286" s="78"/>
-      <c r="C286" s="85"/>
-      <c r="D286" s="80"/>
+      <c r="A286" s="91"/>
+      <c r="B286" s="86"/>
+      <c r="C286" s="92"/>
+      <c r="D286" s="93"/>
     </row>
     <row r="287" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="84"/>
-      <c r="B287" s="78"/>
-      <c r="C287" s="85"/>
-      <c r="D287" s="80"/>
+      <c r="A287" s="91"/>
+      <c r="B287" s="86"/>
+      <c r="C287" s="92"/>
+      <c r="D287" s="93"/>
     </row>
     <row r="288" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="84"/>
-      <c r="B288" s="78"/>
-      <c r="C288" s="85"/>
-      <c r="D288" s="80"/>
+      <c r="A288" s="91"/>
+      <c r="B288" s="86"/>
+      <c r="C288" s="92"/>
+      <c r="D288" s="93"/>
     </row>
     <row r="289" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="84"/>
-      <c r="B289" s="78"/>
-      <c r="C289" s="85"/>
-      <c r="D289" s="80"/>
+      <c r="A289" s="91"/>
+      <c r="B289" s="86"/>
+      <c r="C289" s="92"/>
+      <c r="D289" s="93"/>
     </row>
     <row r="290" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="84"/>
-      <c r="B290" s="78"/>
-      <c r="C290" s="85"/>
-      <c r="D290" s="80"/>
+      <c r="A290" s="91"/>
+      <c r="B290" s="86"/>
+      <c r="C290" s="92"/>
+      <c r="D290" s="93"/>
     </row>
     <row r="291" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="84"/>
-      <c r="B291" s="78"/>
-      <c r="C291" s="85"/>
-      <c r="D291" s="80"/>
+      <c r="A291" s="91"/>
+      <c r="B291" s="86"/>
+      <c r="C291" s="92"/>
+      <c r="D291" s="93"/>
     </row>
     <row r="292" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="84"/>
-      <c r="B292" s="78"/>
-      <c r="C292" s="85"/>
-      <c r="D292" s="80"/>
+      <c r="A292" s="91"/>
+      <c r="B292" s="86"/>
+      <c r="C292" s="92"/>
+      <c r="D292" s="93"/>
     </row>
     <row r="293" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="84"/>
-      <c r="B293" s="78"/>
-      <c r="C293" s="85"/>
-      <c r="D293" s="80"/>
+      <c r="A293" s="91"/>
+      <c r="B293" s="86"/>
+      <c r="C293" s="92"/>
+      <c r="D293" s="93"/>
     </row>
     <row r="294" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="84"/>
-      <c r="B294" s="78"/>
-      <c r="C294" s="85"/>
-      <c r="D294" s="80"/>
+      <c r="A294" s="91"/>
+      <c r="B294" s="86"/>
+      <c r="C294" s="92"/>
+      <c r="D294" s="93"/>
     </row>
     <row r="295" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="84"/>
-      <c r="B295" s="78"/>
-      <c r="C295" s="85"/>
-      <c r="D295" s="80"/>
+      <c r="A295" s="91"/>
+      <c r="B295" s="86"/>
+      <c r="C295" s="92"/>
+      <c r="D295" s="93"/>
     </row>
     <row r="296" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="84"/>
-      <c r="B296" s="78"/>
-      <c r="C296" s="85"/>
-      <c r="D296" s="80"/>
+      <c r="A296" s="91"/>
+      <c r="B296" s="86"/>
+      <c r="C296" s="92"/>
+      <c r="D296" s="93"/>
     </row>
     <row r="297" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="84"/>
-      <c r="B297" s="78"/>
-      <c r="C297" s="85"/>
-      <c r="D297" s="80"/>
+      <c r="A297" s="91"/>
+      <c r="B297" s="86"/>
+      <c r="C297" s="92"/>
+      <c r="D297" s="93"/>
     </row>
     <row r="298" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="84"/>
-      <c r="B298" s="78"/>
-      <c r="C298" s="85"/>
-      <c r="D298" s="80"/>
+      <c r="A298" s="91"/>
+      <c r="B298" s="86"/>
+      <c r="C298" s="92"/>
+      <c r="D298" s="93"/>
     </row>
     <row r="299" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="84"/>
-      <c r="B299" s="78"/>
-      <c r="C299" s="85"/>
-      <c r="D299" s="80"/>
+      <c r="A299" s="91"/>
+      <c r="B299" s="86"/>
+      <c r="C299" s="92"/>
+      <c r="D299" s="93"/>
     </row>
     <row r="300" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="84"/>
-      <c r="B300" s="78"/>
-      <c r="C300" s="85"/>
-      <c r="D300" s="80"/>
+      <c r="A300" s="91"/>
+      <c r="B300" s="86"/>
+      <c r="C300" s="92"/>
+      <c r="D300" s="93"/>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="45"/>
@@ -13766,265 +13704,265 @@
       <c r="M301" s="41"/>
     </row>
     <row r="302" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="84"/>
-      <c r="B302" s="78"/>
-      <c r="C302" s="85"/>
-      <c r="D302" s="80"/>
+      <c r="A302" s="91"/>
+      <c r="B302" s="86"/>
+      <c r="C302" s="92"/>
+      <c r="D302" s="93"/>
     </row>
     <row r="303" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="84"/>
-      <c r="B303" s="78"/>
-      <c r="C303" s="85"/>
-      <c r="D303" s="80"/>
+      <c r="A303" s="91"/>
+      <c r="B303" s="86"/>
+      <c r="C303" s="92"/>
+      <c r="D303" s="93"/>
     </row>
     <row r="304" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="84"/>
-      <c r="B304" s="78"/>
-      <c r="C304" s="85"/>
-      <c r="D304" s="80"/>
+      <c r="A304" s="91"/>
+      <c r="B304" s="86"/>
+      <c r="C304" s="92"/>
+      <c r="D304" s="93"/>
     </row>
     <row r="305" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="84"/>
-      <c r="B305" s="78"/>
-      <c r="C305" s="85"/>
-      <c r="D305" s="80"/>
+      <c r="A305" s="91"/>
+      <c r="B305" s="86"/>
+      <c r="C305" s="92"/>
+      <c r="D305" s="93"/>
     </row>
     <row r="306" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="84"/>
-      <c r="B306" s="78"/>
-      <c r="C306" s="85"/>
-      <c r="D306" s="80"/>
+      <c r="A306" s="91"/>
+      <c r="B306" s="86"/>
+      <c r="C306" s="92"/>
+      <c r="D306" s="93"/>
     </row>
     <row r="307" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="84"/>
-      <c r="B307" s="78"/>
-      <c r="C307" s="85"/>
-      <c r="D307" s="80"/>
+      <c r="A307" s="91"/>
+      <c r="B307" s="86"/>
+      <c r="C307" s="92"/>
+      <c r="D307" s="93"/>
     </row>
     <row r="308" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="84"/>
-      <c r="B308" s="78"/>
-      <c r="C308" s="85"/>
-      <c r="D308" s="80"/>
+      <c r="A308" s="91"/>
+      <c r="B308" s="86"/>
+      <c r="C308" s="92"/>
+      <c r="D308" s="93"/>
     </row>
     <row r="309" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="84"/>
-      <c r="B309" s="78"/>
-      <c r="C309" s="85"/>
-      <c r="D309" s="80"/>
+      <c r="A309" s="91"/>
+      <c r="B309" s="86"/>
+      <c r="C309" s="92"/>
+      <c r="D309" s="93"/>
     </row>
     <row r="310" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="84"/>
-      <c r="B310" s="78"/>
-      <c r="C310" s="85"/>
-      <c r="D310" s="80"/>
+      <c r="A310" s="91"/>
+      <c r="B310" s="86"/>
+      <c r="C310" s="92"/>
+      <c r="D310" s="93"/>
     </row>
     <row r="311" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="84"/>
-      <c r="B311" s="78"/>
-      <c r="C311" s="85"/>
-      <c r="D311" s="80"/>
+      <c r="A311" s="91"/>
+      <c r="B311" s="86"/>
+      <c r="C311" s="92"/>
+      <c r="D311" s="93"/>
     </row>
     <row r="312" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="84"/>
-      <c r="B312" s="78"/>
-      <c r="C312" s="85"/>
-      <c r="D312" s="80"/>
+      <c r="A312" s="91"/>
+      <c r="B312" s="86"/>
+      <c r="C312" s="92"/>
+      <c r="D312" s="93"/>
     </row>
     <row r="313" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="84"/>
-      <c r="B313" s="78"/>
-      <c r="C313" s="85"/>
-      <c r="D313" s="80"/>
+      <c r="A313" s="91"/>
+      <c r="B313" s="86"/>
+      <c r="C313" s="92"/>
+      <c r="D313" s="93"/>
     </row>
     <row r="314" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="84"/>
-      <c r="B314" s="78"/>
-      <c r="C314" s="85"/>
-      <c r="D314" s="80"/>
+      <c r="A314" s="91"/>
+      <c r="B314" s="86"/>
+      <c r="C314" s="92"/>
+      <c r="D314" s="93"/>
     </row>
     <row r="315" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="84"/>
-      <c r="B315" s="78"/>
-      <c r="C315" s="85"/>
-      <c r="D315" s="80"/>
+      <c r="A315" s="91"/>
+      <c r="B315" s="86"/>
+      <c r="C315" s="92"/>
+      <c r="D315" s="93"/>
     </row>
     <row r="316" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A316" s="84"/>
-      <c r="B316" s="78"/>
-      <c r="C316" s="85"/>
-      <c r="D316" s="80"/>
+      <c r="A316" s="91"/>
+      <c r="B316" s="86"/>
+      <c r="C316" s="92"/>
+      <c r="D316" s="93"/>
     </row>
     <row r="317" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="84"/>
-      <c r="B317" s="78"/>
-      <c r="C317" s="85"/>
-      <c r="D317" s="80"/>
+      <c r="A317" s="91"/>
+      <c r="B317" s="86"/>
+      <c r="C317" s="92"/>
+      <c r="D317" s="93"/>
     </row>
     <row r="318" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="84"/>
-      <c r="B318" s="78"/>
-      <c r="C318" s="85"/>
-      <c r="D318" s="80"/>
+      <c r="A318" s="91"/>
+      <c r="B318" s="86"/>
+      <c r="C318" s="92"/>
+      <c r="D318" s="93"/>
     </row>
     <row r="319" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="84"/>
-      <c r="B319" s="78"/>
-      <c r="C319" s="85"/>
-      <c r="D319" s="80"/>
+      <c r="A319" s="91"/>
+      <c r="B319" s="86"/>
+      <c r="C319" s="92"/>
+      <c r="D319" s="93"/>
     </row>
     <row r="320" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="84"/>
-      <c r="B320" s="78"/>
-      <c r="C320" s="85"/>
-      <c r="D320" s="80"/>
+      <c r="A320" s="91"/>
+      <c r="B320" s="86"/>
+      <c r="C320" s="92"/>
+      <c r="D320" s="93"/>
     </row>
     <row r="321" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="84"/>
-      <c r="B321" s="78"/>
-      <c r="C321" s="85"/>
-      <c r="D321" s="80"/>
+      <c r="A321" s="91"/>
+      <c r="B321" s="86"/>
+      <c r="C321" s="92"/>
+      <c r="D321" s="93"/>
     </row>
     <row r="322" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="84"/>
-      <c r="B322" s="78"/>
-      <c r="C322" s="85"/>
-      <c r="D322" s="80"/>
+      <c r="A322" s="91"/>
+      <c r="B322" s="86"/>
+      <c r="C322" s="92"/>
+      <c r="D322" s="93"/>
     </row>
     <row r="323" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="84"/>
-      <c r="B323" s="78"/>
-      <c r="C323" s="85"/>
-      <c r="D323" s="80"/>
+      <c r="A323" s="91"/>
+      <c r="B323" s="86"/>
+      <c r="C323" s="92"/>
+      <c r="D323" s="93"/>
     </row>
     <row r="324" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="84"/>
-      <c r="B324" s="78"/>
-      <c r="C324" s="85"/>
-      <c r="D324" s="80"/>
+      <c r="A324" s="91"/>
+      <c r="B324" s="86"/>
+      <c r="C324" s="92"/>
+      <c r="D324" s="93"/>
     </row>
     <row r="325" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="84"/>
-      <c r="B325" s="78"/>
-      <c r="C325" s="85"/>
-      <c r="D325" s="80"/>
+      <c r="A325" s="91"/>
+      <c r="B325" s="86"/>
+      <c r="C325" s="92"/>
+      <c r="D325" s="93"/>
     </row>
     <row r="326" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="84"/>
-      <c r="B326" s="78"/>
-      <c r="C326" s="85"/>
-      <c r="D326" s="80"/>
+      <c r="A326" s="91"/>
+      <c r="B326" s="86"/>
+      <c r="C326" s="92"/>
+      <c r="D326" s="93"/>
     </row>
     <row r="327" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="84"/>
-      <c r="B327" s="78"/>
-      <c r="C327" s="85"/>
-      <c r="D327" s="80"/>
+      <c r="A327" s="91"/>
+      <c r="B327" s="86"/>
+      <c r="C327" s="92"/>
+      <c r="D327" s="93"/>
     </row>
     <row r="328" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="84"/>
-      <c r="B328" s="78"/>
-      <c r="C328" s="85"/>
-      <c r="D328" s="80"/>
+      <c r="A328" s="91"/>
+      <c r="B328" s="86"/>
+      <c r="C328" s="92"/>
+      <c r="D328" s="93"/>
     </row>
     <row r="329" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="84"/>
-      <c r="B329" s="78"/>
-      <c r="C329" s="85"/>
-      <c r="D329" s="80"/>
+      <c r="A329" s="91"/>
+      <c r="B329" s="86"/>
+      <c r="C329" s="92"/>
+      <c r="D329" s="93"/>
     </row>
     <row r="330" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="84"/>
-      <c r="B330" s="78"/>
-      <c r="C330" s="85"/>
-      <c r="D330" s="80"/>
+      <c r="A330" s="91"/>
+      <c r="B330" s="86"/>
+      <c r="C330" s="92"/>
+      <c r="D330" s="93"/>
     </row>
     <row r="331" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="84"/>
-      <c r="B331" s="78"/>
-      <c r="C331" s="85"/>
-      <c r="D331" s="80"/>
+      <c r="A331" s="91"/>
+      <c r="B331" s="86"/>
+      <c r="C331" s="92"/>
+      <c r="D331" s="93"/>
     </row>
     <row r="332" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A332" s="86"/>
-      <c r="B332" s="86"/>
-      <c r="C332" s="86"/>
-      <c r="D332" s="86"/>
-      <c r="E332" s="86"/>
-      <c r="F332" s="86"/>
-      <c r="G332" s="86"/>
-      <c r="H332" s="86"/>
-      <c r="I332" s="86"/>
-      <c r="J332" s="86"/>
-      <c r="K332" s="86"/>
-      <c r="L332" s="86"/>
+      <c r="A332" s="79"/>
+      <c r="B332" s="79"/>
+      <c r="C332" s="79"/>
+      <c r="D332" s="79"/>
+      <c r="E332" s="79"/>
+      <c r="F332" s="79"/>
+      <c r="G332" s="79"/>
+      <c r="H332" s="79"/>
+      <c r="I332" s="79"/>
+      <c r="J332" s="79"/>
+      <c r="K332" s="79"/>
+      <c r="L332" s="79"/>
       <c r="M332" s="49"/>
     </row>
     <row r="333" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A333" s="86"/>
-      <c r="B333" s="86"/>
-      <c r="C333" s="86"/>
-      <c r="D333" s="86"/>
-      <c r="E333" s="86"/>
-      <c r="F333" s="86"/>
-      <c r="G333" s="86"/>
-      <c r="H333" s="86"/>
-      <c r="I333" s="86"/>
-      <c r="J333" s="86"/>
-      <c r="K333" s="86"/>
-      <c r="L333" s="86"/>
+      <c r="A333" s="79"/>
+      <c r="B333" s="79"/>
+      <c r="C333" s="79"/>
+      <c r="D333" s="79"/>
+      <c r="E333" s="79"/>
+      <c r="F333" s="79"/>
+      <c r="G333" s="79"/>
+      <c r="H333" s="79"/>
+      <c r="I333" s="79"/>
+      <c r="J333" s="79"/>
+      <c r="K333" s="79"/>
+      <c r="L333" s="79"/>
       <c r="M333" s="49"/>
     </row>
     <row r="334" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A334" s="86"/>
-      <c r="B334" s="86"/>
-      <c r="C334" s="86"/>
-      <c r="D334" s="86"/>
-      <c r="E334" s="86"/>
-      <c r="F334" s="86"/>
-      <c r="G334" s="86"/>
-      <c r="H334" s="86"/>
-      <c r="I334" s="86"/>
-      <c r="J334" s="86"/>
-      <c r="K334" s="86"/>
-      <c r="L334" s="86"/>
+      <c r="A334" s="79"/>
+      <c r="B334" s="79"/>
+      <c r="C334" s="79"/>
+      <c r="D334" s="79"/>
+      <c r="E334" s="79"/>
+      <c r="F334" s="79"/>
+      <c r="G334" s="79"/>
+      <c r="H334" s="79"/>
+      <c r="I334" s="79"/>
+      <c r="J334" s="79"/>
+      <c r="K334" s="79"/>
+      <c r="L334" s="79"/>
       <c r="M334" s="49"/>
     </row>
     <row r="335" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A335" s="86"/>
-      <c r="B335" s="86"/>
-      <c r="C335" s="86"/>
-      <c r="D335" s="86"/>
-      <c r="E335" s="86"/>
-      <c r="F335" s="86"/>
-      <c r="G335" s="86"/>
-      <c r="H335" s="86"/>
-      <c r="I335" s="86"/>
-      <c r="J335" s="86"/>
-      <c r="K335" s="86"/>
-      <c r="L335" s="86"/>
+      <c r="A335" s="79"/>
+      <c r="B335" s="79"/>
+      <c r="C335" s="79"/>
+      <c r="D335" s="79"/>
+      <c r="E335" s="79"/>
+      <c r="F335" s="79"/>
+      <c r="G335" s="79"/>
+      <c r="H335" s="79"/>
+      <c r="I335" s="79"/>
+      <c r="J335" s="79"/>
+      <c r="K335" s="79"/>
+      <c r="L335" s="79"/>
       <c r="M335" s="49"/>
     </row>
     <row r="336" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A336" s="86"/>
-      <c r="B336" s="86"/>
-      <c r="C336" s="86"/>
-      <c r="D336" s="86"/>
-      <c r="E336" s="86"/>
-      <c r="F336" s="86"/>
-      <c r="G336" s="86"/>
-      <c r="H336" s="86"/>
-      <c r="I336" s="86"/>
-      <c r="J336" s="86"/>
-      <c r="K336" s="86"/>
-      <c r="L336" s="86"/>
+      <c r="A336" s="79"/>
+      <c r="B336" s="79"/>
+      <c r="C336" s="79"/>
+      <c r="D336" s="79"/>
+      <c r="E336" s="79"/>
+      <c r="F336" s="79"/>
+      <c r="G336" s="79"/>
+      <c r="H336" s="79"/>
+      <c r="I336" s="79"/>
+      <c r="J336" s="79"/>
+      <c r="K336" s="79"/>
+      <c r="L336" s="79"/>
       <c r="M336" s="49"/>
     </row>
     <row r="337" spans="1:15" ht="126.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="87"/>
-      <c r="B337" s="88"/>
-      <c r="C337" s="89"/>
-      <c r="D337" s="90"/>
+      <c r="A337" s="89"/>
+      <c r="B337" s="90"/>
+      <c r="C337" s="84"/>
+      <c r="D337" s="83"/>
       <c r="E337" s="52"/>
       <c r="F337" s="52"/>
       <c r="G337" s="53"/>
@@ -14033,10 +13971,10 @@
       <c r="O337" s="55"/>
     </row>
     <row r="338" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A338" s="87"/>
-      <c r="B338" s="88"/>
-      <c r="C338" s="89"/>
-      <c r="D338" s="90"/>
+      <c r="A338" s="89"/>
+      <c r="B338" s="90"/>
+      <c r="C338" s="84"/>
+      <c r="D338" s="83"/>
       <c r="E338" s="52"/>
       <c r="F338" s="52"/>
       <c r="G338" s="53"/>
@@ -14045,242 +13983,242 @@
       <c r="O338" s="55"/>
     </row>
     <row r="339" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A339" s="87"/>
-      <c r="B339" s="88"/>
-      <c r="C339" s="89"/>
-      <c r="D339" s="90"/>
+      <c r="A339" s="89"/>
+      <c r="B339" s="90"/>
+      <c r="C339" s="84"/>
+      <c r="D339" s="83"/>
       <c r="E339" s="52"/>
       <c r="F339" s="52"/>
       <c r="G339" s="53"/>
     </row>
     <row r="340" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A340" s="87"/>
-      <c r="B340" s="88"/>
-      <c r="C340" s="89"/>
-      <c r="D340" s="90"/>
+      <c r="A340" s="89"/>
+      <c r="B340" s="90"/>
+      <c r="C340" s="84"/>
+      <c r="D340" s="83"/>
       <c r="E340" s="52"/>
       <c r="F340" s="52"/>
       <c r="G340" s="53"/>
     </row>
     <row r="341" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A341" s="87"/>
-      <c r="B341" s="88"/>
-      <c r="C341" s="89"/>
-      <c r="D341" s="90"/>
+      <c r="A341" s="89"/>
+      <c r="B341" s="90"/>
+      <c r="C341" s="84"/>
+      <c r="D341" s="83"/>
       <c r="E341" s="52"/>
       <c r="F341" s="52"/>
       <c r="G341" s="53"/>
     </row>
     <row r="342" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A342" s="87"/>
-      <c r="B342" s="88"/>
-      <c r="C342" s="89"/>
-      <c r="D342" s="90"/>
+      <c r="A342" s="89"/>
+      <c r="B342" s="90"/>
+      <c r="C342" s="84"/>
+      <c r="D342" s="83"/>
       <c r="E342" s="52"/>
       <c r="F342" s="52"/>
       <c r="G342" s="53"/>
     </row>
     <row r="343" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A343" s="87"/>
-      <c r="B343" s="88"/>
-      <c r="C343" s="89"/>
-      <c r="D343" s="90"/>
+      <c r="A343" s="89"/>
+      <c r="B343" s="90"/>
+      <c r="C343" s="84"/>
+      <c r="D343" s="83"/>
       <c r="E343" s="52"/>
       <c r="F343" s="52"/>
       <c r="G343" s="53"/>
     </row>
     <row r="344" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A344" s="87"/>
-      <c r="B344" s="88"/>
-      <c r="C344" s="89"/>
-      <c r="D344" s="90"/>
+      <c r="A344" s="89"/>
+      <c r="B344" s="90"/>
+      <c r="C344" s="84"/>
+      <c r="D344" s="83"/>
       <c r="E344" s="52"/>
       <c r="F344" s="52"/>
       <c r="G344" s="53"/>
     </row>
     <row r="345" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A345" s="87"/>
-      <c r="B345" s="88"/>
-      <c r="C345" s="89"/>
-      <c r="D345" s="90"/>
+      <c r="A345" s="89"/>
+      <c r="B345" s="90"/>
+      <c r="C345" s="84"/>
+      <c r="D345" s="83"/>
       <c r="E345" s="52"/>
       <c r="F345" s="52"/>
       <c r="G345" s="53"/>
     </row>
     <row r="346" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A346" s="87"/>
-      <c r="B346" s="88"/>
-      <c r="C346" s="89"/>
-      <c r="D346" s="90"/>
+      <c r="A346" s="89"/>
+      <c r="B346" s="90"/>
+      <c r="C346" s="84"/>
+      <c r="D346" s="83"/>
       <c r="E346" s="52"/>
       <c r="F346" s="52"/>
       <c r="G346" s="53"/>
     </row>
     <row r="347" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A347" s="87"/>
-      <c r="B347" s="88"/>
-      <c r="C347" s="89"/>
-      <c r="D347" s="90"/>
+      <c r="A347" s="89"/>
+      <c r="B347" s="90"/>
+      <c r="C347" s="84"/>
+      <c r="D347" s="83"/>
       <c r="E347" s="52"/>
       <c r="F347" s="52"/>
       <c r="G347" s="53"/>
     </row>
     <row r="348" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A348" s="87"/>
-      <c r="B348" s="88"/>
-      <c r="C348" s="89"/>
-      <c r="D348" s="90"/>
+      <c r="A348" s="89"/>
+      <c r="B348" s="90"/>
+      <c r="C348" s="84"/>
+      <c r="D348" s="83"/>
       <c r="E348" s="52"/>
       <c r="F348" s="52"/>
       <c r="G348" s="53"/>
     </row>
     <row r="349" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A349" s="87"/>
-      <c r="B349" s="88"/>
-      <c r="C349" s="89"/>
-      <c r="D349" s="90"/>
+      <c r="A349" s="89"/>
+      <c r="B349" s="90"/>
+      <c r="C349" s="84"/>
+      <c r="D349" s="83"/>
       <c r="E349" s="52"/>
       <c r="F349" s="52"/>
       <c r="G349" s="53"/>
     </row>
     <row r="350" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A350" s="87"/>
-      <c r="B350" s="88"/>
-      <c r="C350" s="89"/>
-      <c r="D350" s="90"/>
+      <c r="A350" s="89"/>
+      <c r="B350" s="90"/>
+      <c r="C350" s="84"/>
+      <c r="D350" s="83"/>
       <c r="E350" s="52"/>
       <c r="F350" s="52"/>
       <c r="G350" s="53"/>
     </row>
     <row r="351" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A351" s="87"/>
-      <c r="B351" s="88"/>
-      <c r="C351" s="89"/>
-      <c r="D351" s="90"/>
+      <c r="A351" s="89"/>
+      <c r="B351" s="90"/>
+      <c r="C351" s="84"/>
+      <c r="D351" s="83"/>
       <c r="E351" s="52"/>
       <c r="F351" s="52"/>
       <c r="G351" s="53"/>
     </row>
     <row r="352" spans="1:15" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A352" s="87"/>
-      <c r="B352" s="88"/>
-      <c r="C352" s="89"/>
-      <c r="D352" s="90"/>
+      <c r="A352" s="89"/>
+      <c r="B352" s="90"/>
+      <c r="C352" s="84"/>
+      <c r="D352" s="83"/>
       <c r="E352" s="52"/>
       <c r="F352" s="52"/>
       <c r="G352" s="53"/>
     </row>
     <row r="353" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A353" s="87"/>
-      <c r="B353" s="88"/>
-      <c r="C353" s="89"/>
-      <c r="D353" s="90"/>
+      <c r="A353" s="89"/>
+      <c r="B353" s="90"/>
+      <c r="C353" s="84"/>
+      <c r="D353" s="83"/>
       <c r="E353" s="52"/>
       <c r="F353" s="52"/>
       <c r="G353" s="53"/>
     </row>
     <row r="354" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A354" s="87"/>
-      <c r="B354" s="88"/>
-      <c r="C354" s="89"/>
-      <c r="D354" s="90"/>
+      <c r="A354" s="89"/>
+      <c r="B354" s="90"/>
+      <c r="C354" s="84"/>
+      <c r="D354" s="83"/>
       <c r="E354" s="52"/>
       <c r="F354" s="52"/>
       <c r="G354" s="53"/>
     </row>
     <row r="355" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A355" s="87"/>
-      <c r="B355" s="88"/>
-      <c r="C355" s="89"/>
-      <c r="D355" s="90"/>
+      <c r="A355" s="89"/>
+      <c r="B355" s="90"/>
+      <c r="C355" s="84"/>
+      <c r="D355" s="83"/>
       <c r="E355" s="52"/>
       <c r="F355" s="52"/>
       <c r="G355" s="53"/>
     </row>
     <row r="356" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A356" s="87"/>
-      <c r="B356" s="88"/>
-      <c r="C356" s="89"/>
-      <c r="D356" s="90"/>
+      <c r="A356" s="89"/>
+      <c r="B356" s="90"/>
+      <c r="C356" s="84"/>
+      <c r="D356" s="83"/>
       <c r="E356" s="52"/>
       <c r="F356" s="52"/>
       <c r="G356" s="53"/>
     </row>
     <row r="357" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A357" s="87"/>
-      <c r="B357" s="88"/>
-      <c r="C357" s="89"/>
-      <c r="D357" s="90"/>
+      <c r="A357" s="89"/>
+      <c r="B357" s="90"/>
+      <c r="C357" s="84"/>
+      <c r="D357" s="83"/>
       <c r="E357" s="52"/>
       <c r="F357" s="52"/>
       <c r="G357" s="53"/>
     </row>
     <row r="358" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A358" s="87"/>
-      <c r="B358" s="88"/>
-      <c r="C358" s="89"/>
-      <c r="D358" s="90"/>
+      <c r="A358" s="89"/>
+      <c r="B358" s="90"/>
+      <c r="C358" s="84"/>
+      <c r="D358" s="83"/>
       <c r="E358" s="52"/>
       <c r="F358" s="52"/>
       <c r="G358" s="53"/>
     </row>
     <row r="359" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A359" s="87"/>
-      <c r="B359" s="88"/>
-      <c r="C359" s="89"/>
-      <c r="D359" s="90"/>
+      <c r="A359" s="89"/>
+      <c r="B359" s="90"/>
+      <c r="C359" s="84"/>
+      <c r="D359" s="83"/>
       <c r="E359" s="52"/>
       <c r="F359" s="52"/>
       <c r="G359" s="53"/>
     </row>
     <row r="360" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A360" s="87"/>
-      <c r="B360" s="88"/>
-      <c r="C360" s="89"/>
-      <c r="D360" s="90"/>
+      <c r="A360" s="89"/>
+      <c r="B360" s="90"/>
+      <c r="C360" s="84"/>
+      <c r="D360" s="83"/>
       <c r="E360" s="52"/>
       <c r="F360" s="52"/>
       <c r="G360" s="53"/>
     </row>
     <row r="361" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A361" s="87"/>
-      <c r="B361" s="88"/>
-      <c r="C361" s="89"/>
-      <c r="D361" s="90"/>
+      <c r="A361" s="89"/>
+      <c r="B361" s="90"/>
+      <c r="C361" s="84"/>
+      <c r="D361" s="83"/>
       <c r="E361" s="52"/>
       <c r="F361" s="52"/>
       <c r="G361" s="53"/>
     </row>
     <row r="362" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A362" s="87"/>
-      <c r="B362" s="88"/>
-      <c r="C362" s="89"/>
-      <c r="D362" s="90"/>
+      <c r="A362" s="89"/>
+      <c r="B362" s="90"/>
+      <c r="C362" s="84"/>
+      <c r="D362" s="83"/>
       <c r="E362" s="52"/>
       <c r="F362" s="52"/>
       <c r="G362" s="53"/>
     </row>
     <row r="363" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A363" s="87"/>
-      <c r="B363" s="88"/>
-      <c r="C363" s="89"/>
-      <c r="D363" s="90"/>
+      <c r="A363" s="89"/>
+      <c r="B363" s="90"/>
+      <c r="C363" s="84"/>
+      <c r="D363" s="83"/>
       <c r="E363" s="52"/>
       <c r="F363" s="52"/>
       <c r="G363" s="53"/>
     </row>
     <row r="364" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A364" s="87"/>
-      <c r="B364" s="88"/>
-      <c r="C364" s="89"/>
-      <c r="D364" s="90"/>
+      <c r="A364" s="89"/>
+      <c r="B364" s="90"/>
+      <c r="C364" s="84"/>
+      <c r="D364" s="83"/>
       <c r="E364" s="52"/>
       <c r="F364" s="52"/>
       <c r="G364" s="53"/>
     </row>
     <row r="365" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A365" s="87"/>
-      <c r="B365" s="88"/>
+      <c r="A365" s="89"/>
+      <c r="B365" s="90"/>
       <c r="C365" s="50"/>
       <c r="D365" s="51"/>
       <c r="E365" s="52"/>
@@ -14288,8 +14226,8 @@
       <c r="G365" s="53"/>
     </row>
     <row r="366" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A366" s="87"/>
-      <c r="B366" s="88"/>
+      <c r="A366" s="89"/>
+      <c r="B366" s="90"/>
       <c r="C366" s="50"/>
       <c r="D366" s="51"/>
       <c r="E366" s="52"/>
@@ -14297,1355 +14235,1355 @@
       <c r="G366" s="53"/>
     </row>
     <row r="367" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A367" s="87"/>
-      <c r="B367" s="88"/>
-      <c r="C367" s="89"/>
-      <c r="D367" s="90"/>
+      <c r="A367" s="89"/>
+      <c r="B367" s="90"/>
+      <c r="C367" s="84"/>
+      <c r="D367" s="83"/>
       <c r="E367" s="52"/>
       <c r="F367" s="52"/>
       <c r="G367" s="53"/>
     </row>
     <row r="368" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A368" s="87"/>
-      <c r="B368" s="88"/>
-      <c r="C368" s="89"/>
-      <c r="D368" s="90"/>
+      <c r="A368" s="89"/>
+      <c r="B368" s="90"/>
+      <c r="C368" s="84"/>
+      <c r="D368" s="83"/>
       <c r="E368" s="52"/>
       <c r="F368" s="52"/>
       <c r="G368" s="53"/>
     </row>
     <row r="369" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A369" s="87"/>
-      <c r="B369" s="88"/>
-      <c r="C369" s="89"/>
-      <c r="D369" s="90"/>
+      <c r="A369" s="89"/>
+      <c r="B369" s="90"/>
+      <c r="C369" s="84"/>
+      <c r="D369" s="83"/>
       <c r="E369" s="52"/>
       <c r="F369" s="52"/>
       <c r="G369" s="53"/>
     </row>
     <row r="370" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A370" s="87"/>
-      <c r="B370" s="88"/>
-      <c r="C370" s="89"/>
-      <c r="D370" s="90"/>
+      <c r="A370" s="89"/>
+      <c r="B370" s="90"/>
+      <c r="C370" s="84"/>
+      <c r="D370" s="83"/>
       <c r="E370" s="52"/>
       <c r="F370" s="52"/>
       <c r="G370" s="53"/>
     </row>
     <row r="371" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A371" s="87"/>
-      <c r="B371" s="88"/>
-      <c r="C371" s="89"/>
-      <c r="D371" s="90"/>
+      <c r="A371" s="89"/>
+      <c r="B371" s="90"/>
+      <c r="C371" s="84"/>
+      <c r="D371" s="83"/>
       <c r="E371" s="52"/>
       <c r="F371" s="52"/>
       <c r="G371" s="53"/>
     </row>
     <row r="372" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A372" s="87"/>
-      <c r="B372" s="88"/>
-      <c r="C372" s="89"/>
-      <c r="D372" s="90"/>
+      <c r="A372" s="89"/>
+      <c r="B372" s="90"/>
+      <c r="C372" s="84"/>
+      <c r="D372" s="83"/>
       <c r="E372" s="52"/>
       <c r="F372" s="52"/>
       <c r="G372" s="53"/>
     </row>
     <row r="373" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A373" s="87"/>
-      <c r="B373" s="88"/>
-      <c r="C373" s="89"/>
-      <c r="D373" s="90"/>
+      <c r="A373" s="89"/>
+      <c r="B373" s="90"/>
+      <c r="C373" s="84"/>
+      <c r="D373" s="83"/>
       <c r="E373" s="52"/>
       <c r="F373" s="52"/>
       <c r="G373" s="53"/>
     </row>
     <row r="374" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A374" s="87"/>
-      <c r="B374" s="88"/>
-      <c r="C374" s="89"/>
-      <c r="D374" s="90"/>
+      <c r="A374" s="89"/>
+      <c r="B374" s="90"/>
+      <c r="C374" s="84"/>
+      <c r="D374" s="83"/>
       <c r="E374" s="52"/>
       <c r="F374" s="52"/>
       <c r="G374" s="53"/>
     </row>
     <row r="375" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A375" s="87"/>
-      <c r="B375" s="88"/>
-      <c r="C375" s="89"/>
-      <c r="D375" s="90"/>
+      <c r="A375" s="89"/>
+      <c r="B375" s="90"/>
+      <c r="C375" s="84"/>
+      <c r="D375" s="83"/>
       <c r="E375" s="52"/>
       <c r="F375" s="52"/>
       <c r="G375" s="53"/>
     </row>
     <row r="376" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A376" s="87"/>
-      <c r="B376" s="88"/>
-      <c r="C376" s="89"/>
-      <c r="D376" s="90"/>
+      <c r="A376" s="89"/>
+      <c r="B376" s="90"/>
+      <c r="C376" s="84"/>
+      <c r="D376" s="83"/>
       <c r="E376" s="52"/>
       <c r="F376" s="52"/>
       <c r="G376" s="53"/>
     </row>
     <row r="377" spans="1:13" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A377" s="87"/>
-      <c r="B377" s="88"/>
-      <c r="C377" s="89"/>
-      <c r="D377" s="90"/>
+      <c r="A377" s="89"/>
+      <c r="B377" s="90"/>
+      <c r="C377" s="84"/>
+      <c r="D377" s="83"/>
       <c r="E377" s="52"/>
       <c r="F377" s="52"/>
       <c r="G377" s="53"/>
     </row>
     <row r="378" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="86"/>
-      <c r="B378" s="86"/>
-      <c r="C378" s="86"/>
-      <c r="D378" s="86"/>
-      <c r="E378" s="86"/>
-      <c r="F378" s="86"/>
-      <c r="G378" s="86"/>
-      <c r="H378" s="86"/>
-      <c r="I378" s="86"/>
-      <c r="J378" s="86"/>
-      <c r="K378" s="86"/>
-      <c r="L378" s="86"/>
+      <c r="A378" s="79"/>
+      <c r="B378" s="79"/>
+      <c r="C378" s="79"/>
+      <c r="D378" s="79"/>
+      <c r="E378" s="79"/>
+      <c r="F378" s="79"/>
+      <c r="G378" s="79"/>
+      <c r="H378" s="79"/>
+      <c r="I378" s="79"/>
+      <c r="J378" s="79"/>
+      <c r="K378" s="79"/>
+      <c r="L378" s="79"/>
       <c r="M378" s="49"/>
     </row>
     <row r="379" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="86"/>
-      <c r="B379" s="86"/>
-      <c r="C379" s="86"/>
-      <c r="D379" s="86"/>
-      <c r="E379" s="86"/>
-      <c r="F379" s="86"/>
-      <c r="G379" s="86"/>
-      <c r="H379" s="86"/>
-      <c r="I379" s="86"/>
-      <c r="J379" s="86"/>
-      <c r="K379" s="86"/>
-      <c r="L379" s="86"/>
+      <c r="A379" s="79"/>
+      <c r="B379" s="79"/>
+      <c r="C379" s="79"/>
+      <c r="D379" s="79"/>
+      <c r="E379" s="79"/>
+      <c r="F379" s="79"/>
+      <c r="G379" s="79"/>
+      <c r="H379" s="79"/>
+      <c r="I379" s="79"/>
+      <c r="J379" s="79"/>
+      <c r="K379" s="79"/>
+      <c r="L379" s="79"/>
       <c r="M379" s="49"/>
     </row>
     <row r="380" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="86"/>
-      <c r="B380" s="86"/>
-      <c r="C380" s="86"/>
-      <c r="D380" s="86"/>
-      <c r="E380" s="86"/>
-      <c r="F380" s="86"/>
-      <c r="G380" s="86"/>
-      <c r="H380" s="86"/>
-      <c r="I380" s="86"/>
-      <c r="J380" s="86"/>
-      <c r="K380" s="86"/>
-      <c r="L380" s="86"/>
+      <c r="A380" s="79"/>
+      <c r="B380" s="79"/>
+      <c r="C380" s="79"/>
+      <c r="D380" s="79"/>
+      <c r="E380" s="79"/>
+      <c r="F380" s="79"/>
+      <c r="G380" s="79"/>
+      <c r="H380" s="79"/>
+      <c r="I380" s="79"/>
+      <c r="J380" s="79"/>
+      <c r="K380" s="79"/>
+      <c r="L380" s="79"/>
       <c r="M380" s="49"/>
     </row>
     <row r="381" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="86"/>
-      <c r="B381" s="86"/>
-      <c r="C381" s="86"/>
-      <c r="D381" s="86"/>
-      <c r="E381" s="86"/>
-      <c r="F381" s="86"/>
-      <c r="G381" s="86"/>
-      <c r="H381" s="86"/>
-      <c r="I381" s="86"/>
-      <c r="J381" s="86"/>
-      <c r="K381" s="86"/>
-      <c r="L381" s="86"/>
+      <c r="A381" s="79"/>
+      <c r="B381" s="79"/>
+      <c r="C381" s="79"/>
+      <c r="D381" s="79"/>
+      <c r="E381" s="79"/>
+      <c r="F381" s="79"/>
+      <c r="G381" s="79"/>
+      <c r="H381" s="79"/>
+      <c r="I381" s="79"/>
+      <c r="J381" s="79"/>
+      <c r="K381" s="79"/>
+      <c r="L381" s="79"/>
       <c r="M381" s="49"/>
     </row>
     <row r="382" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="86"/>
-      <c r="B382" s="86"/>
-      <c r="C382" s="86"/>
-      <c r="D382" s="86"/>
-      <c r="E382" s="86"/>
-      <c r="F382" s="86"/>
-      <c r="G382" s="86"/>
-      <c r="H382" s="86"/>
-      <c r="I382" s="86"/>
-      <c r="J382" s="86"/>
-      <c r="K382" s="86"/>
-      <c r="L382" s="86"/>
+      <c r="A382" s="79"/>
+      <c r="B382" s="79"/>
+      <c r="C382" s="79"/>
+      <c r="D382" s="79"/>
+      <c r="E382" s="79"/>
+      <c r="F382" s="79"/>
+      <c r="G382" s="79"/>
+      <c r="H382" s="79"/>
+      <c r="I382" s="79"/>
+      <c r="J382" s="79"/>
+      <c r="K382" s="79"/>
+      <c r="L382" s="79"/>
       <c r="M382" s="49"/>
     </row>
     <row r="383" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="82"/>
-      <c r="B383" s="78"/>
-      <c r="C383" s="93"/>
-      <c r="D383" s="94"/>
+      <c r="A383" s="85"/>
+      <c r="B383" s="86"/>
+      <c r="C383" s="87"/>
+      <c r="D383" s="88"/>
       <c r="E383" s="15"/>
       <c r="F383" s="15"/>
       <c r="G383" s="15"/>
     </row>
     <row r="384" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="82"/>
-      <c r="B384" s="78"/>
-      <c r="C384" s="93"/>
-      <c r="D384" s="94"/>
+      <c r="A384" s="85"/>
+      <c r="B384" s="86"/>
+      <c r="C384" s="87"/>
+      <c r="D384" s="88"/>
       <c r="E384" s="15"/>
       <c r="F384" s="15"/>
       <c r="G384" s="15"/>
     </row>
     <row r="385" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="82"/>
-      <c r="B385" s="78"/>
-      <c r="C385" s="93"/>
-      <c r="D385" s="94"/>
+      <c r="A385" s="85"/>
+      <c r="B385" s="86"/>
+      <c r="C385" s="87"/>
+      <c r="D385" s="88"/>
       <c r="E385" s="15"/>
       <c r="F385" s="15"/>
       <c r="G385" s="15"/>
     </row>
     <row r="386" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="82"/>
-      <c r="B386" s="78"/>
-      <c r="C386" s="93"/>
-      <c r="D386" s="94"/>
+      <c r="A386" s="85"/>
+      <c r="B386" s="86"/>
+      <c r="C386" s="87"/>
+      <c r="D386" s="88"/>
       <c r="E386" s="15"/>
       <c r="F386" s="15"/>
       <c r="G386" s="15"/>
     </row>
     <row r="387" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="82"/>
-      <c r="B387" s="78"/>
-      <c r="C387" s="93"/>
-      <c r="D387" s="94"/>
+      <c r="A387" s="85"/>
+      <c r="B387" s="86"/>
+      <c r="C387" s="87"/>
+      <c r="D387" s="88"/>
       <c r="E387" s="15"/>
       <c r="F387" s="15"/>
       <c r="G387" s="15"/>
     </row>
     <row r="388" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="82"/>
-      <c r="B388" s="78"/>
-      <c r="C388" s="93"/>
-      <c r="D388" s="94"/>
+      <c r="A388" s="85"/>
+      <c r="B388" s="86"/>
+      <c r="C388" s="87"/>
+      <c r="D388" s="88"/>
       <c r="E388" s="15"/>
       <c r="F388" s="15"/>
       <c r="G388" s="15"/>
     </row>
     <row r="389" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="82"/>
-      <c r="B389" s="78"/>
-      <c r="C389" s="93"/>
-      <c r="D389" s="94"/>
+      <c r="A389" s="85"/>
+      <c r="B389" s="86"/>
+      <c r="C389" s="87"/>
+      <c r="D389" s="88"/>
       <c r="E389" s="15"/>
       <c r="F389" s="15"/>
       <c r="G389" s="15"/>
     </row>
     <row r="390" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="82"/>
-      <c r="B390" s="78"/>
-      <c r="C390" s="93"/>
-      <c r="D390" s="94"/>
+      <c r="A390" s="85"/>
+      <c r="B390" s="86"/>
+      <c r="C390" s="87"/>
+      <c r="D390" s="88"/>
       <c r="E390" s="15"/>
       <c r="F390" s="15"/>
       <c r="G390" s="15"/>
     </row>
     <row r="391" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="82"/>
-      <c r="B391" s="78"/>
-      <c r="C391" s="93"/>
-      <c r="D391" s="94"/>
+      <c r="A391" s="85"/>
+      <c r="B391" s="86"/>
+      <c r="C391" s="87"/>
+      <c r="D391" s="88"/>
       <c r="E391" s="15"/>
       <c r="F391" s="15"/>
       <c r="G391" s="15"/>
     </row>
     <row r="392" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="82"/>
-      <c r="B392" s="78"/>
-      <c r="C392" s="93"/>
-      <c r="D392" s="94"/>
+      <c r="A392" s="85"/>
+      <c r="B392" s="86"/>
+      <c r="C392" s="87"/>
+      <c r="D392" s="88"/>
       <c r="E392" s="15"/>
       <c r="F392" s="15"/>
       <c r="G392" s="15"/>
     </row>
     <row r="393" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="82"/>
-      <c r="B393" s="78"/>
-      <c r="C393" s="93"/>
-      <c r="D393" s="94"/>
+      <c r="A393" s="85"/>
+      <c r="B393" s="86"/>
+      <c r="C393" s="87"/>
+      <c r="D393" s="88"/>
       <c r="E393" s="15"/>
       <c r="F393" s="15"/>
       <c r="G393" s="15"/>
     </row>
     <row r="394" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="82"/>
-      <c r="B394" s="78"/>
-      <c r="C394" s="93"/>
-      <c r="D394" s="94"/>
+      <c r="A394" s="85"/>
+      <c r="B394" s="86"/>
+      <c r="C394" s="87"/>
+      <c r="D394" s="88"/>
       <c r="E394" s="15"/>
       <c r="F394" s="15"/>
       <c r="G394" s="15"/>
     </row>
     <row r="395" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="82"/>
-      <c r="B395" s="78"/>
-      <c r="C395" s="93"/>
-      <c r="D395" s="94"/>
+      <c r="A395" s="85"/>
+      <c r="B395" s="86"/>
+      <c r="C395" s="87"/>
+      <c r="D395" s="88"/>
       <c r="E395" s="15"/>
       <c r="F395" s="15"/>
       <c r="G395" s="15"/>
     </row>
     <row r="396" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="82"/>
-      <c r="B396" s="78"/>
-      <c r="C396" s="93"/>
-      <c r="D396" s="94"/>
+      <c r="A396" s="85"/>
+      <c r="B396" s="86"/>
+      <c r="C396" s="87"/>
+      <c r="D396" s="88"/>
       <c r="E396" s="15"/>
       <c r="F396" s="15"/>
       <c r="G396" s="15"/>
     </row>
     <row r="397" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="82"/>
-      <c r="B397" s="78"/>
-      <c r="C397" s="93"/>
-      <c r="D397" s="94"/>
+      <c r="A397" s="85"/>
+      <c r="B397" s="86"/>
+      <c r="C397" s="87"/>
+      <c r="D397" s="88"/>
       <c r="E397" s="15"/>
       <c r="F397" s="15"/>
       <c r="G397" s="15"/>
     </row>
     <row r="398" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="82"/>
-      <c r="B398" s="78"/>
-      <c r="C398" s="93"/>
-      <c r="D398" s="94"/>
+      <c r="A398" s="85"/>
+      <c r="B398" s="86"/>
+      <c r="C398" s="87"/>
+      <c r="D398" s="88"/>
       <c r="E398" s="15"/>
       <c r="F398" s="15"/>
       <c r="G398" s="15"/>
     </row>
     <row r="399" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="82"/>
-      <c r="B399" s="78"/>
-      <c r="C399" s="93"/>
-      <c r="D399" s="94"/>
+      <c r="A399" s="85"/>
+      <c r="B399" s="86"/>
+      <c r="C399" s="87"/>
+      <c r="D399" s="88"/>
       <c r="E399" s="15"/>
       <c r="F399" s="15"/>
       <c r="G399" s="15"/>
     </row>
     <row r="400" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="82"/>
-      <c r="B400" s="78"/>
-      <c r="C400" s="93"/>
-      <c r="D400" s="94"/>
+      <c r="A400" s="85"/>
+      <c r="B400" s="86"/>
+      <c r="C400" s="87"/>
+      <c r="D400" s="88"/>
       <c r="E400" s="15"/>
       <c r="F400" s="15"/>
       <c r="G400" s="15"/>
     </row>
     <row r="401" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="82"/>
-      <c r="B401" s="78"/>
-      <c r="C401" s="93"/>
-      <c r="D401" s="94"/>
+      <c r="A401" s="85"/>
+      <c r="B401" s="86"/>
+      <c r="C401" s="87"/>
+      <c r="D401" s="88"/>
       <c r="E401" s="15"/>
       <c r="F401" s="15"/>
       <c r="G401" s="15"/>
     </row>
     <row r="402" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="82"/>
-      <c r="B402" s="78"/>
-      <c r="C402" s="93"/>
-      <c r="D402" s="94"/>
+      <c r="A402" s="85"/>
+      <c r="B402" s="86"/>
+      <c r="C402" s="87"/>
+      <c r="D402" s="88"/>
       <c r="E402" s="15"/>
       <c r="F402" s="15"/>
       <c r="G402" s="15"/>
     </row>
     <row r="403" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="82"/>
-      <c r="B403" s="78"/>
-      <c r="C403" s="93"/>
-      <c r="D403" s="94"/>
+      <c r="A403" s="85"/>
+      <c r="B403" s="86"/>
+      <c r="C403" s="87"/>
+      <c r="D403" s="88"/>
       <c r="E403" s="15"/>
       <c r="F403" s="15"/>
       <c r="G403" s="15"/>
     </row>
     <row r="404" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="82"/>
-      <c r="B404" s="78"/>
-      <c r="C404" s="93"/>
-      <c r="D404" s="94"/>
+      <c r="A404" s="85"/>
+      <c r="B404" s="86"/>
+      <c r="C404" s="87"/>
+      <c r="D404" s="88"/>
       <c r="E404" s="15"/>
       <c r="F404" s="15"/>
       <c r="G404" s="15"/>
     </row>
     <row r="405" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="82"/>
-      <c r="B405" s="78"/>
-      <c r="C405" s="93"/>
-      <c r="D405" s="94"/>
+      <c r="A405" s="85"/>
+      <c r="B405" s="86"/>
+      <c r="C405" s="87"/>
+      <c r="D405" s="88"/>
       <c r="E405" s="15"/>
       <c r="F405" s="15"/>
       <c r="G405" s="15"/>
     </row>
     <row r="406" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="82"/>
-      <c r="B406" s="78"/>
-      <c r="C406" s="93"/>
-      <c r="D406" s="94"/>
+      <c r="A406" s="85"/>
+      <c r="B406" s="86"/>
+      <c r="C406" s="87"/>
+      <c r="D406" s="88"/>
       <c r="E406" s="15"/>
       <c r="F406" s="15"/>
       <c r="G406" s="15"/>
     </row>
     <row r="407" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="82"/>
-      <c r="B407" s="78"/>
-      <c r="C407" s="93"/>
-      <c r="D407" s="94"/>
+      <c r="A407" s="85"/>
+      <c r="B407" s="86"/>
+      <c r="C407" s="87"/>
+      <c r="D407" s="88"/>
       <c r="E407" s="15"/>
       <c r="F407" s="15"/>
       <c r="G407" s="15"/>
     </row>
     <row r="408" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="82"/>
-      <c r="B408" s="78"/>
-      <c r="C408" s="93"/>
-      <c r="D408" s="94"/>
+      <c r="A408" s="85"/>
+      <c r="B408" s="86"/>
+      <c r="C408" s="87"/>
+      <c r="D408" s="88"/>
       <c r="E408" s="15"/>
       <c r="F408" s="15"/>
       <c r="G408" s="15"/>
     </row>
     <row r="409" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="82"/>
-      <c r="B409" s="78"/>
-      <c r="C409" s="93"/>
-      <c r="D409" s="94"/>
+      <c r="A409" s="85"/>
+      <c r="B409" s="86"/>
+      <c r="C409" s="87"/>
+      <c r="D409" s="88"/>
       <c r="E409" s="15"/>
       <c r="F409" s="15"/>
       <c r="G409" s="15"/>
     </row>
     <row r="410" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="82"/>
-      <c r="B410" s="78"/>
-      <c r="C410" s="93"/>
-      <c r="D410" s="94"/>
+      <c r="A410" s="85"/>
+      <c r="B410" s="86"/>
+      <c r="C410" s="87"/>
+      <c r="D410" s="88"/>
       <c r="E410" s="15"/>
       <c r="F410" s="15"/>
       <c r="G410" s="15"/>
     </row>
     <row r="411" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="82"/>
-      <c r="B411" s="78"/>
-      <c r="C411" s="93"/>
-      <c r="D411" s="94"/>
+      <c r="A411" s="85"/>
+      <c r="B411" s="86"/>
+      <c r="C411" s="87"/>
+      <c r="D411" s="88"/>
       <c r="E411" s="15"/>
       <c r="F411" s="15"/>
       <c r="G411" s="15"/>
     </row>
     <row r="412" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="82"/>
-      <c r="B412" s="78"/>
-      <c r="C412" s="93"/>
-      <c r="D412" s="94"/>
+      <c r="A412" s="85"/>
+      <c r="B412" s="86"/>
+      <c r="C412" s="87"/>
+      <c r="D412" s="88"/>
       <c r="E412" s="15"/>
       <c r="F412" s="15"/>
       <c r="G412" s="15"/>
     </row>
     <row r="413" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="82"/>
-      <c r="B413" s="78"/>
-      <c r="C413" s="93"/>
-      <c r="D413" s="94"/>
+      <c r="A413" s="85"/>
+      <c r="B413" s="86"/>
+      <c r="C413" s="87"/>
+      <c r="D413" s="88"/>
       <c r="E413" s="15"/>
       <c r="F413" s="15"/>
       <c r="G413" s="15"/>
     </row>
     <row r="414" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="82"/>
-      <c r="B414" s="78"/>
-      <c r="C414" s="93"/>
-      <c r="D414" s="94"/>
+      <c r="A414" s="85"/>
+      <c r="B414" s="86"/>
+      <c r="C414" s="87"/>
+      <c r="D414" s="88"/>
       <c r="E414" s="15"/>
       <c r="F414" s="15"/>
       <c r="G414" s="15"/>
     </row>
     <row r="415" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="82"/>
-      <c r="B415" s="78"/>
-      <c r="C415" s="93"/>
-      <c r="D415" s="94"/>
+      <c r="A415" s="85"/>
+      <c r="B415" s="86"/>
+      <c r="C415" s="87"/>
+      <c r="D415" s="88"/>
       <c r="E415" s="15"/>
       <c r="F415" s="15"/>
       <c r="G415" s="15"/>
     </row>
     <row r="416" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="82"/>
-      <c r="B416" s="78"/>
-      <c r="C416" s="93"/>
-      <c r="D416" s="94"/>
+      <c r="A416" s="85"/>
+      <c r="B416" s="86"/>
+      <c r="C416" s="87"/>
+      <c r="D416" s="88"/>
       <c r="E416" s="15"/>
       <c r="F416" s="15"/>
       <c r="G416" s="15"/>
     </row>
     <row r="417" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="82"/>
-      <c r="B417" s="78"/>
-      <c r="C417" s="93"/>
-      <c r="D417" s="94"/>
+      <c r="A417" s="85"/>
+      <c r="B417" s="86"/>
+      <c r="C417" s="87"/>
+      <c r="D417" s="88"/>
       <c r="E417" s="15"/>
       <c r="F417" s="15"/>
       <c r="G417" s="15"/>
     </row>
     <row r="418" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="82"/>
-      <c r="B418" s="78"/>
-      <c r="C418" s="93"/>
-      <c r="D418" s="94"/>
+      <c r="A418" s="85"/>
+      <c r="B418" s="86"/>
+      <c r="C418" s="87"/>
+      <c r="D418" s="88"/>
       <c r="E418" s="15"/>
       <c r="F418" s="15"/>
       <c r="G418" s="15"/>
     </row>
     <row r="419" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="82"/>
-      <c r="B419" s="78"/>
-      <c r="C419" s="93"/>
-      <c r="D419" s="94"/>
+      <c r="A419" s="85"/>
+      <c r="B419" s="86"/>
+      <c r="C419" s="87"/>
+      <c r="D419" s="88"/>
       <c r="E419" s="15"/>
       <c r="F419" s="15"/>
       <c r="G419" s="15"/>
     </row>
     <row r="420" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="82"/>
-      <c r="B420" s="78"/>
-      <c r="C420" s="93"/>
-      <c r="D420" s="94"/>
+      <c r="A420" s="85"/>
+      <c r="B420" s="86"/>
+      <c r="C420" s="87"/>
+      <c r="D420" s="88"/>
       <c r="E420" s="15"/>
       <c r="F420" s="15"/>
       <c r="G420" s="15"/>
     </row>
     <row r="421" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="82"/>
-      <c r="B421" s="78"/>
-      <c r="C421" s="93"/>
-      <c r="D421" s="94"/>
+      <c r="A421" s="85"/>
+      <c r="B421" s="86"/>
+      <c r="C421" s="87"/>
+      <c r="D421" s="88"/>
       <c r="E421" s="15"/>
       <c r="F421" s="15"/>
       <c r="G421" s="15"/>
     </row>
     <row r="422" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="82"/>
-      <c r="B422" s="78"/>
-      <c r="C422" s="93"/>
-      <c r="D422" s="94"/>
+      <c r="A422" s="85"/>
+      <c r="B422" s="86"/>
+      <c r="C422" s="87"/>
+      <c r="D422" s="88"/>
       <c r="E422" s="15"/>
       <c r="F422" s="15"/>
       <c r="G422" s="15"/>
     </row>
     <row r="423" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="82"/>
-      <c r="B423" s="78"/>
-      <c r="C423" s="93"/>
-      <c r="D423" s="94"/>
+      <c r="A423" s="85"/>
+      <c r="B423" s="86"/>
+      <c r="C423" s="87"/>
+      <c r="D423" s="88"/>
       <c r="E423" s="15"/>
       <c r="F423" s="15"/>
       <c r="G423" s="15"/>
     </row>
     <row r="424" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="82"/>
-      <c r="B424" s="78"/>
-      <c r="C424" s="93"/>
-      <c r="D424" s="94"/>
+      <c r="A424" s="85"/>
+      <c r="B424" s="86"/>
+      <c r="C424" s="87"/>
+      <c r="D424" s="88"/>
       <c r="E424" s="15"/>
       <c r="F424" s="15"/>
       <c r="G424" s="15"/>
     </row>
     <row r="425" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="82"/>
-      <c r="B425" s="78"/>
-      <c r="C425" s="93"/>
-      <c r="D425" s="94"/>
+      <c r="A425" s="85"/>
+      <c r="B425" s="86"/>
+      <c r="C425" s="87"/>
+      <c r="D425" s="88"/>
       <c r="E425" s="15"/>
       <c r="F425" s="15"/>
       <c r="G425" s="15"/>
     </row>
     <row r="426" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="82"/>
-      <c r="B426" s="78"/>
-      <c r="C426" s="93"/>
-      <c r="D426" s="94"/>
+      <c r="A426" s="85"/>
+      <c r="B426" s="86"/>
+      <c r="C426" s="87"/>
+      <c r="D426" s="88"/>
       <c r="E426" s="15"/>
       <c r="F426" s="15"/>
       <c r="G426" s="15"/>
     </row>
     <row r="427" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="82"/>
-      <c r="B427" s="78"/>
-      <c r="C427" s="93"/>
-      <c r="D427" s="94"/>
+      <c r="A427" s="85"/>
+      <c r="B427" s="86"/>
+      <c r="C427" s="87"/>
+      <c r="D427" s="88"/>
       <c r="E427" s="15"/>
       <c r="F427" s="15"/>
       <c r="G427" s="15"/>
     </row>
     <row r="428" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="82"/>
-      <c r="B428" s="78"/>
-      <c r="C428" s="93"/>
-      <c r="D428" s="94"/>
+      <c r="A428" s="85"/>
+      <c r="B428" s="86"/>
+      <c r="C428" s="87"/>
+      <c r="D428" s="88"/>
       <c r="E428" s="15"/>
       <c r="F428" s="15"/>
       <c r="G428" s="15"/>
     </row>
     <row r="429" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="82"/>
-      <c r="B429" s="78"/>
-      <c r="C429" s="93"/>
-      <c r="D429" s="94"/>
+      <c r="A429" s="85"/>
+      <c r="B429" s="86"/>
+      <c r="C429" s="87"/>
+      <c r="D429" s="88"/>
       <c r="E429" s="15"/>
       <c r="F429" s="15"/>
       <c r="G429" s="15"/>
     </row>
     <row r="430" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="82"/>
-      <c r="B430" s="78"/>
-      <c r="C430" s="93"/>
-      <c r="D430" s="94"/>
+      <c r="A430" s="85"/>
+      <c r="B430" s="86"/>
+      <c r="C430" s="87"/>
+      <c r="D430" s="88"/>
       <c r="E430" s="15"/>
       <c r="F430" s="15"/>
       <c r="G430" s="15"/>
     </row>
     <row r="431" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="82"/>
-      <c r="B431" s="78"/>
-      <c r="C431" s="93"/>
-      <c r="D431" s="94"/>
+      <c r="A431" s="85"/>
+      <c r="B431" s="86"/>
+      <c r="C431" s="87"/>
+      <c r="D431" s="88"/>
       <c r="E431" s="15"/>
       <c r="F431" s="15"/>
       <c r="G431" s="15"/>
     </row>
     <row r="432" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A432" s="86"/>
-      <c r="B432" s="86"/>
-      <c r="C432" s="86"/>
-      <c r="D432" s="86"/>
-      <c r="E432" s="86"/>
-      <c r="F432" s="86"/>
-      <c r="G432" s="86"/>
-      <c r="H432" s="86"/>
-      <c r="I432" s="86"/>
-      <c r="J432" s="86"/>
-      <c r="K432" s="86"/>
-      <c r="L432" s="86"/>
+      <c r="A432" s="79"/>
+      <c r="B432" s="79"/>
+      <c r="C432" s="79"/>
+      <c r="D432" s="79"/>
+      <c r="E432" s="79"/>
+      <c r="F432" s="79"/>
+      <c r="G432" s="79"/>
+      <c r="H432" s="79"/>
+      <c r="I432" s="79"/>
+      <c r="J432" s="79"/>
+      <c r="K432" s="79"/>
+      <c r="L432" s="79"/>
       <c r="M432" s="49"/>
     </row>
     <row r="433" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A433" s="86"/>
-      <c r="B433" s="86"/>
-      <c r="C433" s="86"/>
-      <c r="D433" s="86"/>
-      <c r="E433" s="86"/>
-      <c r="F433" s="86"/>
-      <c r="G433" s="86"/>
-      <c r="H433" s="86"/>
-      <c r="I433" s="86"/>
-      <c r="J433" s="86"/>
-      <c r="K433" s="86"/>
-      <c r="L433" s="86"/>
+      <c r="A433" s="79"/>
+      <c r="B433" s="79"/>
+      <c r="C433" s="79"/>
+      <c r="D433" s="79"/>
+      <c r="E433" s="79"/>
+      <c r="F433" s="79"/>
+      <c r="G433" s="79"/>
+      <c r="H433" s="79"/>
+      <c r="I433" s="79"/>
+      <c r="J433" s="79"/>
+      <c r="K433" s="79"/>
+      <c r="L433" s="79"/>
       <c r="M433" s="49"/>
     </row>
     <row r="434" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A434" s="86"/>
-      <c r="B434" s="86"/>
-      <c r="C434" s="86"/>
-      <c r="D434" s="86"/>
-      <c r="E434" s="86"/>
-      <c r="F434" s="86"/>
-      <c r="G434" s="86"/>
-      <c r="H434" s="86"/>
-      <c r="I434" s="86"/>
-      <c r="J434" s="86"/>
-      <c r="K434" s="86"/>
-      <c r="L434" s="86"/>
+      <c r="A434" s="79"/>
+      <c r="B434" s="79"/>
+      <c r="C434" s="79"/>
+      <c r="D434" s="79"/>
+      <c r="E434" s="79"/>
+      <c r="F434" s="79"/>
+      <c r="G434" s="79"/>
+      <c r="H434" s="79"/>
+      <c r="I434" s="79"/>
+      <c r="J434" s="79"/>
+      <c r="K434" s="79"/>
+      <c r="L434" s="79"/>
       <c r="M434" s="49"/>
     </row>
     <row r="435" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A435" s="86"/>
-      <c r="B435" s="86"/>
-      <c r="C435" s="86"/>
-      <c r="D435" s="86"/>
-      <c r="E435" s="86"/>
-      <c r="F435" s="86"/>
-      <c r="G435" s="86"/>
-      <c r="H435" s="86"/>
-      <c r="I435" s="86"/>
-      <c r="J435" s="86"/>
-      <c r="K435" s="86"/>
-      <c r="L435" s="86"/>
+      <c r="A435" s="79"/>
+      <c r="B435" s="79"/>
+      <c r="C435" s="79"/>
+      <c r="D435" s="79"/>
+      <c r="E435" s="79"/>
+      <c r="F435" s="79"/>
+      <c r="G435" s="79"/>
+      <c r="H435" s="79"/>
+      <c r="I435" s="79"/>
+      <c r="J435" s="79"/>
+      <c r="K435" s="79"/>
+      <c r="L435" s="79"/>
       <c r="M435" s="49"/>
     </row>
     <row r="436" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A436" s="86"/>
-      <c r="B436" s="86"/>
-      <c r="C436" s="86"/>
-      <c r="D436" s="86"/>
-      <c r="E436" s="86"/>
-      <c r="F436" s="86"/>
-      <c r="G436" s="86"/>
-      <c r="H436" s="86"/>
-      <c r="I436" s="86"/>
-      <c r="J436" s="86"/>
-      <c r="K436" s="86"/>
-      <c r="L436" s="86"/>
+      <c r="A436" s="79"/>
+      <c r="B436" s="79"/>
+      <c r="C436" s="79"/>
+      <c r="D436" s="79"/>
+      <c r="E436" s="79"/>
+      <c r="F436" s="79"/>
+      <c r="G436" s="79"/>
+      <c r="H436" s="79"/>
+      <c r="I436" s="79"/>
+      <c r="J436" s="79"/>
+      <c r="K436" s="79"/>
+      <c r="L436" s="79"/>
       <c r="M436" s="49"/>
     </row>
     <row r="437" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="96"/>
-      <c r="B437" s="97"/>
-      <c r="C437" s="92"/>
-      <c r="D437" s="91"/>
+      <c r="A437" s="80"/>
+      <c r="B437" s="81"/>
+      <c r="C437" s="82"/>
+      <c r="D437" s="78"/>
       <c r="E437" s="17"/>
       <c r="F437" s="17"/>
       <c r="G437" s="17"/>
     </row>
     <row r="438" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="96"/>
-      <c r="B438" s="97"/>
-      <c r="C438" s="92"/>
-      <c r="D438" s="91"/>
+      <c r="A438" s="80"/>
+      <c r="B438" s="81"/>
+      <c r="C438" s="82"/>
+      <c r="D438" s="78"/>
       <c r="E438" s="17"/>
       <c r="F438" s="17"/>
       <c r="G438" s="17"/>
     </row>
     <row r="439" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="96"/>
-      <c r="B439" s="97"/>
-      <c r="C439" s="92"/>
-      <c r="D439" s="91"/>
+      <c r="A439" s="80"/>
+      <c r="B439" s="81"/>
+      <c r="C439" s="82"/>
+      <c r="D439" s="78"/>
       <c r="E439" s="17"/>
       <c r="F439" s="17"/>
       <c r="G439" s="17"/>
     </row>
     <row r="440" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="96"/>
-      <c r="B440" s="97"/>
-      <c r="C440" s="92"/>
-      <c r="D440" s="91"/>
+      <c r="A440" s="80"/>
+      <c r="B440" s="81"/>
+      <c r="C440" s="82"/>
+      <c r="D440" s="78"/>
       <c r="E440" s="17"/>
       <c r="F440" s="17"/>
       <c r="G440" s="17"/>
     </row>
     <row r="441" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="96"/>
-      <c r="B441" s="97"/>
-      <c r="C441" s="92"/>
-      <c r="D441" s="91"/>
+      <c r="A441" s="80"/>
+      <c r="B441" s="81"/>
+      <c r="C441" s="82"/>
+      <c r="D441" s="78"/>
       <c r="E441" s="17"/>
       <c r="F441" s="17"/>
       <c r="G441" s="17"/>
     </row>
     <row r="442" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="96"/>
-      <c r="B442" s="97"/>
-      <c r="C442" s="92"/>
-      <c r="D442" s="91"/>
+      <c r="A442" s="80"/>
+      <c r="B442" s="81"/>
+      <c r="C442" s="82"/>
+      <c r="D442" s="78"/>
       <c r="E442" s="17"/>
       <c r="F442" s="17"/>
       <c r="G442" s="17"/>
     </row>
     <row r="443" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="96"/>
-      <c r="B443" s="97"/>
-      <c r="C443" s="92"/>
-      <c r="D443" s="91"/>
+      <c r="A443" s="80"/>
+      <c r="B443" s="81"/>
+      <c r="C443" s="82"/>
+      <c r="D443" s="78"/>
       <c r="E443" s="17"/>
       <c r="F443" s="17"/>
       <c r="G443" s="17"/>
     </row>
     <row r="444" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="96"/>
-      <c r="B444" s="97"/>
-      <c r="C444" s="92"/>
-      <c r="D444" s="91"/>
+      <c r="A444" s="80"/>
+      <c r="B444" s="81"/>
+      <c r="C444" s="82"/>
+      <c r="D444" s="78"/>
       <c r="E444" s="17"/>
       <c r="F444" s="17"/>
       <c r="G444" s="17"/>
     </row>
     <row r="445" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="96"/>
-      <c r="B445" s="97"/>
-      <c r="C445" s="92"/>
-      <c r="D445" s="91"/>
+      <c r="A445" s="80"/>
+      <c r="B445" s="81"/>
+      <c r="C445" s="82"/>
+      <c r="D445" s="78"/>
       <c r="E445" s="17"/>
       <c r="F445" s="17"/>
       <c r="G445" s="17"/>
     </row>
     <row r="446" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="96"/>
-      <c r="B446" s="97"/>
-      <c r="C446" s="92"/>
-      <c r="D446" s="91"/>
+      <c r="A446" s="80"/>
+      <c r="B446" s="81"/>
+      <c r="C446" s="82"/>
+      <c r="D446" s="78"/>
       <c r="E446" s="17"/>
       <c r="F446" s="17"/>
       <c r="G446" s="17"/>
     </row>
     <row r="447" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="96"/>
-      <c r="B447" s="97"/>
-      <c r="C447" s="92"/>
-      <c r="D447" s="91"/>
+      <c r="A447" s="80"/>
+      <c r="B447" s="81"/>
+      <c r="C447" s="82"/>
+      <c r="D447" s="78"/>
       <c r="E447" s="17"/>
       <c r="F447" s="17"/>
       <c r="G447" s="17"/>
     </row>
     <row r="448" spans="1:13" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="96"/>
-      <c r="B448" s="97"/>
-      <c r="C448" s="92"/>
-      <c r="D448" s="91"/>
+      <c r="A448" s="80"/>
+      <c r="B448" s="81"/>
+      <c r="C448" s="82"/>
+      <c r="D448" s="78"/>
       <c r="E448" s="17"/>
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
     </row>
     <row r="449" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="96"/>
-      <c r="B449" s="97"/>
-      <c r="C449" s="92"/>
-      <c r="D449" s="91"/>
+      <c r="A449" s="80"/>
+      <c r="B449" s="81"/>
+      <c r="C449" s="82"/>
+      <c r="D449" s="78"/>
       <c r="E449" s="17"/>
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
     </row>
     <row r="450" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="96"/>
-      <c r="B450" s="97"/>
-      <c r="C450" s="92"/>
-      <c r="D450" s="91"/>
+      <c r="A450" s="80"/>
+      <c r="B450" s="81"/>
+      <c r="C450" s="82"/>
+      <c r="D450" s="78"/>
       <c r="E450" s="17"/>
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
     </row>
     <row r="451" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="96"/>
-      <c r="B451" s="97"/>
-      <c r="C451" s="92"/>
-      <c r="D451" s="91"/>
+      <c r="A451" s="80"/>
+      <c r="B451" s="81"/>
+      <c r="C451" s="82"/>
+      <c r="D451" s="78"/>
       <c r="E451" s="17"/>
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
     </row>
     <row r="452" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="96"/>
-      <c r="B452" s="97"/>
-      <c r="C452" s="92"/>
-      <c r="D452" s="91"/>
+      <c r="A452" s="80"/>
+      <c r="B452" s="81"/>
+      <c r="C452" s="82"/>
+      <c r="D452" s="78"/>
       <c r="E452" s="17"/>
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
     </row>
     <row r="453" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="96"/>
-      <c r="B453" s="97"/>
-      <c r="C453" s="92"/>
-      <c r="D453" s="91"/>
+      <c r="A453" s="80"/>
+      <c r="B453" s="81"/>
+      <c r="C453" s="82"/>
+      <c r="D453" s="78"/>
       <c r="E453" s="17"/>
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
     </row>
     <row r="454" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="96"/>
-      <c r="B454" s="97"/>
-      <c r="C454" s="92"/>
-      <c r="D454" s="91"/>
+      <c r="A454" s="80"/>
+      <c r="B454" s="81"/>
+      <c r="C454" s="82"/>
+      <c r="D454" s="78"/>
       <c r="E454" s="17"/>
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
     </row>
     <row r="455" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="96"/>
-      <c r="B455" s="97"/>
-      <c r="C455" s="92"/>
-      <c r="D455" s="91"/>
+      <c r="A455" s="80"/>
+      <c r="B455" s="81"/>
+      <c r="C455" s="82"/>
+      <c r="D455" s="78"/>
       <c r="E455" s="17"/>
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
     </row>
     <row r="456" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="96"/>
-      <c r="B456" s="97"/>
-      <c r="C456" s="92"/>
-      <c r="D456" s="91"/>
+      <c r="A456" s="80"/>
+      <c r="B456" s="81"/>
+      <c r="C456" s="82"/>
+      <c r="D456" s="78"/>
       <c r="E456" s="17"/>
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
     </row>
     <row r="457" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="96"/>
-      <c r="B457" s="97"/>
-      <c r="C457" s="92"/>
-      <c r="D457" s="91"/>
+      <c r="A457" s="80"/>
+      <c r="B457" s="81"/>
+      <c r="C457" s="82"/>
+      <c r="D457" s="78"/>
       <c r="E457" s="17"/>
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
     </row>
     <row r="458" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="96"/>
-      <c r="B458" s="97"/>
-      <c r="C458" s="92"/>
-      <c r="D458" s="91"/>
+      <c r="A458" s="80"/>
+      <c r="B458" s="81"/>
+      <c r="C458" s="82"/>
+      <c r="D458" s="78"/>
       <c r="E458" s="17"/>
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
     </row>
     <row r="459" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="96"/>
-      <c r="B459" s="97"/>
-      <c r="C459" s="92"/>
-      <c r="D459" s="91"/>
+      <c r="A459" s="80"/>
+      <c r="B459" s="81"/>
+      <c r="C459" s="82"/>
+      <c r="D459" s="78"/>
       <c r="E459" s="17"/>
       <c r="F459" s="17"/>
       <c r="G459" s="17"/>
     </row>
     <row r="460" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="96"/>
-      <c r="B460" s="97"/>
-      <c r="C460" s="92"/>
-      <c r="D460" s="91"/>
+      <c r="A460" s="80"/>
+      <c r="B460" s="81"/>
+      <c r="C460" s="82"/>
+      <c r="D460" s="78"/>
       <c r="E460" s="17"/>
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
     </row>
     <row r="461" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="96"/>
-      <c r="B461" s="97"/>
-      <c r="C461" s="92"/>
-      <c r="D461" s="91"/>
+      <c r="A461" s="80"/>
+      <c r="B461" s="81"/>
+      <c r="C461" s="82"/>
+      <c r="D461" s="78"/>
       <c r="E461" s="17"/>
       <c r="F461" s="17"/>
       <c r="G461" s="17"/>
     </row>
     <row r="462" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="96"/>
-      <c r="B462" s="97"/>
-      <c r="C462" s="92"/>
-      <c r="D462" s="91"/>
+      <c r="A462" s="80"/>
+      <c r="B462" s="81"/>
+      <c r="C462" s="82"/>
+      <c r="D462" s="78"/>
       <c r="E462" s="17"/>
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
     </row>
     <row r="463" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="96"/>
-      <c r="B463" s="97"/>
-      <c r="C463" s="92"/>
-      <c r="D463" s="91"/>
+      <c r="A463" s="80"/>
+      <c r="B463" s="81"/>
+      <c r="C463" s="82"/>
+      <c r="D463" s="78"/>
       <c r="E463" s="17"/>
       <c r="F463" s="17"/>
       <c r="G463" s="17"/>
     </row>
     <row r="464" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="96"/>
-      <c r="B464" s="97"/>
-      <c r="C464" s="92"/>
-      <c r="D464" s="91"/>
+      <c r="A464" s="80"/>
+      <c r="B464" s="81"/>
+      <c r="C464" s="82"/>
+      <c r="D464" s="78"/>
       <c r="E464" s="17"/>
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
     </row>
     <row r="465" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="96"/>
-      <c r="B465" s="97"/>
-      <c r="C465" s="92"/>
-      <c r="D465" s="91"/>
+      <c r="A465" s="80"/>
+      <c r="B465" s="81"/>
+      <c r="C465" s="82"/>
+      <c r="D465" s="78"/>
       <c r="E465" s="17"/>
       <c r="F465" s="17"/>
       <c r="G465" s="17"/>
     </row>
     <row r="466" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="96"/>
-      <c r="B466" s="97"/>
-      <c r="C466" s="92"/>
-      <c r="D466" s="91"/>
+      <c r="A466" s="80"/>
+      <c r="B466" s="81"/>
+      <c r="C466" s="82"/>
+      <c r="D466" s="78"/>
       <c r="E466" s="17"/>
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
     </row>
     <row r="467" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="96"/>
-      <c r="B467" s="97"/>
-      <c r="C467" s="92"/>
-      <c r="D467" s="91"/>
+      <c r="A467" s="80"/>
+      <c r="B467" s="81"/>
+      <c r="C467" s="82"/>
+      <c r="D467" s="78"/>
       <c r="E467" s="17"/>
       <c r="F467" s="17"/>
       <c r="G467" s="17"/>
     </row>
     <row r="468" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="96"/>
-      <c r="B468" s="97"/>
-      <c r="C468" s="92"/>
-      <c r="D468" s="91"/>
+      <c r="A468" s="80"/>
+      <c r="B468" s="81"/>
+      <c r="C468" s="82"/>
+      <c r="D468" s="78"/>
       <c r="E468" s="17"/>
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
     </row>
     <row r="469" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="96"/>
-      <c r="B469" s="97"/>
-      <c r="C469" s="92"/>
-      <c r="D469" s="91"/>
+      <c r="A469" s="80"/>
+      <c r="B469" s="81"/>
+      <c r="C469" s="82"/>
+      <c r="D469" s="78"/>
       <c r="E469" s="17"/>
       <c r="F469" s="17"/>
       <c r="G469" s="17"/>
     </row>
     <row r="470" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="96"/>
-      <c r="B470" s="97"/>
-      <c r="C470" s="92"/>
-      <c r="D470" s="91"/>
+      <c r="A470" s="80"/>
+      <c r="B470" s="81"/>
+      <c r="C470" s="82"/>
+      <c r="D470" s="78"/>
       <c r="E470" s="17"/>
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
     </row>
     <row r="471" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="96"/>
-      <c r="B471" s="97"/>
-      <c r="C471" s="92"/>
-      <c r="D471" s="91"/>
+      <c r="A471" s="80"/>
+      <c r="B471" s="81"/>
+      <c r="C471" s="82"/>
+      <c r="D471" s="78"/>
       <c r="E471" s="17"/>
       <c r="F471" s="17"/>
       <c r="G471" s="17"/>
     </row>
     <row r="472" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="96"/>
-      <c r="B472" s="97"/>
-      <c r="C472" s="92"/>
-      <c r="D472" s="91"/>
+      <c r="A472" s="80"/>
+      <c r="B472" s="81"/>
+      <c r="C472" s="82"/>
+      <c r="D472" s="78"/>
       <c r="E472" s="17"/>
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
     </row>
     <row r="473" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="96"/>
-      <c r="B473" s="97"/>
-      <c r="C473" s="92"/>
-      <c r="D473" s="91"/>
+      <c r="A473" s="80"/>
+      <c r="B473" s="81"/>
+      <c r="C473" s="82"/>
+      <c r="D473" s="78"/>
       <c r="E473" s="17"/>
       <c r="F473" s="17"/>
       <c r="G473" s="17"/>
     </row>
     <row r="474" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="96"/>
-      <c r="B474" s="97"/>
-      <c r="C474" s="92"/>
-      <c r="D474" s="91"/>
+      <c r="A474" s="80"/>
+      <c r="B474" s="81"/>
+      <c r="C474" s="82"/>
+      <c r="D474" s="78"/>
       <c r="E474" s="17"/>
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
     </row>
     <row r="475" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="96"/>
-      <c r="B475" s="97"/>
-      <c r="C475" s="92"/>
-      <c r="D475" s="91"/>
+      <c r="A475" s="80"/>
+      <c r="B475" s="81"/>
+      <c r="C475" s="82"/>
+      <c r="D475" s="78"/>
       <c r="E475" s="17"/>
       <c r="F475" s="17"/>
       <c r="G475" s="17"/>
     </row>
     <row r="476" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="96"/>
-      <c r="B476" s="97"/>
-      <c r="C476" s="92"/>
-      <c r="D476" s="91"/>
+      <c r="A476" s="80"/>
+      <c r="B476" s="81"/>
+      <c r="C476" s="82"/>
+      <c r="D476" s="78"/>
       <c r="E476" s="17"/>
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
     </row>
     <row r="477" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="96"/>
-      <c r="B477" s="97"/>
-      <c r="C477" s="92"/>
-      <c r="D477" s="91"/>
+      <c r="A477" s="80"/>
+      <c r="B477" s="81"/>
+      <c r="C477" s="82"/>
+      <c r="D477" s="78"/>
       <c r="E477" s="17"/>
       <c r="F477" s="17"/>
       <c r="G477" s="17"/>
     </row>
     <row r="478" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A478" s="96"/>
-      <c r="B478" s="97"/>
-      <c r="C478" s="92"/>
-      <c r="D478" s="91"/>
+      <c r="A478" s="80"/>
+      <c r="B478" s="81"/>
+      <c r="C478" s="82"/>
+      <c r="D478" s="78"/>
       <c r="E478" s="17"/>
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
     </row>
     <row r="479" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A479" s="96"/>
-      <c r="B479" s="97"/>
-      <c r="C479" s="92"/>
-      <c r="D479" s="91"/>
+      <c r="A479" s="80"/>
+      <c r="B479" s="81"/>
+      <c r="C479" s="82"/>
+      <c r="D479" s="78"/>
       <c r="E479" s="17"/>
       <c r="F479" s="17"/>
       <c r="G479" s="17"/>
     </row>
     <row r="480" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A480" s="96"/>
-      <c r="B480" s="97"/>
-      <c r="C480" s="92"/>
-      <c r="D480" s="91"/>
+      <c r="A480" s="80"/>
+      <c r="B480" s="81"/>
+      <c r="C480" s="82"/>
+      <c r="D480" s="78"/>
       <c r="E480" s="17"/>
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
     </row>
     <row r="481" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="96"/>
-      <c r="B481" s="97"/>
-      <c r="C481" s="92"/>
-      <c r="D481" s="91"/>
+      <c r="A481" s="80"/>
+      <c r="B481" s="81"/>
+      <c r="C481" s="82"/>
+      <c r="D481" s="78"/>
       <c r="E481" s="17"/>
       <c r="F481" s="17"/>
       <c r="G481" s="17"/>
     </row>
     <row r="482" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="96"/>
-      <c r="B482" s="97"/>
-      <c r="C482" s="92"/>
-      <c r="D482" s="91"/>
+      <c r="A482" s="80"/>
+      <c r="B482" s="81"/>
+      <c r="C482" s="82"/>
+      <c r="D482" s="78"/>
       <c r="E482" s="17"/>
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
     </row>
     <row r="483" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A483" s="96"/>
-      <c r="B483" s="97"/>
-      <c r="C483" s="92"/>
-      <c r="D483" s="91"/>
+      <c r="A483" s="80"/>
+      <c r="B483" s="81"/>
+      <c r="C483" s="82"/>
+      <c r="D483" s="78"/>
       <c r="E483" s="17"/>
       <c r="F483" s="17"/>
       <c r="G483" s="17"/>
     </row>
     <row r="484" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="96"/>
-      <c r="B484" s="97"/>
-      <c r="C484" s="92"/>
-      <c r="D484" s="91"/>
+      <c r="A484" s="80"/>
+      <c r="B484" s="81"/>
+      <c r="C484" s="82"/>
+      <c r="D484" s="78"/>
       <c r="E484" s="17"/>
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
     </row>
     <row r="485" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="96"/>
-      <c r="B485" s="97"/>
-      <c r="C485" s="92"/>
-      <c r="D485" s="91"/>
+      <c r="A485" s="80"/>
+      <c r="B485" s="81"/>
+      <c r="C485" s="82"/>
+      <c r="D485" s="78"/>
       <c r="E485" s="17"/>
       <c r="F485" s="17"/>
       <c r="G485" s="17"/>
     </row>
     <row r="486" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="96"/>
-      <c r="B486" s="97"/>
-      <c r="C486" s="92"/>
-      <c r="D486" s="91"/>
+      <c r="A486" s="80"/>
+      <c r="B486" s="81"/>
+      <c r="C486" s="82"/>
+      <c r="D486" s="78"/>
       <c r="E486" s="17"/>
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
     </row>
     <row r="487" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="96"/>
-      <c r="B487" s="97"/>
-      <c r="C487" s="92"/>
-      <c r="D487" s="91"/>
+      <c r="A487" s="80"/>
+      <c r="B487" s="81"/>
+      <c r="C487" s="82"/>
+      <c r="D487" s="78"/>
       <c r="E487" s="17"/>
       <c r="F487" s="17"/>
       <c r="G487" s="17"/>
     </row>
     <row r="488" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="96"/>
-      <c r="B488" s="97"/>
-      <c r="C488" s="92"/>
-      <c r="D488" s="91"/>
+      <c r="A488" s="80"/>
+      <c r="B488" s="81"/>
+      <c r="C488" s="82"/>
+      <c r="D488" s="78"/>
       <c r="E488" s="17"/>
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
     </row>
     <row r="489" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A489" s="96"/>
-      <c r="B489" s="97"/>
-      <c r="C489" s="92"/>
-      <c r="D489" s="91"/>
+      <c r="A489" s="80"/>
+      <c r="B489" s="81"/>
+      <c r="C489" s="82"/>
+      <c r="D489" s="78"/>
       <c r="E489" s="17"/>
       <c r="F489" s="17"/>
       <c r="G489" s="17"/>
     </row>
     <row r="490" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="96"/>
-      <c r="B490" s="97"/>
-      <c r="C490" s="92"/>
-      <c r="D490" s="91"/>
+      <c r="A490" s="80"/>
+      <c r="B490" s="81"/>
+      <c r="C490" s="82"/>
+      <c r="D490" s="78"/>
       <c r="E490" s="17"/>
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
     </row>
     <row r="491" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="96"/>
-      <c r="B491" s="97"/>
-      <c r="C491" s="92"/>
-      <c r="D491" s="91"/>
+      <c r="A491" s="80"/>
+      <c r="B491" s="81"/>
+      <c r="C491" s="82"/>
+      <c r="D491" s="78"/>
       <c r="E491" s="17"/>
       <c r="F491" s="17"/>
       <c r="G491" s="17"/>
     </row>
     <row r="492" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="96"/>
-      <c r="B492" s="97"/>
-      <c r="C492" s="92"/>
-      <c r="D492" s="91"/>
+      <c r="A492" s="80"/>
+      <c r="B492" s="81"/>
+      <c r="C492" s="82"/>
+      <c r="D492" s="78"/>
       <c r="E492" s="17"/>
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
     </row>
     <row r="493" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="96"/>
-      <c r="B493" s="97"/>
-      <c r="C493" s="92"/>
-      <c r="D493" s="91"/>
+      <c r="A493" s="80"/>
+      <c r="B493" s="81"/>
+      <c r="C493" s="82"/>
+      <c r="D493" s="78"/>
       <c r="E493" s="17"/>
       <c r="F493" s="17"/>
       <c r="G493" s="17"/>
     </row>
     <row r="494" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="96"/>
-      <c r="B494" s="97"/>
-      <c r="C494" s="92"/>
-      <c r="D494" s="91"/>
+      <c r="A494" s="80"/>
+      <c r="B494" s="81"/>
+      <c r="C494" s="82"/>
+      <c r="D494" s="78"/>
       <c r="E494" s="17"/>
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
     </row>
     <row r="495" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="96"/>
-      <c r="B495" s="97"/>
-      <c r="C495" s="92"/>
-      <c r="D495" s="91"/>
+      <c r="A495" s="80"/>
+      <c r="B495" s="81"/>
+      <c r="C495" s="82"/>
+      <c r="D495" s="78"/>
       <c r="E495" s="17"/>
       <c r="F495" s="17"/>
       <c r="G495" s="17"/>
     </row>
     <row r="496" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="96"/>
-      <c r="B496" s="97"/>
-      <c r="C496" s="92"/>
-      <c r="D496" s="91"/>
+      <c r="A496" s="80"/>
+      <c r="B496" s="81"/>
+      <c r="C496" s="82"/>
+      <c r="D496" s="78"/>
       <c r="E496" s="17"/>
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
     </row>
     <row r="497" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="96"/>
-      <c r="B497" s="97"/>
-      <c r="C497" s="92"/>
-      <c r="D497" s="91"/>
+      <c r="A497" s="80"/>
+      <c r="B497" s="81"/>
+      <c r="C497" s="82"/>
+      <c r="D497" s="78"/>
       <c r="E497" s="17"/>
       <c r="F497" s="17"/>
       <c r="G497" s="17"/>
     </row>
     <row r="498" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A498" s="96"/>
-      <c r="B498" s="97"/>
-      <c r="C498" s="92"/>
-      <c r="D498" s="91"/>
+      <c r="A498" s="80"/>
+      <c r="B498" s="81"/>
+      <c r="C498" s="82"/>
+      <c r="D498" s="78"/>
       <c r="E498" s="17"/>
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
     </row>
     <row r="499" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="96"/>
-      <c r="B499" s="97"/>
-      <c r="C499" s="92"/>
-      <c r="D499" s="91"/>
+      <c r="A499" s="80"/>
+      <c r="B499" s="81"/>
+      <c r="C499" s="82"/>
+      <c r="D499" s="78"/>
       <c r="E499" s="17"/>
       <c r="F499" s="17"/>
       <c r="G499" s="17"/>
     </row>
     <row r="500" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="96"/>
-      <c r="B500" s="97"/>
-      <c r="C500" s="92"/>
-      <c r="D500" s="91"/>
+      <c r="A500" s="80"/>
+      <c r="B500" s="81"/>
+      <c r="C500" s="82"/>
+      <c r="D500" s="78"/>
       <c r="E500" s="17"/>
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
     </row>
     <row r="501" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="96"/>
-      <c r="B501" s="97"/>
-      <c r="C501" s="92"/>
-      <c r="D501" s="91"/>
+      <c r="A501" s="80"/>
+      <c r="B501" s="81"/>
+      <c r="C501" s="82"/>
+      <c r="D501" s="78"/>
       <c r="E501" s="17"/>
       <c r="F501" s="17"/>
       <c r="G501" s="17"/>
     </row>
     <row r="502" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="96"/>
-      <c r="B502" s="97"/>
-      <c r="C502" s="92"/>
-      <c r="D502" s="91"/>
+      <c r="A502" s="80"/>
+      <c r="B502" s="81"/>
+      <c r="C502" s="82"/>
+      <c r="D502" s="78"/>
       <c r="E502" s="17"/>
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
     </row>
     <row r="503" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="96"/>
-      <c r="B503" s="97"/>
-      <c r="C503" s="92"/>
-      <c r="D503" s="91"/>
+      <c r="A503" s="80"/>
+      <c r="B503" s="81"/>
+      <c r="C503" s="82"/>
+      <c r="D503" s="78"/>
       <c r="E503" s="17"/>
       <c r="F503" s="17"/>
       <c r="G503" s="17"/>
     </row>
     <row r="504" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="96"/>
-      <c r="B504" s="97"/>
-      <c r="C504" s="92"/>
-      <c r="D504" s="91"/>
+      <c r="A504" s="80"/>
+      <c r="B504" s="81"/>
+      <c r="C504" s="82"/>
+      <c r="D504" s="78"/>
       <c r="E504" s="17"/>
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
     </row>
     <row r="505" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A505" s="96"/>
-      <c r="B505" s="97"/>
-      <c r="C505" s="92"/>
-      <c r="D505" s="91"/>
+      <c r="A505" s="80"/>
+      <c r="B505" s="81"/>
+      <c r="C505" s="82"/>
+      <c r="D505" s="78"/>
       <c r="E505" s="17"/>
       <c r="F505" s="17"/>
       <c r="G505" s="17"/>
     </row>
     <row r="506" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A506" s="96"/>
-      <c r="B506" s="97"/>
-      <c r="C506" s="92"/>
-      <c r="D506" s="91"/>
+      <c r="A506" s="80"/>
+      <c r="B506" s="81"/>
+      <c r="C506" s="82"/>
+      <c r="D506" s="78"/>
       <c r="E506" s="17"/>
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
     </row>
     <row r="507" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A507" s="96"/>
-      <c r="B507" s="97"/>
-      <c r="C507" s="92"/>
-      <c r="D507" s="91"/>
+      <c r="A507" s="80"/>
+      <c r="B507" s="81"/>
+      <c r="C507" s="82"/>
+      <c r="D507" s="78"/>
       <c r="E507" s="17"/>
       <c r="F507" s="17"/>
       <c r="G507" s="17"/>
     </row>
     <row r="508" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A508" s="96"/>
-      <c r="B508" s="97"/>
-      <c r="C508" s="92"/>
-      <c r="D508" s="91"/>
+      <c r="A508" s="80"/>
+      <c r="B508" s="81"/>
+      <c r="C508" s="82"/>
+      <c r="D508" s="78"/>
       <c r="E508" s="17"/>
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
     </row>
     <row r="509" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A509" s="96"/>
-      <c r="B509" s="97"/>
-      <c r="C509" s="92"/>
-      <c r="D509" s="91"/>
+      <c r="A509" s="80"/>
+      <c r="B509" s="81"/>
+      <c r="C509" s="82"/>
+      <c r="D509" s="78"/>
       <c r="E509" s="17"/>
       <c r="F509" s="17"/>
       <c r="G509" s="17"/>
     </row>
     <row r="510" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A510" s="96"/>
-      <c r="B510" s="97"/>
+      <c r="A510" s="80"/>
+      <c r="B510" s="81"/>
       <c r="C510" s="57"/>
       <c r="D510" s="58"/>
       <c r="E510" s="17"/>
@@ -15653,154 +15591,154 @@
       <c r="G510" s="17"/>
     </row>
     <row r="511" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A511" s="96"/>
-      <c r="B511" s="97"/>
-      <c r="C511" s="92"/>
-      <c r="D511" s="91"/>
+      <c r="A511" s="80"/>
+      <c r="B511" s="81"/>
+      <c r="C511" s="82"/>
+      <c r="D511" s="78"/>
       <c r="E511" s="17"/>
       <c r="F511" s="17"/>
       <c r="G511" s="17"/>
     </row>
     <row r="512" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A512" s="96"/>
-      <c r="B512" s="97"/>
-      <c r="C512" s="92"/>
-      <c r="D512" s="91"/>
+      <c r="A512" s="80"/>
+      <c r="B512" s="81"/>
+      <c r="C512" s="82"/>
+      <c r="D512" s="78"/>
       <c r="E512" s="17"/>
       <c r="F512" s="17"/>
       <c r="G512" s="17"/>
     </row>
     <row r="513" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A513" s="96"/>
-      <c r="B513" s="97"/>
-      <c r="C513" s="92"/>
-      <c r="D513" s="91"/>
+      <c r="A513" s="80"/>
+      <c r="B513" s="81"/>
+      <c r="C513" s="82"/>
+      <c r="D513" s="78"/>
       <c r="E513" s="17"/>
       <c r="F513" s="17"/>
       <c r="G513" s="17"/>
     </row>
     <row r="514" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A514" s="96"/>
-      <c r="B514" s="97"/>
-      <c r="C514" s="92"/>
-      <c r="D514" s="91"/>
+      <c r="A514" s="80"/>
+      <c r="B514" s="81"/>
+      <c r="C514" s="82"/>
+      <c r="D514" s="78"/>
       <c r="E514" s="17"/>
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
     </row>
     <row r="515" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A515" s="96"/>
-      <c r="B515" s="97"/>
-      <c r="C515" s="92"/>
-      <c r="D515" s="91"/>
+      <c r="A515" s="80"/>
+      <c r="B515" s="81"/>
+      <c r="C515" s="82"/>
+      <c r="D515" s="78"/>
       <c r="E515" s="17"/>
       <c r="F515" s="17"/>
       <c r="G515" s="17"/>
     </row>
     <row r="516" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A516" s="96"/>
-      <c r="B516" s="97"/>
-      <c r="C516" s="92"/>
-      <c r="D516" s="91"/>
+      <c r="A516" s="80"/>
+      <c r="B516" s="81"/>
+      <c r="C516" s="82"/>
+      <c r="D516" s="78"/>
       <c r="E516" s="17"/>
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
     </row>
     <row r="517" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A517" s="96"/>
-      <c r="B517" s="97"/>
-      <c r="C517" s="92"/>
-      <c r="D517" s="91"/>
+      <c r="A517" s="80"/>
+      <c r="B517" s="81"/>
+      <c r="C517" s="82"/>
+      <c r="D517" s="78"/>
       <c r="E517" s="17"/>
       <c r="F517" s="17"/>
       <c r="G517" s="17"/>
     </row>
     <row r="518" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A518" s="96"/>
-      <c r="B518" s="97"/>
-      <c r="C518" s="92"/>
-      <c r="D518" s="91"/>
+      <c r="A518" s="80"/>
+      <c r="B518" s="81"/>
+      <c r="C518" s="82"/>
+      <c r="D518" s="78"/>
       <c r="E518" s="17"/>
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
     </row>
     <row r="519" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A519" s="96"/>
-      <c r="B519" s="97"/>
-      <c r="C519" s="95"/>
-      <c r="D519" s="91"/>
+      <c r="A519" s="80"/>
+      <c r="B519" s="81"/>
+      <c r="C519" s="77"/>
+      <c r="D519" s="78"/>
       <c r="E519" s="17"/>
       <c r="F519" s="17"/>
       <c r="G519" s="17"/>
     </row>
     <row r="520" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="96"/>
-      <c r="B520" s="97"/>
-      <c r="C520" s="95"/>
-      <c r="D520" s="91"/>
+      <c r="A520" s="80"/>
+      <c r="B520" s="81"/>
+      <c r="C520" s="77"/>
+      <c r="D520" s="78"/>
       <c r="E520" s="17"/>
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
     </row>
     <row r="521" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="96"/>
-      <c r="B521" s="97"/>
-      <c r="C521" s="95"/>
-      <c r="D521" s="91"/>
+      <c r="A521" s="80"/>
+      <c r="B521" s="81"/>
+      <c r="C521" s="77"/>
+      <c r="D521" s="78"/>
       <c r="E521" s="17"/>
       <c r="F521" s="17"/>
       <c r="G521" s="17"/>
     </row>
     <row r="522" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="96"/>
-      <c r="B522" s="97"/>
-      <c r="C522" s="95"/>
-      <c r="D522" s="91"/>
+      <c r="A522" s="80"/>
+      <c r="B522" s="81"/>
+      <c r="C522" s="77"/>
+      <c r="D522" s="78"/>
       <c r="E522" s="17"/>
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
     </row>
     <row r="523" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="96"/>
-      <c r="B523" s="97"/>
-      <c r="C523" s="95"/>
-      <c r="D523" s="91"/>
+      <c r="A523" s="80"/>
+      <c r="B523" s="81"/>
+      <c r="C523" s="77"/>
+      <c r="D523" s="78"/>
       <c r="E523" s="17"/>
       <c r="F523" s="17"/>
       <c r="G523" s="17"/>
     </row>
     <row r="524" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="96"/>
-      <c r="B524" s="97"/>
-      <c r="C524" s="95"/>
-      <c r="D524" s="91"/>
+      <c r="A524" s="80"/>
+      <c r="B524" s="81"/>
+      <c r="C524" s="77"/>
+      <c r="D524" s="78"/>
       <c r="E524" s="17"/>
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
     </row>
     <row r="525" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="96"/>
-      <c r="B525" s="97"/>
-      <c r="C525" s="95"/>
-      <c r="D525" s="91"/>
+      <c r="A525" s="80"/>
+      <c r="B525" s="81"/>
+      <c r="C525" s="77"/>
+      <c r="D525" s="78"/>
       <c r="E525" s="17"/>
       <c r="F525" s="17"/>
       <c r="G525" s="17"/>
     </row>
     <row r="526" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="96"/>
-      <c r="B526" s="97"/>
-      <c r="C526" s="95"/>
-      <c r="D526" s="91"/>
+      <c r="A526" s="80"/>
+      <c r="B526" s="81"/>
+      <c r="C526" s="77"/>
+      <c r="D526" s="78"/>
       <c r="E526" s="17"/>
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
     </row>
     <row r="527" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="96"/>
-      <c r="B527" s="97"/>
-      <c r="C527" s="95"/>
-      <c r="D527" s="91"/>
+      <c r="A527" s="80"/>
+      <c r="B527" s="81"/>
+      <c r="C527" s="77"/>
+      <c r="D527" s="78"/>
       <c r="E527" s="17"/>
       <c r="F527" s="17"/>
       <c r="G527" s="17"/>
@@ -15813,6 +15751,151 @@
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B16"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A22:A40"/>
+    <mergeCell ref="B22:B40"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="A96:A239"/>
+    <mergeCell ref="B96:B239"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="C119:C122"/>
+    <mergeCell ref="D119:D122"/>
+    <mergeCell ref="C123:C128"/>
+    <mergeCell ref="D123:D128"/>
+    <mergeCell ref="C129:C135"/>
+    <mergeCell ref="D129:D135"/>
+    <mergeCell ref="C136:C143"/>
+    <mergeCell ref="D136:D143"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C150:C155"/>
+    <mergeCell ref="D150:D155"/>
+    <mergeCell ref="C156:C162"/>
+    <mergeCell ref="D156:D162"/>
+    <mergeCell ref="C163:C168"/>
+    <mergeCell ref="D163:D168"/>
+    <mergeCell ref="C169:C174"/>
+    <mergeCell ref="D169:D174"/>
+    <mergeCell ref="C175:C180"/>
+    <mergeCell ref="D175:D180"/>
+    <mergeCell ref="C181:C187"/>
+    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="C188:C199"/>
+    <mergeCell ref="D188:D199"/>
+    <mergeCell ref="C200:C211"/>
+    <mergeCell ref="D200:D211"/>
+    <mergeCell ref="C212:C218"/>
+    <mergeCell ref="D212:D218"/>
+    <mergeCell ref="C219:C226"/>
+    <mergeCell ref="D219:D226"/>
+    <mergeCell ref="C227:C231"/>
+    <mergeCell ref="D227:D231"/>
+    <mergeCell ref="C232:C235"/>
+    <mergeCell ref="D232:D235"/>
+    <mergeCell ref="C236:C239"/>
+    <mergeCell ref="D236:D239"/>
+    <mergeCell ref="A241:A300"/>
+    <mergeCell ref="B241:B300"/>
+    <mergeCell ref="C241:C248"/>
+    <mergeCell ref="D241:D248"/>
+    <mergeCell ref="C249:C255"/>
+    <mergeCell ref="D249:D255"/>
+    <mergeCell ref="C256:C260"/>
+    <mergeCell ref="D256:D260"/>
+    <mergeCell ref="C261:C266"/>
+    <mergeCell ref="D261:D266"/>
+    <mergeCell ref="C267:C275"/>
+    <mergeCell ref="D267:D275"/>
+    <mergeCell ref="C276:C281"/>
+    <mergeCell ref="D276:D281"/>
+    <mergeCell ref="C282:C288"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="C289:C295"/>
+    <mergeCell ref="D289:D295"/>
+    <mergeCell ref="C296:C300"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="A302:A331"/>
+    <mergeCell ref="B302:B331"/>
+    <mergeCell ref="C302:C307"/>
+    <mergeCell ref="D302:D307"/>
+    <mergeCell ref="C308:C315"/>
+    <mergeCell ref="D308:D315"/>
+    <mergeCell ref="C316:C319"/>
+    <mergeCell ref="D316:D319"/>
+    <mergeCell ref="C320:C327"/>
+    <mergeCell ref="D320:D327"/>
+    <mergeCell ref="C328:C331"/>
+    <mergeCell ref="D328:D331"/>
+    <mergeCell ref="A332:L336"/>
+    <mergeCell ref="A337:A377"/>
+    <mergeCell ref="B337:B377"/>
+    <mergeCell ref="C337:C341"/>
+    <mergeCell ref="D337:D341"/>
+    <mergeCell ref="C342:C343"/>
+    <mergeCell ref="D342:D343"/>
+    <mergeCell ref="C344:C345"/>
+    <mergeCell ref="D344:D345"/>
+    <mergeCell ref="C346:C348"/>
+    <mergeCell ref="D346:D348"/>
+    <mergeCell ref="C349:C353"/>
+    <mergeCell ref="D349:D353"/>
+    <mergeCell ref="C354:C358"/>
+    <mergeCell ref="D354:D358"/>
+    <mergeCell ref="C359:C360"/>
+    <mergeCell ref="D359:D360"/>
+    <mergeCell ref="C361:C362"/>
+    <mergeCell ref="D361:D362"/>
+    <mergeCell ref="C363:C364"/>
+    <mergeCell ref="D363:D364"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="D367:D368"/>
+    <mergeCell ref="C369:C372"/>
+    <mergeCell ref="D507:D509"/>
+    <mergeCell ref="C511:C518"/>
+    <mergeCell ref="D369:D372"/>
+    <mergeCell ref="C373:C375"/>
+    <mergeCell ref="D373:D375"/>
+    <mergeCell ref="C376:C377"/>
+    <mergeCell ref="D376:D377"/>
+    <mergeCell ref="A378:L382"/>
+    <mergeCell ref="A383:A431"/>
+    <mergeCell ref="B383:B431"/>
+    <mergeCell ref="C383:C392"/>
+    <mergeCell ref="D383:D392"/>
+    <mergeCell ref="C393:C399"/>
+    <mergeCell ref="D393:D399"/>
+    <mergeCell ref="C400:C410"/>
+    <mergeCell ref="D400:D410"/>
+    <mergeCell ref="C411:C415"/>
+    <mergeCell ref="D411:D415"/>
+    <mergeCell ref="C416:C425"/>
+    <mergeCell ref="D416:D425"/>
+    <mergeCell ref="C426:C431"/>
+    <mergeCell ref="D426:D431"/>
+    <mergeCell ref="D511:D518"/>
     <mergeCell ref="C519:C527"/>
     <mergeCell ref="D519:D527"/>
     <mergeCell ref="A432:L436"/>
@@ -15837,151 +15920,6 @@
     <mergeCell ref="C502:C506"/>
     <mergeCell ref="D502:D506"/>
     <mergeCell ref="C507:C509"/>
-    <mergeCell ref="D507:D509"/>
-    <mergeCell ref="C511:C518"/>
-    <mergeCell ref="D369:D372"/>
-    <mergeCell ref="C373:C375"/>
-    <mergeCell ref="D373:D375"/>
-    <mergeCell ref="C376:C377"/>
-    <mergeCell ref="D376:D377"/>
-    <mergeCell ref="A378:L382"/>
-    <mergeCell ref="A383:A431"/>
-    <mergeCell ref="B383:B431"/>
-    <mergeCell ref="C383:C392"/>
-    <mergeCell ref="D383:D392"/>
-    <mergeCell ref="C393:C399"/>
-    <mergeCell ref="D393:D399"/>
-    <mergeCell ref="C400:C410"/>
-    <mergeCell ref="D400:D410"/>
-    <mergeCell ref="C411:C415"/>
-    <mergeCell ref="D411:D415"/>
-    <mergeCell ref="C416:C425"/>
-    <mergeCell ref="D416:D425"/>
-    <mergeCell ref="C426:C431"/>
-    <mergeCell ref="D426:D431"/>
-    <mergeCell ref="D511:D518"/>
-    <mergeCell ref="A332:L336"/>
-    <mergeCell ref="A337:A377"/>
-    <mergeCell ref="B337:B377"/>
-    <mergeCell ref="C337:C341"/>
-    <mergeCell ref="D337:D341"/>
-    <mergeCell ref="C342:C343"/>
-    <mergeCell ref="D342:D343"/>
-    <mergeCell ref="C344:C345"/>
-    <mergeCell ref="D344:D345"/>
-    <mergeCell ref="C346:C348"/>
-    <mergeCell ref="D346:D348"/>
-    <mergeCell ref="C349:C353"/>
-    <mergeCell ref="D349:D353"/>
-    <mergeCell ref="C354:C358"/>
-    <mergeCell ref="D354:D358"/>
-    <mergeCell ref="C359:C360"/>
-    <mergeCell ref="D359:D360"/>
-    <mergeCell ref="C361:C362"/>
-    <mergeCell ref="D361:D362"/>
-    <mergeCell ref="C363:C364"/>
-    <mergeCell ref="D363:D364"/>
-    <mergeCell ref="C367:C368"/>
-    <mergeCell ref="D367:D368"/>
-    <mergeCell ref="C369:C372"/>
-    <mergeCell ref="A302:A331"/>
-    <mergeCell ref="B302:B331"/>
-    <mergeCell ref="C302:C307"/>
-    <mergeCell ref="D302:D307"/>
-    <mergeCell ref="C308:C315"/>
-    <mergeCell ref="D308:D315"/>
-    <mergeCell ref="C316:C319"/>
-    <mergeCell ref="D316:D319"/>
-    <mergeCell ref="C320:C327"/>
-    <mergeCell ref="D320:D327"/>
-    <mergeCell ref="C328:C331"/>
-    <mergeCell ref="D328:D331"/>
-    <mergeCell ref="A241:A300"/>
-    <mergeCell ref="B241:B300"/>
-    <mergeCell ref="C241:C248"/>
-    <mergeCell ref="D241:D248"/>
-    <mergeCell ref="C249:C255"/>
-    <mergeCell ref="D249:D255"/>
-    <mergeCell ref="C256:C260"/>
-    <mergeCell ref="D256:D260"/>
-    <mergeCell ref="C261:C266"/>
-    <mergeCell ref="D261:D266"/>
-    <mergeCell ref="C267:C275"/>
-    <mergeCell ref="D267:D275"/>
-    <mergeCell ref="C276:C281"/>
-    <mergeCell ref="D276:D281"/>
-    <mergeCell ref="C282:C288"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="C289:C295"/>
-    <mergeCell ref="D289:D295"/>
-    <mergeCell ref="C296:C300"/>
-    <mergeCell ref="D296:D300"/>
-    <mergeCell ref="C212:C218"/>
-    <mergeCell ref="D212:D218"/>
-    <mergeCell ref="C219:C226"/>
-    <mergeCell ref="D219:D226"/>
-    <mergeCell ref="C227:C231"/>
-    <mergeCell ref="D227:D231"/>
-    <mergeCell ref="C232:C235"/>
-    <mergeCell ref="D232:D235"/>
-    <mergeCell ref="C236:C239"/>
-    <mergeCell ref="D236:D239"/>
-    <mergeCell ref="C169:C174"/>
-    <mergeCell ref="D169:D174"/>
-    <mergeCell ref="C175:C180"/>
-    <mergeCell ref="D175:D180"/>
-    <mergeCell ref="C181:C187"/>
-    <mergeCell ref="D181:D187"/>
-    <mergeCell ref="C188:C199"/>
-    <mergeCell ref="D188:D199"/>
-    <mergeCell ref="C200:C211"/>
-    <mergeCell ref="D200:D211"/>
-    <mergeCell ref="A96:A239"/>
-    <mergeCell ref="B96:B239"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="C119:C122"/>
-    <mergeCell ref="D119:D122"/>
-    <mergeCell ref="C123:C128"/>
-    <mergeCell ref="D123:D128"/>
-    <mergeCell ref="C129:C135"/>
-    <mergeCell ref="D129:D135"/>
-    <mergeCell ref="C136:C143"/>
-    <mergeCell ref="D136:D143"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="C150:C155"/>
-    <mergeCell ref="D150:D155"/>
-    <mergeCell ref="C156:C162"/>
-    <mergeCell ref="D156:D162"/>
-    <mergeCell ref="C163:C168"/>
-    <mergeCell ref="D163:D168"/>
-    <mergeCell ref="A22:A40"/>
-    <mergeCell ref="B22:B40"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="B2:B16"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
   </mergeCells>
   <conditionalFormatting sqref="J337:J377 J383:J431 J437:J1048576 J2:J4 J42:J331 J6:J20 J23:J39">
     <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="None">
@@ -16058,16 +15996,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="62" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B1" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E1" s="61"/>
     </row>
@@ -16076,13 +16014,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E2" s="64"/>
     </row>
@@ -16091,13 +16029,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E3" s="64"/>
     </row>
@@ -16106,13 +16044,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C4" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>171</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>174</v>
       </c>
       <c r="E4" s="64"/>
     </row>
@@ -16121,13 +16059,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E5" s="64"/>
     </row>
@@ -16136,13 +16074,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E6" s="64"/>
     </row>
@@ -16151,13 +16089,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E7" s="64"/>
     </row>
@@ -16166,28 +16104,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" s="63" t="s">
         <v>183</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>186</v>
       </c>
       <c r="E9" s="64"/>
     </row>
@@ -16196,28 +16134,28 @@
         <v>15</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E10" s="64"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E11" s="64"/>
     </row>
@@ -16248,7 +16186,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="98" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B17" s="98"/>
       <c r="C17" s="98"/>
@@ -16259,13 +16197,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E18" s="64"/>
     </row>
@@ -16274,13 +16212,13 @@
         <v>14</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E19" s="64"/>
     </row>
@@ -16289,13 +16227,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E20" s="64"/>
     </row>
@@ -16304,13 +16242,13 @@
         <v>12</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C21" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E21" s="64"/>
     </row>
@@ -16319,13 +16257,13 @@
         <v>11</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E22" s="64"/>
     </row>
@@ -16334,13 +16272,13 @@
         <v>10</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E23" s="64"/>
     </row>
@@ -16349,13 +16287,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E24" s="64"/>
     </row>
@@ -16364,13 +16302,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E25" s="64"/>
     </row>
@@ -16379,34 +16317,34 @@
         <v>7</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E26" s="64"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="63" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E27" s="64"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="98" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B33" s="98"/>
       <c r="C33" s="98"/>
@@ -16414,46 +16352,46 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="63" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B34" s="63" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E34" s="64"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="63" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C35" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D35" s="63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E35" s="64"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D36" s="63" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E36" s="64"/>
     </row>
@@ -16462,13 +16400,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D37" s="63" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E37" s="64"/>
     </row>
@@ -16477,13 +16415,13 @@
         <v>5</v>
       </c>
       <c r="B38" s="63" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C38" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E38" s="64"/>
     </row>
@@ -16492,13 +16430,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D39" s="63" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E39" s="64"/>
     </row>
@@ -16507,13 +16445,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D40" s="63" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E40" s="64"/>
     </row>
@@ -16522,13 +16460,13 @@
         <v>2</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C41" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D41" s="63" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E41" s="64"/>
     </row>
@@ -16537,13 +16475,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="63" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E42" s="64"/>
     </row>
@@ -16552,13 +16490,13 @@
         <v>0</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E43" s="64"/>
     </row>
@@ -16622,7 +16560,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="98" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -16699,10 +16637,10 @@
         <v>72</v>
       </c>
       <c r="G3" s="63" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H3" s="63" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I3" s="63" t="s">
         <v>76</v>
@@ -16729,10 +16667,10 @@
         <v>78</v>
       </c>
       <c r="G4" s="63" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H4" s="63" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I4" s="63" t="s">
         <v>18</v>
@@ -16759,10 +16697,10 @@
         <v>82</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H5" s="63" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I5" s="63" t="s">
         <v>18</v>
@@ -16789,10 +16727,10 @@
         <v>86</v>
       </c>
       <c r="G6" s="63" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H6" s="63" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I6" s="63" t="s">
         <v>18</v>
@@ -16819,10 +16757,10 @@
         <v>90</v>
       </c>
       <c r="G7" s="63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H7" s="63" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I7" s="63" t="s">
         <v>18</v>
@@ -16833,7 +16771,7 @@
       <c r="K7" s="65"/>
       <c r="L7" s="65"/>
       <c r="M7" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N7" s="64"/>
     </row>
@@ -16846,13 +16784,13 @@
         <v>6</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G8" s="63" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H8" s="63" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I8" s="63" t="s">
         <v>18</v>
@@ -16863,7 +16801,7 @@
       <c r="K8" s="65"/>
       <c r="L8" s="65"/>
       <c r="M8" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N8" s="64"/>
     </row>
@@ -16874,19 +16812,19 @@
         <v>2</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" s="63">
         <v>7</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I9" s="63" t="s">
         <v>18</v>
@@ -16897,7 +16835,7 @@
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
       <c r="M9" s="63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N9" s="64"/>
     </row>
@@ -16910,13 +16848,13 @@
         <v>8</v>
       </c>
       <c r="F10" s="63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="63" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H10" s="63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I10" s="63" t="s">
         <v>18</v>
@@ -16927,7 +16865,7 @@
       <c r="K10" s="65"/>
       <c r="L10" s="65"/>
       <c r="M10" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="64"/>
     </row>
@@ -16940,13 +16878,13 @@
         <v>9</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" s="63" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H11" s="63" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I11" s="63" t="s">
         <v>18</v>
@@ -16957,7 +16895,7 @@
       <c r="K11" s="65"/>
       <c r="L11" s="65"/>
       <c r="M11" s="63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N11" s="64"/>
     </row>
@@ -16968,19 +16906,19 @@
         <v>3</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E12" s="63">
         <v>10</v>
       </c>
       <c r="F12" s="63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G12" s="63" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H12" s="63" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I12" s="63" t="s">
         <v>32</v>
@@ -16991,7 +16929,7 @@
       <c r="K12" s="65"/>
       <c r="L12" s="65"/>
       <c r="M12" s="63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N12" s="64"/>
     </row>
@@ -17004,24 +16942,24 @@
         <v>11</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G13" s="63" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H13" s="63" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I13" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="65"/>
       <c r="L13" s="65"/>
       <c r="M13" s="63" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N13" s="64"/>
     </row>
@@ -17034,24 +16972,24 @@
         <v>12</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G14" s="63" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I14" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="65"/>
       <c r="M14" s="63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N14" s="64"/>
     </row>
@@ -17062,30 +17000,30 @@
         <v>4</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E15" s="63">
         <v>13</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G15" s="63" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I15" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K15" s="65"/>
       <c r="L15" s="65"/>
       <c r="M15" s="63" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N15" s="64"/>
     </row>
@@ -17098,24 +17036,24 @@
         <v>14</v>
       </c>
       <c r="F16" s="63" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G16" s="63" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H16" s="63" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I16" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J16" s="63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K16" s="65"/>
       <c r="L16" s="65"/>
       <c r="M16" s="63" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N16" s="64"/>
     </row>
@@ -17128,24 +17066,24 @@
         <v>15</v>
       </c>
       <c r="F17" s="63" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I17" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K17" s="65"/>
       <c r="L17" s="65"/>
       <c r="M17" s="63" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N17" s="64"/>
     </row>
@@ -17158,24 +17096,24 @@
         <v>16</v>
       </c>
       <c r="F18" s="63" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G18" s="63" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I18" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J18" s="63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K18" s="65"/>
       <c r="L18" s="65"/>
       <c r="M18" s="63" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N18" s="64"/>
     </row>
@@ -17186,30 +17124,30 @@
         <v>5</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E19" s="63">
         <v>17</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G19" s="63" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J19" s="63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K19" s="65"/>
       <c r="L19" s="65"/>
       <c r="M19" s="63" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="N19" s="64"/>
     </row>
@@ -17222,24 +17160,24 @@
         <v>18</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G20" s="63" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I20" s="63" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="63" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K20" s="65"/>
       <c r="L20" s="65"/>
       <c r="M20" s="63" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="N20" s="64"/>
     </row>
@@ -17252,24 +17190,24 @@
         <v>19</v>
       </c>
       <c r="F21" s="63" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G21" s="63" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H21" s="63" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I21" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J21" s="63" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K21" s="65"/>
       <c r="L21" s="65"/>
       <c r="M21" s="63" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N21" s="64"/>
     </row>
@@ -17280,30 +17218,30 @@
         <v>6</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" s="63">
         <v>20</v>
       </c>
       <c r="F22" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="H22" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="63" t="s">
-        <v>127</v>
-      </c>
       <c r="I22" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="63" t="s">
         <v>129</v>
-      </c>
-      <c r="J22" s="63" t="s">
-        <v>130</v>
       </c>
       <c r="K22" s="65"/>
       <c r="L22" s="65"/>
       <c r="M22" s="63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N22" s="64"/>
     </row>
@@ -17316,24 +17254,24 @@
         <v>21</v>
       </c>
       <c r="F23" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G23" s="63" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H23" s="63" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I23" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="63" t="s">
         <v>129</v>
-      </c>
-      <c r="J23" s="63" t="s">
-        <v>130</v>
       </c>
       <c r="K23" s="65"/>
       <c r="L23" s="65"/>
       <c r="M23" s="63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N23" s="64"/>
     </row>
@@ -17346,24 +17284,24 @@
         <v>22</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G24" s="63" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I24" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="63" t="s">
         <v>129</v>
-      </c>
-      <c r="J24" s="63" t="s">
-        <v>130</v>
       </c>
       <c r="K24" s="65"/>
       <c r="L24" s="65"/>
       <c r="M24" s="63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N24" s="64"/>
     </row>
@@ -17376,24 +17314,24 @@
         <v>23</v>
       </c>
       <c r="F25" s="63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G25" s="63" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I25" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="63" t="s">
         <v>129</v>
-      </c>
-      <c r="J25" s="63" t="s">
-        <v>130</v>
       </c>
       <c r="K25" s="65"/>
       <c r="L25" s="65"/>
       <c r="M25" s="63" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N25" s="64"/>
     </row>
@@ -17406,24 +17344,24 @@
         <v>24</v>
       </c>
       <c r="F26" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G26" s="63" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I26" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K26" s="65"/>
       <c r="L26" s="65"/>
       <c r="M26" s="63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N26" s="64"/>
     </row>
@@ -17436,24 +17374,24 @@
         <v>25</v>
       </c>
       <c r="F27" s="63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G27" s="63" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I27" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J27" s="63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K27" s="65"/>
       <c r="L27" s="65"/>
       <c r="M27" s="63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N27" s="64"/>
     </row>
@@ -17464,30 +17402,30 @@
         <v>7</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E28" s="63">
         <v>26</v>
       </c>
       <c r="F28" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G28" s="63" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H28" s="63" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I28" s="63" t="s">
         <v>32</v>
       </c>
       <c r="J28" s="63" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K28" s="65"/>
       <c r="L28" s="65"/>
       <c r="M28" s="63" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N28" s="64"/>
     </row>
@@ -17524,7 +17462,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="98" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B34" s="98"/>
       <c r="C34" s="98"/>
@@ -17542,19 +17480,19 @@
     </row>
     <row r="35" spans="1:14" s="69" customFormat="1" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" s="60" t="s">
+        <v>302</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="D35" s="60" t="s">
         <v>304</v>
       </c>
-      <c r="B35" s="60" t="s">
+      <c r="E35" s="60" t="s">
         <v>305</v>
-      </c>
-      <c r="C35" s="60" t="s">
-        <v>306</v>
-      </c>
-      <c r="D35" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="E35" s="60" t="s">
-        <v>308</v>
       </c>
       <c r="F35" s="68"/>
       <c r="G35" s="71"/>
@@ -17567,109 +17505,109 @@
     </row>
     <row r="36" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
+        <v>306</v>
+      </c>
+      <c r="B36" s="63" t="s">
+        <v>307</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="63" t="s">
         <v>309</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="E36" s="63" t="s">
         <v>310</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>311</v>
-      </c>
-      <c r="D36" s="63" t="s">
-        <v>312</v>
-      </c>
-      <c r="E36" s="63" t="s">
-        <v>313</v>
       </c>
       <c r="F36" s="64"/>
     </row>
     <row r="37" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="63" t="s">
+        <v>311</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="D37" s="63" t="s">
         <v>314</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="E37" s="63" t="s">
         <v>315</v>
-      </c>
-      <c r="C37" s="63" t="s">
-        <v>316</v>
-      </c>
-      <c r="D37" s="63" t="s">
-        <v>317</v>
-      </c>
-      <c r="E37" s="63" t="s">
-        <v>318</v>
       </c>
       <c r="F37" s="64"/>
     </row>
     <row r="38" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="B38" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="D38" s="63" t="s">
         <v>319</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="E38" s="63" t="s">
         <v>320</v>
-      </c>
-      <c r="C38" s="63" t="s">
-        <v>321</v>
-      </c>
-      <c r="D38" s="63" t="s">
-        <v>322</v>
-      </c>
-      <c r="E38" s="63" t="s">
-        <v>323</v>
       </c>
       <c r="F38" s="64"/>
     </row>
     <row r="39" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B39" s="63" t="s">
+        <v>322</v>
+      </c>
+      <c r="C39" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="D39" s="63" t="s">
         <v>324</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="E39" s="63" t="s">
         <v>325</v>
-      </c>
-      <c r="C39" s="63" t="s">
-        <v>326</v>
-      </c>
-      <c r="D39" s="63" t="s">
-        <v>327</v>
-      </c>
-      <c r="E39" s="63" t="s">
-        <v>328</v>
       </c>
       <c r="F39" s="64"/>
     </row>
     <row r="40" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="B40" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="D40" s="63" t="s">
         <v>329</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="E40" s="63" t="s">
         <v>330</v>
-      </c>
-      <c r="C40" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="D40" s="63" t="s">
-        <v>332</v>
-      </c>
-      <c r="E40" s="63" t="s">
-        <v>333</v>
       </c>
       <c r="F40" s="64"/>
     </row>
     <row r="41" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="C41" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="D41" s="63" t="s">
         <v>334</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="E41" s="63" t="s">
         <v>335</v>
-      </c>
-      <c r="C41" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="D41" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="E41" s="63" t="s">
-        <v>338</v>
       </c>
       <c r="F41" s="64"/>
     </row>
@@ -17681,10 +17619,10 @@
         <v>62</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D42" s="63" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E42" s="63" t="s">
         <v>63</v>
@@ -17699,10 +17637,10 @@
         <v>65</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E43" s="63" t="s">
         <v>66</v>
@@ -17717,10 +17655,10 @@
         <v>68</v>
       </c>
       <c r="C44" s="63" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D44" s="63" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E44" s="63" t="s">
         <v>69</v>
@@ -17732,88 +17670,88 @@
         <v>54</v>
       </c>
       <c r="B45" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="C45" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="D45" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" s="63" t="s">
         <v>345</v>
-      </c>
-      <c r="C45" s="63" t="s">
-        <v>346</v>
-      </c>
-      <c r="D45" s="63" t="s">
-        <v>347</v>
-      </c>
-      <c r="E45" s="63" t="s">
-        <v>348</v>
       </c>
       <c r="F45" s="64"/>
     </row>
     <row r="46" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="B46" s="63" t="s">
+        <v>347</v>
+      </c>
+      <c r="C46" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="D46" s="63" t="s">
         <v>349</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="E46" s="63" t="s">
         <v>350</v>
-      </c>
-      <c r="C46" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="D46" s="63" t="s">
-        <v>352</v>
-      </c>
-      <c r="E46" s="63" t="s">
-        <v>353</v>
       </c>
       <c r="F46" s="64"/>
     </row>
     <row r="47" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="63" t="s">
+        <v>351</v>
+      </c>
+      <c r="B47" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="C47" s="63" t="s">
+        <v>353</v>
+      </c>
+      <c r="D47" s="63" t="s">
         <v>354</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="E47" s="63" t="s">
         <v>355</v>
-      </c>
-      <c r="C47" s="63" t="s">
-        <v>356</v>
-      </c>
-      <c r="D47" s="63" t="s">
-        <v>357</v>
-      </c>
-      <c r="E47" s="63" t="s">
-        <v>358</v>
       </c>
       <c r="F47" s="64"/>
     </row>
     <row r="48" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>357</v>
+      </c>
+      <c r="C48" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="D48" s="63" t="s">
         <v>359</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="E48" s="63" t="s">
         <v>360</v>
-      </c>
-      <c r="C48" s="63" t="s">
-        <v>361</v>
-      </c>
-      <c r="D48" s="63" t="s">
-        <v>362</v>
-      </c>
-      <c r="E48" s="63" t="s">
-        <v>363</v>
       </c>
       <c r="F48" s="64"/>
     </row>
     <row r="49" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="B49" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="D49" s="63" t="s">
         <v>364</v>
       </c>
-      <c r="B49" s="63" t="s">
+      <c r="E49" s="63" t="s">
         <v>365</v>
-      </c>
-      <c r="C49" s="63" t="s">
-        <v>366</v>
-      </c>
-      <c r="D49" s="63" t="s">
-        <v>367</v>
-      </c>
-      <c r="E49" s="63" t="s">
-        <v>368</v>
       </c>
       <c r="F49" s="64"/>
     </row>
@@ -17822,88 +17760,88 @@
         <v>43</v>
       </c>
       <c r="B50" s="63" t="s">
+        <v>366</v>
+      </c>
+      <c r="C50" s="63" t="s">
+        <v>367</v>
+      </c>
+      <c r="D50" s="63" t="s">
+        <v>368</v>
+      </c>
+      <c r="E50" s="63" t="s">
         <v>369</v>
-      </c>
-      <c r="C50" s="63" t="s">
-        <v>370</v>
-      </c>
-      <c r="D50" s="63" t="s">
-        <v>371</v>
-      </c>
-      <c r="E50" s="63" t="s">
-        <v>372</v>
       </c>
       <c r="F50" s="64"/>
     </row>
     <row r="51" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="63" t="s">
+        <v>370</v>
+      </c>
+      <c r="B51" s="63" t="s">
+        <v>371</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>372</v>
+      </c>
+      <c r="D51" s="63" t="s">
         <v>373</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="E51" s="63" t="s">
         <v>374</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>375</v>
-      </c>
-      <c r="D51" s="63" t="s">
-        <v>376</v>
-      </c>
-      <c r="E51" s="63" t="s">
-        <v>377</v>
       </c>
       <c r="F51" s="64"/>
     </row>
     <row r="52" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="63" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B52" s="63" t="s">
         <v>58</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D52" s="63" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E52" s="63" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F52" s="64"/>
     </row>
     <row r="53" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="63" t="s">
+        <v>379</v>
+      </c>
+      <c r="B53" s="63" t="s">
+        <v>380</v>
+      </c>
+      <c r="C53" s="63" t="s">
+        <v>381</v>
+      </c>
+      <c r="D53" s="63" t="s">
         <v>382</v>
       </c>
-      <c r="B53" s="63" t="s">
+      <c r="E53" s="63" t="s">
         <v>383</v>
-      </c>
-      <c r="C53" s="63" t="s">
-        <v>384</v>
-      </c>
-      <c r="D53" s="63" t="s">
-        <v>385</v>
-      </c>
-      <c r="E53" s="63" t="s">
-        <v>386</v>
       </c>
       <c r="F53" s="64"/>
     </row>
     <row r="54" spans="1:6" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="63" t="s">
+        <v>384</v>
+      </c>
+      <c r="B54" s="63" t="s">
+        <v>385</v>
+      </c>
+      <c r="C54" s="63" t="s">
+        <v>386</v>
+      </c>
+      <c r="D54" s="63" t="s">
         <v>387</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="E54" s="63" t="s">
         <v>388</v>
-      </c>
-      <c r="C54" s="63" t="s">
-        <v>389</v>
-      </c>
-      <c r="D54" s="63" t="s">
-        <v>390</v>
-      </c>
-      <c r="E54" s="63" t="s">
-        <v>391</v>
       </c>
       <c r="F54" s="64"/>
     </row>
